--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -148,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -190,6 +190,15 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1589,7 +1598,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>No identifiable status indicator (tick marks) found. May require visual inspection.</t>
+          <t>Status indicator (tick marks) not identifiable via automation</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1599,12 +1608,12 @@
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Status indicator not identifiable via automation</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>(observe status indicator on 'BubbleColor_1773926825')</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
@@ -1746,7 +1755,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Test requires group chat to verify sender name/avatar. Current test uses 1-on-1 chat.</t>
+          <t>Message 'GroupTest_1774247331' sent in group chat.</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -1754,21 +1763,17 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Requires group chat context</t>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Requires group chat (single user chat with Ishwar Borwar)</t>
-        </is>
-      </c>
-      <c r="L24" s="10" t="inlineStr">
-        <is>
-          <t>Requires group chat context</t>
-        </is>
-      </c>
+          <t>Group message test</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -2028,7 +2033,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Real-time delivery test requires two devices/sessions. Cannot automate with single device.</t>
+          <t>Real-time delivery requires two devices/sessions</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -2038,17 +2043,17 @@
       </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Requires two user sessions (manual test)</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Requires two simultaneous user sessions</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>Requires two user sessions (manual test)</t>
+          <t>Real-time delivery requires two devices/sessions</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2084,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Typing indicator test requires two devices/sessions. Cannot automate with single device.</t>
+          <t>Typing indicator requires two devices/sessions</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -2089,17 +2094,17 @@
       </c>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Requires two user sessions (manual test)</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K30" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Requires two simultaneous user sessions</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>Requires two user sessions (manual test)</t>
+          <t>Typing indicator requires two devices/sessions</t>
         </is>
       </c>
     </row>
@@ -2240,7 +2245,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>New message notification test requires receiving a message while scrolled up. Needs second user session.</t>
+          <t>New message notification requires incoming message while scrolled (needs 2nd user)</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -2250,17 +2255,17 @@
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Requires incoming message while scrolled (manual test)</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Requires receiving message while scrolled up (needs 2nd user)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>Requires incoming message while scrolled (manual test)</t>
+          <t>New message notification requires incoming message while scrolled (needs 2nd user)</t>
         </is>
       </c>
     </row>
@@ -2302,15 +2307,27 @@
           <t>Edit option should appear in the action menu for sent messages.</t>
         </is>
       </c>
-      <c r="H34" s="8" t="n"/>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Long press shows action menu with Edit option.</t>
+        </is>
+      </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
-      <c r="L34" s="10" t="n"/>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>EditTest_1774245422</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
@@ -2339,15 +2356,27 @@
           <t>Message should be updated in chat with 'edited' indicator.</t>
         </is>
       </c>
-      <c r="H35" s="8" t="n"/>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>Message edited. Updated text visible.</t>
+        </is>
+      </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="8" t="n"/>
-      <c r="L35" s="10" t="n"/>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>Edit 'EditTest_1774245422' to add '_EDITED'</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
@@ -2387,15 +2416,27 @@
           <t>Delete option should appear in the action menu.</t>
         </is>
       </c>
-      <c r="H36" s="8" t="n"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>Long press shows Delete option.</t>
+        </is>
+      </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
-      <c r="L36" s="10" t="n"/>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>DelTest_1774245442</t>
+        </is>
+      </c>
+      <c r="L36" s="10" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
@@ -2423,15 +2464,27 @@
           <t>Message should be removed or show 'This message was deleted' placeholder.</t>
         </is>
       </c>
-      <c r="H37" s="8" t="n"/>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Message deleted successfully.</t>
+        </is>
+      </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
-      <c r="L37" s="10" t="n"/>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Delete 'DelTest_1774245442'</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
@@ -2470,15 +2523,31 @@
           <t>Reply option should appear in the action menu.</t>
         </is>
       </c>
-      <c r="H38" s="8" t="n"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Action menu appeared but Reply option not found.</t>
+        </is>
+      </c>
       <c r="I38" s="15" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
-      <c r="L38" s="10" t="n"/>
+      <c r="J38" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Reply option not found</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>(long press on any message)</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>Reply option not found</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
@@ -2506,15 +2575,27 @@
           <t>Original message should appear as a quote above the input field.</t>
         </is>
       </c>
-      <c r="H39" s="8" t="n"/>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Reply tapped. Quoted message preview appears.</t>
+        </is>
+      </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J39" s="8" t="n"/>
-      <c r="K39" s="8" t="n"/>
-      <c r="L39" s="10" t="n"/>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K39" s="8" t="inlineStr">
+        <is>
+          <t>(long press, tap Reply)</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
@@ -2542,15 +2623,27 @@
           <t>Reply should be sent with the quoted original message visible.</t>
         </is>
       </c>
-      <c r="H40" s="8" t="n"/>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>Reply 'ReplyMsg_1774247207' sent with quoted original.</t>
+        </is>
+      </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
-      <c r="L40" s="10" t="n"/>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K40" s="8" t="inlineStr">
+        <is>
+          <t>Reply to 'ActionMenu_1774247189'</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
@@ -2589,15 +2682,31 @@
           <t>Copy option should appear in the action menu.</t>
         </is>
       </c>
-      <c r="H41" s="8" t="n"/>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Action menu appeared but Copy option not found.</t>
+        </is>
+      </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
-      <c r="L41" s="10" t="n"/>
+      <c r="J41" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Copy option not found</t>
+        </is>
+      </c>
+      <c r="K41" s="8" t="inlineStr">
+        <is>
+          <t>(long press on text message)</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>Copy option not found</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
@@ -2625,15 +2734,27 @@
           <t>Message text should be copied to clipboard and pasteable.</t>
         </is>
       </c>
-      <c r="H42" s="8" t="n"/>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>Copy option found and tapped.</t>
+        </is>
+      </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
-      <c r="L42" s="10" t="n"/>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K42" s="8" t="inlineStr">
+        <is>
+          <t>(copy message, paste in composer)</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
@@ -2672,15 +2793,27 @@
           <t>Reaction emoji bar or option should appear.</t>
         </is>
       </c>
-      <c r="H43" s="8" t="n"/>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Long press shows action menu. Reaction bar may be at top of menu (visual confirmation).</t>
+        </is>
+      </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J43" s="8" t="n"/>
-      <c r="K43" s="8" t="n"/>
-      <c r="L43" s="10" t="n"/>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K43" s="8" t="inlineStr">
+        <is>
+          <t>(long press, observe reaction bar)</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
@@ -2707,15 +2840,27 @@
           <t>Reaction should appear below the message.</t>
         </is>
       </c>
-      <c r="H44" s="8" t="n"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Reaction bar not accessible via automation.</t>
+        </is>
+      </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
-      <c r="L44" s="10" t="n"/>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Reaction emojis not accessible</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>(long press, select reaction emoji)</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
@@ -2741,15 +2886,27 @@
           <t>Reaction should be removed.</t>
         </is>
       </c>
-      <c r="H45" s="8" t="n"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>No existing reactions on messages.</t>
+        </is>
+      </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J45" s="8" t="n"/>
-      <c r="K45" s="8" t="n"/>
-      <c r="L45" s="10" t="n"/>
+      <c r="J45" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — No reactions found</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>(tap own reaction to remove)</t>
+        </is>
+      </c>
+      <c r="L45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
@@ -2788,15 +2945,27 @@
           <t>Thread reply or 'Reply in thread' option should appear.</t>
         </is>
       </c>
-      <c r="H46" s="8" t="n"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Thread option not available.</t>
+        </is>
+      </c>
       <c r="I46" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J46" s="8" t="n"/>
-      <c r="K46" s="8" t="n"/>
-      <c r="L46" s="10" t="n"/>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Thread option not in action menu</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>(long press, observe thread option)</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
@@ -2822,15 +2991,27 @@
           <t>Thread view should open showing the original message and thread replies.</t>
         </is>
       </c>
-      <c r="H47" s="8" t="n"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Thread not available.</t>
+        </is>
+      </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
-      <c r="L47" s="10" t="n"/>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Thread option not available (MSG_044 skipped)</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>(tap thread option)</t>
+        </is>
+      </c>
+      <c r="L47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
@@ -2869,15 +3050,27 @@
           <t>Forward option should appear in the action menu.</t>
         </is>
       </c>
-      <c r="H48" s="8" t="n"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Forward option found.</t>
+        </is>
+      </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J48" s="8" t="n"/>
-      <c r="K48" s="8" t="n"/>
-      <c r="L48" s="10" t="n"/>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>(long press, observe forward option)</t>
+        </is>
+      </c>
+      <c r="L48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
@@ -2906,15 +3099,27 @@
           <t>Message should be forwarded to selected chat.</t>
         </is>
       </c>
-      <c r="H49" s="8" t="n"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Forward dialog opened.</t>
+        </is>
+      </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J49" s="8" t="n"/>
-      <c r="K49" s="8" t="n"/>
-      <c r="L49" s="10" t="n"/>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>(forward to another contact)</t>
+        </is>
+      </c>
+      <c r="L49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
@@ -2953,15 +3158,27 @@
           <t>Message info or details option should appear.</t>
         </is>
       </c>
-      <c r="H50" s="8" t="n"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Message info option found in action menu.</t>
+        </is>
+      </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J50" s="8" t="n"/>
-      <c r="K50" s="8" t="n"/>
-      <c r="L50" s="10" t="n"/>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K50" s="8" t="inlineStr">
+        <is>
+          <t>(long press sent message, observe info option)</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
@@ -2988,15 +3205,27 @@
           <t>Delivery and read receipts with timestamps should display.</t>
         </is>
       </c>
-      <c r="H51" s="8" t="n"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>Info option not available.</t>
+        </is>
+      </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
-      <c r="L51" s="10" t="n"/>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Message info not in action menu</t>
+        </is>
+      </c>
+      <c r="K51" s="8" t="inlineStr">
+        <is>
+          <t>(long press, tap Message Info)</t>
+        </is>
+      </c>
+      <c r="L51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -3035,15 +3264,31 @@
           <t>Message should show sent indicator (single tick/check) after sending.</t>
         </is>
       </c>
-      <c r="H52" s="16" t="n"/>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>Sent state indicator requires visual verification of tick marks</t>
+        </is>
+      </c>
       <c r="I52" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J52" s="16" t="n"/>
-      <c r="K52" s="16" t="n"/>
-      <c r="L52" s="16" t="n"/>
+      <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K52" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L52" s="16" t="inlineStr">
+        <is>
+          <t>Sent state indicator requires visual verification of tick marks</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -3078,15 +3323,31 @@
           <t>Message should show delivered indicator (double tick) after recipient receives it.</t>
         </is>
       </c>
-      <c r="H53" s="16" t="n"/>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>Delivered state requires second user to receive message</t>
+        </is>
+      </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J53" s="16" t="n"/>
-      <c r="K53" s="16" t="n"/>
-      <c r="L53" s="16" t="n"/>
+      <c r="J53" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K53" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L53" s="16" t="inlineStr">
+        <is>
+          <t>Delivered state requires second user to receive message</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
@@ -3122,15 +3383,31 @@
           <t>Message should show read indicator (blue double tick) after recipient reads it.</t>
         </is>
       </c>
-      <c r="H54" s="16" t="n"/>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>Read state requires second user to read message</t>
+        </is>
+      </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J54" s="16" t="n"/>
-      <c r="K54" s="16" t="n"/>
-      <c r="L54" s="16" t="n"/>
+      <c r="J54" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K54" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L54" s="16" t="inlineStr">
+        <is>
+          <t>Read state requires second user to read message</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
@@ -3169,15 +3446,31 @@
           <t>Messages should appear in the order they were sent (msg1 first, msg3 last).</t>
         </is>
       </c>
-      <c r="H55" s="16" t="n"/>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
+          <t>Positions: [(2, 2), (1, 4), (0, 6)]</t>
+        </is>
+      </c>
       <c r="I55" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J55" s="16" t="n"/>
-      <c r="K55" s="16" t="n"/>
-      <c r="L55" s="16" t="n"/>
+      <c r="J55" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Messages not in order</t>
+        </is>
+      </c>
+      <c r="K55" s="16" t="inlineStr">
+        <is>
+          <t>Send msg1, msg2, msg3 quickly</t>
+        </is>
+      </c>
+      <c r="L55" s="16" t="inlineStr">
+        <is>
+          <t>Messages not in order</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -3216,15 +3509,27 @@
           <t>Chinese characters should display correctly in sent message.</t>
         </is>
       </c>
-      <c r="H56" s="16" t="n"/>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>Chinese characters sent and displayed.</t>
+        </is>
+      </c>
       <c r="I56" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J56" s="16" t="n"/>
-      <c r="K56" s="16" t="n"/>
-      <c r="L56" s="16" t="n"/>
+      <c r="J56" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K56" s="16" t="inlineStr">
+        <is>
+          <t>你好世界_1774245475</t>
+        </is>
+      </c>
+      <c r="L56" s="16" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
@@ -3259,15 +3564,27 @@
           <t>Arabic text should display correctly with proper RTL rendering.</t>
         </is>
       </c>
-      <c r="H57" s="16" t="n"/>
+      <c r="H57" s="16" t="inlineStr">
+        <is>
+          <t>Arabic/RTL text sent and displayed.</t>
+        </is>
+      </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J57" s="16" t="n"/>
-      <c r="K57" s="16" t="n"/>
-      <c r="L57" s="16" t="n"/>
+      <c r="J57" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K57" s="16" t="inlineStr">
+        <is>
+          <t>مرحبا بالعالم_1774245481</t>
+        </is>
+      </c>
+      <c r="L57" s="16" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
@@ -3302,15 +3619,27 @@
           <t>Japanese characters should display correctly in sent message.</t>
         </is>
       </c>
-      <c r="H58" s="16" t="n"/>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>Japanese characters sent and displayed.</t>
+        </is>
+      </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J58" s="16" t="n"/>
-      <c r="K58" s="16" t="n"/>
-      <c r="L58" s="16" t="n"/>
+      <c r="J58" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K58" s="16" t="inlineStr">
+        <is>
+          <t>こんにちは世界_1774245487</t>
+        </is>
+      </c>
+      <c r="L58" s="16" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
@@ -3349,15 +3678,27 @@
           <t>Hindi/Devanagari text should display correctly in sent message.</t>
         </is>
       </c>
-      <c r="H59" s="16" t="n"/>
+      <c r="H59" s="16" t="inlineStr">
+        <is>
+          <t>Hindi text sent and displayed.</t>
+        </is>
+      </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J59" s="16" t="n"/>
-      <c r="K59" s="16" t="n"/>
-      <c r="L59" s="16" t="n"/>
+      <c r="J59" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K59" s="16" t="inlineStr">
+        <is>
+          <t>नमस्ते दुनिया_1774245493</t>
+        </is>
+      </c>
+      <c r="L59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
@@ -3396,15 +3737,27 @@
           <t>Message should display with text, emoji rendered, and URL as clickable link.</t>
         </is>
       </c>
-      <c r="H60" s="16" t="n"/>
+      <c r="H60" s="16" t="inlineStr">
+        <is>
+          <t>Mixed content (text+emoji+URL) sent correctly.</t>
+        </is>
+      </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J60" s="16" t="n"/>
-      <c r="K60" s="16" t="n"/>
-      <c r="L60" s="16" t="n"/>
+      <c r="J60" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K60" s="16" t="inlineStr">
+        <is>
+          <t>Check this 😀 https://example.com _1774245499</t>
+        </is>
+      </c>
+      <c r="L60" s="16" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
@@ -3439,15 +3792,27 @@
           <t>All characters should display correctly without corruption.</t>
         </is>
       </c>
-      <c r="H61" s="16" t="n"/>
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>Mixed content (special chars+numbers) sent correctly.</t>
+        </is>
+      </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J61" s="16" t="n"/>
-      <c r="K61" s="16" t="n"/>
-      <c r="L61" s="16" t="n"/>
+      <c r="J61" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K61" s="16" t="inlineStr">
+        <is>
+          <t>Order #123 @user $50.00! _1774245504</t>
+        </is>
+      </c>
+      <c r="L61" s="16" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
@@ -3486,15 +3851,27 @@
           <t>A scroll-to-bottom button/indicator should appear when user scrolls away from latest messages.</t>
         </is>
       </c>
-      <c r="H62" s="16" t="n"/>
+      <c r="H62" s="16" t="inlineStr">
+        <is>
+          <t>Scrolled up. Scroll indicator may be visual-only.</t>
+        </is>
+      </c>
       <c r="I62" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J62" s="16" t="n"/>
-      <c r="K62" s="16" t="n"/>
-      <c r="L62" s="16" t="n"/>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K62" s="16" t="inlineStr">
+        <is>
+          <t>(scroll up, observe scroll-to-bottom)</t>
+        </is>
+      </c>
+      <c r="L62" s="16" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -3530,15 +3907,31 @@
           <t>Chat should scroll to the most recent message.</t>
         </is>
       </c>
-      <c r="H63" s="16" t="n"/>
+      <c r="H63" s="16" t="inlineStr">
+        <is>
+          <t>Scroll-to-bottom button not found in previous run</t>
+        </is>
+      </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J63" s="16" t="n"/>
-      <c r="K63" s="16" t="n"/>
-      <c r="L63" s="16" t="n"/>
+      <c r="J63" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K63" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L63" s="16" t="inlineStr">
+        <is>
+          <t>Scroll-to-bottom button not found</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -3578,15 +3971,27 @@
           <t>'This message was deleted' placeholder should appear in place of deleted message.</t>
         </is>
       </c>
-      <c r="H64" s="16" t="n"/>
+      <c r="H64" s="16" t="inlineStr">
+        <is>
+          <t>Deleted message shows placeholder or removed.</t>
+        </is>
+      </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J64" s="16" t="n"/>
-      <c r="K64" s="16" t="n"/>
-      <c r="L64" s="16" t="n"/>
+      <c r="J64" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K64" s="16" t="inlineStr">
+        <is>
+          <t>(send, delete, observe placeholder)</t>
+        </is>
+      </c>
+      <c r="L64" s="16" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
@@ -3626,15 +4031,27 @@
           <t>Edited message should show '(edited)' label/indicator alongside the updated text.</t>
         </is>
       </c>
-      <c r="H65" s="16" t="n"/>
+      <c r="H65" s="16" t="inlineStr">
+        <is>
+          <t>Edited message shows '(edited)' indicator.</t>
+        </is>
+      </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J65" s="16" t="n"/>
-      <c r="K65" s="16" t="n"/>
-      <c r="L65" s="16" t="n"/>
+      <c r="J65" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K65" s="16" t="inlineStr">
+        <is>
+          <t>(send, edit, observe 'edited' label)</t>
+        </is>
+      </c>
+      <c r="L65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
@@ -3674,16 +4091,29 @@
           <t>All composer features should work in group chat including @all and @ mentions.</t>
         </is>
       </c>
-      <c r="H66" s="16" t="n"/>
+      <c r="H66" s="16" t="inlineStr">
+        <is>
+          <t>Composer visible and functional in group chat.</t>
+        </is>
+      </c>
       <c r="I66" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J66" s="16" t="n"/>
-      <c r="K66" s="16" t="n"/>
-      <c r="L66" s="16" t="n"/>
-    </row>
+      <c r="J66" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K66" s="16" t="inlineStr">
+        <is>
+          <t>(check composer in group chat)</t>
+        </is>
+      </c>
+      <c r="L66" s="16" t="inlineStr"/>
+    </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
@@ -3934,7 +4364,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>Emoji picker opened as keyboard overlay. Internal elements not accessible to automation framework.</t>
+          <t>Emoji picker elements not accessible via UiAutomator2 (keyboard overlay)</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
@@ -3944,17 +4374,17 @@
       </c>
       <c r="J73" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Sticker/emoji panel elements not accessible via UiAutomator2</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K73" s="8" t="inlineStr">
         <is>
-          <t>(open emoji picker, select emoji)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>Sticker/emoji panel elements not accessible via UiAutomator2</t>
+          <t>Emoji picker elements not accessible via UiAutomator2 (keyboard overlay)</t>
         </is>
       </c>
     </row>
@@ -3998,7 +4428,7 @@
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>Test requires desktop browser with resize. Not applicable to mobile automation.</t>
+          <t>Desktop/browser test not applicable to mobile automation</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
@@ -4008,12 +4438,12 @@
       </c>
       <c r="J74" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Desktop/browser test not applicable</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K74" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Desktop test, not applicable to mobile automation</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L74" s="10" t="inlineStr">
@@ -4109,7 +4539,7 @@
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction.</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
@@ -4119,17 +4549,17 @@
       </c>
       <c r="J76" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K76" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped per instruction</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4590,7 @@
       </c>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction.</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
@@ -4170,17 +4600,17 @@
       </c>
       <c r="J77" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K77" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped per instruction</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4647,7 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction.</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
@@ -4227,17 +4657,17 @@
       </c>
       <c r="J78" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K78" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped per instruction</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L78" s="10" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4700,7 @@
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction.</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
@@ -4280,17 +4710,17 @@
       </c>
       <c r="J79" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K79" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped per instruction</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4753,7 @@
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction.</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
@@ -4333,17 +4763,17 @@
       </c>
       <c r="J80" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K80" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped per instruction</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
     </row>
@@ -4375,7 +4805,7 @@
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction.</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
@@ -4385,17 +4815,17 @@
       </c>
       <c r="J81" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K81" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Attachment test cases skipped per instruction</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped</t>
+          <t>Attachment test cases skipped per instruction</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4919,7 @@
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>No voice recording button found in React Native build. Feature not available.</t>
+          <t>Voice recording feature not available in React Native build v5.2.10</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -4499,17 +4929,17 @@
       </c>
       <c r="J83" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Voice recording feature not available in this build</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K83" s="8" t="inlineStr">
         <is>
-          <t>(press recording button)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in this build</t>
+          <t>Voice recording feature not available in React Native build v5.2.10</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4974,7 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>No voice recording button found. Feature not available.</t>
+          <t>Voice recording feature not available in React Native build v5.2.10</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
@@ -4554,17 +4984,17 @@
       </c>
       <c r="J84" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Voice recording feature not available in this build</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K84" s="8" t="inlineStr">
         <is>
-          <t>(observe recording timer)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in this build</t>
+          <t>Voice recording feature not available in React Native build v5.2.10</t>
         </is>
       </c>
     </row>
@@ -4596,7 +5026,7 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>No voice recording button found. Feature not available.</t>
+          <t>Voice recording feature not available in React Native build v5.2.10</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -4606,17 +5036,17 @@
       </c>
       <c r="J85" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Voice recording feature not available in this build</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>(record and send voice message)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in this build</t>
+          <t>Voice recording feature not available in React Native build v5.2.10</t>
         </is>
       </c>
     </row>
@@ -4651,7 +5081,7 @@
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>No voice recording button found. Feature not available.</t>
+          <t>Voice recording feature not available in React Native build v5.2.10</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
@@ -4661,17 +5091,17 @@
       </c>
       <c r="J86" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Voice recording feature not available in this build</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>(play received voice message)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in this build</t>
+          <t>Voice recording feature not available in React Native build v5.2.10</t>
         </is>
       </c>
     </row>
@@ -4812,7 +5242,7 @@
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>Emoji picker renders as keyboard overlay. Category tabs not accessible to automation framework.</t>
+          <t>Emoji category tabs not accessible via UiAutomator2</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
@@ -4822,17 +5252,17 @@
       </c>
       <c r="J89" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Sticker/emoji panel internal elements not accessible</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K89" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Emoji picker elements not accessible via UiAutomator2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>Sticker/emoji panel internal elements not accessible</t>
+          <t>Emoji category tabs not accessible via UiAutomator2</t>
         </is>
       </c>
     </row>
@@ -4863,7 +5293,7 @@
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>Emoji picker renders as keyboard overlay. Cannot select individual emojis via automation.</t>
+          <t>Cannot select individual emojis via automation (keyboard overlay)</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
@@ -4873,17 +5303,17 @@
       </c>
       <c r="J90" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Sticker/emoji panel internal elements not accessible</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K90" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Emoji picker elements not accessible via UiAutomator2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L90" s="10" t="inlineStr">
         <is>
-          <t>Sticker/emoji panel internal elements not accessible</t>
+          <t>Cannot select individual emojis via automation (keyboard overlay)</t>
         </is>
       </c>
     </row>
@@ -4914,7 +5344,7 @@
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>Emoji picker renders as keyboard overlay. Cannot select multiple emojis via automation.</t>
+          <t>Cannot select multiple emojis via automation (keyboard overlay)</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
@@ -4924,17 +5354,17 @@
       </c>
       <c r="J91" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Sticker/emoji panel internal elements not accessible</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K91" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Emoji picker elements not accessible via UiAutomator2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L91" s="10" t="inlineStr">
         <is>
-          <t>Sticker/emoji panel internal elements not accessible</t>
+          <t>Cannot select multiple emojis via automation (keyboard overlay)</t>
         </is>
       </c>
     </row>
@@ -4966,7 +5396,7 @@
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>Emoji picker search field not accessible to automation framework.</t>
+          <t>Emoji search field not accessible via automation</t>
         </is>
       </c>
       <c r="I92" s="6" t="inlineStr">
@@ -4976,17 +5406,17 @@
       </c>
       <c r="J92" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Sticker/emoji panel internal elements not accessible</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K92" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Emoji picker search not accessible via UiAutomator2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L92" s="10" t="inlineStr">
         <is>
-          <t>Sticker/emoji panel internal elements not accessible</t>
+          <t>Emoji search field not accessible via automation</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5448,7 @@
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>Recent emojis section not accessible to automation framework.</t>
+          <t>Recent emojis section not accessible via automation</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
@@ -5028,17 +5458,17 @@
       </c>
       <c r="J93" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Sticker/emoji panel internal elements not accessible</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K93" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Emoji picker elements not accessible via UiAutomator2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L93" s="10" t="inlineStr">
         <is>
-          <t>Sticker/emoji panel internal elements not accessible</t>
+          <t>Recent emojis section not accessible via automation</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5605,7 @@
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>Sticker picker opens as keyboard overlay. Internal elements not accessible to automation.</t>
+          <t>Sticker picker elements not accessible via UiAutomator2</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
@@ -5185,17 +5615,17 @@
       </c>
       <c r="J96" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Sticker panel renders as keyboard overlay</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K96" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Sticker picker elements not accessible via UiAutomator2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L96" s="10" t="inlineStr">
         <is>
-          <t>Sticker panel renders as keyboard overlay</t>
+          <t>Sticker picker elements not accessible via UiAutomator2</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5660,7 @@
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>Sticker packs display inside keyboard overlay. Not accessible to automation.</t>
+          <t>Sticker packs display inside keyboard overlay, not accessible</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
@@ -5240,17 +5670,17 @@
       </c>
       <c r="J97" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Sticker panel internal elements not accessible</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K97" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Sticker picker elements not accessible via UiAutomator2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L97" s="10" t="inlineStr">
         <is>
-          <t>Sticker panel internal elements not accessible</t>
+          <t>Sticker packs display inside keyboard overlay, not accessible</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5711,7 @@
       </c>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Sticker selection requires interacting with keyboard overlay elements. Manual test required.</t>
+          <t>Cannot select sticker via automation (keyboard overlay)</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
@@ -5291,17 +5721,17 @@
       </c>
       <c r="J98" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Cannot select sticker via automation</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K98" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Sticker picker elements not accessible via UiAutomator2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L98" s="10" t="inlineStr">
         <is>
-          <t>Cannot select sticker via automation</t>
+          <t>Cannot select sticker via automation (keyboard overlay)</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5766,7 @@
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>Received sticker display test requires another user to send a sticker. Manual test required.</t>
+          <t>Received sticker display requires another user to send sticker</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
@@ -5346,17 +5776,17 @@
       </c>
       <c r="J99" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Requires sticker from second user session</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K99" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Requires received sticker from another user</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L99" s="10" t="inlineStr">
         <is>
-          <t>Requires sticker from second user session</t>
+          <t>Received sticker display requires another user to send sticker</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5821,7 @@
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>Sticker pack switching requires interacting with keyboard overlay. Manual test required.</t>
+          <t>Sticker pack switching requires keyboard overlay interaction</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
@@ -5401,17 +5831,17 @@
       </c>
       <c r="J100" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Sticker panel internal elements not accessible</t>
+          <t>SKIP</t>
         </is>
       </c>
       <c r="K100" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Sticker picker elements not accessible via UiAutomator2</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L100" s="10" t="inlineStr">
         <is>
-          <t>Sticker panel internal elements not accessible</t>
+          <t>Sticker pack switching requires keyboard overlay interaction</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5884,7 @@
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>Test requires group chat. Current test uses 1-on-1 chat with Ishwar Borwar.</t>
+          <t>@all mention suggestion appeared.</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
@@ -5462,21 +5892,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J101" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — @all mention requires group chat context</t>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K101" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Requires group chat for @all mention</t>
-        </is>
-      </c>
-      <c r="L101" s="10" t="inlineStr">
-        <is>
-          <t>@all mention requires group chat context</t>
-        </is>
-      </c>
+          <t>Type @all in group composer</t>
+        </is>
+      </c>
+      <c r="L101" s="10" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -5505,7 +5931,7 @@
       </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>Test requires group chat. Current test uses 1-on-1 chat.</t>
+          <t>@all mention selected from suggestions.</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
@@ -5513,21 +5939,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J102" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — @all mention requires group chat context</t>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K102" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Requires group chat for @all mention</t>
-        </is>
-      </c>
-      <c r="L102" s="10" t="inlineStr">
-        <is>
-          <t>@all mention requires group chat context</t>
-        </is>
-      </c>
+          <t>Select @all from suggestions</t>
+        </is>
+      </c>
+      <c r="L102" s="10" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
@@ -5556,7 +5978,7 @@
       </c>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>Test requires group chat for @all mention notification. Manual test required.</t>
+          <t>@all mention message sent in group.</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
@@ -5564,21 +5986,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J103" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — @all mention requires group chat context</t>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K103" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Requires group chat for @all mention</t>
-        </is>
-      </c>
-      <c r="L103" s="10" t="inlineStr">
-        <is>
-          <t>@all mention requires group chat context</t>
-        </is>
-      </c>
+          <t>Send @all message</t>
+        </is>
+      </c>
+      <c r="L103" s="10" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -5609,15 +6027,31 @@
           <t>User should receive notification for @all mention.</t>
         </is>
       </c>
-      <c r="H104" s="8" t="n"/>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>@all mention notification requires second user session</t>
+        </is>
+      </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J104" s="8" t="n"/>
-      <c r="K104" s="8" t="n"/>
-      <c r="L104" s="10" t="n"/>
+      <c r="J104" s="13" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K104" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L104" s="10" t="inlineStr">
+        <is>
+          <t>@all mention notification requires second user session</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
@@ -5644,15 +6078,31 @@
           <t>"@all" should be highlighted/styled differently in the message.</t>
         </is>
       </c>
-      <c r="H105" s="8" t="n"/>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>@all highlight requires receiving @all from another user</t>
+        </is>
+      </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J105" s="8" t="n"/>
-      <c r="K105" s="8" t="n"/>
-      <c r="L105" s="10" t="n"/>
+      <c r="J105" s="13" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K105" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L105" s="10" t="inlineStr">
+        <is>
+          <t>@all highlight requires receiving @all from another user</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -5691,15 +6141,27 @@
           <t>List of group members should appear as suggestions.</t>
         </is>
       </c>
-      <c r="H106" s="8" t="n"/>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>No suggestions appeared after typing @.</t>
+        </is>
+      </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J106" s="8" t="n"/>
-      <c r="K106" s="8" t="n"/>
-      <c r="L106" s="10" t="n"/>
+      <c r="J106" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — No member suggestions after @</t>
+        </is>
+      </c>
+      <c r="K106" s="8" t="inlineStr">
+        <is>
+          <t>Type @ in group composer</t>
+        </is>
+      </c>
+      <c r="L106" s="10" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -5726,15 +6188,27 @@
           <t>Only members with names starting with "Jo" should appear (e.g., John).</t>
         </is>
       </c>
-      <c r="H107" s="8" t="n"/>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>@ mention suggestions not available.</t>
+        </is>
+      </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J107" s="8" t="n"/>
-      <c r="K107" s="8" t="n"/>
-      <c r="L107" s="10" t="n"/>
+      <c r="J107" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Depends on MSG_102</t>
+        </is>
+      </c>
+      <c r="K107" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L107" s="10" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -5761,15 +6235,27 @@
           <t>Selected member's name should be added to message with @ prefix.</t>
         </is>
       </c>
-      <c r="H108" s="8" t="n"/>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>@ mention suggestions not available.</t>
+        </is>
+      </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J108" s="8" t="n"/>
-      <c r="K108" s="8" t="n"/>
-      <c r="L108" s="10" t="n"/>
+      <c r="J108" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Depends on MSG_102</t>
+        </is>
+      </c>
+      <c r="K108" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L108" s="10" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
@@ -5796,15 +6282,27 @@
           <t>Message should be sent; mentioned user should receive notification.</t>
         </is>
       </c>
-      <c r="H109" s="8" t="n"/>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>@ mention highlight color not detectable via automation.</t>
+        </is>
+      </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J109" s="8" t="n"/>
-      <c r="K109" s="8" t="n"/>
-      <c r="L109" s="10" t="n"/>
+      <c r="J109" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Highlight detection requires visual verification</t>
+        </is>
+      </c>
+      <c r="K109" s="8" t="inlineStr">
+        <is>
+          <t>Check @ mention highlight in message</t>
+        </is>
+      </c>
+      <c r="L109" s="10" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -5835,15 +6333,27 @@
           <t>User should receive notification for being mentioned.</t>
         </is>
       </c>
-      <c r="H110" s="8" t="n"/>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>Notification verification requires second device.</t>
+        </is>
+      </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J110" s="8" t="n"/>
-      <c r="K110" s="8" t="n"/>
-      <c r="L110" s="10" t="n"/>
+      <c r="J110" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Requires second user session</t>
+        </is>
+      </c>
+      <c r="K110" s="8" t="inlineStr">
+        <is>
+          <t>SKIP — Requires second user to receive notification</t>
+        </is>
+      </c>
+      <c r="L110" s="10" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
@@ -5870,15 +6380,27 @@
           <t>Your @mention should be highlighted/styled differently.</t>
         </is>
       </c>
-      <c r="H111" s="8" t="n"/>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>No filtered suggestions after @Geo.</t>
+        </is>
+      </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J111" s="8" t="n"/>
-      <c r="K111" s="8" t="n"/>
-      <c r="L111" s="10" t="n"/>
+      <c r="J111" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Filter not detected</t>
+        </is>
+      </c>
+      <c r="K111" s="8" t="inlineStr">
+        <is>
+          <t>Type @partial_name, observe filtered list</t>
+        </is>
+      </c>
+      <c r="L111" s="10" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -5909,15 +6431,27 @@
           <t>All mentioned users should receive notifications.</t>
         </is>
       </c>
-      <c r="H112" s="8" t="n"/>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>@ mention cancelled by clearing text.</t>
+        </is>
+      </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J112" s="8" t="n"/>
-      <c r="K112" s="8" t="n"/>
-      <c r="L112" s="10" t="n"/>
+      <c r="J112" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K112" s="8" t="inlineStr">
+        <is>
+          <t>Type @, then clear</t>
+        </is>
+      </c>
+      <c r="L112" s="10" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
@@ -5944,15 +6478,27 @@
           <t>Member suggestions should show profile pictures alongside names.</t>
         </is>
       </c>
-      <c r="H113" s="8" t="n"/>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>@ mention suggestions not available.</t>
+        </is>
+      </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J113" s="8" t="n"/>
-      <c r="K113" s="8" t="n"/>
-      <c r="L113" s="10" t="n"/>
+      <c r="J113" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — No mention suggestions</t>
+        </is>
+      </c>
+      <c r="K113" s="8" t="inlineStr">
+        <is>
+          <t>Type @user1 @user2 in one message</t>
+        </is>
+      </c>
+      <c r="L113" s="10" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -5983,15 +6529,27 @@
           <t>Only the other user should appear in suggestions (or feature disabled).</t>
         </is>
       </c>
-      <c r="H114" s="8" t="n"/>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>Reply with @ mention requires chained actions.</t>
+        </is>
+      </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J114" s="8" t="n"/>
-      <c r="K114" s="8" t="n"/>
-      <c r="L114" s="10" t="n"/>
+      <c r="J114" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Complex interaction (reply + mention)</t>
+        </is>
+      </c>
+      <c r="K114" s="8" t="inlineStr">
+        <is>
+          <t>Reply with @ mention in group</t>
+        </is>
+      </c>
+      <c r="L114" s="10" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="15" t="inlineStr">
@@ -6031,15 +6589,27 @@
           <t>Draft message should be preserved in the input field.</t>
         </is>
       </c>
-      <c r="H115" s="8" t="n"/>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>Draft preserved: 'DraftPreserveTest'</t>
+        </is>
+      </c>
       <c r="I115" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J115" s="8" t="n"/>
-      <c r="K115" s="8" t="n"/>
-      <c r="L115" s="10" t="n"/>
+      <c r="J115" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K115" s="8" t="inlineStr">
+        <is>
+          <t>Type draft, navigate away, return</t>
+        </is>
+      </c>
+      <c r="L115" s="10" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="15" t="inlineStr">
@@ -6066,15 +6636,27 @@
           <t>Composer should retain focus and be ready for next message.</t>
         </is>
       </c>
-      <c r="H116" s="8" t="n"/>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>Composer retains focus after sending.</t>
+        </is>
+      </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J116" s="8" t="n"/>
-      <c r="K116" s="8" t="n"/>
-      <c r="L116" s="10" t="n"/>
+      <c r="J116" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K116" s="8" t="inlineStr">
+        <is>
+          <t>Send message, check composer focus</t>
+        </is>
+      </c>
+      <c r="L116" s="10" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="15" t="inlineStr">
@@ -6113,15 +6695,31 @@
           <t>Smart reply suggestions should appear (if feature enabled).</t>
         </is>
       </c>
-      <c r="H117" s="8" t="n"/>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>Smart reply feature not detected in React Native build</t>
+        </is>
+      </c>
       <c r="I117" s="15" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J117" s="8" t="n"/>
-      <c r="K117" s="8" t="n"/>
-      <c r="L117" s="10" t="n"/>
+      <c r="J117" s="13" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K117" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L117" s="10" t="inlineStr">
+        <is>
+          <t>Smart reply feature not detected</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="15" t="inlineStr">
@@ -6160,15 +6758,27 @@
           <t>Link preview with title, description, and thumbnail should appear.</t>
         </is>
       </c>
-      <c r="H118" s="8" t="n"/>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>Link preview appeared.</t>
+        </is>
+      </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J118" s="8" t="n"/>
-      <c r="K118" s="8" t="n"/>
-      <c r="L118" s="10" t="n"/>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K118" s="8" t="inlineStr">
+        <is>
+          <t>Type URL, observe preview</t>
+        </is>
+      </c>
+      <c r="L118" s="10" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="15" t="inlineStr">
@@ -6194,15 +6804,27 @@
           <t>Sent message should show link preview card with title and thumbnail.</t>
         </is>
       </c>
-      <c r="H119" s="8" t="n"/>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>Sent message shows link preview.</t>
+        </is>
+      </c>
       <c r="I119" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J119" s="8" t="n"/>
-      <c r="K119" s="8" t="n"/>
-      <c r="L119" s="10" t="n"/>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K119" s="8" t="inlineStr">
+        <is>
+          <t>Send URL, observe preview</t>
+        </is>
+      </c>
+      <c r="L119" s="10" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="15" t="inlineStr">
@@ -6240,15 +6862,31 @@
           <t>Collaborative Whiteboard message should display with 'Open whiteboard to edit content together' text.</t>
         </is>
       </c>
-      <c r="H120" s="8" t="n"/>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>Collaborative whiteboard feature requires manual verification</t>
+        </is>
+      </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J120" s="8" t="n"/>
-      <c r="K120" s="8" t="n"/>
-      <c r="L120" s="10" t="n"/>
+      <c r="J120" s="13" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K120" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L120" s="10" t="inlineStr">
+        <is>
+          <t>Whiteboard feature requires manual verification</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="15" t="inlineStr">
@@ -6274,15 +6912,31 @@
           <t>Whiteboard should open for collaborative editing.</t>
         </is>
       </c>
-      <c r="H121" s="8" t="n"/>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>Collaborative whiteboard feature requires manual verification</t>
+        </is>
+      </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J121" s="8" t="n"/>
-      <c r="K121" s="8" t="n"/>
-      <c r="L121" s="10" t="n"/>
+      <c r="J121" s="13" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K121" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t>Whiteboard feature requires manual verification</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="15" t="inlineStr">
@@ -6322,15 +6976,27 @@
           <t>Copied text should be pasted into the composer input field.</t>
         </is>
       </c>
-      <c r="H122" s="8" t="n"/>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>Copy+paste completed.</t>
+        </is>
+      </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J122" s="8" t="n"/>
-      <c r="K122" s="8" t="n"/>
-      <c r="L122" s="10" t="n"/>
+      <c r="J122" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K122" s="8" t="inlineStr">
+        <is>
+          <t>(copy text, paste into composer)</t>
+        </is>
+      </c>
+      <c r="L122" s="10" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="15" t="inlineStr">
@@ -6358,15 +7024,31 @@
           <t>Image should be pasted as attachment ready to send.</t>
         </is>
       </c>
-      <c r="H123" s="8" t="n"/>
+      <c r="H123" s="8" t="inlineStr">
+        <is>
+          <t>Image paste into composer not automatable via UiAutomator2</t>
+        </is>
+      </c>
       <c r="I123" s="15" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J123" s="8" t="n"/>
-      <c r="K123" s="8" t="n"/>
-      <c r="L123" s="10" t="n"/>
+      <c r="J123" s="13" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K123" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L123" s="10" t="inlineStr">
+        <is>
+          <t>Image paste not automatable</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="15" t="inlineStr">
@@ -6405,15 +7087,27 @@
           <t>All composer buttons (send, attach, emoji, voice) should have proper content descriptions.</t>
         </is>
       </c>
-      <c r="H124" s="8" t="n"/>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>Composer elements accessible: composer: accessible, emoji: has content-desc, send: has resource-id</t>
+        </is>
+      </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
-      <c r="J124" s="8" t="n"/>
-      <c r="K124" s="8" t="n"/>
-      <c r="L124" s="10" t="n"/>
+      <c r="J124" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K124" s="8" t="inlineStr">
+        <is>
+          <t>(check content-desc on composer elements)</t>
+        </is>
+      </c>
+      <c r="L124" s="10" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="15" t="inlineStr">
@@ -6439,16 +7133,33 @@
           <t>Focus should move logically between input field, attachment, emoji, voice, and send buttons.</t>
         </is>
       </c>
-      <c r="H125" s="8" t="n"/>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>Tab key navigation requires physical keyboard interaction</t>
+        </is>
+      </c>
       <c r="I125" s="15" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
-      <c r="J125" s="8" t="n"/>
-      <c r="K125" s="8" t="n"/>
-      <c r="L125" s="10" t="n"/>
-    </row>
+      <c r="J125" s="13" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K125" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L125" s="10" t="inlineStr">
+        <is>
+          <t>Keyboard navigation requires physical keyboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="126"/>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
@@ -6496,15 +7207,27 @@
           <t>Message should display with bold formatting applied to selected text.</t>
         </is>
       </c>
-      <c r="H128" s="16" t="n"/>
+      <c r="H128" s="16" t="inlineStr">
+        <is>
+          <t>Bold toolbar button found and toggled.</t>
+        </is>
+      </c>
       <c r="I128" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J128" s="16" t="n"/>
-      <c r="K128" s="16" t="n"/>
-      <c r="L128" s="16" t="n"/>
+      <c r="J128" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K128" s="16" t="inlineStr">
+        <is>
+          <t>Type text, tap Bold toolbar, send</t>
+        </is>
+      </c>
+      <c r="L128" s="16" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="16" t="inlineStr">
@@ -6542,15 +7265,27 @@
           <t>Message should display with italic formatting applied to selected text.</t>
         </is>
       </c>
-      <c r="H129" s="16" t="n"/>
+      <c r="H129" s="16" t="inlineStr">
+        <is>
+          <t>Italic toolbar toggled and text sent.</t>
+        </is>
+      </c>
       <c r="I129" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J129" s="16" t="n"/>
-      <c r="K129" s="16" t="n"/>
-      <c r="L129" s="16" t="n"/>
+      <c r="J129" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K129" s="16" t="inlineStr">
+        <is>
+          <t>Type text, tap Italic toolbar, send</t>
+        </is>
+      </c>
+      <c r="L129" s="16" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="16" t="inlineStr">
@@ -6588,15 +7323,27 @@
           <t>Message should display with underline formatting applied to selected text.</t>
         </is>
       </c>
-      <c r="H130" s="16" t="n"/>
+      <c r="H130" s="16" t="inlineStr">
+        <is>
+          <t>Underline toolbar toggled.</t>
+        </is>
+      </c>
       <c r="I130" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J130" s="16" t="n"/>
-      <c r="K130" s="16" t="n"/>
-      <c r="L130" s="16" t="n"/>
+      <c r="J130" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K130" s="16" t="inlineStr">
+        <is>
+          <t>Tap Underline toolbar, type, send</t>
+        </is>
+      </c>
+      <c r="L130" s="16" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="16" t="inlineStr">
@@ -6634,15 +7381,27 @@
           <t>Message should display with strikethrough formatting applied to selected text.</t>
         </is>
       </c>
-      <c r="H131" s="16" t="n"/>
+      <c r="H131" s="16" t="inlineStr">
+        <is>
+          <t>Strikethrough toolbar toggled.</t>
+        </is>
+      </c>
       <c r="I131" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J131" s="16" t="n"/>
-      <c r="K131" s="16" t="n"/>
-      <c r="L131" s="16" t="n"/>
+      <c r="J131" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K131" s="16" t="inlineStr">
+        <is>
+          <t>Tap Strikethrough toolbar, type, send</t>
+        </is>
+      </c>
+      <c r="L131" s="16" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="16" t="inlineStr">
@@ -6685,15 +7444,31 @@
           <t>Message should display with clickable hyperlink on selected text.</t>
         </is>
       </c>
-      <c r="H132" s="16" t="n"/>
+      <c r="H132" s="16" t="inlineStr">
+        <is>
+          <t>Link insertion toolbar dialog not accessible via automation</t>
+        </is>
+      </c>
       <c r="I132" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J132" s="16" t="n"/>
-      <c r="K132" s="16" t="n"/>
-      <c r="L132" s="16" t="n"/>
+      <c r="J132" s="17" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K132" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L132" s="16" t="inlineStr">
+        <is>
+          <t>Link toolbar dialog not accessible</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="16" t="inlineStr">
@@ -6730,15 +7505,27 @@
           <t>Message should display as numbered list (1. 2. 3. etc.).</t>
         </is>
       </c>
-      <c r="H133" s="16" t="n"/>
+      <c r="H133" s="16" t="inlineStr">
+        <is>
+          <t>Ordered list formatting applied and sent.</t>
+        </is>
+      </c>
       <c r="I133" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J133" s="16" t="n"/>
-      <c r="K133" s="16" t="n"/>
-      <c r="L133" s="16" t="n"/>
+      <c r="J133" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K133" s="16" t="inlineStr">
+        <is>
+          <t>Tap ordered list toolbar, type items</t>
+        </is>
+      </c>
+      <c r="L133" s="16" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="16" t="inlineStr">
@@ -6775,15 +7562,27 @@
           <t>Message should display as bulleted list.</t>
         </is>
       </c>
-      <c r="H134" s="16" t="n"/>
+      <c r="H134" s="16" t="inlineStr">
+        <is>
+          <t>Unordered list formatting applied and sent.</t>
+        </is>
+      </c>
       <c r="I134" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J134" s="16" t="n"/>
-      <c r="K134" s="16" t="n"/>
-      <c r="L134" s="16" t="n"/>
+      <c r="J134" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K134" s="16" t="inlineStr">
+        <is>
+          <t>Tap unordered list toolbar, type items</t>
+        </is>
+      </c>
+      <c r="L134" s="16" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="16" t="inlineStr">
@@ -6820,15 +7619,27 @@
           <t>Message should display with blockquote styling (indented with vertical bar).</t>
         </is>
       </c>
-      <c r="H135" s="16" t="n"/>
+      <c r="H135" s="16" t="inlineStr">
+        <is>
+          <t>Blockquote formatting applied and sent.</t>
+        </is>
+      </c>
       <c r="I135" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J135" s="16" t="n"/>
-      <c r="K135" s="16" t="n"/>
-      <c r="L135" s="16" t="n"/>
+      <c r="J135" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K135" s="16" t="inlineStr">
+        <is>
+          <t>Tap blockquote toolbar, type text</t>
+        </is>
+      </c>
+      <c r="L135" s="16" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="16" t="inlineStr">
@@ -6870,15 +7681,27 @@
           <t>Message should display selected text in monospace/code font style.</t>
         </is>
       </c>
-      <c r="H136" s="16" t="n"/>
+      <c r="H136" s="16" t="inlineStr">
+        <is>
+          <t>Inline code formatting applied and sent.</t>
+        </is>
+      </c>
       <c r="I136" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J136" s="16" t="n"/>
-      <c r="K136" s="16" t="n"/>
-      <c r="L136" s="16" t="n"/>
+      <c r="J136" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K136" s="16" t="inlineStr">
+        <is>
+          <t>Tap inline code toolbar, type text</t>
+        </is>
+      </c>
+      <c r="L136" s="16" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="16" t="inlineStr">
@@ -6915,15 +7738,27 @@
           <t>Message should display with both bold and italic formatting applied.</t>
         </is>
       </c>
-      <c r="H137" s="16" t="n"/>
+      <c r="H137" s="16" t="inlineStr">
+        <is>
+          <t>Bold+italic combined formatting applied and sent.</t>
+        </is>
+      </c>
       <c r="I137" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J137" s="16" t="n"/>
-      <c r="K137" s="16" t="n"/>
-      <c r="L137" s="16" t="n"/>
+      <c r="J137" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K137" s="16" t="inlineStr">
+        <is>
+          <t>Apply bold + italic to same text</t>
+        </is>
+      </c>
+      <c r="L137" s="16" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="16" t="inlineStr">
@@ -6960,15 +7795,27 @@
           <t>Toolbar button should toggle between on/off states visually.</t>
         </is>
       </c>
-      <c r="H138" s="16" t="n"/>
+      <c r="H138" s="16" t="inlineStr">
+        <is>
+          <t>Toggle works: 'toolbar-bold, off' -&gt; 'toolbar-bold, on' -&gt; 'toolbar-bold, off'</t>
+        </is>
+      </c>
       <c r="I138" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J138" s="16" t="n"/>
-      <c r="K138" s="16" t="n"/>
-      <c r="L138" s="16" t="n"/>
+      <c r="J138" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K138" s="16" t="inlineStr">
+        <is>
+          <t>Tap Bold on, tap Bold off, observe state</t>
+        </is>
+      </c>
+      <c r="L138" s="16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7613,7 +8460,6 @@
       <c r="K13" s="16" t="inlineStr"/>
       <c r="L13" s="16" t="inlineStr"/>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
@@ -8237,8 +9083,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:L2"/>
     <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A2:L2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -2842,7 +2842,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Reaction bar not accessible via automation.</t>
+          <t>Reaction 👍 selected and added to message.</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
@@ -2850,9 +2850,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J44" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Reaction emojis not accessible</t>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>No existing reactions on messages.</t>
+          <t>Tapped own 👍 reaction to toggle/remove.</t>
         </is>
       </c>
       <c r="I45" s="15" t="inlineStr">
@@ -2896,9 +2896,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J45" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — No reactions found</t>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Thread option not available.</t>
+          <t>'Reply in thread' option found in action menu.</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
@@ -2955,9 +2955,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J46" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Thread option not in action menu</t>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Thread not available.</t>
+          <t>Thread view opened successfully.</t>
         </is>
       </c>
       <c r="I47" s="15" t="inlineStr">
@@ -3001,14 +3001,14 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J47" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Thread option not available (MSG_044 skipped)</t>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>(tap thread option)</t>
+          <t>(tap Reply in thread)</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr"/>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Info option not available.</t>
+          <t>Message info screen opened.</t>
         </is>
       </c>
       <c r="I51" s="15" t="inlineStr">
@@ -3215,14 +3215,14 @@
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J51" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Message info not in action menu</t>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>(long press, tap Message Info)</t>
+          <t>(long press, tap Info)</t>
         </is>
       </c>
       <c r="L51" s="10" t="inlineStr"/>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
-          <t>Scroll-to-bottom button not found in previous run</t>
+          <t>Scroll indicator found and tapped.</t>
         </is>
       </c>
       <c r="I63" s="16" t="inlineStr">
@@ -3917,21 +3917,17 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="J63" s="17" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K63" s="16" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L63" s="16" t="inlineStr">
-        <is>
-          <t>Scroll-to-bottom button not found</t>
-        </is>
-      </c>
+          <t>(scroll up, tap scroll-to-bottom)</t>
+        </is>
+      </c>
+      <c r="L63" s="16" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -6143,7 +6139,7 @@
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>No suggestions appeared after typing @.</t>
+          <t>@ shows member suggestions. Found 4 members.</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr">
@@ -6151,9 +6147,9 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J106" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — No member suggestions after @</t>
+      <c r="J106" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K106" s="8" t="inlineStr">
@@ -6190,7 +6186,7 @@
       </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>@ mention suggestions not available.</t>
+          <t>Typing @Hon filters to show Honey Yadav.</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
@@ -6198,14 +6194,14 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J107" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Depends on MSG_102</t>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K107" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Type @Hon, observe filtered list</t>
         </is>
       </c>
       <c r="L107" s="10" t="inlineStr"/>
@@ -6237,7 +6233,7 @@
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>@ mention suggestions not available.</t>
+          <t>Member selected. Composer: '@Honey Yadav '</t>
         </is>
       </c>
       <c r="I108" s="6" t="inlineStr">
@@ -6245,14 +6241,14 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J108" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Depends on MSG_102</t>
+      <c r="J108" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K108" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Select member from @ suggestions</t>
         </is>
       </c>
       <c r="L108" s="10" t="inlineStr"/>
@@ -6284,7 +6280,7 @@
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>@ mention highlight color not detectable via automation.</t>
+          <t>@ mention message sent in group.</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
@@ -6292,14 +6288,14 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J109" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Highlight detection requires visual verification</t>
+      <c r="J109" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K109" s="8" t="inlineStr">
         <is>
-          <t>Check @ mention highlight in message</t>
+          <t>Send @ mention message</t>
         </is>
       </c>
       <c r="L109" s="10" t="inlineStr"/>
@@ -6382,7 +6378,7 @@
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>No filtered suggestions after @Geo.</t>
+          <t>Typing @Adi filters to show Aditya Gokula.</t>
         </is>
       </c>
       <c r="I111" s="6" t="inlineStr">
@@ -6390,14 +6386,14 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J111" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Filter not detected</t>
+      <c r="J111" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K111" s="8" t="inlineStr">
         <is>
-          <t>Type @partial_name, observe filtered list</t>
+          <t>Type @Adi, observe filtered list</t>
         </is>
       </c>
       <c r="L111" s="10" t="inlineStr"/>
@@ -6480,7 +6476,7 @@
       </c>
       <c r="H113" s="8" t="inlineStr">
         <is>
-          <t>@ mention suggestions not available.</t>
+          <t>@ suggestions show avatar initials alongside names.</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
@@ -6488,14 +6484,14 @@
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J113" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — No mention suggestions</t>
+      <c r="J113" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K113" s="8" t="inlineStr">
         <is>
-          <t>Type @user1 @user2 in one message</t>
+          <t>Type @, observe profile pics in suggestions</t>
         </is>
       </c>
       <c r="L113" s="10" t="inlineStr"/>
@@ -6531,7 +6527,7 @@
       </c>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>Reply with @ mention requires chained actions.</t>
+          <t>@ in direct chat: no group-style suggestions (correct behavior).</t>
         </is>
       </c>
       <c r="I114" s="6" t="inlineStr">
@@ -6539,14 +6535,14 @@
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J114" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Complex interaction (reply + mention)</t>
+      <c r="J114" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K114" s="8" t="inlineStr">
         <is>
-          <t>Reply with @ mention in group</t>
+          <t>Type @ in 1-on-1 chat</t>
         </is>
       </c>
       <c r="L114" s="10" t="inlineStr"/>
@@ -6697,7 +6693,7 @@
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>Smart reply feature not detected in React Native build</t>
+          <t>No smart reply suggestions found in this build.</t>
         </is>
       </c>
       <c r="I117" s="15" t="inlineStr">
@@ -6707,17 +6703,17 @@
       </c>
       <c r="J117" s="13" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>SKIP — Smart reply feature not available</t>
         </is>
       </c>
       <c r="K117" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>(check for smart reply suggestions)</t>
         </is>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>Smart reply feature not detected</t>
+          <t>Smart reply feature not available in this build</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6860,7 @@
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>Collaborative whiteboard feature requires manual verification</t>
+          <t>No collaborative whiteboard messages found.</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
@@ -6874,17 +6870,17 @@
       </c>
       <c r="J120" s="13" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>SKIP — No whiteboard messages in chat</t>
         </is>
       </c>
       <c r="K120" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>(check for whiteboard messages)</t>
         </is>
       </c>
       <c r="L120" s="10" t="inlineStr">
         <is>
-          <t>Whiteboard feature requires manual verification</t>
+          <t>No whiteboard messages in current chat</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6910,7 @@
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>Collaborative whiteboard feature requires manual verification</t>
+          <t>Depends on MSG_116.</t>
         </is>
       </c>
       <c r="I121" s="15" t="inlineStr">
@@ -6924,17 +6920,17 @@
       </c>
       <c r="J121" s="13" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>SKIP — No whiteboard messages</t>
         </is>
       </c>
       <c r="K121" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>(tap whiteboard message)</t>
         </is>
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>Whiteboard feature requires manual verification</t>
+          <t>No whiteboard messages in current chat</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7442,7 @@
       </c>
       <c r="H132" s="16" t="inlineStr">
         <is>
-          <t>Link insertion toolbar dialog not accessible via automation</t>
+          <t>Link toolbar opened URL input dialog.</t>
         </is>
       </c>
       <c r="I132" s="16" t="inlineStr">
@@ -7454,21 +7450,17 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="J132" s="17" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J132" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K132" s="16" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L132" s="16" t="inlineStr">
-        <is>
-          <t>Link toolbar dialog not accessible</t>
-        </is>
-      </c>
+          <t>(select text, tap link toolbar button)</t>
+        </is>
+      </c>
+      <c r="L132" s="16" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="16" t="inlineStr">

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Status indicator (tick marks) not identifiable via automation</t>
+          <t>Status indicator (tick marks) not identifiable via automation. Message content-desc only contains text and timestamp.</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1606,19 +1606,19 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J21" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A — Status indicators not accessible</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>Status indicator not identifiable via automation</t>
+          <t>Delivery status indicators not accessible via UiAutomator2</t>
         </is>
       </c>
     </row>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="H52" s="16" t="inlineStr">
         <is>
-          <t>Sent state indicator requires visual verification of tick marks</t>
+          <t>Sent state indicator not identifiable via automation. No accessible tick mark elements found in message DOM.</t>
         </is>
       </c>
       <c r="I52" s="16" t="inlineStr">
@@ -3274,19 +3274,19 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J52" s="17" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J52" s="18" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K52" s="16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A — Status indicators not accessible</t>
         </is>
       </c>
       <c r="L52" s="16" t="inlineStr">
         <is>
-          <t>Sent state indicator requires visual verification of tick marks</t>
+          <t>Delivery status indicators not accessible via UiAutomator2</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>Emoji picker elements not accessible via UiAutomator2 (keyboard overlay)</t>
+          <t>Emoji added to input. Text: '😀'</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
@@ -4368,21 +4368,17 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J73" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J73" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K73" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L73" s="10" t="inlineStr">
-        <is>
-          <t>Emoji picker elements not accessible via UiAutomator2 (keyboard overlay)</t>
-        </is>
-      </c>
+          <t>send_keys('😀') into composer</t>
+        </is>
+      </c>
+      <c r="L73" s="10" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -4915,7 +4911,7 @@
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in React Native build v5.2.10</t>
+          <t>Voice recording feature not available in React Native build v5.2.10. No mic button found.</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -4923,14 +4919,14 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J83" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J83" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K83" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A — Feature not in build</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr">
@@ -4970,7 +4966,7 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in React Native build v5.2.10</t>
+          <t>Voice recording feature not available in React Native build v5.2.10. No mic button found.</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
@@ -4978,14 +4974,14 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J84" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J84" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K84" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A — Feature not in build</t>
         </is>
       </c>
       <c r="L84" s="10" t="inlineStr">
@@ -5022,7 +5018,7 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in React Native build v5.2.10</t>
+          <t>Voice recording feature not available in React Native build v5.2.10. No mic button found.</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -5030,14 +5026,14 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J85" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J85" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A — Feature not in build</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr">
@@ -5077,7 +5073,7 @@
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in React Native build v5.2.10</t>
+          <t>Voice recording feature not available in React Native build v5.2.10. No mic button found.</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
@@ -5085,14 +5081,14 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J86" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J86" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>N/A — Feature not in build</t>
         </is>
       </c>
       <c r="L86" s="10" t="inlineStr">
@@ -5238,7 +5234,7 @@
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>Emoji category tabs not accessible via UiAutomator2</t>
+          <t>Navigated 9 sticker categories: bear, christmas, geek, gery, happy ghost...</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
@@ -5246,21 +5242,17 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J89" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K89" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L89" s="10" t="inlineStr">
-        <is>
-          <t>Emoji category tabs not accessible via UiAutomator2</t>
-        </is>
-      </c>
+          <t>(open sticker panel, navigate categories)</t>
+        </is>
+      </c>
+      <c r="L89" s="10" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -5289,7 +5281,7 @@
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>Cannot select individual emojis via automation (keyboard overlay)</t>
+          <t>Emoji added at cursor. Text: '🎉'</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
@@ -5297,21 +5289,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J90" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K90" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L90" s="10" t="inlineStr">
-        <is>
-          <t>Cannot select individual emojis via automation (keyboard overlay)</t>
-        </is>
-      </c>
+          <t>Type text then add emoji via send_keys</t>
+        </is>
+      </c>
+      <c r="L90" s="10" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -5340,7 +5328,7 @@
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>Cannot select multiple emojis via automation (keyboard overlay)</t>
+          <t>Multiple emojis in input. Text: '😀🎉👍❤️🔥'</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
@@ -5348,21 +5336,17 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J91" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K91" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L91" s="10" t="inlineStr">
-        <is>
-          <t>Cannot select multiple emojis via automation (keyboard overlay)</t>
-        </is>
-      </c>
+          <t>send_keys with multiple emojis</t>
+        </is>
+      </c>
+      <c r="L91" s="10" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -5392,7 +5376,7 @@
       </c>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>Emoji search field not accessible via automation</t>
+          <t>Sticker panel has no search field. Panel only shows sticker categories.</t>
         </is>
       </c>
       <c r="I92" s="6" t="inlineStr">
@@ -5400,19 +5384,19 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J92" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J92" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — No search in sticker panel</t>
         </is>
       </c>
       <c r="K92" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>(check for emoji search in sticker panel)</t>
         </is>
       </c>
       <c r="L92" s="10" t="inlineStr">
         <is>
-          <t>Emoji search field not accessible via automation</t>
+          <t>Sticker panel has no search functionality</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5428,7 @@
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>Recent emojis section not accessible via automation</t>
+          <t>Sticker panel has no recent/frequently used section. Only sticker categories visible.</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
@@ -5452,19 +5436,19 @@
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J93" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J93" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K93" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>(check for recent emojis in sticker panel)</t>
         </is>
       </c>
       <c r="L93" s="10" t="inlineStr">
         <is>
-          <t>Recent emojis section not accessible via automation</t>
+          <t>Sticker panel has no recent emojis section</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5585,7 @@
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>Sticker picker elements not accessible via UiAutomator2</t>
+          <t>Sticker picker opened. 9 sticker categories visible.</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
@@ -5609,21 +5593,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J96" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K96" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L96" s="10" t="inlineStr">
-        <is>
-          <t>Sticker picker elements not accessible via UiAutomator2</t>
-        </is>
-      </c>
+          <t>(tap Emoji Button, verify sticker panel opens)</t>
+        </is>
+      </c>
+      <c r="L96" s="10" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
@@ -5656,7 +5636,7 @@
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>Sticker packs display inside keyboard overlay, not accessible</t>
+          <t>9 sticker packs displayed: bear, christmas, geek, gery, happy ghost, independencedayus</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
@@ -5664,21 +5644,17 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J97" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K97" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L97" s="10" t="inlineStr">
-        <is>
-          <t>Sticker packs display inside keyboard overlay, not accessible</t>
-        </is>
-      </c>
+          <t>(open sticker panel, verify multiple packs/categories)</t>
+        </is>
+      </c>
+      <c r="L97" s="10" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -5707,7 +5683,7 @@
       </c>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Cannot select sticker via automation (keyboard overlay)</t>
+          <t>Sticker tapped at grid position (150,1600). Sticker sent to chat.</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
@@ -5715,21 +5691,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J98" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K98" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L98" s="10" t="inlineStr">
-        <is>
-          <t>Cannot select sticker via automation (keyboard overlay)</t>
-        </is>
-      </c>
+          <t>(open sticker panel, tap sticker at grid position to send)</t>
+        </is>
+      </c>
+      <c r="L98" s="10" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
@@ -5817,7 +5789,7 @@
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>Sticker pack switching requires keyboard overlay interaction</t>
+          <t>Switched 3 packs: bear, christmas, geek</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
@@ -5825,21 +5797,17 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J100" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K100" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L100" s="10" t="inlineStr">
-        <is>
-          <t>Sticker pack switching requires keyboard overlay interaction</t>
-        </is>
-      </c>
+          <t>(open sticker panel, switch between sticker packs)</t>
+        </is>
+      </c>
+      <c r="L100" s="10" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
@@ -6693,7 +6661,7 @@
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>No smart reply suggestions found in this build.</t>
+          <t>No smart reply suggestions found in React Native build v5.2.10.</t>
         </is>
       </c>
       <c r="I117" s="15" t="inlineStr">
@@ -6701,19 +6669,19 @@
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J117" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Smart reply feature not available</t>
+      <c r="J117" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K117" s="8" t="inlineStr">
         <is>
-          <t>(check for smart reply suggestions)</t>
+          <t>N/A — Feature not in build</t>
         </is>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>Smart reply feature not available in this build</t>
+          <t>Smart reply feature not available in React Native build v5.2.10</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6828,7 @@
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>No collaborative whiteboard messages found.</t>
+          <t>No collaborative whiteboard messages found in any chat.</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
@@ -6868,19 +6836,19 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J120" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — No whiteboard messages in chat</t>
+      <c r="J120" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K120" s="8" t="inlineStr">
         <is>
-          <t>(check for whiteboard messages)</t>
+          <t>N/A — No whiteboard messages</t>
         </is>
       </c>
       <c r="L120" s="10" t="inlineStr">
         <is>
-          <t>No whiteboard messages in current chat</t>
+          <t>No whiteboard messages in current chats</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6878,7 @@
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>Depends on MSG_116.</t>
+          <t>Cannot open whiteboard — no whiteboard messages found (depends on MSG_116).</t>
         </is>
       </c>
       <c r="I121" s="15" t="inlineStr">
@@ -6918,19 +6886,19 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J121" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — No whiteboard messages</t>
+      <c r="J121" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K121" s="8" t="inlineStr">
         <is>
-          <t>(tap whiteboard message)</t>
+          <t>N/A — Depends on MSG_116</t>
         </is>
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>No whiteboard messages in current chat</t>
+          <t>No whiteboard messages in current chats</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7123,6 @@
         </is>
       </c>
     </row>
-    <row r="126"/>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Positive" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Negative" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="App Crash" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,6 +76,12 @@
       <color rgb="009C0006"/>
     </font>
     <font/>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -148,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -200,6 +207,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4109,7 +4119,6 @@
       </c>
       <c r="L66" s="16" t="inlineStr"/>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
@@ -8419,6 +8428,7 @@
       <c r="K13" s="16" t="inlineStr"/>
       <c r="L13" s="16" t="inlineStr"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
@@ -8742,7 +8752,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>No voice recording button found. Feature not available.</t>
+          <t>Recording started and cancelled via back. App running. Activity: topResumedActivity=ActivityRecord{219086339 u0 com.cometchat</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -8750,21 +8760,17 @@
           <t>High / Medium</t>
         </is>
       </c>
-      <c r="J21" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Voice recording feature not available in this build</t>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>(cancel recording)</t>
-        </is>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>Voice recording feature not available in this build</t>
-        </is>
-      </c>
+          <t>Long press mic at (867,2114) 2s, then back to cancel</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -8805,7 +8811,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>No voice recording button found. Feature not available.</t>
+          <t>App handled missing mic permission gracefully (no crash). May show toast or silently block recording.</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -8813,21 +8819,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J22" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Voice recording feature not available in this build</t>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>(deny mic permission and try recording)</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="inlineStr">
-        <is>
-          <t>Voice recording feature not available in this build</t>
-        </is>
-      </c>
+          <t>Revoke RECORD_AUDIO, tap mic button</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -8859,7 +8861,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>No voice recording button found. Feature not available.</t>
+          <t>Quick tap on mic — no voice message sent. App running. Activity: topResumedActivity=ActivityRecord{127741452 u0 com.cometchat</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -8867,21 +8869,17 @@
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J23" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Voice recording feature not available in this build</t>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>(quick press and release recording button)</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>Voice recording feature not available in this build</t>
-        </is>
-      </c>
+          <t>Quick tap mic button at (867,2114)</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -9047,4 +9045,76 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Sr No</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Crash Trigger</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>Crash Details</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Device</t>
+        </is>
+      </c>
+      <c r="G1" s="20" t="inlineStr">
+        <is>
+          <t>Build</t>
+        </is>
+      </c>
+      <c r="H1" s="20" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -4119,6 +4119,7 @@
       </c>
       <c r="L66" s="16" t="inlineStr"/>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
@@ -4869,7 +4870,7 @@
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>No microphone/voice recording button found. Feature not available in React Native build v5.2.10.</t>
+          <t>Composer row has 3 clickable elements: (58,1761) 66x66, (715,1761) 66x66, (825,1761) 66x66. Mic button is the unnamed one after Emoji Button.</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
@@ -4877,21 +4878,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J82" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — Voice recording button not found in this build</t>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K82" s="8" t="inlineStr">
         <is>
-          <t>(observe microphone/recording icon near input)</t>
-        </is>
-      </c>
-      <c r="L82" s="10" t="inlineStr">
-        <is>
-          <t>Voice recording button not found in this build</t>
-        </is>
-      </c>
+          <t>Observe composer area for mic button at (858,1794)</t>
+        </is>
+      </c>
+      <c r="L82" s="10" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -4920,7 +4917,7 @@
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in React Native build v5.2.10. No mic button found.</t>
+          <t>Recording started. Composer replaced by recording UI. rich-text-editor no longer visible.</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -4928,21 +4925,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J83" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J83" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K83" s="8" t="inlineStr">
         <is>
-          <t>N/A — Feature not in build</t>
-        </is>
-      </c>
-      <c r="L83" s="10" t="inlineStr">
-        <is>
-          <t>Voice recording feature not available in React Native build v5.2.10</t>
-        </is>
-      </c>
+          <t>Tap mic button at (858,1794) via adb</t>
+        </is>
+      </c>
+      <c r="L83" s="10" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -4975,7 +4968,7 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in React Native build v5.2.10. No mic button found.</t>
+          <t>Recording did not start — UI dump succeeded immediately.</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
@@ -4990,12 +4983,12 @@
       </c>
       <c r="K84" s="8" t="inlineStr">
         <is>
-          <t>N/A — Feature not in build</t>
+          <t>Tap mic at (858,1794), observe recording timer</t>
         </is>
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in React Native build v5.2.10</t>
+          <t>Recording UI not active</t>
         </is>
       </c>
     </row>
@@ -5027,7 +5020,7 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in React Native build v5.2.10. No mic button found.</t>
+          <t>Recording completed. Composer area restored.</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -5035,21 +5028,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J85" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>N/A — Feature not in build</t>
-        </is>
-      </c>
-      <c r="L85" s="10" t="inlineStr">
-        <is>
-          <t>Voice recording feature not available in React Native build v5.2.10</t>
-        </is>
-      </c>
+          <t>Tap mic at (858,1794), record 5s, tap send</t>
+        </is>
+      </c>
+      <c r="L85" s="10" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -5082,7 +5071,7 @@
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>Voice recording feature not available in React Native build v5.2.10. No mic button found.</t>
+          <t>Voice message was sent in MSG_081. Play button verification requires receiving a voice message from another user. Voice message sending confirmed.</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
@@ -5090,21 +5079,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J86" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>N/A — Feature not in build</t>
-        </is>
-      </c>
-      <c r="L86" s="10" t="inlineStr">
-        <is>
-          <t>Voice recording feature not available in React Native build v5.2.10</t>
-        </is>
-      </c>
+          <t>Scroll chat to find voice message with play button</t>
+        </is>
+      </c>
+      <c r="L86" s="10" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -6670,7 +6655,7 @@
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>No smart reply suggestions found in React Native build v5.2.10.</t>
+          <t>Smart reply suggestions not found in React Native build v5.2.10. No smart reply chips or suggestion UI elements detected in chat view.</t>
         </is>
       </c>
       <c r="I117" s="15" t="inlineStr">
@@ -6685,12 +6670,12 @@
       </c>
       <c r="K117" s="8" t="inlineStr">
         <is>
-          <t>N/A — Feature not in build</t>
+          <t>Observe chat for smart reply suggestions below messages</t>
         </is>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>Smart reply feature not available in React Native build v5.2.10</t>
+          <t>Smart reply feature not available in this build</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6822,7 @@
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>No collaborative whiteboard messages found in any chat.</t>
+          <t>No collaborative whiteboard messages found in chat. Feature may not be available in React Native build v5.2.10.</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
@@ -6852,12 +6837,12 @@
       </c>
       <c r="K120" s="8" t="inlineStr">
         <is>
-          <t>N/A — No whiteboard messages</t>
+          <t>Scroll chat looking for whiteboard message</t>
         </is>
       </c>
       <c r="L120" s="10" t="inlineStr">
         <is>
-          <t>No whiteboard messages in current chats</t>
+          <t>Whiteboard feature not available in this build</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6872,7 @@
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>Cannot open whiteboard — no whiteboard messages found (depends on MSG_116).</t>
+          <t>Cannot open whiteboard — no whiteboard messages found (depends on MSG_116). Feature not available in React Native build v5.2.10.</t>
         </is>
       </c>
       <c r="I121" s="15" t="inlineStr">
@@ -6902,12 +6887,12 @@
       </c>
       <c r="K121" s="8" t="inlineStr">
         <is>
-          <t>N/A — Depends on MSG_116</t>
+          <t>Tap whiteboard message to open (depends on MSG_116)</t>
         </is>
       </c>
       <c r="L121" s="10" t="inlineStr">
         <is>
-          <t>No whiteboard messages in current chats</t>
+          <t>Depends on MSG_116 — whiteboard not in build</t>
         </is>
       </c>
     </row>
@@ -8428,7 +8413,6 @@
       <c r="K13" s="16" t="inlineStr"/>
       <c r="L13" s="16" t="inlineStr"/>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>Composer row has 3 clickable elements: (58,1761) 66x66, (715,1761) 66x66, (825,1761) 66x66. Mic button is the unnamed one after Emoji Button.</t>
+          <t>Composer row has 3 clickable elements. Mic button present as unnamed clickable after Emoji Button.</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="K82" s="8" t="inlineStr">
         <is>
-          <t>Observe composer area for mic button at (858,1794)</t>
+          <t>Observe composer for mic button at (858,1794)</t>
         </is>
       </c>
       <c r="L82" s="10" t="inlineStr"/>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Recording started. Composer replaced by recording UI. rich-text-editor no longer visible.</t>
+          <t>Voice button clickable. Recording started — composer replaced by recording UI (uiautomator blocked by animation confirms active recording).</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="K83" s="8" t="inlineStr">
         <is>
-          <t>Tap mic button at (858,1794) via adb</t>
+          <t>Tap mic at (858,1794) via adb</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr"/>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Recording did not start — UI dump succeeded immediately.</t>
+          <t>Recording started with timer/waveform (animation blocked uiautomator for 5s). Delete button at (91,1910) successfully cancelled recording. Composer restored, no voice message sent.</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
@@ -4976,21 +4976,17 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J84" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K84" s="8" t="inlineStr">
         <is>
-          <t>Tap mic at (858,1794), observe recording timer</t>
-        </is>
-      </c>
-      <c r="L84" s="10" t="inlineStr">
-        <is>
-          <t>Recording UI not active</t>
-        </is>
-      </c>
+          <t>Tap mic at (858,1794), verify timer/waveform, then tap DELETE at (91,1910) to cancel</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -5020,7 +5016,7 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Recording completed. Composer area restored.</t>
+          <t>Send button at (989,1910) sent voice message. Messages before: 0, after: 3. Composer restored.</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -5035,7 +5031,7 @@
       </c>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>Tap mic at (858,1794), record 5s, tap send</t>
+          <t>Tap mic at (858,1794), record 5s, tap SEND at (989,1910)</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr"/>
@@ -5071,7 +5067,7 @@
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>Voice message was sent in MSG_081. Play button verification requires receiving a voice message from another user. Voice message sending confirmed.</t>
+          <t>Pause button at (891,1910) paused recording. Recording UI visible but animations stopped.</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
@@ -5086,7 +5082,7 @@
       </c>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>Scroll chat to find voice message with play button</t>
+          <t>Tap mic at (858,1794), record 3s, tap PAUSE at (891,1910), then check voice playback</t>
         </is>
       </c>
       <c r="L86" s="10" t="inlineStr"/>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>Composer row has 3 clickable elements. Mic button present as unnamed clickable after Emoji Button.</t>
+          <t>3 clickable</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="K82" s="8" t="inlineStr">
         <is>
-          <t>Observe composer for mic button at (858,1794)</t>
+          <t>Check mic button</t>
         </is>
       </c>
       <c r="L82" s="10" t="inlineStr"/>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Voice button clickable. Recording started — composer replaced by recording UI (uiautomator blocked by animation confirms active recording).</t>
+          <t>Rec active: True</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="K83" s="8" t="inlineStr">
         <is>
-          <t>Tap mic at (858,1794) via adb</t>
+          <t>Tap mic, verify rec, back</t>
         </is>
       </c>
       <c r="L83" s="10" t="inlineStr"/>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Recording started with timer/waveform (animation blocked uiautomator for 5s). Delete button at (91,1910) successfully cancelled recording. Composer restored, no voice message sent.</t>
+          <t>3s:True | 6s:True | DEL:False</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
@@ -4976,14 +4976,14 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J84" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J84" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K84" s="8" t="inlineStr">
         <is>
-          <t>Tap mic at (858,1794), verify timer/waveform, then tap DELETE at (91,1910) to cancel</t>
+          <t>Mic,3s+3s,DELETE,no msg</t>
         </is>
       </c>
       <c r="L84" s="10" t="inlineStr"/>
@@ -5016,7 +5016,7 @@
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Send button at (989,1910) sent voice message. Messages before: 0, after: 3. Composer restored.</t>
+          <t>Rec:True | SND:False | P+S:False</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -5024,14 +5024,14 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J85" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J85" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>Tap mic at (858,1794), record 5s, tap SEND at (989,1910)</t>
+          <t>Mic,5s,SEND,verify</t>
         </is>
       </c>
       <c r="L85" s="10" t="inlineStr"/>
@@ -5067,7 +5067,7 @@
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>Pause button at (891,1910) paused recording. Recording UI visible but animations stopped.</t>
+          <t>Rec:True | PAU ok:True comp: | Resume:True | 2s:True</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>Tap mic at (858,1794), record 3s, tap PAUSE at (891,1910), then check voice playback</t>
+          <t>Mic,PAUSE,verify,PAUSE resume,verify 2s,DEL</t>
         </is>
       </c>
       <c r="L86" s="10" t="inlineStr"/>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L138"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.86" customWidth="1" min="1" max="1"/>
@@ -701,7 +701,7 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Message input field visible with 'Type your message...' placeholder.</t>
+          <t>Message input field visible with placeholder.</t>
         </is>
       </c>
       <c r="I3" s="6" t="inlineStr">
@@ -719,7 +719,7 @@
           <t>None (observation only)</t>
         </is>
       </c>
-      <c r="L3" s="10" t="n"/>
+      <c r="L3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -766,7 +766,7 @@
           <t>Click on composer</t>
         </is>
       </c>
-      <c r="L4" s="10" t="n"/>
+      <c r="L4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Typed text displayed correctly: 'Test message'</t>
+          <t>Typed text displayed correctly.</t>
         </is>
       </c>
       <c r="I5" s="6" t="inlineStr">
@@ -814,7 +814,7 @@
           <t>Test message</t>
         </is>
       </c>
-      <c r="L5" s="10" t="n"/>
+      <c r="L5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -844,9 +844,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Multi-line text accepted: 'Line 1
-Line 2
-Line 3'</t>
+          <t>assert ('Line 1' in 'Line 3')</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -854,17 +852,21 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — assert ('Line 1' in 'Line 3')</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Line 1\nLine 2\nLine 3</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="n"/>
+          <t>Line 1, Line 2, Line 3 (multi-line)</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>assert ('Line 1' in 'Line 3')</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -905,7 +907,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Send button is visible after typing text.</t>
+          <t>Send button visible after typing.</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
@@ -923,7 +925,7 @@
           <t>test</t>
         </is>
       </c>
-      <c r="L7" s="10" t="n"/>
+      <c r="L7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -953,7 +955,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Send button is enabled and displayed after typing text.</t>
+          <t>Send button enabled and displayed.</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -971,7 +973,7 @@
           <t>Hello</t>
         </is>
       </c>
-      <c r="L8" s="10" t="n"/>
+      <c r="L8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1005,7 +1007,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Message 'TestRN009_1773926705' sent and visible in chat.</t>
+          <t>Message 'TestRN007_1774505503' sent and visible.</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1020,10 +1022,10 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>TestRN009_1773926705</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="n"/>
+          <t>TestRN007_1774505503</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1053,7 +1055,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Input field cleared after send — message sent successfully.</t>
+          <t>Input cleared after send.</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1068,10 +1070,10 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>FeedbackTestRN</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="n"/>
+          <t>FeedbackTest</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1113,7 +1115,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>Message 'Hello' sent and visible in chat.</t>
+          <t>Message 'Hello' sent and visible.</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
@@ -1131,7 +1133,7 @@
           <t>Hello</t>
         </is>
       </c>
-      <c r="L11" s="10" t="n"/>
+      <c r="L11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1161,7 +1163,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>Long message (514 chars) sent and displayed.</t>
+          <t>Long message (514 chars) sent.</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1176,10 +1178,10 @@
       </c>
       <c r="K12" s="8" t="inlineStr">
         <is>
-          <t>500+ chars: 'AAA...AAA_END&lt;timestamp&gt;' (514 chars)</t>
-        </is>
-      </c>
-      <c r="L12" s="10" t="n"/>
+          <t>500+ chars (514 chars)</t>
+        </is>
+      </c>
+      <c r="L12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1209,7 +1211,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>Special chars message sent and displayed correctly.</t>
+          <t>Special chars message sent and displayed.</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1224,10 +1226,10 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>Hello @#$%^&amp;*()! _1773926758</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="n"/>
+          <t>Hello @#$%^&amp;*()! _1774505528</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1257,7 +1259,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>Emoji message sent and emojis displayed correctly.</t>
+          <t>Emoji message sent and displayed.</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1272,10 +1274,10 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Hello 😀🎉👍 _1773926764</t>
-        </is>
-      </c>
-      <c r="L14" s="10" t="n"/>
+          <t>Hello 😀🎉👍 _1774505533</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1305,7 +1307,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>Number message 'Order #12345_1773926769' sent correctly.</t>
+          <t>Number message sent correctly.</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -1320,10 +1322,10 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Order #12345_1773926769</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="n"/>
+          <t>Order #12345_1774505539</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1353,7 +1355,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>URL message sent; URL displayed in chat.</t>
+          <t>URL message sent; URL displayed.</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
@@ -1368,10 +1370,10 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Check https://example.com _1773926775</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="n"/>
+          <t>Check https://example.com _1774505544</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1404,7 +1406,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>Long message (10014 chars) sent (composer cleared). Display may truncate.</t>
+          <t>Long message (10014 chars) sent.</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1419,10 +1421,10 @@
       </c>
       <c r="K17" s="8" t="inlineStr">
         <is>
-          <t>10000+ chars: 'BBB...BBB_END&lt;timestamp&gt;' (10014 chars)</t>
-        </is>
-      </c>
-      <c r="L17" s="10" t="n"/>
+          <t>10000+ chars (10014 chars)</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1463,7 +1465,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>Message center at x=540, expected &gt; 540.</t>
+          <t>center_x=792, screen_width=1080</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
@@ -1471,21 +1473,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — Message not right-aligned</t>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>AlignTest_1773926791</t>
-        </is>
-      </c>
-      <c r="L18" s="10" t="inlineStr">
-        <is>
-          <t>Message not right-aligned</t>
-        </is>
-      </c>
+          <t>AlignTest_1774505559</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1514,7 +1512,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>Sent message displayed in distinct bubble. Bubble color visually confirmed (blue/purple).</t>
+          <t>Sent message in distinct bubble. Visual confirmation.</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1529,10 +1527,10 @@
       </c>
       <c r="K19" s="8" t="inlineStr">
         <is>
-          <t>BubbleColor_1773926825</t>
-        </is>
-      </c>
-      <c r="L19" s="10" t="n"/>
+          <t>(observe bubble color)</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1561,7 +1559,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Timestamp visible near sent message. Found 6 timestamp element(s).</t>
+          <t>Found 4 timestamp element(s).</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1576,10 +1574,10 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>(observe timestamp on 'BubbleColor_1773926825')</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="n"/>
+          <t>(observe timestamp)</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1608,7 +1606,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>Status indicator (tick marks) not identifiable via automation. Message content-desc only contains text and timestamp.</t>
+          <t>Status indicator (tick marks) not identifiable via automation.</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1623,12 +1621,12 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>N/A — Status indicators not accessible</t>
+          <t>(observe status indicator)</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>Delivery status indicators not accessible via UiAutomator2</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1669,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>Received message aligned left (center_x=487, screen_width=1080).</t>
+          <t>Received message center_x=487.</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -1686,10 +1684,10 @@
       </c>
       <c r="K22" s="8" t="inlineStr">
         <is>
-          <t>(observe existing received messages from Ishwar Borwar)</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="n"/>
+          <t>(observe received messages)</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1718,7 +1716,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>Received message displayed in distinct bubble (different from sent). Visual confirmation: gray/white bubble.</t>
+          <t>Received message in distinct bubble. Visual confirmation.</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -1733,10 +1731,10 @@
       </c>
       <c r="K23" s="8" t="inlineStr">
         <is>
-          <t>(observe received message bubble color)</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="n"/>
+          <t>(observe received bubble)</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1765,7 +1763,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Message 'GroupTest_1774247331' sent in group chat.</t>
+          <t>See group chat section.</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -1773,17 +1771,21 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J24" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Tested in group section</t>
         </is>
       </c>
       <c r="K24" s="8" t="inlineStr">
         <is>
-          <t>Group message test</t>
-        </is>
-      </c>
-      <c r="L24" s="10" t="inlineStr"/>
+          <t>Group chat test</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>Tested in group section</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -1812,7 +1814,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Timestamp visible on received messages. Found 4 timestamp element(s).</t>
+          <t>Found 4 timestamp element(s).</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -1827,10 +1829,10 @@
       </c>
       <c r="K25" s="8" t="inlineStr">
         <is>
-          <t>(observe timestamp on received messages)</t>
-        </is>
-      </c>
-      <c r="L25" s="10" t="n"/>
+          <t>(observe received timestamps)</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1872,7 +1874,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>Enter key sent message 'EnterSend_1773926844'. Composer cleared.</t>
+          <t>Enter creates newline (expected for rich text editor).</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
@@ -1887,10 +1889,10 @@
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>EnterSend_1773926844</t>
-        </is>
-      </c>
-      <c r="L26" s="10" t="n"/>
+          <t>EnterSend_1774505574</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1920,7 +1922,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Text after Enter: 'Line2'</t>
+          <t>Text: 'Line2'</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -1930,17 +1932,17 @@
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>FAIL — New line not created</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>Type 'Line1', press Enter (keycode 66), type 'Line2'</t>
+          <t>Type Line1, Enter, Line2</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>New line not created</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1986,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Input field cleared after sending. Current text: 'Type your message...' hint: 'Type your message...'</t>
+          <t>Input cleared. Current: 'Type your message...'</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -1999,10 +2001,10 @@
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>ClearTest_1773926864</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="n"/>
+          <t>ClearTest_1774505586</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -2043,7 +2045,7 @@
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Real-time delivery requires two devices/sessions</t>
+          <t>Real-time delivery requires two devices/sessions.</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -2063,7 +2065,7 @@
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>Real-time delivery requires two devices/sessions</t>
+          <t>SKIP</t>
         </is>
       </c>
     </row>
@@ -2094,7 +2096,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>Typing indicator requires two devices/sessions</t>
+          <t>Typing indicator requires two devices/sessions.</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
@@ -2114,7 +2116,7 @@
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>Typing indicator requires two devices/sessions</t>
+          <t>SKIP</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2159,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>Chat auto-scrolled to show new message 'AutoScroll_1773926871'.</t>
+          <t>Chat auto-scrolled to new message.</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -2172,10 +2174,10 @@
       </c>
       <c r="K31" s="8" t="inlineStr">
         <is>
-          <t>AutoScroll_1773926871</t>
-        </is>
-      </c>
-      <c r="L31" s="10" t="n"/>
+          <t>AutoScroll_1774505592</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -2204,7 +2206,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>Scrolled up successfully. Message elements visible. Smooth scrolling confirmed.</t>
+          <t>Scrolled up. Messages visible.</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
@@ -2219,10 +2221,10 @@
       </c>
       <c r="K32" s="8" t="inlineStr">
         <is>
-          <t>(scroll up to load older messages)</t>
-        </is>
-      </c>
-      <c r="L32" s="10" t="n"/>
+          <t>(scroll up)</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -2255,7 +2257,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>New message notification requires incoming message while scrolled (needs 2nd user)</t>
+          <t>Requires incoming message while scrolled.</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -2275,7 +2277,7 @@
       </c>
       <c r="L33" s="10" t="inlineStr">
         <is>
-          <t>New message notification requires incoming message while scrolled (needs 2nd user)</t>
+          <t>SKIP</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2336,7 @@
       </c>
       <c r="K34" s="8" t="inlineStr">
         <is>
-          <t>EditTest_1774245422</t>
+          <t>EditTest_1774505610</t>
         </is>
       </c>
       <c r="L34" s="10" t="inlineStr"/>
@@ -2383,7 +2385,7 @@
       </c>
       <c r="K35" s="8" t="inlineStr">
         <is>
-          <t>Edit 'EditTest_1774245422' to add '_EDITED'</t>
+          <t>Edit 'EditTest_1774505610' to add '_EDITED'</t>
         </is>
       </c>
       <c r="L35" s="10" t="inlineStr"/>
@@ -2391,7 +2393,7 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>MSG_034</t>
+          <t>MSG_036</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
@@ -2401,34 +2403,33 @@
       </c>
       <c r="C36" s="15" t="inlineStr">
         <is>
-          <t>Verify Delete message</t>
+          <t>Verify Reply to message</t>
         </is>
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>User has sent a message</t>
+          <t>User is in a chat with messages</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Verify long press on sent message shows delete option</t>
+          <t>Verify long press shows reply option</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>1. Send a message.
-2. Long press on the sent message.
-3. Observe action menu.</t>
+          <t>1. Long press on any message.
+2. Observe action menu.</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>Delete option should appear in the action menu.</t>
+          <t>Reply option should appear in the action menu.</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>Long press shows Delete option.</t>
+          <t>Reply option found.</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
@@ -2443,7 +2444,7 @@
       </c>
       <c r="K36" s="8" t="inlineStr">
         <is>
-          <t>DelTest_1774245442</t>
+          <t>(long press on any message)</t>
         </is>
       </c>
       <c r="L36" s="10" t="inlineStr"/>
@@ -2451,7 +2452,7 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>MSG_035</t>
+          <t>MSG_037</t>
         </is>
       </c>
       <c r="B37" s="15" t="n"/>
@@ -2459,158 +2460,162 @@
       <c r="D37" s="15" t="n"/>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>Verify deleting a sent message</t>
+          <t>Verify reply shows quoted message</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr">
-        <is>
-          <t>1. Long press on sent message.
-2. Tap Delete.
-3. Confirm deletion.</t>
-        </is>
-      </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>Message should be removed or show 'This message was deleted' placeholder.</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Message deleted successfully.</t>
-        </is>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K37" s="8" t="inlineStr">
-        <is>
-          <t>Delete 'DelTest_1774245442'</t>
-        </is>
-      </c>
-      <c r="L37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>MSG_036</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr">
-        <is>
-          <t>Verify Reply to message</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="inlineStr">
-        <is>
-          <t>User is in a chat with messages</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>Verify long press shows reply option</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>1. Long press on any message.
-2. Observe action menu.</t>
-        </is>
-      </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>Reply option should appear in the action menu.</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Action menu appeared but Reply option not found.</t>
-        </is>
-      </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J38" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — Reply option not found</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t>(long press on any message)</t>
-        </is>
-      </c>
-      <c r="L38" s="10" t="inlineStr">
-        <is>
-          <t>Reply option not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>MSG_037</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="n"/>
-      <c r="C39" s="15" t="n"/>
-      <c r="D39" s="15" t="n"/>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
-          <t>Verify reply shows quoted message</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="inlineStr">
         <is>
           <t>1. Long press on a message.
 2. Tap Reply.
 3. Observe composer area.</t>
         </is>
       </c>
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>Original message should appear as a quote above the input field.</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Reply tapped. Quoted message preview appears above composer.</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>(tap Reply, observe composer)</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>MSG_038</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="inlineStr">
+        <is>
+          <t>Verify sending reply message</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>1. Reply to a message.
+2. Type reply text.
+3. Send.</t>
+        </is>
+      </c>
+      <c r="G38" s="15" t="inlineStr">
+        <is>
+          <t>Reply should be sent with the quoted original message visible.</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>Reply not in action menu.</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Reply option not available</t>
+        </is>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>ReplyMsg_1774505650</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>Reply option not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>MSG_039</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="inlineStr">
+        <is>
+          <t>Verify Copy message</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="inlineStr">
+        <is>
+          <t>User is in a chat with messages</t>
+        </is>
+      </c>
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>Verify long press shows copy option</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr">
+        <is>
+          <t>1. Long press on a text message.
+2. Observe action menu.</t>
+        </is>
+      </c>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Original message should appear as a quote above the input field.</t>
+          <t>Copy option should appear in the action menu.</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>Reply tapped. Quoted message preview appears.</t>
+          <t>Copy not found in action menu.</t>
         </is>
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J39" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Copy option not found</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>(long press, tap Reply)</t>
-        </is>
-      </c>
-      <c r="L39" s="10" t="inlineStr"/>
+          <t>(long press on text message)</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>Copy option not found</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>MSG_038</t>
+          <t>MSG_040</t>
         </is>
       </c>
       <c r="B40" s="15" t="n"/>
@@ -2618,47 +2623,51 @@
       <c r="D40" s="15" t="n"/>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Verify sending reply message</t>
+          <t>Verify copying message text</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>1. Reply to a message.
-2. Type reply text.
-3. Send.</t>
+          <t>1. Long press on a text message.
+2. Tap Copy.
+3. Paste in input field.</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr">
         <is>
-          <t>Reply should be sent with the quoted original message visible.</t>
+          <t>Message text should be copied to clipboard and pasteable.</t>
         </is>
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Reply 'ReplyMsg_1774247207' sent with quoted original.</t>
+          <t>Copy not found.</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Copy option not available</t>
         </is>
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>Reply to 'ActionMenu_1774247189'</t>
-        </is>
-      </c>
-      <c r="L40" s="10" t="inlineStr"/>
+          <t>(copy message, paste in composer)</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>Copy option not available</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>MSG_039</t>
+          <t>MSG_041</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
@@ -2668,7 +2677,7 @@
       </c>
       <c r="C41" s="15" t="inlineStr">
         <is>
-          <t>Verify Copy message</t>
+          <t>Verify Message reactions</t>
         </is>
       </c>
       <c r="D41" s="15" t="inlineStr">
@@ -2678,23 +2687,23 @@
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Verify long press shows copy option</t>
+          <t>Verify long press shows reaction option</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
         <is>
-          <t>1. Long press on a text message.
+          <t>1. Long press on any message.
 2. Observe action menu.</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
         <is>
-          <t>Copy option should appear in the action menu.</t>
+          <t>Reaction emoji bar or option should appear.</t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Action menu appeared but Copy option not found.</t>
+          <t>Action menu shown. Reaction bar may be visual-only.</t>
         </is>
       </c>
       <c r="I41" s="15" t="inlineStr">
@@ -2702,26 +2711,22 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J41" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — Copy option not found</t>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>(long press on text message)</t>
-        </is>
-      </c>
-      <c r="L41" s="10" t="inlineStr">
-        <is>
-          <t>Copy option not found</t>
-        </is>
-      </c>
+          <t>(long press, observe reaction bar)</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>MSG_040</t>
+          <t>MSG_042</t>
         </is>
       </c>
       <c r="B42" s="15" t="n"/>
@@ -2729,24 +2734,23 @@
       <c r="D42" s="15" t="n"/>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>Verify copying message text</t>
+          <t>Verify adding reaction to message</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>1. Long press on a text message.
-2. Tap Copy.
-3. Paste in input field.</t>
+          <t>1. Long press on a message.
+2. Select a reaction emoji.</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
         <is>
-          <t>Message text should be copied to clipboard and pasteable.</t>
+          <t>Reaction should appear below the message.</t>
         </is>
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Copy option found and tapped.</t>
+          <t>Reaction bar not accessible via automation.</t>
         </is>
       </c>
       <c r="I42" s="15" t="inlineStr">
@@ -2754,58 +2758,49 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Reaction emoji not accessible</t>
         </is>
       </c>
       <c r="K42" s="8" t="inlineStr">
         <is>
-          <t>(copy message, paste in composer)</t>
-        </is>
-      </c>
-      <c r="L42" s="10" t="inlineStr"/>
+          <t>(long press, select reaction emoji)</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>Reaction emoji not accessible</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>MSG_041</t>
-        </is>
-      </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C43" s="15" t="inlineStr">
-        <is>
-          <t>Verify Message reactions</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>User is in a chat with messages</t>
-        </is>
-      </c>
+          <t>MSG_043</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>Verify long press shows reaction option</t>
+          <t>Verify removing own reaction</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr">
         <is>
-          <t>1. Long press on any message.
-2. Observe action menu.</t>
+          <t>1. Tap on your own reaction on a message.</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>Reaction emoji bar or option should appear.</t>
+          <t>Reaction should be removed.</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Long press shows action menu. Reaction bar may be at top of menu (visual confirmation).</t>
+          <t>No existing reactions on messages.</t>
         </is>
       </c>
       <c r="I43" s="15" t="inlineStr">
@@ -2813,46 +2808,62 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — No reactions found</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>(long press, observe reaction bar)</t>
-        </is>
-      </c>
-      <c r="L43" s="10" t="inlineStr"/>
+          <t>(tap own reaction to remove)</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>No reactions found</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>MSG_042</t>
-        </is>
-      </c>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="15" t="n"/>
-      <c r="D44" s="15" t="n"/>
+          <t>MSG_044</t>
+        </is>
+      </c>
+      <c r="B44" s="15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C44" s="15" t="inlineStr">
+        <is>
+          <t>Verify Thread replies</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="inlineStr">
+        <is>
+          <t>User is in a chat with messages</t>
+        </is>
+      </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Verify adding reaction to message</t>
+          <t>Verify thread reply option available</t>
         </is>
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
           <t>1. Long press on a message.
-2. Select a reaction emoji.</t>
+2. Observe action menu.</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
         <is>
-          <t>Reaction should appear below the message.</t>
+          <t>Thread reply or 'Reply in thread' option should appear.</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Reaction 👍 selected and added to message.</t>
+          <t>Thread reply option found.</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
@@ -2867,7 +2878,7 @@
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>(long press, select reaction emoji)</t>
+          <t>(long press, observe thread option)</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr"/>
@@ -2875,7 +2886,7 @@
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>MSG_043</t>
+          <t>MSG_045</t>
         </is>
       </c>
       <c r="B45" s="15" t="n"/>
@@ -2883,22 +2894,22 @@
       <c r="D45" s="15" t="n"/>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>Verify removing own reaction</t>
+          <t>Verify opening thread view</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
-          <t>1. Tap on your own reaction on a message.</t>
+          <t>1. Tap thread reply on a message.</t>
         </is>
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>Reaction should be removed.</t>
+          <t>Thread view should open showing the original message and thread replies.</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Tapped own 👍 reaction to toggle/remove.</t>
+          <t>Thread view opened.</t>
         </is>
       </c>
       <c r="I45" s="15" t="inlineStr">
@@ -2913,7 +2924,7 @@
       </c>
       <c r="K45" s="8" t="inlineStr">
         <is>
-          <t>(tap own reaction to remove)</t>
+          <t>(tap thread reply option)</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr"/>
@@ -2921,7 +2932,7 @@
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>MSG_044</t>
+          <t>MSG_046</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
@@ -2931,7 +2942,7 @@
       </c>
       <c r="C46" s="15" t="inlineStr">
         <is>
-          <t>Verify Thread replies</t>
+          <t>Verify Forward message</t>
         </is>
       </c>
       <c r="D46" s="15" t="inlineStr">
@@ -2941,7 +2952,7 @@
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Verify thread reply option available</t>
+          <t>Verify forward option available</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
@@ -2952,12 +2963,12 @@
       </c>
       <c r="G46" s="15" t="inlineStr">
         <is>
-          <t>Thread reply or 'Reply in thread' option should appear.</t>
+          <t>Forward option should appear in the action menu.</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>'Reply in thread' option found in action menu.</t>
+          <t>Forward option found.</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
@@ -2972,7 +2983,7 @@
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>(long press, observe thread option)</t>
+          <t>(long press, observe forward option)</t>
         </is>
       </c>
       <c r="L46" s="10" t="inlineStr"/>
@@ -2980,7 +2991,7 @@
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>MSG_045</t>
+          <t>MSG_047</t>
         </is>
       </c>
       <c r="B47" s="15" t="n"/>
@@ -2988,22 +2999,25 @@
       <c r="D47" s="15" t="n"/>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>Verify opening thread view</t>
+          <t>Verify forwarding message to another chat</t>
         </is>
       </c>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>1. Tap thread reply on a message.</t>
+          <t>1. Long press on a message.
+2. Tap Forward.
+3. Select a contact/group.
+4. Confirm.</t>
         </is>
       </c>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>Thread view should open showing the original message and thread replies.</t>
+          <t>Message should be forwarded to selected chat.</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Thread view opened successfully.</t>
+          <t>Forward not found.</t>
         </is>
       </c>
       <c r="I47" s="15" t="inlineStr">
@@ -3011,22 +3025,26 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Forward not available</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>(tap Reply in thread)</t>
-        </is>
-      </c>
-      <c r="L47" s="10" t="inlineStr"/>
+          <t>(forward to another contact)</t>
+        </is>
+      </c>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
+          <t>Forward not available</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>MSG_046</t>
+          <t>MSG_048</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
@@ -3036,38 +3054,38 @@
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Verify Forward message</t>
+          <t>Verify Message info</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>User is in a chat with messages</t>
+          <t>User has sent a message</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Verify forward option available</t>
+          <t>Verify message info option available</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>1. Long press on a message.
+          <t>1. Long press on sent message.
 2. Observe action menu.</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>Forward option should appear in the action menu.</t>
+          <t>Message info or details option should appear.</t>
         </is>
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Forward option found.</t>
+          <t>Message info option found.</t>
         </is>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
       <c r="J48" s="9" t="inlineStr">
@@ -3077,7 +3095,7 @@
       </c>
       <c r="K48" s="8" t="inlineStr">
         <is>
-          <t>(long press, observe forward option)</t>
+          <t>(long press, observe info option)</t>
         </is>
       </c>
       <c r="L48" s="10" t="inlineStr"/>
@@ -3085,7 +3103,7 @@
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>MSG_047</t>
+          <t>MSG_049</t>
         </is>
       </c>
       <c r="B49" s="15" t="n"/>
@@ -3093,154 +3111,172 @@
       <c r="D49" s="15" t="n"/>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>Verify forwarding message to another chat</t>
+          <t>Verify message info shows delivery/read status</t>
         </is>
       </c>
       <c r="F49" s="15" t="inlineStr">
-        <is>
-          <t>1. Long press on a message.
-2. Tap Forward.
-3. Select a contact/group.
-4. Confirm.</t>
-        </is>
-      </c>
-      <c r="G49" s="15" t="inlineStr">
-        <is>
-          <t>Message should be forwarded to selected chat.</t>
-        </is>
-      </c>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>Forward dialog opened.</t>
-        </is>
-      </c>
-      <c r="I49" s="15" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K49" s="8" t="inlineStr">
-        <is>
-          <t>(forward to another contact)</t>
-        </is>
-      </c>
-      <c r="L49" s="10" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>MSG_048</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>Verify Message info</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="inlineStr">
-        <is>
-          <t>User has sent a message</t>
-        </is>
-      </c>
-      <c r="E50" s="15" t="inlineStr">
-        <is>
-          <t>Verify message info option available</t>
-        </is>
-      </c>
-      <c r="F50" s="15" t="inlineStr">
-        <is>
-          <t>1. Long press on sent message.
-2. Observe action menu.</t>
-        </is>
-      </c>
-      <c r="G50" s="15" t="inlineStr">
-        <is>
-          <t>Message info or details option should appear.</t>
-        </is>
-      </c>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>Message info option found in action menu.</t>
-        </is>
-      </c>
-      <c r="I50" s="15" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K50" s="8" t="inlineStr">
-        <is>
-          <t>(long press sent message, observe info option)</t>
-        </is>
-      </c>
-      <c r="L50" s="10" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>MSG_049</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="n"/>
-      <c r="C51" s="15" t="n"/>
-      <c r="D51" s="15" t="n"/>
-      <c r="E51" s="15" t="inlineStr">
-        <is>
-          <t>Verify message info shows delivery/read status</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="inlineStr">
         <is>
           <t>1. Long press on sent message.
 2. Tap Message Info.</t>
         </is>
       </c>
-      <c r="G51" s="15" t="inlineStr">
+      <c r="G49" s="15" t="inlineStr">
         <is>
           <t>Delivery and read receipts with timestamps should display.</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
-        <is>
-          <t>Message info screen opened.</t>
-        </is>
-      </c>
-      <c r="I51" s="15" t="inlineStr">
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Info not in action menu.</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K51" s="8" t="inlineStr">
-        <is>
-          <t>(long press, tap Info)</t>
-        </is>
-      </c>
-      <c r="L51" s="10" t="inlineStr"/>
+      <c r="J49" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Info option not found</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>(tap Message Info)</t>
+        </is>
+      </c>
+      <c r="L49" s="10" t="inlineStr">
+        <is>
+          <t>Info option not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>MSG_050</t>
+        </is>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>Verify Message Delivery States</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation.</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="inlineStr">
+        <is>
+          <t>Verify message shows 'sent' state after sending</t>
+        </is>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Observe message status indicator immediately after send.</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>Message should show sent indicator (single tick/check) after sending.</t>
+        </is>
+      </c>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>Message sent state requires second device/user.</t>
+        </is>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J50" s="17" t="inlineStr">
+        <is>
+          <t>SKIP — Requires two user sessions for sent state</t>
+        </is>
+      </c>
+      <c r="K50" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L50" s="16" t="inlineStr">
+        <is>
+          <t>Requires two user sessions for sent state</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>MSG_051</t>
+        </is>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation with online user.</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="inlineStr">
+        <is>
+          <t>Verify message shows 'delivered' state</t>
+        </is>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>1. Send a message to an online user.
+2. Observe message status indicator after delivery.</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="inlineStr">
+        <is>
+          <t>Message should show delivered indicator (double tick) after recipient receives it.</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>Message delivered state requires second device/user.</t>
+        </is>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J51" s="17" t="inlineStr">
+        <is>
+          <t>SKIP — Requires two user sessions for delivered state</t>
+        </is>
+      </c>
+      <c r="K51" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L51" s="16" t="inlineStr">
+        <is>
+          <t>Requires two user sessions for delivered state</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>MSG_050</t>
+          <t>MSG_052</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
@@ -3248,11 +3284,7 @@
           <t>Positive</t>
         </is>
       </c>
-      <c r="C52" s="16" t="inlineStr">
-        <is>
-          <t>Verify Message Delivery States</t>
-        </is>
-      </c>
+      <c r="C52" s="16" t="n"/>
       <c r="D52" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
@@ -3260,169 +3292,173 @@
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
-          <t>Verify message shows 'sent' state after sending</t>
+          <t>Verify message shows 'read' state</t>
         </is>
       </c>
       <c r="F52" s="16" t="inlineStr">
-        <is>
-          <t>1. Send a message.
-2. Observe message status indicator immediately after send.</t>
-        </is>
-      </c>
-      <c r="G52" s="16" t="inlineStr">
-        <is>
-          <t>Message should show sent indicator (single tick/check) after sending.</t>
-        </is>
-      </c>
-      <c r="H52" s="16" t="inlineStr">
-        <is>
-          <t>Sent state indicator not identifiable via automation. No accessible tick mark elements found in message DOM.</t>
-        </is>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J52" s="18" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K52" s="16" t="inlineStr">
-        <is>
-          <t>N/A — Status indicators not accessible</t>
-        </is>
-      </c>
-      <c r="L52" s="16" t="inlineStr">
-        <is>
-          <t>Delivery status indicators not accessible via UiAutomator2</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>MSG_051</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation with online user.</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>Verify message shows 'delivered' state</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>1. Send a message to an online user.
-2. Observe message status indicator after delivery.</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="inlineStr">
-        <is>
-          <t>Message should show delivered indicator (double tick) after recipient receives it.</t>
-        </is>
-      </c>
-      <c r="H53" s="16" t="inlineStr">
-        <is>
-          <t>Delivered state requires second user to receive message</t>
-        </is>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J53" s="17" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="K53" s="16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L53" s="16" t="inlineStr">
-        <is>
-          <t>Delivered state requires second user to receive message</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>MSG_052</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation.</t>
-        </is>
-      </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>Verify message shows 'read' state</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Recipient opens and reads the message.
 3. Observe message status indicator.</t>
         </is>
       </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>Message should show read indicator (blue double tick) after recipient reads it.</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>Message read state requires second device/user.</t>
+        </is>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J52" s="17" t="inlineStr">
+        <is>
+          <t>SKIP — Requires two user sessions for read state</t>
+        </is>
+      </c>
+      <c r="K52" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L52" s="16" t="inlineStr">
+        <is>
+          <t>Requires two user sessions for read state</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>MSG_053</t>
+        </is>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>Verify Message Ordering</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation.</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="inlineStr">
+        <is>
+          <t>Verify messages appear in chronological order</t>
+        </is>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>1. Send multiple messages quickly (msg1, msg2, msg3).
+2. Observe message order in chat.</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>Messages should appear in the order they were sent (msg1 first, msg3 last).</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>Positions: [(2, 2), (1, 4), (0, 6)]</t>
+        </is>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J53" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Messages not in order</t>
+        </is>
+      </c>
+      <c r="K53" s="16" t="inlineStr">
+        <is>
+          <t>Send msg1, msg2, msg3 quickly</t>
+        </is>
+      </c>
+      <c r="L53" s="16" t="inlineStr">
+        <is>
+          <t>Messages not in order</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>MSG_054</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>Verify International Text Support</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation.</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="inlineStr">
+        <is>
+          <t>Verify sending message with Chinese characters</t>
+        </is>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>1. Type Chinese text (e.g., '你好世界') in composer.
+2. Send message.</t>
+        </is>
+      </c>
       <c r="G54" s="16" t="inlineStr">
         <is>
-          <t>Message should show read indicator (blue double tick) after recipient reads it.</t>
+          <t>Chinese characters should display correctly in sent message.</t>
         </is>
       </c>
       <c r="H54" s="16" t="inlineStr">
         <is>
-          <t>Read state requires second user to read message</t>
+          <t>Chinese characters sent and displayed.</t>
         </is>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J54" s="17" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J54" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K54" s="16" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L54" s="16" t="inlineStr">
-        <is>
-          <t>Read state requires second user to read message</t>
-        </is>
-      </c>
+          <t>你好世界_1774505814</t>
+        </is>
+      </c>
+      <c r="L54" s="16" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>MSG_053</t>
+          <t>MSG_055</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
@@ -3430,11 +3466,7 @@
           <t>Positive</t>
         </is>
       </c>
-      <c r="C55" s="16" t="inlineStr">
-        <is>
-          <t>Verify Message Ordering</t>
-        </is>
-      </c>
+      <c r="C55" s="16" t="n"/>
       <c r="D55" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
@@ -3442,50 +3474,46 @@
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
-          <t>Verify messages appear in chronological order</t>
+          <t>Verify sending message with Arabic/RTL text</t>
         </is>
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
-          <t>1. Send multiple messages quickly (msg1, msg2, msg3).
-2. Observe message order in chat.</t>
+          <t>1. Type Arabic text (e.g., 'مرحبا بالعالم') in composer.
+2. Send message.</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr">
         <is>
-          <t>Messages should appear in the order they were sent (msg1 first, msg3 last).</t>
+          <t>Arabic text should display correctly with proper RTL rendering.</t>
         </is>
       </c>
       <c r="H55" s="16" t="inlineStr">
         <is>
-          <t>Positions: [(2, 2), (1, 4), (0, 6)]</t>
+          <t>Arabic/RTL text sent and displayed.</t>
         </is>
       </c>
       <c r="I55" s="16" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J55" s="18" t="inlineStr">
-        <is>
-          <t>FAIL — Messages not in order</t>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K55" s="16" t="inlineStr">
         <is>
-          <t>Send msg1, msg2, msg3 quickly</t>
-        </is>
-      </c>
-      <c r="L55" s="16" t="inlineStr">
-        <is>
-          <t>Messages not in order</t>
-        </is>
-      </c>
+          <t>مرحبا بالعالم_1774505820</t>
+        </is>
+      </c>
+      <c r="L55" s="16" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>MSG_054</t>
+          <t>MSG_056</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
@@ -3493,11 +3521,7 @@
           <t>Positive</t>
         </is>
       </c>
-      <c r="C56" s="16" t="inlineStr">
-        <is>
-          <t>Verify International Text Support</t>
-        </is>
-      </c>
+      <c r="C56" s="16" t="n"/>
       <c r="D56" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
@@ -3505,23 +3529,23 @@
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>Verify sending message with Chinese characters</t>
+          <t>Verify sending message with Japanese characters</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>1. Type Chinese text (e.g., '你好世界') in composer.
+          <t>1. Type Japanese text (e.g., 'こんにちは世界') in composer.
 2. Send message.</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>Chinese characters should display correctly in sent message.</t>
+          <t>Japanese characters should display correctly in sent message.</t>
         </is>
       </c>
       <c r="H56" s="16" t="inlineStr">
         <is>
-          <t>Chinese characters sent and displayed.</t>
+          <t>Japanese characters sent and displayed.</t>
         </is>
       </c>
       <c r="I56" s="16" t="inlineStr">
@@ -3536,7 +3560,7 @@
       </c>
       <c r="K56" s="16" t="inlineStr">
         <is>
-          <t>你好世界_1774245475</t>
+          <t>こんにちは世界_1774505825</t>
         </is>
       </c>
       <c r="L56" s="16" t="inlineStr"/>
@@ -3544,7 +3568,7 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>MSG_055</t>
+          <t>MSG_057</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
@@ -3552,7 +3576,11 @@
           <t>Positive</t>
         </is>
       </c>
-      <c r="C57" s="16" t="n"/>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>Verify International Text Support</t>
+        </is>
+      </c>
       <c r="D57" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
@@ -3560,23 +3588,23 @@
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
-          <t>Verify sending message with Arabic/RTL text</t>
+          <t>Verify sending message with Hindi/Devanagari text</t>
         </is>
       </c>
       <c r="F57" s="16" t="inlineStr">
         <is>
-          <t>1. Type Arabic text (e.g., 'مرحبا بالعالم') in composer.
+          <t>1. Type Hindi text (e.g., 'नमस्ते दुनिया') in composer.
 2. Send message.</t>
         </is>
       </c>
       <c r="G57" s="16" t="inlineStr">
         <is>
-          <t>Arabic text should display correctly with proper RTL rendering.</t>
+          <t>Hindi/Devanagari text should display correctly in sent message.</t>
         </is>
       </c>
       <c r="H57" s="16" t="inlineStr">
         <is>
-          <t>Arabic/RTL text sent and displayed.</t>
+          <t>Hindi text sent and displayed.</t>
         </is>
       </c>
       <c r="I57" s="16" t="inlineStr">
@@ -3591,7 +3619,7 @@
       </c>
       <c r="K57" s="16" t="inlineStr">
         <is>
-          <t>مرحبا بالعالم_1774245481</t>
+          <t>नमस्ते दुनिया_1774505831</t>
         </is>
       </c>
       <c r="L57" s="16" t="inlineStr"/>
@@ -3599,7 +3627,7 @@
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>MSG_056</t>
+          <t>MSG_058</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
@@ -3607,7 +3635,11 @@
           <t>Positive</t>
         </is>
       </c>
-      <c r="C58" s="16" t="n"/>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>Verify Mixed Content Messages</t>
+        </is>
+      </c>
       <c r="D58" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
@@ -3615,23 +3647,23 @@
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>Verify sending message with Japanese characters</t>
+          <t>Verify sending message with text + emoji + URL combined</t>
         </is>
       </c>
       <c r="F58" s="16" t="inlineStr">
         <is>
-          <t>1. Type Japanese text (e.g., 'こんにちは世界') in composer.
+          <t>1. Type message combining text, emoji, and URL (e.g., 'Check this 😀 https://example.com').
 2. Send message.</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
-          <t>Japanese characters should display correctly in sent message.</t>
+          <t>Message should display with text, emoji rendered, and URL as clickable link.</t>
         </is>
       </c>
       <c r="H58" s="16" t="inlineStr">
         <is>
-          <t>Japanese characters sent and displayed.</t>
+          <t>Mixed content (text+emoji+URL) sent.</t>
         </is>
       </c>
       <c r="I58" s="16" t="inlineStr">
@@ -3646,7 +3678,7 @@
       </c>
       <c r="K58" s="16" t="inlineStr">
         <is>
-          <t>こんにちは世界_1774245487</t>
+          <t>Check this 😀 https://example.com _1774505836</t>
         </is>
       </c>
       <c r="L58" s="16" t="inlineStr"/>
@@ -3654,7 +3686,7 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>MSG_057</t>
+          <t>MSG_059</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
@@ -3662,11 +3694,7 @@
           <t>Positive</t>
         </is>
       </c>
-      <c r="C59" s="16" t="inlineStr">
-        <is>
-          <t>Verify International Text Support</t>
-        </is>
-      </c>
+      <c r="C59" s="16" t="n"/>
       <c r="D59" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
@@ -3674,23 +3702,23 @@
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
-          <t>Verify sending message with Hindi/Devanagari text</t>
+          <t>Verify sending message with text + special chars + numbers</t>
         </is>
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>1. Type Hindi text (e.g., 'नमस्ते दुनिया') in composer.
+          <t>1. Type message with mixed content (e.g., 'Order #123 @user $50.00!').
 2. Send message.</t>
         </is>
       </c>
       <c r="G59" s="16" t="inlineStr">
         <is>
-          <t>Hindi/Devanagari text should display correctly in sent message.</t>
+          <t>All characters should display correctly without corruption.</t>
         </is>
       </c>
       <c r="H59" s="16" t="inlineStr">
         <is>
-          <t>Hindi text sent and displayed.</t>
+          <t>Mixed content (special chars+numbers) sent.</t>
         </is>
       </c>
       <c r="I59" s="16" t="inlineStr">
@@ -3705,7 +3733,7 @@
       </c>
       <c r="K59" s="16" t="inlineStr">
         <is>
-          <t>नमस्ते दुनिया_1774245493</t>
+          <t>Order #123 @user $50.00! _1774505842</t>
         </is>
       </c>
       <c r="L59" s="16" t="inlineStr"/>
@@ -3713,7 +3741,7 @@
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>MSG_058</t>
+          <t>MSG_060</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
@@ -3723,33 +3751,33 @@
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>Verify Mixed Content Messages</t>
+          <t>Verify Scroll to Bottom</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
         <is>
-          <t>User is logged in and in a chat conversation.</t>
+          <t>User is logged in and in a chat with message history.</t>
         </is>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
-          <t>Verify sending message with text + emoji + URL combined</t>
+          <t>Verify scroll to bottom button appears when scrolled up</t>
         </is>
       </c>
       <c r="F60" s="16" t="inlineStr">
         <is>
-          <t>1. Type message combining text, emoji, and URL (e.g., 'Check this 😀 https://example.com').
-2. Send message.</t>
+          <t>1. Scroll up in chat to view older messages.
+2. Observe if scroll-to-bottom button appears.</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
-          <t>Message should display with text, emoji rendered, and URL as clickable link.</t>
+          <t>A scroll-to-bottom button/indicator should appear when user scrolls away from latest messages.</t>
         </is>
       </c>
       <c r="H60" s="16" t="inlineStr">
         <is>
-          <t>Mixed content (text+emoji+URL) sent correctly.</t>
+          <t>Scrolled up. Scroll indicator may be visual-only.</t>
         </is>
       </c>
       <c r="I60" s="16" t="inlineStr">
@@ -3764,7 +3792,7 @@
       </c>
       <c r="K60" s="16" t="inlineStr">
         <is>
-          <t>Check this 😀 https://example.com _1774245499</t>
+          <t>(scroll up, observe scroll-to-bottom)</t>
         </is>
       </c>
       <c r="L60" s="16" t="inlineStr"/>
@@ -3772,7 +3800,7 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>MSG_059</t>
+          <t>MSG_061</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
@@ -3783,390 +3811,448 @@
       <c r="C61" s="16" t="n"/>
       <c r="D61" s="16" t="inlineStr">
         <is>
-          <t>User is logged in and in a chat conversation.</t>
+          <t>User is scrolled up in chat.</t>
         </is>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
-          <t>Verify sending message with text + special chars + numbers</t>
+          <t>Verify tapping scroll to bottom button scrolls to latest message</t>
         </is>
       </c>
       <c r="F61" s="16" t="inlineStr">
-        <is>
-          <t>1. Type message with mixed content (e.g., 'Order #123 @user $50.00!').
-2. Send message.</t>
-        </is>
-      </c>
-      <c r="G61" s="16" t="inlineStr">
-        <is>
-          <t>All characters should display correctly without corruption.</t>
-        </is>
-      </c>
-      <c r="H61" s="16" t="inlineStr">
-        <is>
-          <t>Mixed content (special chars+numbers) sent correctly.</t>
-        </is>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J61" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K61" s="16" t="inlineStr">
-        <is>
-          <t>Order #123 @user $50.00! _1774245504</t>
-        </is>
-      </c>
-      <c r="L61" s="16" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="16" t="inlineStr">
-        <is>
-          <t>MSG_060</t>
-        </is>
-      </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C62" s="16" t="inlineStr">
-        <is>
-          <t>Verify Scroll to Bottom</t>
-        </is>
-      </c>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat with message history.</t>
-        </is>
-      </c>
-      <c r="E62" s="16" t="inlineStr">
-        <is>
-          <t>Verify scroll to bottom button appears when scrolled up</t>
-        </is>
-      </c>
-      <c r="F62" s="16" t="inlineStr">
-        <is>
-          <t>1. Scroll up in chat to view older messages.
-2. Observe if scroll-to-bottom button appears.</t>
-        </is>
-      </c>
-      <c r="G62" s="16" t="inlineStr">
-        <is>
-          <t>A scroll-to-bottom button/indicator should appear when user scrolls away from latest messages.</t>
-        </is>
-      </c>
-      <c r="H62" s="16" t="inlineStr">
-        <is>
-          <t>Scrolled up. Scroll indicator may be visual-only.</t>
-        </is>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J62" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K62" s="16" t="inlineStr">
-        <is>
-          <t>(scroll up, observe scroll-to-bottom)</t>
-        </is>
-      </c>
-      <c r="L62" s="16" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>MSG_061</t>
-        </is>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="n"/>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>User is scrolled up in chat.</t>
-        </is>
-      </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>Verify tapping scroll to bottom button scrolls to latest message</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="inlineStr">
         <is>
           <t>1. Scroll up in chat.
 2. Tap scroll-to-bottom button.
 3. Observe chat position.</t>
         </is>
       </c>
-      <c r="G63" s="16" t="inlineStr">
+      <c r="G61" s="16" t="inlineStr">
         <is>
           <t>Chat should scroll to the most recent message.</t>
         </is>
       </c>
-      <c r="H63" s="16" t="inlineStr">
-        <is>
-          <t>Scroll indicator found and tapped.</t>
-        </is>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>No scroll-to-bottom button found.</t>
+        </is>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J63" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K63" s="16" t="inlineStr">
+      <c r="J61" s="17" t="inlineStr">
+        <is>
+          <t>SKIP — Scroll-to-bottom button not found</t>
+        </is>
+      </c>
+      <c r="K61" s="16" t="inlineStr">
         <is>
           <t>(scroll up, tap scroll-to-bottom)</t>
         </is>
       </c>
-      <c r="L63" s="16" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="16" t="inlineStr">
+      <c r="L61" s="16" t="inlineStr">
+        <is>
+          <t>Scroll-to-bottom button not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
         <is>
           <t>MSG_062</t>
         </is>
       </c>
-      <c r="B64" s="16" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C64" s="16" t="inlineStr">
+      <c r="C62" s="16" t="inlineStr">
         <is>
           <t>Verify Deleted Message Display</t>
         </is>
       </c>
-      <c r="D64" s="16" t="inlineStr">
+      <c r="D62" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="E62" s="16" t="inlineStr">
         <is>
           <t>Verify deleted message shows placeholder text</t>
         </is>
       </c>
-      <c r="F64" s="16" t="inlineStr">
+      <c r="F62" s="16" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Delete the message.
 3. Observe chat.</t>
         </is>
       </c>
-      <c r="G64" s="16" t="inlineStr">
+      <c r="G62" s="16" t="inlineStr">
         <is>
           <t>'This message was deleted' placeholder should appear in place of deleted message.</t>
         </is>
       </c>
-      <c r="H64" s="16" t="inlineStr">
+      <c r="H62" s="16" t="inlineStr">
         <is>
           <t>Deleted message shows placeholder or removed.</t>
         </is>
       </c>
-      <c r="I64" s="16" t="inlineStr">
+      <c r="I62" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J64" s="19" t="inlineStr">
+      <c r="J62" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K64" s="16" t="inlineStr">
+      <c r="K62" s="16" t="inlineStr">
         <is>
           <t>(send, delete, observe placeholder)</t>
         </is>
       </c>
-      <c r="L64" s="16" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="16" t="inlineStr">
+      <c r="L62" s="16" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>MSG_063</t>
         </is>
       </c>
-      <c r="B65" s="16" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C65" s="16" t="inlineStr">
+      <c r="C63" s="16" t="inlineStr">
         <is>
           <t>Verify Edited Message Display</t>
         </is>
       </c>
-      <c r="D65" s="16" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E65" s="16" t="inlineStr">
+      <c r="E63" s="16" t="inlineStr">
         <is>
           <t>Verify edited message shows 'edited' indicator</t>
         </is>
       </c>
-      <c r="F65" s="16" t="inlineStr">
+      <c r="F63" s="16" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Edit the message.
 3. Observe chat.</t>
         </is>
       </c>
-      <c r="G65" s="16" t="inlineStr">
+      <c r="G63" s="16" t="inlineStr">
         <is>
           <t>Edited message should show '(edited)' label/indicator alongside the updated text.</t>
         </is>
       </c>
-      <c r="H65" s="16" t="inlineStr">
-        <is>
-          <t>Edited message shows '(edited)' indicator.</t>
-        </is>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
+      <c r="H63" s="16" t="inlineStr">
+        <is>
+          <t>Message edited. Edited indicator may be subtle.</t>
+        </is>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J65" s="19" t="inlineStr">
+      <c r="J63" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K65" s="16" t="inlineStr">
+      <c r="K63" s="16" t="inlineStr">
         <is>
           <t>(send, edit, observe 'edited' label)</t>
         </is>
       </c>
-      <c r="L65" s="16" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="16" t="inlineStr">
+      <c r="L63" s="16" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
         <is>
           <t>MSG_064</t>
         </is>
       </c>
-      <c r="B66" s="16" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C66" s="16" t="inlineStr">
+      <c r="C64" s="16" t="inlineStr">
         <is>
           <t>Verify Composer in Group Chat</t>
         </is>
       </c>
-      <c r="D66" s="16" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a group chat.</t>
         </is>
       </c>
-      <c r="E66" s="16" t="inlineStr">
+      <c r="E64" s="16" t="inlineStr">
         <is>
           <t>Verify all composer features work in group chat</t>
         </is>
       </c>
-      <c r="F66" s="16" t="inlineStr">
+      <c r="F64" s="16" t="inlineStr">
         <is>
           <t>1. Open a group chat.
 2. Verify composer input, send button, emoji button, attachment button are functional.
 3. Send a text message.</t>
         </is>
       </c>
-      <c r="G66" s="16" t="inlineStr">
+      <c r="G64" s="16" t="inlineStr">
         <is>
           <t>All composer features should work in group chat including @all and @ mentions.</t>
         </is>
       </c>
-      <c r="H66" s="16" t="inlineStr">
-        <is>
-          <t>Composer visible and functional in group chat.</t>
-        </is>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
+      <c r="H64" s="16" t="inlineStr">
+        <is>
+          <t>See group chat section.</t>
+        </is>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J66" s="19" t="inlineStr">
+      <c r="J64" s="17" t="inlineStr">
+        <is>
+          <t>SKIP — Tested in group section</t>
+        </is>
+      </c>
+      <c r="K64" s="16" t="inlineStr">
+        <is>
+          <t>Group chat test</t>
+        </is>
+      </c>
+      <c r="L64" s="16" t="inlineStr">
+        <is>
+          <t>Tested in group section</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="inlineStr">
+        <is>
+          <t>MSG_034</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr">
+        <is>
+          <t>Verify Delete message</t>
+        </is>
+      </c>
+      <c r="D65" s="15" t="inlineStr">
+        <is>
+          <t>User has sent a message</t>
+        </is>
+      </c>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>Verify long press on sent message shows delete option</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Long press on the sent message.
+3. Observe action menu.</t>
+        </is>
+      </c>
+      <c r="G65" s="15" t="inlineStr">
+        <is>
+          <t>Delete option should appear in the action menu.</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Long press shows Delete option.</t>
+        </is>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K66" s="16" t="inlineStr">
-        <is>
-          <t>(check composer in group chat)</t>
-        </is>
-      </c>
-      <c r="L66" s="16" t="inlineStr"/>
-    </row>
-    <row r="67"/>
+      <c r="K65" s="8" t="inlineStr">
+        <is>
+          <t>DelTest_1774505629</t>
+        </is>
+      </c>
+      <c r="L65" s="10" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>MSG_035</t>
+        </is>
+      </c>
+      <c r="B66" s="15" t="n"/>
+      <c r="C66" s="15" t="n"/>
+      <c r="D66" s="15" t="n"/>
+      <c r="E66" s="15" t="inlineStr">
+        <is>
+          <t>Verify deleting a sent message</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="inlineStr">
+        <is>
+          <t>1. Long press on sent message.
+2. Tap Delete.
+3. Confirm deletion.</t>
+        </is>
+      </c>
+      <c r="G66" s="15" t="inlineStr">
+        <is>
+          <t>Message should be removed or show 'This message was deleted' placeholder.</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J66" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+      <c r="K66" s="8" t="inlineStr">
+        <is>
+          <t>Delete 'DelTest_1774505629'</t>
+        </is>
+      </c>
+      <c r="L66" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Single Line Composer Test Cases</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>Single Line Composer Test Cases</t>
-        </is>
-      </c>
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>MSG_065</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Verify Attachment button</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Verify attachment button is visible</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Observe attachment button.</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>Attachment button (paperclip/+ icon) should be visible near input field.</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Emoji button visible.</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
+          <t>(observe emoji button)</t>
+        </is>
+      </c>
+      <c r="L68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>MSG_065</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>Verify Attachment button</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_066</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="n"/>
+      <c r="C69" s="12" t="n"/>
+      <c r="D69" s="12" t="n"/>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Verify attachment button is visible</t>
+          <t>Verify attachment button click opens options</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
-2. Observe attachment button.</t>
+2. Click attachment button.</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr">
         <is>
-          <t>Attachment button (paperclip/+ icon) should be visible near input field.</t>
+          <t>Attachment options should appear (image, file, camera, etc.).</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>Attachment button area identified left of composer at approx (80, 1091).</t>
+          <t>Emoji/sticker panel opened. 8 categories.</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
@@ -4181,98 +4267,104 @@
       </c>
       <c r="K69" s="8" t="inlineStr">
         <is>
-          <t>(observe attachment button near input field)</t>
-        </is>
-      </c>
-      <c r="L69" s="10" t="n"/>
+          <t>(tap Emoji Button)</t>
+        </is>
+      </c>
+      <c r="L69" s="10" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>MSG_066</t>
-        </is>
-      </c>
-      <c r="B70" s="12" t="n"/>
-      <c r="C70" s="12" t="n"/>
-      <c r="D70" s="12" t="n"/>
+          <t>MSG_067</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Verify Emoji button</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Verify attachment button click opens options</t>
+          <t>Verify emoji button is visible</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
-2. Click attachment button.</t>
+2. Observe emoji button.</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr">
         <is>
-          <t>Attachment options should appear (image, file, camera, etc.).</t>
+          <t>Emoji button (smiley icon) should be visible near input field.</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>Attachment options appeared after tapping at (80, 1091).</t>
+          <t>0 sticker categories found.</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J70" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J70" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Less than 2 categories</t>
         </is>
       </c>
       <c r="K70" s="8" t="inlineStr">
         <is>
-          <t>(click attachment button)</t>
-        </is>
-      </c>
-      <c r="L70" s="10" t="n"/>
+          <t>(open panel, check categories)</t>
+        </is>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>Less than 2 categories</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>MSG_067</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>Verify Emoji button</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_068</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n"/>
+      <c r="C71" s="11" t="n"/>
+      <c r="D71" s="12" t="n"/>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Verify emoji button is visible</t>
+          <t>Verify emoji button click opens picker</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
-2. Observe emoji button.</t>
+2. Click emoji button.</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
         <is>
-          <t>Emoji button (smiley icon) should be visible near input field.</t>
+          <t>Emoji picker should open with emoji categories.</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>Emoji button visible near input field.</t>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
@@ -4280,46 +4372,60 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J71" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K71" s="8" t="inlineStr">
         <is>
-          <t>(observe emoji button near input field)</t>
-        </is>
-      </c>
-      <c r="L71" s="10" t="n"/>
+          <t>(open panel, press back to close)</t>
+        </is>
+      </c>
+      <c r="L71" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>MSG_068</t>
-        </is>
-      </c>
-      <c r="B72" s="11" t="n"/>
-      <c r="C72" s="11" t="n"/>
-      <c r="D72" s="12" t="n"/>
+          <t>MSG_069</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="n"/>
+      <c r="C72" s="12" t="n"/>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and emoji picker open</t>
+        </is>
+      </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Verify emoji button click opens picker</t>
+          <t>Verify selecting emoji adds to input</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Click emoji button.</t>
+          <t>1. Open emoji picker.
+2. Click on an emoji.</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>Emoji picker should open with emoji categories.</t>
+          <t>Selected emoji should be added to message input field.</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>Emoji/sticker button clicked successfully. Sticker panel opened as keyboard overlay.</t>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
@@ -4327,221 +4433,233 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J72" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J72" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K72" s="8" t="inlineStr">
         <is>
-          <t>(click emoji button)</t>
-        </is>
-      </c>
-      <c r="L72" s="10" t="n"/>
+          <t>send_keys('😀') into composer</t>
+        </is>
+      </c>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>MSG_069</t>
-        </is>
-      </c>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="12" t="n"/>
+          <t>MSG_070</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Verify UI responsiveness</t>
+        </is>
+      </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>User is logged in and emoji picker open</t>
+          <t>User is logged in</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Verify selecting emoji adds to input</t>
+          <t>Verify message input on desktop</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>1. Open emoji picker.
-2. Click on an emoji.</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>Selected emoji should be added to message input field.</t>
-        </is>
-      </c>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Emoji added to input. Text: '😀'</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J73" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K73" s="8" t="inlineStr">
-        <is>
-          <t>send_keys('😀') into composer</t>
-        </is>
-      </c>
-      <c r="L73" s="10" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>MSG_070</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>Verify UI responsiveness</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>Verify message input on desktop</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>1. Open application on desktop.
 2. Open chat.
 3. Resize browser.</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>Message input and send button should remain functional and visible.</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>Desktop/browser test not applicable to mobile automation</t>
-        </is>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Attachment tests skipped per user instruction.</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
-      <c r="J74" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="K74" s="8" t="inlineStr">
+      <c r="J73" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Attachment tests skipped per instruction</t>
+        </is>
+      </c>
+      <c r="K73" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L74" s="10" t="inlineStr">
-        <is>
-          <t>Desktop/browser test not applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>Attachment tests skipped per instruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>MSG_071</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n"/>
-      <c r="C75" s="12" t="n"/>
-      <c r="D75" s="12" t="n"/>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="B74" s="12" t="n"/>
+      <c r="C74" s="12" t="n"/>
+      <c r="D74" s="12" t="n"/>
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>Verify message input on mobile</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>1. Open application on mobile.
 2. Open chat.
 3. Check keyboard interaction.</t>
         </is>
       </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>Input field should work with mobile keyboard; send button should be accessible.</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Attachment tests skipped per user instruction.</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+      <c r="J74" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Attachment tests skipped per instruction</t>
+        </is>
+      </c>
+      <c r="K74" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L74" s="10" t="inlineStr">
+        <is>
+          <t>Attachment tests skipped per instruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>MSG_072</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Verify Attachment feature</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Verify attachment icon is visible</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Observe attachment icon near input field.</t>
+        </is>
+      </c>
       <c r="G75" s="6" t="inlineStr">
         <is>
-          <t>Input field should work with mobile keyboard; send button should be accessible.</t>
+          <t>Attachment icon (paperclip/+ icon) should be visible.</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>Input field works with mobile keyboard. Send button accessible after typing.</t>
+          <t>Attachment tests skipped per user instruction.</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-      <c r="J75" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J75" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Attachment tests skipped per instruction</t>
         </is>
       </c>
       <c r="K75" s="8" t="inlineStr">
         <is>
-          <t>(verify keyboard interaction on mobile)</t>
-        </is>
-      </c>
-      <c r="L75" s="10" t="n"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>Attachment tests skipped per instruction</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>MSG_072</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Verify Attachment feature</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_073</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n"/>
+      <c r="C76" s="11" t="n"/>
+      <c r="D76" s="12" t="n"/>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Verify attachment icon is visible</t>
+          <t>Verify attachment options menu</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe attachment icon near input field.</t>
+          <t>1. Click on attachment icon.
+2. Observe options menu.</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Attachment icon (paperclip/+ icon) should be visible.</t>
+          <t>Options menu should display (Image, Video, Document, Camera, etc.).</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction</t>
+          <t>Attachment tests skipped per user instruction.</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
@@ -4551,7 +4669,7 @@
       </c>
       <c r="J76" s="13" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>SKIP — Attachment tests skipped per instruction</t>
         </is>
       </c>
       <c r="K76" s="8" t="inlineStr">
@@ -4561,80 +4679,29 @@
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction</t>
+          <t>Attachment tests skipped per instruction</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>MSG_073</t>
+          <t>MSG_074</t>
         </is>
       </c>
       <c r="B77" s="11" t="n"/>
       <c r="C77" s="11" t="n"/>
-      <c r="D77" s="12" t="n"/>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and attachment menu open</t>
+        </is>
+      </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Verify attachment options menu</t>
+          <t>Verify sending image attachment</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>1. Click on attachment icon.
-2. Observe options menu.</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>Options menu should display (Image, Video, Document, Camera, etc.).</t>
-        </is>
-      </c>
-      <c r="H77" s="8" t="inlineStr">
-        <is>
-          <t>Attachment test cases skipped per instruction</t>
-        </is>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J77" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="K77" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L77" s="10" t="inlineStr">
-        <is>
-          <t>Attachment test cases skipped per instruction</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>MSG_074</t>
-        </is>
-      </c>
-      <c r="B78" s="11" t="n"/>
-      <c r="C78" s="11" t="n"/>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and attachment menu open</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>Verify sending image attachment</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Select Image option.
@@ -4642,14 +4709,67 @@
 4. Send.</t>
         </is>
       </c>
+      <c r="G77" s="6" t="inlineStr">
+        <is>
+          <t>Image should be uploaded and sent; preview should display in chat.</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>Attachment tests skipped per user instruction.</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J77" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Attachment tests skipped per instruction</t>
+        </is>
+      </c>
+      <c r="K77" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L77" s="10" t="inlineStr">
+        <is>
+          <t>Attachment tests skipped per instruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>MSG_075</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n"/>
+      <c r="C78" s="11" t="n"/>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Verify sending document attachment</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>1. Click attachment icon.
+2. Select Document option.
+3. Choose a file.
+4. Send.</t>
+        </is>
+      </c>
       <c r="G78" s="6" t="inlineStr">
         <is>
-          <t>Image should be uploaded and sent; preview should display in chat.</t>
+          <t>Document should be uploaded and sent; file icon with name should display.</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction</t>
+          <t>Attachment tests skipped per user instruction.</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
@@ -4659,7 +4779,7 @@
       </c>
       <c r="J78" s="13" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>SKIP — Attachment tests skipped per instruction</t>
         </is>
       </c>
       <c r="K78" s="8" t="inlineStr">
@@ -4669,14 +4789,14 @@
       </c>
       <c r="L78" s="10" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction</t>
+          <t>Attachment tests skipped per instruction</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>MSG_075</t>
+          <t>MSG_076</t>
         </is>
       </c>
       <c r="B79" s="11" t="n"/>
@@ -4684,63 +4804,10 @@
       <c r="D79" s="11" t="n"/>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Verify sending document attachment</t>
+          <t>Verify sending video attachment</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>1. Click attachment icon.
-2. Select Document option.
-3. Choose a file.
-4. Send.</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>Document should be uploaded and sent; file icon with name should display.</t>
-        </is>
-      </c>
-      <c r="H79" s="8" t="inlineStr">
-        <is>
-          <t>Attachment test cases skipped per instruction</t>
-        </is>
-      </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J79" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="K79" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L79" s="10" t="inlineStr">
-        <is>
-          <t>Attachment test cases skipped per instruction</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>MSG_076</t>
-        </is>
-      </c>
-      <c r="B80" s="11" t="n"/>
-      <c r="C80" s="11" t="n"/>
-      <c r="D80" s="11" t="n"/>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>Verify sending video attachment</t>
-        </is>
-      </c>
-      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Select Video option.
@@ -4748,76 +4815,139 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>Video should be uploaded and sent; video thumbnail should display.</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr">
-        <is>
-          <t>Attachment test cases skipped per instruction</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Attachment tests skipped per user instruction.</t>
+        </is>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J80" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="K80" s="8" t="inlineStr">
+      <c r="J79" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Attachment tests skipped per instruction</t>
+        </is>
+      </c>
+      <c r="K79" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L80" s="10" t="inlineStr">
-        <is>
-          <t>Attachment test cases skipped per instruction</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+      <c r="L79" s="10" t="inlineStr">
+        <is>
+          <t>Attachment tests skipped per instruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>MSG_077</t>
         </is>
       </c>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="12" t="n"/>
-      <c r="D81" s="12" t="n"/>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="12" t="n"/>
+      <c r="D80" s="12" t="n"/>
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>Verify attachment upload progress</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Select a large file.
 3. Observe upload.</t>
         </is>
       </c>
+      <c r="G80" s="6" t="inlineStr">
+        <is>
+          <t>Upload progress indicator should display during file upload.</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>Attachment tests skipped per user instruction.</t>
+        </is>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J80" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Attachment tests skipped per instruction</t>
+        </is>
+      </c>
+      <c r="K80" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>Attachment tests skipped per instruction</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>MSG_078</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Verify Voice Recording feature</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Verify recording button is visible</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>1. Open any chat conversation.
+2. Observe microphone/recording icon.</t>
+        </is>
+      </c>
       <c r="G81" s="6" t="inlineStr">
         <is>
-          <t>Upload progress indicator should display during file upload.</t>
+          <t>Recording button (microphone icon) should be visible near input field.</t>
         </is>
       </c>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction</t>
+          <t>Voice recording tested in test_voice().</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
       <c r="J81" s="13" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>SKIP — See test_voice()</t>
         </is>
       </c>
       <c r="K81" s="8" t="inlineStr">
@@ -4827,50 +4957,38 @@
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>Attachment test cases skipped per instruction</t>
+          <t>See test_voice()</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>MSG_078</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>Verify Voice Recording feature</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_079</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="n"/>
+      <c r="C82" s="11" t="n"/>
+      <c r="D82" s="12" t="n"/>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Verify recording button is visible</t>
+          <t>Verify recording starts on button press</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe microphone/recording icon.</t>
+          <t>1. Press and hold recording button.
+2. Observe recording indicator.</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr">
         <is>
-          <t>Recording button (microphone icon) should be visible near input field.</t>
+          <t>Recording should start; timer and waveform indicator should display.</t>
         </is>
       </c>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>3 clickable</t>
+          <t>Voice recording tested in test_voice().</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
@@ -4878,145 +4996,161 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J82" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J82" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — See test_voice()</t>
         </is>
       </c>
       <c r="K82" s="8" t="inlineStr">
         <is>
-          <t>Check mic button</t>
-        </is>
-      </c>
-      <c r="L82" s="10" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>See test_voice()</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>MSG_079</t>
+          <t>MSG_080</t>
         </is>
       </c>
       <c r="B83" s="11" t="n"/>
       <c r="C83" s="11" t="n"/>
-      <c r="D83" s="12" t="n"/>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>User is recording voice message</t>
+        </is>
+      </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Verify recording starts on button press</t>
+          <t>Verify recording timer display</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>1. Press and hold recording button.
-2. Observe recording indicator.</t>
+          <t>1. Start recording.
+2. Observe timer.</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
-          <t>Recording should start; timer and waveform indicator should display.</t>
+          <t>Recording duration timer should display and increment.</t>
         </is>
       </c>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Rec active: True</t>
+          <t>Voice recording tested in test_voice().</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J83" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J83" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — See test_voice()</t>
         </is>
       </c>
       <c r="K83" s="8" t="inlineStr">
         <is>
-          <t>Tap mic, verify rec, back</t>
-        </is>
-      </c>
-      <c r="L83" s="10" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L83" s="10" t="inlineStr">
+        <is>
+          <t>See test_voice()</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>MSG_080</t>
+          <t>MSG_081</t>
         </is>
       </c>
       <c r="B84" s="11" t="n"/>
       <c r="C84" s="11" t="n"/>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>User is recording voice message</t>
-        </is>
-      </c>
+      <c r="D84" s="11" t="n"/>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Verify recording timer display</t>
+          <t>Verify sending voice message</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
-        <is>
-          <t>1. Start recording.
-2. Observe timer.</t>
-        </is>
-      </c>
-      <c r="G84" s="6" t="inlineStr">
-        <is>
-          <t>Recording duration timer should display and increment.</t>
-        </is>
-      </c>
-      <c r="H84" s="8" t="inlineStr">
-        <is>
-          <t>3s:True | 6s:True | DEL:False</t>
-        </is>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J84" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K84" s="8" t="inlineStr">
-        <is>
-          <t>Mic,3s+3s,DELETE,no msg</t>
-        </is>
-      </c>
-      <c r="L84" s="10" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>MSG_081</t>
-        </is>
-      </c>
-      <c r="B85" s="11" t="n"/>
-      <c r="C85" s="11" t="n"/>
-      <c r="D85" s="11" t="n"/>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>Verify sending voice message</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>1. Record a voice message.
 2. Release button or click send.
 3. Observe chat.</t>
         </is>
       </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>Voice message should be sent and appear in chat with play button.</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>Voice recording tested in test_voice().</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J84" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — See test_voice()</t>
+        </is>
+      </c>
+      <c r="K84" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>See test_voice()</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>MSG_082</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="n"/>
+      <c r="C85" s="12" t="n"/>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>User has received voice message</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Verify playing received voice message</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>1. Receive a voice message.
+2. Click play button.</t>
+        </is>
+      </c>
       <c r="G85" s="6" t="inlineStr">
         <is>
-          <t>Voice message should be sent and appear in chat with play button.</t>
+          <t>Voice message should play; progress indicator should show.</t>
         </is>
       </c>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Rec:True | SND:False | P+S:False</t>
+          <t>Voice recording tested in test_voice().</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -5024,50 +5158,62 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J85" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="J85" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — See test_voice()</t>
         </is>
       </c>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>Mic,5s,SEND,verify</t>
-        </is>
-      </c>
-      <c r="L85" s="10" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L85" s="10" t="inlineStr">
+        <is>
+          <t>See test_voice()</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>MSG_082</t>
-        </is>
-      </c>
-      <c r="B86" s="12" t="n"/>
-      <c r="C86" s="12" t="n"/>
+          <t>MSG_083</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Verify Emoji feature</t>
+        </is>
+      </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>User has received voice message</t>
+          <t>User is logged in and chat is open</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Verify playing received voice message</t>
+          <t>Verify emoji button is visible</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>1. Receive a voice message.
-2. Click play button.</t>
+          <t>1. Open any chat conversation.
+2. Observe emoji button.</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr">
         <is>
-          <t>Voice message should play; progress indicator should show.</t>
+          <t>Emoji button (smiley face icon) should be visible near input field.</t>
         </is>
       </c>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>Rec:True | PAU ok:True comp: | Resume:True | 2s:True</t>
+          <t>Voice button tested in test_voice().</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
@@ -5075,58 +5221,50 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J86" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J86" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — See MSG_078 in test_voice()</t>
         </is>
       </c>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>Mic,PAUSE,verify,PAUSE resume,verify 2s,DEL</t>
-        </is>
-      </c>
-      <c r="L86" s="10" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>See MSG_078 in test_voice()</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>MSG_083</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>Verify Emoji feature</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_084</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="n"/>
+      <c r="C87" s="11" t="n"/>
+      <c r="D87" s="12" t="n"/>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Verify emoji button is visible</t>
+          <t>Verify emoji picker opens</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe emoji button.</t>
+          <t>1. Click on emoji button.
+2. Observe emoji picker.</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>Emoji button (smiley face icon) should be visible near input field.</t>
+          <t>Emoji picker should open with categories (Smileys, Animals, Food, etc.).</t>
         </is>
       </c>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>Emoji button (smiley face icon) visible near input field.</t>
+          <t>Voice timer tested in test_voice().</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
@@ -5134,120 +5272,144 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J87" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J87" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — See test_voice()</t>
         </is>
       </c>
       <c r="K87" s="8" t="inlineStr">
         <is>
-          <t>(observe emoji button near input field)</t>
-        </is>
-      </c>
-      <c r="L87" s="10" t="n"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>See test_voice()</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>MSG_084</t>
+          <t>MSG_085</t>
         </is>
       </c>
       <c r="B88" s="11" t="n"/>
       <c r="C88" s="11" t="n"/>
-      <c r="D88" s="12" t="n"/>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and emoji picker open</t>
+        </is>
+      </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Verify emoji picker opens</t>
+          <t>Verify emoji categories navigation</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>1. Click on emoji button.
-2. Observe emoji picker.</t>
+          <t>1. Open emoji picker.
+2. Click on different category tabs.</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr">
         <is>
-          <t>Emoji picker should open with categories (Smileys, Animals, Food, etc.).</t>
+          <t>Different emoji categories should display when tabs are clicked.</t>
         </is>
       </c>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>Emoji picker opened as keyboard overlay after clicking emoji button.</t>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J88" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J88" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K88" s="8" t="inlineStr">
         <is>
-          <t>(click emoji button, observe picker)</t>
-        </is>
-      </c>
-      <c r="L88" s="10" t="n"/>
+          <t>(open sticker panel, navigate categories)</t>
+        </is>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>MSG_085</t>
+          <t>MSG_086</t>
         </is>
       </c>
       <c r="B89" s="11" t="n"/>
       <c r="C89" s="11" t="n"/>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and emoji picker open</t>
-        </is>
-      </c>
+      <c r="D89" s="11" t="n"/>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Verify emoji categories navigation</t>
+          <t>Verify selecting emoji adds to input</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
           <t>1. Open emoji picker.
-2. Click on different category tabs.</t>
+2. Click on any emoji.</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr">
         <is>
-          <t>Different emoji categories should display when tabs are clicked.</t>
+          <t>Selected emoji should be added to message input field at cursor position.</t>
         </is>
       </c>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>Navigated 9 sticker categories: bear, christmas, geek, gery, happy ghost...</t>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J89" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K89" s="8" t="inlineStr">
         <is>
-          <t>(open sticker panel, navigate categories)</t>
-        </is>
-      </c>
-      <c r="L89" s="10" t="inlineStr"/>
+          <t>Type text then add emoji via send_keys</t>
+        </is>
+      </c>
+      <c r="L89" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>MSG_086</t>
+          <t>MSG_087</t>
         </is>
       </c>
       <c r="B90" s="11" t="n"/>
@@ -5255,46 +5417,56 @@
       <c r="D90" s="11" t="n"/>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Verify selecting emoji adds to input</t>
+          <t>Verify multiple emoji selection</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
           <t>1. Open emoji picker.
-2. Click on any emoji.</t>
+2. Click multiple emojis.</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>Selected emoji should be added to message input field at cursor position.</t>
+          <t>All selected emojis should be added to input field.</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>Emoji added at cursor. Text: '🎉'</t>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J90" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J90" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K90" s="8" t="inlineStr">
         <is>
-          <t>Type text then add emoji via send_keys</t>
-        </is>
-      </c>
-      <c r="L90" s="10" t="inlineStr"/>
+          <t>send_keys with multiple emojis</t>
+        </is>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>MSG_087</t>
+          <t>MSG_088</t>
         </is>
       </c>
       <c r="B91" s="11" t="n"/>
@@ -5302,23 +5474,26 @@
       <c r="D91" s="11" t="n"/>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Verify multiple emoji selection</t>
+          <t>Verify emoji search functionality</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
           <t>1. Open emoji picker.
-2. Click multiple emojis.</t>
+2. Type in emoji search field.
+3. Observe results.</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>All selected emojis should be added to input field.</t>
+          <t>Matching emojis should display based on search term.</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
         <is>
-          <t>Multiple emojis in input. Text: '😀🎉👍❤️🔥'</t>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
@@ -5326,22 +5501,30 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J91" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K91" s="8" t="inlineStr">
         <is>
-          <t>send_keys with multiple emojis</t>
-        </is>
-      </c>
-      <c r="L91" s="10" t="inlineStr"/>
+          <t>(check for emoji search in sticker panel)</t>
+        </is>
+      </c>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>MSG_088</t>
+          <t>MSG_089</t>
         </is>
       </c>
       <c r="B92" s="11" t="n"/>
@@ -5349,186 +5532,207 @@
       <c r="D92" s="11" t="n"/>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Verify emoji search functionality</t>
+          <t>Verify recent emojis section</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>1. Open emoji picker.
-2. Type in emoji search field.
-3. Observe results.</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>Matching emojis should display based on search term.</t>
-        </is>
-      </c>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t>Sticker panel has no search field. Panel only shows sticker categories.</t>
-        </is>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J92" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — No search in sticker panel</t>
-        </is>
-      </c>
-      <c r="K92" s="8" t="inlineStr">
-        <is>
-          <t>(check for emoji search in sticker panel)</t>
-        </is>
-      </c>
-      <c r="L92" s="10" t="inlineStr">
-        <is>
-          <t>Sticker panel has no search functionality</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
-        <is>
-          <t>MSG_089</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="n"/>
-      <c r="C93" s="11" t="n"/>
-      <c r="D93" s="11" t="n"/>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>Verify recent emojis section</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>1. Send message with emoji.
 2. Open emoji picker again.
 3. Check recent section.</t>
         </is>
       </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Recently used emojis should appear in recent/frequently used section.</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+      <c r="J92" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>(check for recent emojis in sticker panel)</t>
+        </is>
+      </c>
+      <c r="L92" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>MSG_090</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="n"/>
+      <c r="C93" s="12" t="n"/>
+      <c r="D93" s="12" t="n"/>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Verify closing emoji picker</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>1. Open emoji picker.
+2. Click outside picker or close button.</t>
+        </is>
+      </c>
       <c r="G93" s="6" t="inlineStr">
         <is>
-          <t>Recently used emojis should appear in recent/frequently used section.</t>
+          <t>Emoji picker should close.</t>
         </is>
       </c>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>Sticker panel has no recent/frequently used section. Only sticker categories visible.</t>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
       <c r="J93" s="14" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K93" s="8" t="inlineStr">
         <is>
-          <t>(check for recent emojis in sticker panel)</t>
+          <t>😀🎉👍_1774504471</t>
         </is>
       </c>
       <c r="L93" s="10" t="inlineStr">
         <is>
-          <t>Sticker panel has no recent emojis section</t>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>MSG_090</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="n"/>
-      <c r="C94" s="12" t="n"/>
-      <c r="D94" s="12" t="n"/>
+          <t>MSG_091</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Verify Sticker feature</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and chat is open</t>
+        </is>
+      </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>Verify closing emoji picker</t>
+          <t>Verify sticker button/tab is visible</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>1. Open emoji picker.
-2. Click outside picker or close button.</t>
+          <t>1. Open any chat conversation.
+2. Observe sticker option.</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>Emoji picker should close.</t>
+          <t>Sticker button or tab should be visible (may be in emoji picker).</t>
         </is>
       </c>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>Emoji picker closed successfully. Composer accessible again.</t>
+          <t>See MSG_090.</t>
         </is>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J94" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J94" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K94" s="8" t="inlineStr">
         <is>
-          <t>(open emoji picker, then close it)</t>
-        </is>
-      </c>
-      <c r="L94" s="10" t="n"/>
+          <t>(observe emoji rendering)</t>
+        </is>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>MSG_091</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>Verify Sticker feature</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
+          <t>MSG_092</t>
+        </is>
+      </c>
+      <c r="B95" s="11" t="n"/>
+      <c r="C95" s="11" t="n"/>
+      <c r="D95" s="12" t="n"/>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>Verify sticker button/tab is visible</t>
+          <t>Verify sticker picker opens</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>1. Open any chat conversation.
-2. Observe sticker option.</t>
+          <t>1. Click on sticker button/tab.
+2. Observe sticker picker.</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
         <is>
-          <t>Sticker button or tab should be visible (may be in emoji picker).</t>
+          <t>Sticker picker should open with sticker packs.</t>
         </is>
       </c>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>Sticker/emoji button visible. Picker opens with sticker panel as keyboard overlay.</t>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
@@ -5536,195 +5740,237 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J95" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K95" s="8" t="inlineStr">
         <is>
-          <t>(observe sticker option in emoji picker)</t>
-        </is>
-      </c>
-      <c r="L95" s="10" t="n"/>
+          <t>(tap Emoji Button, verify sticker panel)</t>
+        </is>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>MSG_092</t>
+          <t>MSG_093</t>
         </is>
       </c>
       <c r="B96" s="11" t="n"/>
       <c r="C96" s="11" t="n"/>
-      <c r="D96" s="12" t="n"/>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and sticker picker open</t>
+        </is>
+      </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>Verify sticker picker opens</t>
+          <t>Verify sticker packs display</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>1. Click on sticker button/tab.
-2. Observe sticker picker.</t>
+          <t>1. Open sticker picker.
+2. Observe available sticker packs.</t>
         </is>
       </c>
       <c r="G96" s="6" t="inlineStr">
         <is>
-          <t>Sticker picker should open with sticker packs.</t>
+          <t>Different sticker packs should be visible and selectable.</t>
         </is>
       </c>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>Sticker picker opened. 9 sticker categories visible.</t>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J96" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J96" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K96" s="8" t="inlineStr">
         <is>
-          <t>(tap Emoji Button, verify sticker panel opens)</t>
-        </is>
-      </c>
-      <c r="L96" s="10" t="inlineStr"/>
+          <t>(open sticker panel, verify multiple packs)</t>
+        </is>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>MSG_093</t>
+          <t>MSG_094</t>
         </is>
       </c>
       <c r="B97" s="11" t="n"/>
       <c r="C97" s="11" t="n"/>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and sticker picker open</t>
-        </is>
-      </c>
+      <c r="D97" s="12" t="n"/>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>Verify sticker packs display</t>
+          <t>Verify sending sticker</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
           <t>1. Open sticker picker.
-2. Observe available sticker packs.</t>
+2. Click on any sticker.</t>
         </is>
       </c>
       <c r="G97" s="6" t="inlineStr">
         <is>
-          <t>Different sticker packs should be visible and selectable.</t>
+          <t>Sticker should be sent immediately and appear in chat.</t>
         </is>
       </c>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>9 sticker packs displayed: bear, christmas, geek, gery, happy ghost, independencedayus</t>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J97" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K97" s="8" t="inlineStr">
         <is>
-          <t>(open sticker panel, verify multiple packs/categories)</t>
-        </is>
-      </c>
-      <c r="L97" s="10" t="inlineStr"/>
+          <t>(open sticker panel, tap sticker to send)</t>
+        </is>
+      </c>
+      <c r="L97" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>MSG_094</t>
+          <t>MSG_095</t>
         </is>
       </c>
       <c r="B98" s="11" t="n"/>
       <c r="C98" s="11" t="n"/>
-      <c r="D98" s="12" t="n"/>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>User has received sticker</t>
+        </is>
+      </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>Verify sending sticker</t>
+          <t>Verify received sticker display</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>1. Open sticker picker.
-2. Click on any sticker.</t>
+          <t>1. Receive a sticker from another user.
+2. Observe chat.</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>Sticker should be sent immediately and appear in chat.</t>
+          <t>Sticker should display properly in chat on left side.</t>
         </is>
       </c>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Sticker tapped at grid position (150,1600). Sticker sent to chat.</t>
+          <t>See MSG_094.</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J98" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J98" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K98" s="8" t="inlineStr">
         <is>
-          <t>(open sticker panel, tap sticker at grid position to send)</t>
-        </is>
-      </c>
-      <c r="L98" s="10" t="inlineStr"/>
+          <t>(observe sticker rendering)</t>
+        </is>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>MSG_095</t>
-        </is>
-      </c>
-      <c r="B99" s="11" t="n"/>
-      <c r="C99" s="11" t="n"/>
+          <t>MSG_096</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="n"/>
+      <c r="C99" s="12" t="n"/>
       <c r="D99" s="6" t="inlineStr">
         <is>
-          <t>User has received sticker</t>
+          <t>User is logged in and sticker picker open</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>Verify received sticker display</t>
+          <t>Verify sticker pack switching</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>1. Receive a sticker from another user.
-2. Observe chat.</t>
+          <t>1. Open sticker picker.
+2. Click on different sticker pack.</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>Sticker should display properly in chat on left side.</t>
+          <t>Selected sticker pack's stickers should display.</t>
         </is>
       </c>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>Received sticker display requires another user to send sticker</t>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
@@ -5732,59 +5978,71 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J99" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="J99" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K99" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>(open sticker panel, switch between packs)</t>
         </is>
       </c>
       <c r="L99" s="10" t="inlineStr">
         <is>
-          <t>Received sticker display requires another user to send sticker</t>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>MSG_096</t>
-        </is>
-      </c>
-      <c r="B100" s="12" t="n"/>
-      <c r="C100" s="12" t="n"/>
+          <t>MSG_097</t>
+        </is>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Verify @all mention feature</t>
+        </is>
+      </c>
       <c r="D100" s="6" t="inlineStr">
         <is>
-          <t>User is logged in and sticker picker open</t>
+          <t>User is logged in and group chat is open</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>Verify sticker pack switching</t>
+          <t>Verify typing @all shows suggestion</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>1. Open sticker picker.
-2. Click on different sticker pack.</t>
+          <t>1. Open group chat.
+2. Type "@all" in input field.</t>
         </is>
       </c>
       <c r="G100" s="6" t="inlineStr">
         <is>
-          <t>Selected sticker pack's stickers should display.</t>
+          <t>"@all" suggestion should appear to mention all group members.</t>
         </is>
       </c>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>Switched 3 packs: bear, christmas, geek</t>
+          <t>@all mention suggestion appeared.</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
       <c r="J100" s="9" t="inlineStr">
@@ -5794,7 +6052,7 @@
       </c>
       <c r="K100" s="8" t="inlineStr">
         <is>
-          <t>(open sticker panel, switch between sticker packs)</t>
+          <t>Type @all in group composer</t>
         </is>
       </c>
       <c r="L100" s="10" t="inlineStr"/>
@@ -5802,43 +6060,31 @@
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>MSG_097</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>Verify @all mention feature</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
+          <t>MSG_098</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="n"/>
+      <c r="C101" s="11" t="n"/>
+      <c r="D101" s="11" t="n"/>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>Verify typing @all shows suggestion</t>
+          <t>Verify selecting @all mention</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>1. Open group chat.
-2. Type "@all" in input field.</t>
+          <t>1. Type "@all".
+2. Select @all from suggestions.</t>
         </is>
       </c>
       <c r="G101" s="6" t="inlineStr">
         <is>
-          <t>"@all" suggestion should appear to mention all group members.</t>
+          <t>"@all" should be added to message with special formatting.</t>
         </is>
       </c>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>@all mention suggestion appeared.</t>
+          <t>@all mention selected.</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
@@ -5853,7 +6099,7 @@
       </c>
       <c r="K101" s="8" t="inlineStr">
         <is>
-          <t>Type @all in group composer</t>
+          <t>Select @all</t>
         </is>
       </c>
       <c r="L101" s="10" t="inlineStr"/>
@@ -5861,31 +6107,31 @@
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>MSG_098</t>
+          <t>MSG_099</t>
         </is>
       </c>
       <c r="B102" s="11" t="n"/>
       <c r="C102" s="11" t="n"/>
-      <c r="D102" s="11" t="n"/>
+      <c r="D102" s="12" t="n"/>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>Verify selecting @all mention</t>
+          <t>Verify sending message with @all</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>1. Type "@all".
-2. Select @all from suggestions.</t>
+          <t>1. Type message with @all.
+2. Send message.</t>
         </is>
       </c>
       <c r="G102" s="6" t="inlineStr">
         <is>
-          <t>"@all" should be added to message with special formatting.</t>
+          <t>Message should be sent; all group members should receive notification.</t>
         </is>
       </c>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>@all mention selected from suggestions.</t>
+          <t>@all mention message sent.</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
@@ -5900,7 +6146,7 @@
       </c>
       <c r="K102" s="8" t="inlineStr">
         <is>
-          <t>Select @all from suggestions</t>
+          <t>Send @all message</t>
         </is>
       </c>
       <c r="L102" s="10" t="inlineStr"/>
@@ -5908,31 +6154,35 @@
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>MSG_099</t>
+          <t>MSG_100</t>
         </is>
       </c>
       <c r="B103" s="11" t="n"/>
       <c r="C103" s="11" t="n"/>
-      <c r="D103" s="12" t="n"/>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>User has received @all mention</t>
+        </is>
+      </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>Verify sending message with @all</t>
+          <t>Verify @all mention notification</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>1. Type message with @all.
-2. Send message.</t>
+          <t>1. Another user sends @all in group.
+2. Observe notification.</t>
         </is>
       </c>
       <c r="G103" s="6" t="inlineStr">
         <is>
-          <t>Message should be sent; all group members should receive notification.</t>
+          <t>User should receive notification for @all mention.</t>
         </is>
       </c>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>@all mention message sent in group.</t>
+          <t>@all notification requires second device.</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
@@ -5940,60 +6190,60 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J103" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J103" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Requires second user session</t>
         </is>
       </c>
       <c r="K103" s="8" t="inlineStr">
         <is>
-          <t>Send @all message</t>
-        </is>
-      </c>
-      <c r="L103" s="10" t="inlineStr"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L103" s="10" t="inlineStr">
+        <is>
+          <t>Requires second user session</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>MSG_100</t>
-        </is>
-      </c>
-      <c r="B104" s="11" t="n"/>
-      <c r="C104" s="11" t="n"/>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>User has received @all mention</t>
-        </is>
-      </c>
+          <t>MSG_101</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="n"/>
+      <c r="C104" s="12" t="n"/>
+      <c r="D104" s="12" t="n"/>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>Verify @all mention notification</t>
+          <t>Verify @all highlight in message</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>1. Another user sends @all in group.
-2. Observe notification.</t>
+          <t>1. Receive message with @all.
+2. Observe message display.</t>
         </is>
       </c>
       <c r="G104" s="6" t="inlineStr">
         <is>
-          <t>User should receive notification for @all mention.</t>
+          <t>"@all" should be highlighted/styled differently in the message.</t>
         </is>
       </c>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>@all mention notification requires second user session</t>
+          <t>@all notification requires second device.</t>
         </is>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
       <c r="J104" s="13" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>SKIP — Requires second user session</t>
         </is>
       </c>
       <c r="K104" s="8" t="inlineStr">
@@ -6003,101 +6253,97 @@
       </c>
       <c r="L104" s="10" t="inlineStr">
         <is>
-          <t>@all mention notification requires second user session</t>
+          <t>Requires second user session</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>MSG_101</t>
-        </is>
-      </c>
-      <c r="B105" s="12" t="n"/>
-      <c r="C105" s="12" t="n"/>
-      <c r="D105" s="12" t="n"/>
+          <t>MSG_102</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Verify @ mention feature</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>Verify @all highlight in message</t>
+          <t>Verify typing @ shows member suggestions</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>1. Receive message with @all.
-2. Observe message display.</t>
+          <t>1. Open group chat.
+2. Type "@" in input field.</t>
         </is>
       </c>
       <c r="G105" s="6" t="inlineStr">
         <is>
-          <t>"@all" should be highlighted/styled differently in the message.</t>
+          <t>List of group members should appear as suggestions.</t>
         </is>
       </c>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>@all highlight requires receiving @all from another user</t>
+          <t>@ shows 1 member suggestions.</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J105" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K105" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L105" s="10" t="inlineStr">
-        <is>
-          <t>@all highlight requires receiving @all from another user</t>
-        </is>
-      </c>
+          <t>Type @ in group composer</t>
+        </is>
+      </c>
+      <c r="L105" s="10" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>MSG_102</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>Verify @ mention feature</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
+          <t>MSG_103</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="n"/>
+      <c r="C106" s="11" t="n"/>
+      <c r="D106" s="11" t="n"/>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>Verify typing @ shows member suggestions</t>
+          <t>Verify filtering members by name</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>1. Open group chat.
-2. Type "@" in input field.</t>
+          <t>1. Type "@Jo" in input field.
+2. Observe suggestions.</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
         <is>
-          <t>List of group members should appear as suggestions.</t>
+          <t>Only members with names starting with "Jo" should appear (e.g., John).</t>
         </is>
       </c>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>@ shows member suggestions. Found 4 members.</t>
+          <t>Typing @Hon filters to Honey Yadav.</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr">
@@ -6112,7 +6358,7 @@
       </c>
       <c r="K106" s="8" t="inlineStr">
         <is>
-          <t>Type @ in group composer</t>
+          <t>Type @Hon, observe filtered list</t>
         </is>
       </c>
       <c r="L106" s="10" t="inlineStr"/>
@@ -6120,7 +6366,7 @@
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>MSG_103</t>
+          <t>MSG_104</t>
         </is>
       </c>
       <c r="B107" s="11" t="n"/>
@@ -6128,23 +6374,23 @@
       <c r="D107" s="11" t="n"/>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>Verify filtering members by name</t>
+          <t>Verify selecting member from suggestions</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>1. Type "@Jo" in input field.
-2. Observe suggestions.</t>
+          <t>1. Type "@".
+2. Click on a member name.</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
         <is>
-          <t>Only members with names starting with "Jo" should appear (e.g., John).</t>
+          <t>Selected member's name should be added to message with @ prefix.</t>
         </is>
       </c>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>Typing @Hon filters to show Honey Yadav.</t>
+          <t>Member suggestions not available.</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
@@ -6152,46 +6398,50 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J107" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — No member suggestions</t>
         </is>
       </c>
       <c r="K107" s="8" t="inlineStr">
         <is>
-          <t>Type @Hon, observe filtered list</t>
-        </is>
-      </c>
-      <c r="L107" s="10" t="inlineStr"/>
+          <t>Select member from @ suggestions</t>
+        </is>
+      </c>
+      <c r="L107" s="10" t="inlineStr">
+        <is>
+          <t>No member suggestions</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>MSG_104</t>
+          <t>MSG_105</t>
         </is>
       </c>
       <c r="B108" s="11" t="n"/>
       <c r="C108" s="11" t="n"/>
-      <c r="D108" s="11" t="n"/>
+      <c r="D108" s="12" t="n"/>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>Verify selecting member from suggestions</t>
+          <t>Verify sending message with @ mention</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>1. Type "@".
-2. Click on a member name.</t>
+          <t>1. Type message with @username.
+2. Send message.</t>
         </is>
       </c>
       <c r="G108" s="6" t="inlineStr">
         <is>
-          <t>Selected member's name should be added to message with @ prefix.</t>
+          <t>Message should be sent; mentioned user should receive notification.</t>
         </is>
       </c>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>Member selected. Composer: '@Honey Yadav '</t>
+          <t>Cannot send @ mention.</t>
         </is>
       </c>
       <c r="I108" s="6" t="inlineStr">
@@ -6199,46 +6449,54 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J108" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J108" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — No member suggestions</t>
         </is>
       </c>
       <c r="K108" s="8" t="inlineStr">
         <is>
-          <t>Select member from @ suggestions</t>
-        </is>
-      </c>
-      <c r="L108" s="10" t="inlineStr"/>
+          <t>Send @ mention message</t>
+        </is>
+      </c>
+      <c r="L108" s="10" t="inlineStr">
+        <is>
+          <t>No member suggestions</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>MSG_105</t>
+          <t>MSG_106</t>
         </is>
       </c>
       <c r="B109" s="11" t="n"/>
       <c r="C109" s="11" t="n"/>
-      <c r="D109" s="12" t="n"/>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>User has been mentioned</t>
+        </is>
+      </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>Verify sending message with @ mention</t>
+          <t>Verify @ mention notification</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>1. Type message with @username.
-2. Send message.</t>
+          <t>1. Another user mentions you with @.
+2. Observe notification.</t>
         </is>
       </c>
       <c r="G109" s="6" t="inlineStr">
         <is>
-          <t>Message should be sent; mentioned user should receive notification.</t>
+          <t>User should receive notification for being mentioned.</t>
         </is>
       </c>
       <c r="H109" s="8" t="inlineStr">
         <is>
-          <t>@ mention message sent in group.</t>
+          <t>See MSG_105.</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
@@ -6246,65 +6504,65 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J109" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J109" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — No member suggestions</t>
         </is>
       </c>
       <c r="K109" s="8" t="inlineStr">
         <is>
-          <t>Send @ mention message</t>
-        </is>
-      </c>
-      <c r="L109" s="10" t="inlineStr"/>
+          <t>(observe highlight)</t>
+        </is>
+      </c>
+      <c r="L109" s="10" t="inlineStr">
+        <is>
+          <t>No member suggestions</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>MSG_106</t>
+          <t>MSG_107</t>
         </is>
       </c>
       <c r="B110" s="11" t="n"/>
       <c r="C110" s="11" t="n"/>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>User has been mentioned</t>
-        </is>
-      </c>
+      <c r="D110" s="12" t="n"/>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>Verify @ mention notification</t>
+          <t>Verify @ mention highlight in message</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>1. Another user mentions you with @.
-2. Observe notification.</t>
+          <t>1. Receive message where you are mentioned.
+2. Observe message.</t>
         </is>
       </c>
       <c r="G110" s="6" t="inlineStr">
         <is>
-          <t>User should receive notification for being mentioned.</t>
+          <t>Your @mention should be highlighted/styled differently.</t>
         </is>
       </c>
       <c r="H110" s="8" t="inlineStr">
         <is>
-          <t>Notification verification requires second device.</t>
+          <t>Typing @Adi filters to Aditya.</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J110" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Requires second user session</t>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K110" s="8" t="inlineStr">
         <is>
-          <t>SKIP — Requires second user to receive notification</t>
+          <t>Type @Adi, observe filtered list</t>
         </is>
       </c>
       <c r="L110" s="10" t="inlineStr"/>
@@ -6312,31 +6570,35 @@
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>MSG_107</t>
+          <t>MSG_108</t>
         </is>
       </c>
       <c r="B111" s="11" t="n"/>
       <c r="C111" s="11" t="n"/>
-      <c r="D111" s="12" t="n"/>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and group chat is open</t>
+        </is>
+      </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>Verify @ mention highlight in message</t>
+          <t>Verify multiple @ mentions in one message</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>1. Receive message where you are mentioned.
-2. Observe message.</t>
+          <t>1. Type message with multiple @mentions.
+2. Send message.</t>
         </is>
       </c>
       <c r="G111" s="6" t="inlineStr">
         <is>
-          <t>Your @mention should be highlighted/styled differently.</t>
+          <t>All mentioned users should receive notifications.</t>
         </is>
       </c>
       <c r="H111" s="8" t="inlineStr">
         <is>
-          <t>Typing @Adi filters to show Aditya Gokula.</t>
+          <t>See MSG_105.</t>
         </is>
       </c>
       <c r="I111" s="6" t="inlineStr">
@@ -6344,255 +6606,295 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J111" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J111" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — No member suggestions</t>
         </is>
       </c>
       <c r="K111" s="8" t="inlineStr">
         <is>
-          <t>Type @Adi, observe filtered list</t>
-        </is>
-      </c>
-      <c r="L111" s="10" t="inlineStr"/>
+          <t>(observe mention in body)</t>
+        </is>
+      </c>
+      <c r="L111" s="10" t="inlineStr">
+        <is>
+          <t>No member suggestions</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>MSG_108</t>
-        </is>
-      </c>
-      <c r="B112" s="11" t="n"/>
-      <c r="C112" s="11" t="n"/>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and group chat is open</t>
-        </is>
-      </c>
+          <t>MSG_109</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="n"/>
+      <c r="C112" s="12" t="n"/>
+      <c r="D112" s="12" t="n"/>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>Verify multiple @ mentions in one message</t>
+          <t>Verify @ mention with profile picture in suggestions</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>1. Type message with multiple @mentions.
-2. Send message.</t>
+          <t>1. Type "@" in input field.
+2. Observe suggestion list.</t>
         </is>
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>All mentioned users should receive notifications.</t>
+          <t>Member suggestions should show profile pictures alongside names.</t>
         </is>
       </c>
       <c r="H112" s="8" t="inlineStr">
         <is>
-          <t>@ mention cancelled by clearing text.</t>
+          <t>No suggestions.</t>
         </is>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J112" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Low / Low</t>
+        </is>
+      </c>
+      <c r="J112" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — No suggestions</t>
         </is>
       </c>
       <c r="K112" s="8" t="inlineStr">
         <is>
-          <t>Type @, then clear</t>
-        </is>
-      </c>
-      <c r="L112" s="10" t="inlineStr"/>
+          <t>Type @, observe profile pics in suggestions</t>
+        </is>
+      </c>
+      <c r="L112" s="10" t="inlineStr">
+        <is>
+          <t>No suggestions</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>MSG_109</t>
+          <t>MSG_110</t>
         </is>
       </c>
       <c r="B113" s="12" t="n"/>
       <c r="C113" s="12" t="n"/>
-      <c r="D113" s="12" t="n"/>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and one-on-one chat is open</t>
+        </is>
+      </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>Verify @ mention with profile picture in suggestions</t>
+          <t>Verify @ mention in direct chat</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
-        <is>
-          <t>1. Type "@" in input field.
-2. Observe suggestion list.</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>Member suggestions should show profile pictures alongside names.</t>
-        </is>
-      </c>
-      <c r="H113" s="8" t="inlineStr">
-        <is>
-          <t>@ suggestions show avatar initials alongside names.</t>
-        </is>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-      <c r="J113" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K113" s="8" t="inlineStr">
-        <is>
-          <t>Type @, observe profile pics in suggestions</t>
-        </is>
-      </c>
-      <c r="L113" s="10" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="inlineStr">
-        <is>
-          <t>MSG_110</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="n"/>
-      <c r="C114" s="12" t="n"/>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and one-on-one chat is open</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>Verify @ mention in direct chat</t>
-        </is>
-      </c>
-      <c r="F114" s="6" t="inlineStr">
         <is>
           <t>1. Open one-on-one chat.
 2. Type "@".</t>
         </is>
       </c>
-      <c r="G114" s="6" t="inlineStr">
+      <c r="G113" s="6" t="inlineStr">
         <is>
           <t>Only the other user should appear in suggestions (or feature disabled).</t>
         </is>
       </c>
-      <c r="H114" s="8" t="inlineStr">
-        <is>
-          <t>@ in direct chat: no group-style suggestions (correct behavior).</t>
-        </is>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J114" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K114" s="8" t="inlineStr">
+      <c r="J113" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+      <c r="K113" s="8" t="inlineStr">
         <is>
           <t>Type @ in 1-on-1 chat</t>
         </is>
       </c>
-      <c r="L114" s="10" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="15" t="inlineStr">
+      <c r="L113" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="15" t="inlineStr">
         <is>
           <t>MSG_111</t>
         </is>
       </c>
-      <c r="B115" s="15" t="inlineStr">
+      <c r="B114" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C115" s="15" t="inlineStr">
+      <c r="C114" s="15" t="inlineStr">
         <is>
           <t>Verify Composer state</t>
         </is>
       </c>
-      <c r="D115" s="15" t="inlineStr">
+      <c r="D114" s="15" t="inlineStr">
         <is>
           <t>User is typing in composer</t>
         </is>
       </c>
-      <c r="E115" s="15" t="inlineStr">
+      <c r="E114" s="15" t="inlineStr">
         <is>
           <t>Verify draft message preserved on navigation</t>
         </is>
       </c>
-      <c r="F115" s="15" t="inlineStr">
+      <c r="F114" s="15" t="inlineStr">
         <is>
           <t>1. Type a message in composer (don't send).
 2. Navigate away.
 3. Return to same chat.</t>
         </is>
       </c>
+      <c r="G114" s="15" t="inlineStr">
+        <is>
+          <t>Draft message should be preserved in the input field.</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J114" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+      <c r="K114" s="8" t="inlineStr">
+        <is>
+          <t>Type draft, navigate away, return</t>
+        </is>
+      </c>
+      <c r="L114" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>MSG_112</t>
+        </is>
+      </c>
+      <c r="B115" s="15" t="n"/>
+      <c r="C115" s="15" t="n"/>
+      <c r="D115" s="15" t="n"/>
+      <c r="E115" s="15" t="inlineStr">
+        <is>
+          <t>Verify composer focus after sending</t>
+        </is>
+      </c>
+      <c r="F115" s="15" t="inlineStr">
+        <is>
+          <t>1. Type and send a message.
+2. Observe composer.</t>
+        </is>
+      </c>
       <c r="G115" s="15" t="inlineStr">
         <is>
-          <t>Draft message should be preserved in the input field.</t>
+          <t>Composer should retain focus and be ready for next message.</t>
         </is>
       </c>
       <c r="H115" s="8" t="inlineStr">
         <is>
-          <t>Draft preserved: 'DraftPreserveTest'</t>
+          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="I115" s="15" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J115" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+          <t>Low / Low</t>
+        </is>
+      </c>
+      <c r="J115" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="K115" s="8" t="inlineStr">
         <is>
-          <t>Type draft, navigate away, return</t>
-        </is>
-      </c>
-      <c r="L115" s="10" t="inlineStr"/>
+          <t>Send message, check composer focus</t>
+        </is>
+      </c>
+      <c r="L115" s="10" t="inlineStr">
+        <is>
+          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="15" t="inlineStr">
         <is>
-          <t>MSG_112</t>
-        </is>
-      </c>
-      <c r="B116" s="15" t="n"/>
-      <c r="C116" s="15" t="n"/>
-      <c r="D116" s="15" t="n"/>
+          <t>MSG_113</t>
+        </is>
+      </c>
+      <c r="B116" s="15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C116" s="15" t="inlineStr">
+        <is>
+          <t>Verify Smart replies</t>
+        </is>
+      </c>
+      <c r="D116" s="15" t="inlineStr">
+        <is>
+          <t>User has received a message</t>
+        </is>
+      </c>
       <c r="E116" s="15" t="inlineStr">
         <is>
-          <t>Verify composer focus after sending</t>
+          <t>Verify smart reply suggestions appear</t>
         </is>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>1. Type and send a message.
-2. Observe composer.</t>
+          <t>1. Receive a message.
+2. Observe below the message or above composer.</t>
         </is>
       </c>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>Composer should retain focus and be ready for next message.</t>
+          <t>Smart reply suggestions should appear (if feature enabled).</t>
         </is>
       </c>
       <c r="H116" s="8" t="inlineStr">
         <is>
-          <t>Composer retains focus after sending.</t>
+          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
@@ -6600,22 +6902,26 @@
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J116" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J116" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="K116" s="8" t="inlineStr">
         <is>
-          <t>Send message, check composer focus</t>
-        </is>
-      </c>
-      <c r="L116" s="10" t="inlineStr"/>
+          <t>(check for smart reply suggestions)</t>
+        </is>
+      </c>
+      <c r="L116" s="10" t="inlineStr">
+        <is>
+          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="15" t="inlineStr">
         <is>
-          <t>MSG_113</t>
+          <t>MSG_114</t>
         </is>
       </c>
       <c r="B117" s="15" t="inlineStr">
@@ -6625,96 +6931,83 @@
       </c>
       <c r="C117" s="15" t="inlineStr">
         <is>
-          <t>Verify Smart replies</t>
+          <t>Verify Link preview</t>
         </is>
       </c>
       <c r="D117" s="15" t="inlineStr">
         <is>
-          <t>User has received a message</t>
+          <t>User is in a chat</t>
         </is>
       </c>
       <c r="E117" s="15" t="inlineStr">
         <is>
-          <t>Verify smart reply suggestions appear</t>
+          <t>Verify link preview when typing URL</t>
         </is>
       </c>
       <c r="F117" s="15" t="inlineStr">
         <is>
-          <t>1. Receive a message.
-2. Observe below the message or above composer.</t>
+          <t>1. Type a URL in the composer.
+2. Observe preview.</t>
         </is>
       </c>
       <c r="G117" s="15" t="inlineStr">
         <is>
-          <t>Smart reply suggestions should appear (if feature enabled).</t>
+          <t>Link preview with title, description, and thumbnail should appear.</t>
         </is>
       </c>
       <c r="H117" s="8" t="inlineStr">
         <is>
-          <t>Smart reply suggestions not found in React Native build v5.2.10. No smart reply chips or suggestion UI elements detected in chat view.</t>
+          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="I117" s="15" t="inlineStr">
         <is>
-          <t>Low / Low</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
       <c r="J117" s="14" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="K117" s="8" t="inlineStr">
         <is>
-          <t>Observe chat for smart reply suggestions below messages</t>
+          <t>Type URL, observe preview</t>
         </is>
       </c>
       <c r="L117" s="10" t="inlineStr">
         <is>
-          <t>Smart reply feature not available in this build</t>
+          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="15" t="inlineStr">
         <is>
-          <t>MSG_114</t>
-        </is>
-      </c>
-      <c r="B118" s="15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C118" s="15" t="inlineStr">
-        <is>
-          <t>Verify Link preview</t>
-        </is>
-      </c>
-      <c r="D118" s="15" t="inlineStr">
-        <is>
-          <t>User is in a chat</t>
-        </is>
-      </c>
+          <t>MSG_115</t>
+        </is>
+      </c>
+      <c r="B118" s="15" t="n"/>
+      <c r="C118" s="15" t="n"/>
+      <c r="D118" s="15" t="n"/>
       <c r="E118" s="15" t="inlineStr">
         <is>
-          <t>Verify link preview when typing URL</t>
+          <t>Verify link preview in sent message</t>
         </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
-          <t>1. Type a URL in the composer.
-2. Observe preview.</t>
+          <t>1. Send a message containing a URL.</t>
         </is>
       </c>
       <c r="G118" s="15" t="inlineStr">
         <is>
-          <t>Link preview with title, description, and thumbnail should appear.</t>
+          <t>Sent message should show link preview card with title and thumbnail.</t>
         </is>
       </c>
       <c r="H118" s="8" t="inlineStr">
         <is>
-          <t>Link preview appeared.</t>
+          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
@@ -6722,45 +7015,61 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J118" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J118" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="K118" s="8" t="inlineStr">
         <is>
-          <t>Type URL, observe preview</t>
-        </is>
-      </c>
-      <c r="L118" s="10" t="inlineStr"/>
+          <t>Send URL, observe preview</t>
+        </is>
+      </c>
+      <c r="L118" s="10" t="inlineStr">
+        <is>
+          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="15" t="inlineStr">
         <is>
-          <t>MSG_115</t>
-        </is>
-      </c>
-      <c r="B119" s="15" t="n"/>
-      <c r="C119" s="15" t="n"/>
-      <c r="D119" s="15" t="n"/>
+          <t>MSG_116</t>
+        </is>
+      </c>
+      <c r="B119" s="15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C119" s="15" t="inlineStr">
+        <is>
+          <t>Verify Collaborative Whiteboard</t>
+        </is>
+      </c>
+      <c r="D119" s="15" t="inlineStr">
+        <is>
+          <t>User is in a chat</t>
+        </is>
+      </c>
       <c r="E119" s="15" t="inlineStr">
         <is>
-          <t>Verify link preview in sent message</t>
+          <t>Verify collaborative whiteboard message display</t>
         </is>
       </c>
       <c r="F119" s="15" t="inlineStr">
         <is>
-          <t>1. Send a message containing a URL.</t>
+          <t>1. Observe chat with whiteboard message.</t>
         </is>
       </c>
       <c r="G119" s="15" t="inlineStr">
         <is>
-          <t>Sent message should show link preview card with title and thumbnail.</t>
+          <t>Collaborative Whiteboard message should display with 'Open whiteboard to edit content together' text.</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
         <is>
-          <t>Sent message shows link preview.</t>
+          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="I119" s="15" t="inlineStr">
@@ -6768,57 +7077,49 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J119" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J119" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="K119" s="8" t="inlineStr">
         <is>
-          <t>Send URL, observe preview</t>
-        </is>
-      </c>
-      <c r="L119" s="10" t="inlineStr"/>
+          <t>(check for whiteboard messages)</t>
+        </is>
+      </c>
+      <c r="L119" s="10" t="inlineStr">
+        <is>
+          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="15" t="inlineStr">
         <is>
-          <t>MSG_116</t>
-        </is>
-      </c>
-      <c r="B120" s="15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C120" s="15" t="inlineStr">
-        <is>
-          <t>Verify Collaborative Whiteboard</t>
-        </is>
-      </c>
-      <c r="D120" s="15" t="inlineStr">
-        <is>
-          <t>User is in a chat</t>
-        </is>
-      </c>
+          <t>MSG_117</t>
+        </is>
+      </c>
+      <c r="B120" s="15" t="n"/>
+      <c r="C120" s="15" t="n"/>
+      <c r="D120" s="15" t="n"/>
       <c r="E120" s="15" t="inlineStr">
         <is>
-          <t>Verify collaborative whiteboard message display</t>
+          <t>Verify opening collaborative whiteboard</t>
         </is>
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
-          <t>1. Observe chat with whiteboard message.</t>
+          <t>1. Tap on collaborative whiteboard message.</t>
         </is>
       </c>
       <c r="G120" s="15" t="inlineStr">
         <is>
-          <t>Collaborative Whiteboard message should display with 'Open whiteboard to edit content together' text.</t>
+          <t>Whiteboard should open for collaborative editing.</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>No collaborative whiteboard messages found in chat. Feature may not be available in React Native build v5.2.10.</t>
+          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
@@ -6828,325 +7129,284 @@
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="K120" s="8" t="inlineStr">
         <is>
-          <t>Scroll chat looking for whiteboard message</t>
+          <t>(tap whiteboard message)</t>
         </is>
       </c>
       <c r="L120" s="10" t="inlineStr">
         <is>
-          <t>Whiteboard feature not available in this build</t>
+          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="15" t="inlineStr">
         <is>
-          <t>MSG_117</t>
-        </is>
-      </c>
-      <c r="B121" s="15" t="n"/>
-      <c r="C121" s="15" t="n"/>
-      <c r="D121" s="15" t="n"/>
+          <t>MSG_118</t>
+        </is>
+      </c>
+      <c r="B121" s="15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="inlineStr">
+        <is>
+          <t>Verify Paste in composer</t>
+        </is>
+      </c>
+      <c r="D121" s="15" t="inlineStr">
+        <is>
+          <t>User has text in clipboard</t>
+        </is>
+      </c>
       <c r="E121" s="15" t="inlineStr">
         <is>
-          <t>Verify opening collaborative whiteboard</t>
+          <t>Verify pasting text into composer</t>
         </is>
       </c>
       <c r="F121" s="15" t="inlineStr">
-        <is>
-          <t>1. Tap on collaborative whiteboard message.</t>
-        </is>
-      </c>
-      <c r="G121" s="15" t="inlineStr">
-        <is>
-          <t>Whiteboard should open for collaborative editing.</t>
-        </is>
-      </c>
-      <c r="H121" s="8" t="inlineStr">
-        <is>
-          <t>Cannot open whiteboard — no whiteboard messages found (depends on MSG_116). Feature not available in React Native build v5.2.10.</t>
-        </is>
-      </c>
-      <c r="I121" s="15" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J121" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K121" s="8" t="inlineStr">
-        <is>
-          <t>Tap whiteboard message to open (depends on MSG_116)</t>
-        </is>
-      </c>
-      <c r="L121" s="10" t="inlineStr">
-        <is>
-          <t>Depends on MSG_116 — whiteboard not in build</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="15" t="inlineStr">
-        <is>
-          <t>MSG_118</t>
-        </is>
-      </c>
-      <c r="B122" s="15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C122" s="15" t="inlineStr">
-        <is>
-          <t>Verify Paste in composer</t>
-        </is>
-      </c>
-      <c r="D122" s="15" t="inlineStr">
-        <is>
-          <t>User has text in clipboard</t>
-        </is>
-      </c>
-      <c r="E122" s="15" t="inlineStr">
-        <is>
-          <t>Verify pasting text into composer</t>
-        </is>
-      </c>
-      <c r="F122" s="15" t="inlineStr">
         <is>
           <t>1. Copy text from outside the app.
 2. Long press in composer.
 3. Tap Paste.</t>
         </is>
       </c>
-      <c r="G122" s="15" t="inlineStr">
+      <c r="G121" s="15" t="inlineStr">
         <is>
           <t>Copied text should be pasted into the composer input field.</t>
         </is>
       </c>
-      <c r="H122" s="8" t="inlineStr">
-        <is>
-          <t>Copy+paste completed.</t>
-        </is>
-      </c>
-      <c r="I122" s="15" t="inlineStr">
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J122" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K122" s="8" t="inlineStr">
+      <c r="J121" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
+      <c r="K121" s="8" t="inlineStr">
         <is>
           <t>(copy text, paste into composer)</t>
         </is>
       </c>
-      <c r="L122" s="10" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="15" t="inlineStr">
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="inlineStr">
         <is>
           <t>MSG_119</t>
         </is>
       </c>
-      <c r="B123" s="15" t="n"/>
-      <c r="C123" s="15" t="n"/>
-      <c r="D123" s="15" t="n"/>
-      <c r="E123" s="15" t="inlineStr">
+      <c r="B122" s="15" t="n"/>
+      <c r="C122" s="15" t="n"/>
+      <c r="D122" s="15" t="n"/>
+      <c r="E122" s="15" t="inlineStr">
         <is>
           <t>Verify pasting image into composer</t>
         </is>
       </c>
-      <c r="F123" s="15" t="inlineStr">
+      <c r="F122" s="15" t="inlineStr">
         <is>
           <t>1. Copy an image.
 2. Long press in composer.
 3. Tap Paste.</t>
         </is>
       </c>
+      <c r="G122" s="15" t="inlineStr">
+        <is>
+          <t>Image should be pasted as attachment ready to send.</t>
+        </is>
+      </c>
+      <c r="H122" s="8" t="inlineStr">
+        <is>
+          <t>Undo/redo not available in mobile composer.</t>
+        </is>
+      </c>
+      <c r="I122" s="15" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+      <c r="J122" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Undo/redo not standard on mobile</t>
+        </is>
+      </c>
+      <c r="K122" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L122" s="10" t="inlineStr">
+        <is>
+          <t>Undo/redo not standard on mobile</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="15" t="inlineStr">
+        <is>
+          <t>MSG_120</t>
+        </is>
+      </c>
+      <c r="B123" s="15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C123" s="15" t="inlineStr">
+        <is>
+          <t>Verify Composer accessibility</t>
+        </is>
+      </c>
+      <c r="D123" s="15" t="inlineStr">
+        <is>
+          <t>User is in a chat</t>
+        </is>
+      </c>
+      <c r="E123" s="15" t="inlineStr">
+        <is>
+          <t>Verify composer elements have content descriptions</t>
+        </is>
+      </c>
+      <c r="F123" s="15" t="inlineStr">
+        <is>
+          <t>1. Enable TalkBack/screen reader.
+2. Navigate to composer area.</t>
+        </is>
+      </c>
       <c r="G123" s="15" t="inlineStr">
         <is>
-          <t>Image should be pasted as attachment ready to send.</t>
+          <t>All composer buttons (send, attach, emoji, voice) should have proper content descriptions.</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
-          <t>Image paste into composer not automatable via UiAutomator2</t>
+          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="I123" s="15" t="inlineStr">
         <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-      <c r="J123" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+          <t>Medium / High</t>
+        </is>
+      </c>
+      <c r="J123" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
       <c r="K123" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>(check content-desc on composer elements)</t>
         </is>
       </c>
       <c r="L123" s="10" t="inlineStr">
         <is>
-          <t>Image paste not automatable</t>
+          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="15" t="inlineStr">
         <is>
-          <t>MSG_120</t>
-        </is>
-      </c>
-      <c r="B124" s="15" t="inlineStr">
+          <t>MSG_121</t>
+        </is>
+      </c>
+      <c r="B124" s="15" t="n"/>
+      <c r="C124" s="15" t="n"/>
+      <c r="D124" s="15" t="n"/>
+      <c r="E124" s="15" t="inlineStr">
+        <is>
+          <t>Verify keyboard navigation in composer</t>
+        </is>
+      </c>
+      <c r="F124" s="15" t="inlineStr">
+        <is>
+          <t>1. Use Tab key to navigate composer elements.</t>
+        </is>
+      </c>
+      <c r="G124" s="15" t="inlineStr">
+        <is>
+          <t>Focus should move logically between input field, attachment, emoji, voice, and send buttons.</t>
+        </is>
+      </c>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>CometChat does not enforce a visible character limit.</t>
+        </is>
+      </c>
+      <c r="I124" s="15" t="inlineStr">
+        <is>
+          <t>Low / Medium</t>
+        </is>
+      </c>
+      <c r="J124" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — No explicit char limit in CometChat</t>
+        </is>
+      </c>
+      <c r="K124" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L124" s="10" t="inlineStr">
+        <is>
+          <t>No explicit char limit in CometChat</t>
+        </is>
+      </c>
+    </row>
+    <row r="125"/>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>Rich Media Formatting Test Cases</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="16" t="inlineStr">
+        <is>
+          <t>MSG_122</t>
+        </is>
+      </c>
+      <c r="B127" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C124" s="15" t="inlineStr">
-        <is>
-          <t>Verify Composer accessibility</t>
-        </is>
-      </c>
-      <c r="D124" s="15" t="inlineStr">
-        <is>
-          <t>User is in a chat</t>
-        </is>
-      </c>
-      <c r="E124" s="15" t="inlineStr">
-        <is>
-          <t>Verify composer elements have content descriptions</t>
-        </is>
-      </c>
-      <c r="F124" s="15" t="inlineStr">
-        <is>
-          <t>1. Enable TalkBack/screen reader.
-2. Navigate to composer area.</t>
-        </is>
-      </c>
-      <c r="G124" s="15" t="inlineStr">
-        <is>
-          <t>All composer buttons (send, attach, emoji, voice) should have proper content descriptions.</t>
-        </is>
-      </c>
-      <c r="H124" s="8" t="inlineStr">
-        <is>
-          <t>Composer elements accessible: composer: accessible, emoji: has content-desc, send: has resource-id</t>
-        </is>
-      </c>
-      <c r="I124" s="15" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
-        </is>
-      </c>
-      <c r="J124" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K124" s="8" t="inlineStr">
-        <is>
-          <t>(check content-desc on composer elements)</t>
-        </is>
-      </c>
-      <c r="L124" s="10" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="15" t="inlineStr">
-        <is>
-          <t>MSG_121</t>
-        </is>
-      </c>
-      <c r="B125" s="15" t="n"/>
-      <c r="C125" s="15" t="n"/>
-      <c r="D125" s="15" t="n"/>
-      <c r="E125" s="15" t="inlineStr">
-        <is>
-          <t>Verify keyboard navigation in composer</t>
-        </is>
-      </c>
-      <c r="F125" s="15" t="inlineStr">
-        <is>
-          <t>1. Use Tab key to navigate composer elements.</t>
-        </is>
-      </c>
-      <c r="G125" s="15" t="inlineStr">
-        <is>
-          <t>Focus should move logically between input field, attachment, emoji, voice, and send buttons.</t>
-        </is>
-      </c>
-      <c r="H125" s="8" t="inlineStr">
-        <is>
-          <t>Tab key navigation requires physical keyboard interaction</t>
-        </is>
-      </c>
-      <c r="I125" s="15" t="inlineStr">
-        <is>
-          <t>Low / Medium</t>
-        </is>
-      </c>
-      <c r="J125" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="K125" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L125" s="10" t="inlineStr">
-        <is>
-          <t>Keyboard navigation requires physical keyboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="4" t="inlineStr">
-        <is>
-          <t>Rich Media Formatting Test Cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="16" t="inlineStr">
-        <is>
-          <t>MSG_122</t>
-        </is>
-      </c>
-      <c r="B128" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C128" s="16" t="inlineStr">
+      <c r="C127" s="16" t="inlineStr">
         <is>
           <t>Verify Rich Text Formatting</t>
         </is>
       </c>
-      <c r="D128" s="16" t="inlineStr">
+      <c r="D127" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E128" s="16" t="inlineStr">
+      <c r="E127" s="16" t="inlineStr">
         <is>
           <t>Verify bold text formatting via toolbar</t>
         </is>
       </c>
-      <c r="F128" s="16" t="inlineStr">
+      <c r="F127" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text in composer.
@@ -7155,56 +7415,60 @@
 5. Send message.</t>
         </is>
       </c>
-      <c r="G128" s="16" t="inlineStr">
+      <c r="G127" s="16" t="inlineStr">
         <is>
           <t>Message should display with bold formatting applied to selected text.</t>
         </is>
       </c>
-      <c r="H128" s="16" t="inlineStr">
-        <is>
-          <t>Bold toolbar button found and toggled.</t>
-        </is>
-      </c>
-      <c r="I128" s="16" t="inlineStr">
+      <c r="H127" s="16" t="inlineStr">
+        <is>
+          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J128" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K128" s="16" t="inlineStr">
+      <c r="J127" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
+      <c r="K127" s="16" t="inlineStr">
         <is>
           <t>Type text, tap Bold toolbar, send</t>
         </is>
       </c>
-      <c r="L128" s="16" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="16" t="inlineStr">
+      <c r="L127" s="16" t="inlineStr">
+        <is>
+          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="16" t="inlineStr">
         <is>
           <t>MSG_123</t>
         </is>
       </c>
-      <c r="B129" s="16" t="inlineStr">
+      <c r="B128" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C129" s="16" t="n"/>
-      <c r="D129" s="16" t="inlineStr">
+      <c r="C128" s="16" t="n"/>
+      <c r="D128" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E129" s="16" t="inlineStr">
+      <c r="E128" s="16" t="inlineStr">
         <is>
           <t>Verify italic text formatting via toolbar</t>
         </is>
       </c>
-      <c r="F129" s="16" t="inlineStr">
+      <c r="F128" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text in composer.
@@ -7213,56 +7477,60 @@
 5. Send message.</t>
         </is>
       </c>
-      <c r="G129" s="16" t="inlineStr">
+      <c r="G128" s="16" t="inlineStr">
         <is>
           <t>Message should display with italic formatting applied to selected text.</t>
         </is>
       </c>
-      <c r="H129" s="16" t="inlineStr">
-        <is>
-          <t>Italic toolbar toggled and text sent.</t>
-        </is>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
+      <c r="H128" s="16" t="inlineStr">
+        <is>
+          <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J129" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K129" s="16" t="inlineStr">
-        <is>
-          <t>Type text, tap Italic toolbar, send</t>
-        </is>
-      </c>
-      <c r="L129" s="16" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="16" t="inlineStr">
+      <c r="J128" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="K128" s="16" t="inlineStr">
+        <is>
+          <t>Tap Italic toolbar, type, send</t>
+        </is>
+      </c>
+      <c r="L128" s="16" t="inlineStr">
+        <is>
+          <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="16" t="inlineStr">
         <is>
           <t>MSG_124</t>
         </is>
       </c>
-      <c r="B130" s="16" t="inlineStr">
+      <c r="B129" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C130" s="16" t="n"/>
-      <c r="D130" s="16" t="inlineStr">
+      <c r="C129" s="16" t="n"/>
+      <c r="D129" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E130" s="16" t="inlineStr">
+      <c r="E129" s="16" t="inlineStr">
         <is>
           <t>Verify underline text formatting via toolbar</t>
         </is>
       </c>
-      <c r="F130" s="16" t="inlineStr">
+      <c r="F129" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text in composer.
@@ -7271,56 +7539,60 @@
 5. Send message.</t>
         </is>
       </c>
-      <c r="G130" s="16" t="inlineStr">
+      <c r="G129" s="16" t="inlineStr">
         <is>
           <t>Message should display with underline formatting applied to selected text.</t>
         </is>
       </c>
-      <c r="H130" s="16" t="inlineStr">
-        <is>
-          <t>Underline toolbar toggled.</t>
-        </is>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
+      <c r="H129" s="16" t="inlineStr">
+        <is>
+          <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J130" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K130" s="16" t="inlineStr">
+      <c r="J129" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="K129" s="16" t="inlineStr">
         <is>
           <t>Tap Underline toolbar, type, send</t>
         </is>
       </c>
-      <c r="L130" s="16" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="16" t="inlineStr">
+      <c r="L129" s="16" t="inlineStr">
+        <is>
+          <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="16" t="inlineStr">
         <is>
           <t>MSG_125</t>
         </is>
       </c>
-      <c r="B131" s="16" t="inlineStr">
+      <c r="B130" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C131" s="16" t="n"/>
-      <c r="D131" s="16" t="inlineStr">
+      <c r="C130" s="16" t="n"/>
+      <c r="D130" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E131" s="16" t="inlineStr">
+      <c r="E130" s="16" t="inlineStr">
         <is>
           <t>Verify strikethrough text formatting via toolbar</t>
         </is>
       </c>
-      <c r="F131" s="16" t="inlineStr">
+      <c r="F130" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text in composer.
@@ -7329,60 +7601,64 @@
 5. Send message.</t>
         </is>
       </c>
-      <c r="G131" s="16" t="inlineStr">
+      <c r="G130" s="16" t="inlineStr">
         <is>
           <t>Message should display with strikethrough formatting applied to selected text.</t>
         </is>
       </c>
-      <c r="H131" s="16" t="inlineStr">
-        <is>
-          <t>Strikethrough toolbar toggled.</t>
-        </is>
-      </c>
-      <c r="I131" s="16" t="inlineStr">
+      <c r="H130" s="16" t="inlineStr">
+        <is>
+          <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J131" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K131" s="16" t="inlineStr">
+      <c r="J130" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="K130" s="16" t="inlineStr">
         <is>
           <t>Tap Strikethrough toolbar, type, send</t>
         </is>
       </c>
-      <c r="L131" s="16" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="16" t="inlineStr">
+      <c r="L130" s="16" t="inlineStr">
+        <is>
+          <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
         <is>
           <t>MSG_126</t>
         </is>
       </c>
-      <c r="B132" s="16" t="inlineStr">
+      <c r="B131" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C132" s="16" t="inlineStr">
+      <c r="C131" s="16" t="inlineStr">
         <is>
           <t>Verify Rich Text Formatting</t>
         </is>
       </c>
-      <c r="D132" s="16" t="inlineStr">
+      <c r="D131" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E132" s="16" t="inlineStr">
+      <c r="E131" s="16" t="inlineStr">
         <is>
           <t>Verify link insertion via toolbar</t>
         </is>
       </c>
-      <c r="F132" s="16" t="inlineStr">
+      <c r="F131" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text in composer.
@@ -7392,56 +7668,60 @@
 6. Send message.</t>
         </is>
       </c>
-      <c r="G132" s="16" t="inlineStr">
+      <c r="G131" s="16" t="inlineStr">
         <is>
           <t>Message should display with clickable hyperlink on selected text.</t>
         </is>
       </c>
-      <c r="H132" s="16" t="inlineStr">
-        <is>
-          <t>Link toolbar opened URL input dialog.</t>
-        </is>
-      </c>
-      <c r="I132" s="16" t="inlineStr">
+      <c r="H131" s="16" t="inlineStr">
+        <is>
+          <t>Error: Message: 'POST /element' cannot be proxied to UiAutomator2 server because the in</t>
+        </is>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J132" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K132" s="16" t="inlineStr">
+      <c r="J131" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 'POST /element' cannot be proxied to UiAutomator2 server because the in</t>
+        </is>
+      </c>
+      <c r="K131" s="16" t="inlineStr">
         <is>
           <t>(select text, tap link toolbar button)</t>
         </is>
       </c>
-      <c r="L132" s="16" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="16" t="inlineStr">
+      <c r="L131" s="16" t="inlineStr">
+        <is>
+          <t>Message: 'POST /element' cannot be proxied to UiAutomator2 server because the in</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="16" t="inlineStr">
         <is>
           <t>MSG_127</t>
         </is>
       </c>
-      <c r="B133" s="16" t="inlineStr">
+      <c r="B132" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C133" s="16" t="n"/>
-      <c r="D133" s="16" t="inlineStr">
+      <c r="C132" s="16" t="n"/>
+      <c r="D132" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E133" s="16" t="inlineStr">
+      <c r="E132" s="16" t="inlineStr">
         <is>
           <t>Verify ordered list formatting via toolbar</t>
         </is>
       </c>
-      <c r="F133" s="16" t="inlineStr">
+      <c r="F132" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Tap Ordered List toolbar button.
@@ -7449,56 +7729,60 @@
 4. Send message.</t>
         </is>
       </c>
-      <c r="G133" s="16" t="inlineStr">
+      <c r="G132" s="16" t="inlineStr">
         <is>
           <t>Message should display as numbered list (1. 2. 3. etc.).</t>
         </is>
       </c>
-      <c r="H133" s="16" t="inlineStr">
-        <is>
-          <t>Ordered list formatting applied and sent.</t>
-        </is>
-      </c>
-      <c r="I133" s="16" t="inlineStr">
+      <c r="H132" s="16" t="inlineStr">
+        <is>
+          <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J133" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K133" s="16" t="inlineStr">
+      <c r="J132" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="K132" s="16" t="inlineStr">
         <is>
           <t>Tap ordered list toolbar, type items</t>
         </is>
       </c>
-      <c r="L133" s="16" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="16" t="inlineStr">
+      <c r="L132" s="16" t="inlineStr">
+        <is>
+          <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="16" t="inlineStr">
         <is>
           <t>MSG_128</t>
         </is>
       </c>
-      <c r="B134" s="16" t="inlineStr">
+      <c r="B133" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C134" s="16" t="n"/>
-      <c r="D134" s="16" t="inlineStr">
+      <c r="C133" s="16" t="n"/>
+      <c r="D133" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E134" s="16" t="inlineStr">
+      <c r="E133" s="16" t="inlineStr">
         <is>
           <t>Verify unordered list formatting via toolbar</t>
         </is>
       </c>
-      <c r="F134" s="16" t="inlineStr">
+      <c r="F133" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Tap Unordered List toolbar button.
@@ -7506,56 +7790,60 @@
 4. Send message.</t>
         </is>
       </c>
-      <c r="G134" s="16" t="inlineStr">
+      <c r="G133" s="16" t="inlineStr">
         <is>
           <t>Message should display as bulleted list.</t>
         </is>
       </c>
-      <c r="H134" s="16" t="inlineStr">
-        <is>
-          <t>Unordered list formatting applied and sent.</t>
-        </is>
-      </c>
-      <c r="I134" s="16" t="inlineStr">
+      <c r="H133" s="16" t="inlineStr">
+        <is>
+          <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="I133" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J134" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K134" s="16" t="inlineStr">
+      <c r="J133" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="K133" s="16" t="inlineStr">
         <is>
           <t>Tap unordered list toolbar, type items</t>
         </is>
       </c>
-      <c r="L134" s="16" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="16" t="inlineStr">
+      <c r="L133" s="16" t="inlineStr">
+        <is>
+          <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="16" t="inlineStr">
         <is>
           <t>MSG_129</t>
         </is>
       </c>
-      <c r="B135" s="16" t="inlineStr">
+      <c r="B134" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C135" s="16" t="n"/>
-      <c r="D135" s="16" t="inlineStr">
+      <c r="C134" s="16" t="n"/>
+      <c r="D134" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E135" s="16" t="inlineStr">
+      <c r="E134" s="16" t="inlineStr">
         <is>
           <t>Verify blockquote formatting via toolbar</t>
         </is>
       </c>
-      <c r="F135" s="16" t="inlineStr">
+      <c r="F134" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Tap Blockquote toolbar button.
@@ -7563,60 +7851,64 @@
 4. Send message.</t>
         </is>
       </c>
-      <c r="G135" s="16" t="inlineStr">
+      <c r="G134" s="16" t="inlineStr">
         <is>
           <t>Message should display with blockquote styling (indented with vertical bar).</t>
         </is>
       </c>
-      <c r="H135" s="16" t="inlineStr">
-        <is>
-          <t>Blockquote formatting applied and sent.</t>
-        </is>
-      </c>
-      <c r="I135" s="16" t="inlineStr">
+      <c r="H134" s="16" t="inlineStr">
+        <is>
+          <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J135" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K135" s="16" t="inlineStr">
+      <c r="J134" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="K134" s="16" t="inlineStr">
         <is>
           <t>Tap blockquote toolbar, type text</t>
         </is>
       </c>
-      <c r="L135" s="16" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="16" t="inlineStr">
+      <c r="L134" s="16" t="inlineStr">
+        <is>
+          <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="16" t="inlineStr">
         <is>
           <t>MSG_130</t>
         </is>
       </c>
-      <c r="B136" s="16" t="inlineStr">
+      <c r="B135" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C136" s="16" t="inlineStr">
+      <c r="C135" s="16" t="inlineStr">
         <is>
           <t>Verify Rich Text Formatting</t>
         </is>
       </c>
-      <c r="D136" s="16" t="inlineStr">
+      <c r="D135" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E136" s="16" t="inlineStr">
+      <c r="E135" s="16" t="inlineStr">
         <is>
           <t>Verify inline code formatting via toolbar</t>
         </is>
       </c>
-      <c r="F136" s="16" t="inlineStr">
+      <c r="F135" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text in composer.
@@ -7625,56 +7917,60 @@
 5. Send message.</t>
         </is>
       </c>
-      <c r="G136" s="16" t="inlineStr">
+      <c r="G135" s="16" t="inlineStr">
         <is>
           <t>Message should display selected text in monospace/code font style.</t>
         </is>
       </c>
-      <c r="H136" s="16" t="inlineStr">
-        <is>
-          <t>Inline code formatting applied and sent.</t>
-        </is>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
+      <c r="H135" s="16" t="inlineStr">
+        <is>
+          <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J136" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K136" s="16" t="inlineStr">
+      <c r="J135" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="K135" s="16" t="inlineStr">
         <is>
           <t>Tap inline code toolbar, type text</t>
         </is>
       </c>
-      <c r="L136" s="16" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="16" t="inlineStr">
+      <c r="L135" s="16" t="inlineStr">
+        <is>
+          <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="16" t="inlineStr">
         <is>
           <t>MSG_131</t>
         </is>
       </c>
-      <c r="B137" s="16" t="inlineStr">
+      <c r="B136" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C137" s="16" t="n"/>
-      <c r="D137" s="16" t="inlineStr">
+      <c r="C136" s="16" t="n"/>
+      <c r="D136" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E137" s="16" t="inlineStr">
+      <c r="E136" s="16" t="inlineStr">
         <is>
           <t>Verify multiple formatting styles combined</t>
         </is>
       </c>
-      <c r="F137" s="16" t="inlineStr">
+      <c r="F136" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text.
@@ -7682,56 +7978,60 @@
 4. Send message.</t>
         </is>
       </c>
-      <c r="G137" s="16" t="inlineStr">
+      <c r="G136" s="16" t="inlineStr">
         <is>
           <t>Message should display with both bold and italic formatting applied.</t>
         </is>
       </c>
-      <c r="H137" s="16" t="inlineStr">
-        <is>
-          <t>Bold+italic combined formatting applied and sent.</t>
-        </is>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
+      <c r="H136" s="16" t="inlineStr">
+        <is>
+          <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J137" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K137" s="16" t="inlineStr">
+      <c r="J136" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="K136" s="16" t="inlineStr">
         <is>
           <t>Apply bold + italic to same text</t>
         </is>
       </c>
-      <c r="L137" s="16" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="16" t="inlineStr">
+      <c r="L136" s="16" t="inlineStr">
+        <is>
+          <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="16" t="inlineStr">
         <is>
           <t>MSG_132</t>
         </is>
       </c>
-      <c r="B138" s="16" t="inlineStr">
+      <c r="B137" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C138" s="16" t="n"/>
-      <c r="D138" s="16" t="inlineStr">
+      <c r="C137" s="16" t="n"/>
+      <c r="D137" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E138" s="16" t="inlineStr">
+      <c r="E137" s="16" t="inlineStr">
         <is>
           <t>Verify toolbar toggle on/off state</t>
         </is>
       </c>
-      <c r="F138" s="16" t="inlineStr">
+      <c r="F137" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Tap Bold toolbar button (should show 'on').
@@ -7739,32 +8039,36 @@
 4. Observe toolbar state.</t>
         </is>
       </c>
-      <c r="G138" s="16" t="inlineStr">
+      <c r="G137" s="16" t="inlineStr">
         <is>
           <t>Toolbar button should toggle between on/off states visually.</t>
         </is>
       </c>
-      <c r="H138" s="16" t="inlineStr">
-        <is>
-          <t>Toggle works: 'toolbar-bold, off' -&gt; 'toolbar-bold, on' -&gt; 'toolbar-bold, off'</t>
-        </is>
-      </c>
-      <c r="I138" s="16" t="inlineStr">
+      <c r="H137" s="16" t="inlineStr">
+        <is>
+          <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J138" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K138" s="16" t="inlineStr">
+      <c r="J137" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
+      <c r="K137" s="16" t="inlineStr">
         <is>
           <t>Tap Bold on, tap Bold off, observe state</t>
         </is>
       </c>
-      <c r="L138" s="16" t="inlineStr"/>
+      <c r="L137" s="16" t="inlineStr">
+        <is>
+          <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -127,7 +127,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -151,11 +151,39 @@
       <bottom style="thin"/>
     </border>
     <border/>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -211,6 +239,8 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -576,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L137"/>
+  <dimension ref="A1:L138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.86" customWidth="1" min="1" max="1"/>
@@ -4159,232 +4189,191 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Single Line Composer Test Cases</t>
         </is>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>MSG_065</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>Verify Attachment button</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and chat is open</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>Verify attachment button is visible</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>1. Open any chat conversation.
-2. Observe attachment button.</t>
-        </is>
-      </c>
-      <c r="G68" s="6" t="inlineStr">
-        <is>
-          <t>Attachment button (paperclip/+ icon) should be visible near input field.</t>
-        </is>
-      </c>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>Emoji button visible.</t>
-        </is>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J68" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K68" s="8" t="inlineStr">
-        <is>
-          <t>(observe emoji button)</t>
-        </is>
-      </c>
-      <c r="L68" s="10" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
+          <t>MSG_065</t>
+        </is>
+      </c>
+      <c r="B69" s="21" t="n"/>
+      <c r="C69" s="21" t="n"/>
+      <c r="D69" s="21" t="n"/>
+      <c r="E69" s="21" t="n"/>
+      <c r="F69" s="21" t="n"/>
+      <c r="G69" s="21" t="n"/>
+      <c r="H69" s="21" t="n"/>
+      <c r="I69" s="21" t="n"/>
+      <c r="J69" s="21" t="n"/>
+      <c r="K69" s="21" t="n"/>
+      <c r="L69" s="22" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
           <t>MSG_066</t>
         </is>
       </c>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
-      <c r="D69" s="12" t="n"/>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="B70" s="12" t="n"/>
+      <c r="C70" s="12" t="n"/>
+      <c r="D70" s="12" t="n"/>
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>Verify attachment button click opens options</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Click attachment button.</t>
         </is>
       </c>
-      <c r="G69" s="6" t="inlineStr">
+      <c r="G70" s="6" t="inlineStr">
         <is>
           <t>Attachment options should appear (image, file, camera, etc.).</t>
         </is>
       </c>
-      <c r="H69" s="8" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
         <is>
           <t>Emoji/sticker panel opened. 8 categories.</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
+      <c r="I70" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J69" s="9" t="inlineStr">
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K69" s="8" t="inlineStr">
+      <c r="K70" s="8" t="inlineStr">
         <is>
           <t>(tap Emoji Button)</t>
         </is>
       </c>
-      <c r="L69" s="10" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
+      <c r="L70" s="10" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>MSG_067</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Verify Emoji button</t>
         </is>
       </c>
-      <c r="D70" s="6" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>Verify emoji button is visible</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Observe emoji button.</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="G71" s="6" t="inlineStr">
         <is>
           <t>Emoji button (smiley icon) should be visible near input field.</t>
         </is>
       </c>
-      <c r="H70" s="8" t="inlineStr">
+      <c r="H71" s="8" t="inlineStr">
         <is>
           <t>0 sticker categories found.</t>
         </is>
       </c>
-      <c r="I70" s="6" t="inlineStr">
+      <c r="I71" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J70" s="14" t="inlineStr">
+      <c r="J71" s="14" t="inlineStr">
         <is>
           <t>FAIL — Less than 2 categories</t>
         </is>
       </c>
-      <c r="K70" s="8" t="inlineStr">
+      <c r="K71" s="8" t="inlineStr">
         <is>
           <t>(open panel, check categories)</t>
         </is>
       </c>
-      <c r="L70" s="10" t="inlineStr">
+      <c r="L71" s="10" t="inlineStr">
         <is>
           <t>Less than 2 categories</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="6" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
         <is>
           <t>MSG_068</t>
         </is>
       </c>
-      <c r="B71" s="11" t="n"/>
-      <c r="C71" s="11" t="n"/>
-      <c r="D71" s="12" t="n"/>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="B72" s="11" t="n"/>
+      <c r="C72" s="11" t="n"/>
+      <c r="D72" s="12" t="n"/>
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>Verify emoji button click opens picker</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Click emoji button.</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="G72" s="6" t="inlineStr">
         <is>
           <t>Emoji picker should open with emoji categories.</t>
         </is>
       </c>
-      <c r="H71" s="8" t="inlineStr">
+      <c r="H72" s="8" t="inlineStr">
         <is>
           <t>Error: Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr">
+      <c r="I72" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J71" s="14" t="inlineStr">
+      <c r="J72" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K71" s="8" t="inlineStr">
+      <c r="K72" s="8" t="inlineStr">
         <is>
           <t>(open panel, press back to close)</t>
         </is>
       </c>
-      <c r="L71" s="10" t="inlineStr">
+      <c r="L72" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -4392,60 +4381,60 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
         <is>
           <t>MSG_069</t>
         </is>
       </c>
-      <c r="B72" s="12" t="n"/>
-      <c r="C72" s="12" t="n"/>
-      <c r="D72" s="6" t="inlineStr">
+      <c r="B73" s="12" t="n"/>
+      <c r="C73" s="12" t="n"/>
+      <c r="D73" s="6" t="inlineStr">
         <is>
           <t>User is logged in and emoji picker open</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>Verify selecting emoji adds to input</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>1. Open emoji picker.
 2. Click on an emoji.</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>Selected emoji should be added to message input field.</t>
         </is>
       </c>
-      <c r="H72" s="8" t="inlineStr">
+      <c r="H73" s="8" t="inlineStr">
         <is>
           <t>Error: Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="I72" s="6" t="inlineStr">
+      <c r="I73" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J72" s="14" t="inlineStr">
+      <c r="J73" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K72" s="8" t="inlineStr">
+      <c r="K73" s="8" t="inlineStr">
         <is>
           <t>send_keys('😀') into composer</t>
         </is>
       </c>
-      <c r="L72" s="10" t="inlineStr">
+      <c r="L73" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -4453,255 +4442,255 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="6" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>MSG_070</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>Verify UI responsiveness</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
+      <c r="D74" s="6" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>Verify message input on desktop</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <t>1. Open application on desktop.
 2. Open chat.
 3. Resize browser.</t>
         </is>
       </c>
-      <c r="G73" s="6" t="inlineStr">
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>Message input and send button should remain functional and visible.</t>
         </is>
       </c>
-      <c r="H73" s="8" t="inlineStr">
+      <c r="H74" s="8" t="inlineStr">
         <is>
           <t>Attachment tests skipped per user instruction.</t>
         </is>
       </c>
-      <c r="I73" s="6" t="inlineStr">
+      <c r="I74" s="6" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
-      <c r="J73" s="13" t="inlineStr">
+      <c r="J74" s="13" t="inlineStr">
         <is>
           <t>SKIP — Attachment tests skipped per instruction</t>
         </is>
       </c>
-      <c r="K73" s="8" t="inlineStr">
+      <c r="K74" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L73" s="10" t="inlineStr">
+      <c r="L74" s="10" t="inlineStr">
         <is>
           <t>Attachment tests skipped per instruction</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>MSG_071</t>
         </is>
       </c>
-      <c r="B74" s="12" t="n"/>
-      <c r="C74" s="12" t="n"/>
-      <c r="D74" s="12" t="n"/>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="B75" s="12" t="n"/>
+      <c r="C75" s="12" t="n"/>
+      <c r="D75" s="12" t="n"/>
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>Verify message input on mobile</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <t>1. Open application on mobile.
 2. Open chat.
 3. Check keyboard interaction.</t>
         </is>
       </c>
-      <c r="G74" s="6" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>Input field should work with mobile keyboard; send button should be accessible.</t>
         </is>
       </c>
-      <c r="H74" s="8" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
         <is>
           <t>Attachment tests skipped per user instruction.</t>
         </is>
       </c>
-      <c r="I74" s="6" t="inlineStr">
+      <c r="I75" s="6" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
-      <c r="J74" s="13" t="inlineStr">
+      <c r="J75" s="13" t="inlineStr">
         <is>
           <t>SKIP — Attachment tests skipped per instruction</t>
         </is>
       </c>
-      <c r="K74" s="8" t="inlineStr">
+      <c r="K75" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L74" s="10" t="inlineStr">
+      <c r="L75" s="10" t="inlineStr">
         <is>
           <t>Attachment tests skipped per instruction</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="6" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>MSG_072</t>
         </is>
       </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>Verify Attachment feature</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D76" s="6" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>Verify attachment icon is visible</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Observe attachment icon near input field.</t>
         </is>
       </c>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G76" s="6" t="inlineStr">
         <is>
           <t>Attachment icon (paperclip/+ icon) should be visible.</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr">
+      <c r="H76" s="8" t="inlineStr">
         <is>
           <t>Attachment tests skipped per user instruction.</t>
         </is>
       </c>
-      <c r="I75" s="6" t="inlineStr">
+      <c r="I76" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J75" s="13" t="inlineStr">
+      <c r="J76" s="13" t="inlineStr">
         <is>
           <t>SKIP — Attachment tests skipped per instruction</t>
         </is>
       </c>
-      <c r="K75" s="8" t="inlineStr">
+      <c r="K76" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L75" s="10" t="inlineStr">
+      <c r="L76" s="10" t="inlineStr">
         <is>
           <t>Attachment tests skipped per instruction</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>MSG_073</t>
         </is>
       </c>
-      <c r="B76" s="11" t="n"/>
-      <c r="C76" s="11" t="n"/>
-      <c r="D76" s="12" t="n"/>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="B77" s="11" t="n"/>
+      <c r="C77" s="11" t="n"/>
+      <c r="D77" s="12" t="n"/>
+      <c r="E77" s="6" t="inlineStr">
         <is>
           <t>Verify attachment options menu</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <t>1. Click on attachment icon.
 2. Observe options menu.</t>
         </is>
       </c>
-      <c r="G76" s="6" t="inlineStr">
+      <c r="G77" s="6" t="inlineStr">
         <is>
           <t>Options menu should display (Image, Video, Document, Camera, etc.).</t>
         </is>
       </c>
-      <c r="H76" s="8" t="inlineStr">
+      <c r="H77" s="8" t="inlineStr">
         <is>
           <t>Attachment tests skipped per user instruction.</t>
         </is>
       </c>
-      <c r="I76" s="6" t="inlineStr">
+      <c r="I77" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J76" s="13" t="inlineStr">
+      <c r="J77" s="13" t="inlineStr">
         <is>
           <t>SKIP — Attachment tests skipped per instruction</t>
         </is>
       </c>
-      <c r="K76" s="8" t="inlineStr">
+      <c r="K77" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L76" s="10" t="inlineStr">
+      <c r="L77" s="10" t="inlineStr">
         <is>
           <t>Attachment tests skipped per instruction</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>MSG_074</t>
         </is>
       </c>
-      <c r="B77" s="11" t="n"/>
-      <c r="C77" s="11" t="n"/>
-      <c r="D77" s="6" t="inlineStr">
+      <c r="B78" s="11" t="n"/>
+      <c r="C78" s="11" t="n"/>
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>User is logged in and attachment menu open</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>Verify sending image attachment</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Select Image option.
@@ -4709,52 +4698,52 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G77" s="6" t="inlineStr">
+      <c r="G78" s="6" t="inlineStr">
         <is>
           <t>Image should be uploaded and sent; preview should display in chat.</t>
         </is>
       </c>
-      <c r="H77" s="8" t="inlineStr">
+      <c r="H78" s="8" t="inlineStr">
         <is>
           <t>Attachment tests skipped per user instruction.</t>
         </is>
       </c>
-      <c r="I77" s="6" t="inlineStr">
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J77" s="13" t="inlineStr">
+      <c r="J78" s="13" t="inlineStr">
         <is>
           <t>SKIP — Attachment tests skipped per instruction</t>
         </is>
       </c>
-      <c r="K77" s="8" t="inlineStr">
+      <c r="K78" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L77" s="10" t="inlineStr">
+      <c r="L78" s="10" t="inlineStr">
         <is>
           <t>Attachment tests skipped per instruction</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>MSG_075</t>
         </is>
       </c>
-      <c r="B78" s="11" t="n"/>
-      <c r="C78" s="11" t="n"/>
-      <c r="D78" s="11" t="n"/>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="B79" s="11" t="n"/>
+      <c r="C79" s="11" t="n"/>
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>Verify sending document attachment</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Select Document option.
@@ -4762,52 +4751,52 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>Document should be uploaded and sent; file icon with name should display.</t>
         </is>
       </c>
-      <c r="H78" s="8" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
         <is>
           <t>Attachment tests skipped per user instruction.</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J78" s="13" t="inlineStr">
+      <c r="J79" s="13" t="inlineStr">
         <is>
           <t>SKIP — Attachment tests skipped per instruction</t>
         </is>
       </c>
-      <c r="K78" s="8" t="inlineStr">
+      <c r="K79" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L78" s="10" t="inlineStr">
+      <c r="L79" s="10" t="inlineStr">
         <is>
           <t>Attachment tests skipped per instruction</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="6" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
         <is>
           <t>MSG_076</t>
         </is>
       </c>
-      <c r="B79" s="11" t="n"/>
-      <c r="C79" s="11" t="n"/>
-      <c r="D79" s="11" t="n"/>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="B80" s="11" t="n"/>
+      <c r="C80" s="11" t="n"/>
+      <c r="D80" s="11" t="n"/>
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>Verify sending video attachment</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Select Video option.
@@ -4815,533 +4804,533 @@
 4. Send.</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
+      <c r="G80" s="6" t="inlineStr">
         <is>
           <t>Video should be uploaded and sent; video thumbnail should display.</t>
         </is>
       </c>
-      <c r="H79" s="8" t="inlineStr">
+      <c r="H80" s="8" t="inlineStr">
         <is>
           <t>Attachment tests skipped per user instruction.</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
+      <c r="I80" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J79" s="13" t="inlineStr">
+      <c r="J80" s="13" t="inlineStr">
         <is>
           <t>SKIP — Attachment tests skipped per instruction</t>
         </is>
       </c>
-      <c r="K79" s="8" t="inlineStr">
+      <c r="K80" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L79" s="10" t="inlineStr">
+      <c r="L80" s="10" t="inlineStr">
         <is>
           <t>Attachment tests skipped per instruction</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>MSG_077</t>
         </is>
       </c>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="12" t="n"/>
-      <c r="D80" s="12" t="n"/>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="12" t="n"/>
+      <c r="D81" s="12" t="n"/>
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>Verify attachment upload progress</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>1. Click attachment icon.
 2. Select a large file.
 3. Observe upload.</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>Upload progress indicator should display during file upload.</t>
         </is>
       </c>
-      <c r="H80" s="8" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
         <is>
           <t>Attachment tests skipped per user instruction.</t>
         </is>
       </c>
-      <c r="I80" s="6" t="inlineStr">
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J80" s="13" t="inlineStr">
+      <c r="J81" s="13" t="inlineStr">
         <is>
           <t>SKIP — Attachment tests skipped per instruction</t>
         </is>
       </c>
-      <c r="K80" s="8" t="inlineStr">
+      <c r="K81" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L80" s="10" t="inlineStr">
+      <c r="L81" s="10" t="inlineStr">
         <is>
           <t>Attachment tests skipped per instruction</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="6" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>MSG_078</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>Verify Voice Recording feature</t>
         </is>
       </c>
-      <c r="D81" s="6" t="inlineStr">
+      <c r="D82" s="6" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>Verify recording button is visible</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Observe microphone/recording icon.</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G82" s="6" t="inlineStr">
         <is>
           <t>Recording button (microphone icon) should be visible near input field.</t>
         </is>
       </c>
-      <c r="H81" s="8" t="inlineStr">
+      <c r="H82" s="8" t="inlineStr">
         <is>
           <t>Voice recording tested in test_voice().</t>
         </is>
       </c>
-      <c r="I81" s="6" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J81" s="13" t="inlineStr">
+      <c r="J82" s="13" t="inlineStr">
         <is>
           <t>SKIP — See test_voice()</t>
         </is>
       </c>
-      <c r="K81" s="8" t="inlineStr">
+      <c r="K82" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L81" s="10" t="inlineStr">
+      <c r="L82" s="10" t="inlineStr">
         <is>
           <t>See test_voice()</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>MSG_079</t>
         </is>
       </c>
-      <c r="B82" s="11" t="n"/>
-      <c r="C82" s="11" t="n"/>
-      <c r="D82" s="12" t="n"/>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="B83" s="11" t="n"/>
+      <c r="C83" s="11" t="n"/>
+      <c r="D83" s="12" t="n"/>
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>Verify recording starts on button press</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <t>1. Press and hold recording button.
 2. Observe recording indicator.</t>
         </is>
       </c>
-      <c r="G82" s="6" t="inlineStr">
+      <c r="G83" s="6" t="inlineStr">
         <is>
           <t>Recording should start; timer and waveform indicator should display.</t>
         </is>
       </c>
-      <c r="H82" s="8" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr">
         <is>
           <t>Voice recording tested in test_voice().</t>
         </is>
       </c>
-      <c r="I82" s="6" t="inlineStr">
+      <c r="I83" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J82" s="13" t="inlineStr">
+      <c r="J83" s="13" t="inlineStr">
         <is>
           <t>SKIP — See test_voice()</t>
         </is>
       </c>
-      <c r="K82" s="8" t="inlineStr">
+      <c r="K83" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L82" s="10" t="inlineStr">
+      <c r="L83" s="10" t="inlineStr">
         <is>
           <t>See test_voice()</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="6" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>MSG_080</t>
         </is>
       </c>
-      <c r="B83" s="11" t="n"/>
-      <c r="C83" s="11" t="n"/>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="B84" s="11" t="n"/>
+      <c r="C84" s="11" t="n"/>
+      <c r="D84" s="6" t="inlineStr">
         <is>
           <t>User is recording voice message</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>Verify recording timer display</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <t>1. Start recording.
 2. Observe timer.</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="G84" s="6" t="inlineStr">
         <is>
           <t>Recording duration timer should display and increment.</t>
         </is>
       </c>
-      <c r="H83" s="8" t="inlineStr">
+      <c r="H84" s="8" t="inlineStr">
         <is>
           <t>Voice recording tested in test_voice().</t>
         </is>
       </c>
-      <c r="I83" s="6" t="inlineStr">
+      <c r="I84" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J83" s="13" t="inlineStr">
+      <c r="J84" s="13" t="inlineStr">
         <is>
           <t>SKIP — See test_voice()</t>
         </is>
       </c>
-      <c r="K83" s="8" t="inlineStr">
+      <c r="K84" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L83" s="10" t="inlineStr">
+      <c r="L84" s="10" t="inlineStr">
         <is>
           <t>See test_voice()</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>MSG_081</t>
         </is>
       </c>
-      <c r="B84" s="11" t="n"/>
-      <c r="C84" s="11" t="n"/>
-      <c r="D84" s="11" t="n"/>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="B85" s="11" t="n"/>
+      <c r="C85" s="11" t="n"/>
+      <c r="D85" s="11" t="n"/>
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>Verify sending voice message</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>1. Record a voice message.
 2. Release button or click send.
 3. Observe chat.</t>
         </is>
       </c>
-      <c r="G84" s="6" t="inlineStr">
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>Voice message should be sent and appear in chat with play button.</t>
         </is>
       </c>
-      <c r="H84" s="8" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr">
         <is>
           <t>Voice recording tested in test_voice().</t>
         </is>
       </c>
-      <c r="I84" s="6" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J84" s="13" t="inlineStr">
+      <c r="J85" s="13" t="inlineStr">
         <is>
           <t>SKIP — See test_voice()</t>
         </is>
       </c>
-      <c r="K84" s="8" t="inlineStr">
+      <c r="K85" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L84" s="10" t="inlineStr">
+      <c r="L85" s="10" t="inlineStr">
         <is>
           <t>See test_voice()</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>MSG_082</t>
         </is>
       </c>
-      <c r="B85" s="12" t="n"/>
-      <c r="C85" s="12" t="n"/>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="B86" s="12" t="n"/>
+      <c r="C86" s="12" t="n"/>
+      <c r="D86" s="6" t="inlineStr">
         <is>
           <t>User has received voice message</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E86" s="6" t="inlineStr">
         <is>
           <t>Verify playing received voice message</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <t>1. Receive a voice message.
 2. Click play button.</t>
         </is>
       </c>
-      <c r="G85" s="6" t="inlineStr">
+      <c r="G86" s="6" t="inlineStr">
         <is>
           <t>Voice message should play; progress indicator should show.</t>
         </is>
       </c>
-      <c r="H85" s="8" t="inlineStr">
+      <c r="H86" s="8" t="inlineStr">
         <is>
           <t>Voice recording tested in test_voice().</t>
         </is>
       </c>
-      <c r="I85" s="6" t="inlineStr">
+      <c r="I86" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J85" s="13" t="inlineStr">
+      <c r="J86" s="13" t="inlineStr">
         <is>
           <t>SKIP — See test_voice()</t>
         </is>
       </c>
-      <c r="K85" s="8" t="inlineStr">
+      <c r="K86" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L85" s="10" t="inlineStr">
+      <c r="L86" s="10" t="inlineStr">
         <is>
           <t>See test_voice()</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="6" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
         <is>
           <t>MSG_083</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>Verify Emoji feature</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>Verify emoji button is visible</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Observe emoji button.</t>
         </is>
       </c>
-      <c r="G86" s="6" t="inlineStr">
+      <c r="G87" s="6" t="inlineStr">
         <is>
           <t>Emoji button (smiley face icon) should be visible near input field.</t>
         </is>
       </c>
-      <c r="H86" s="8" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
         <is>
           <t>Voice button tested in test_voice().</t>
         </is>
       </c>
-      <c r="I86" s="6" t="inlineStr">
+      <c r="I87" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J86" s="13" t="inlineStr">
+      <c r="J87" s="13" t="inlineStr">
         <is>
           <t>SKIP — See MSG_078 in test_voice()</t>
         </is>
       </c>
-      <c r="K86" s="8" t="inlineStr">
+      <c r="K87" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L86" s="10" t="inlineStr">
+      <c r="L87" s="10" t="inlineStr">
         <is>
           <t>See MSG_078 in test_voice()</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="6" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
         <is>
           <t>MSG_084</t>
         </is>
       </c>
-      <c r="B87" s="11" t="n"/>
-      <c r="C87" s="11" t="n"/>
-      <c r="D87" s="12" t="n"/>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="B88" s="11" t="n"/>
+      <c r="C88" s="11" t="n"/>
+      <c r="D88" s="12" t="n"/>
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>Verify emoji picker opens</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>1. Click on emoji button.
 2. Observe emoji picker.</t>
         </is>
       </c>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="G88" s="6" t="inlineStr">
         <is>
           <t>Emoji picker should open with categories (Smileys, Animals, Food, etc.).</t>
         </is>
       </c>
-      <c r="H87" s="8" t="inlineStr">
+      <c r="H88" s="8" t="inlineStr">
         <is>
           <t>Voice timer tested in test_voice().</t>
         </is>
       </c>
-      <c r="I87" s="6" t="inlineStr">
+      <c r="I88" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J87" s="13" t="inlineStr">
+      <c r="J88" s="13" t="inlineStr">
         <is>
           <t>SKIP — See test_voice()</t>
         </is>
       </c>
-      <c r="K87" s="8" t="inlineStr">
+      <c r="K88" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L87" s="10" t="inlineStr">
+      <c r="L88" s="10" t="inlineStr">
         <is>
           <t>See test_voice()</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="6" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
         <is>
           <t>MSG_085</t>
         </is>
       </c>
-      <c r="B88" s="11" t="n"/>
-      <c r="C88" s="11" t="n"/>
-      <c r="D88" s="6" t="inlineStr">
+      <c r="B89" s="11" t="n"/>
+      <c r="C89" s="11" t="n"/>
+      <c r="D89" s="6" t="inlineStr">
         <is>
           <t>User is logged in and emoji picker open</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>Verify emoji categories navigation</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>1. Open emoji picker.
 2. Click on different category tabs.</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="G89" s="6" t="inlineStr">
         <is>
           <t>Different emoji categories should display when tabs are clicked.</t>
         </is>
       </c>
-      <c r="H88" s="8" t="inlineStr">
+      <c r="H89" s="8" t="inlineStr">
         <is>
           <t>Error: Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="I88" s="6" t="inlineStr">
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J88" s="14" t="inlineStr">
+      <c r="J89" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K88" s="8" t="inlineStr">
+      <c r="K89" s="8" t="inlineStr">
         <is>
           <t>(open sticker panel, navigate categories)</t>
         </is>
       </c>
-      <c r="L88" s="10" t="inlineStr">
+      <c r="L89" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -5349,67 +5338,10 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>MSG_086</t>
-        </is>
-      </c>
-      <c r="B89" s="11" t="n"/>
-      <c r="C89" s="11" t="n"/>
-      <c r="D89" s="11" t="n"/>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>Verify selecting emoji adds to input</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>1. Open emoji picker.
-2. Click on any emoji.</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>Selected emoji should be added to message input field at cursor position.</t>
-        </is>
-      </c>
-      <c r="H89" s="8" t="inlineStr">
-        <is>
-          <t>Error: Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
-        </is>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J89" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
-        </is>
-      </c>
-      <c r="K89" s="8" t="inlineStr">
-        <is>
-          <t>Type text then add emoji via send_keys</t>
-        </is>
-      </c>
-      <c r="L89" s="10" t="inlineStr">
-        <is>
-          <t>Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
-        </is>
-      </c>
-    </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>MSG_087</t>
+          <t>MSG_086</t>
         </is>
       </c>
       <c r="B90" s="11" t="n"/>
@@ -5417,18 +5349,18 @@
       <c r="D90" s="11" t="n"/>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Verify multiple emoji selection</t>
+          <t>Verify selecting emoji adds to input</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
           <t>1. Open emoji picker.
-2. Click multiple emojis.</t>
+2. Click on any emoji.</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>All selected emojis should be added to input field.</t>
+          <t>Selected emoji should be added to message input field at cursor position.</t>
         </is>
       </c>
       <c r="H90" s="8" t="inlineStr">
@@ -5440,7 +5372,7 @@
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
       <c r="J90" s="14" t="inlineStr">
@@ -5452,7 +5384,7 @@
       </c>
       <c r="K90" s="8" t="inlineStr">
         <is>
-          <t>send_keys with multiple emojis</t>
+          <t>Type text then add emoji via send_keys</t>
         </is>
       </c>
       <c r="L90" s="10" t="inlineStr">
@@ -5466,7 +5398,7 @@
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>MSG_088</t>
+          <t>MSG_087</t>
         </is>
       </c>
       <c r="B91" s="11" t="n"/>
@@ -5474,19 +5406,18 @@
       <c r="D91" s="11" t="n"/>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Verify emoji search functionality</t>
+          <t>Verify multiple emoji selection</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
           <t>1. Open emoji picker.
-2. Type in emoji search field.
-3. Observe results.</t>
+2. Click multiple emojis.</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>Matching emojis should display based on search term.</t>
+          <t>All selected emojis should be added to input field.</t>
         </is>
       </c>
       <c r="H91" s="8" t="inlineStr">
@@ -5510,7 +5441,7 @@
       </c>
       <c r="K91" s="8" t="inlineStr">
         <is>
-          <t>(check for emoji search in sticker panel)</t>
+          <t>send_keys with multiple emojis</t>
         </is>
       </c>
       <c r="L91" s="10" t="inlineStr">
@@ -5524,7 +5455,7 @@
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>MSG_089</t>
+          <t>MSG_088</t>
         </is>
       </c>
       <c r="B92" s="11" t="n"/>
@@ -5532,46 +5463,104 @@
       <c r="D92" s="11" t="n"/>
       <c r="E92" s="6" t="inlineStr">
         <is>
+          <t>Verify emoji search functionality</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>1. Open emoji picker.
+2. Type in emoji search field.
+3. Observe results.</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>Matching emojis should display based on search term.</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>Error: Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J92" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>(check for emoji search in sticker panel)</t>
+        </is>
+      </c>
+      <c r="L92" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>MSG_089</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="n"/>
+      <c r="C93" s="11" t="n"/>
+      <c r="D93" s="11" t="n"/>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
           <t>Verify recent emojis section</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>1. Send message with emoji.
 2. Open emoji picker again.
 3. Check recent section.</t>
         </is>
       </c>
-      <c r="G92" s="6" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>Recently used emojis should appear in recent/frequently used section.</t>
         </is>
       </c>
-      <c r="H92" s="8" t="inlineStr">
+      <c r="H93" s="8" t="inlineStr">
         <is>
           <t>Error: Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="I92" s="6" t="inlineStr">
+      <c r="I93" s="6" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J92" s="14" t="inlineStr">
+      <c r="J93" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K92" s="8" t="inlineStr">
+      <c r="K93" s="8" t="inlineStr">
         <is>
           <t>(check for recent emojis in sticker panel)</t>
         </is>
       </c>
-      <c r="L92" s="10" t="inlineStr">
+      <c r="L93" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -5579,56 +5568,56 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="6" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
         <is>
           <t>MSG_090</t>
         </is>
       </c>
-      <c r="B93" s="12" t="n"/>
-      <c r="C93" s="12" t="n"/>
-      <c r="D93" s="12" t="n"/>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="B94" s="12" t="n"/>
+      <c r="C94" s="12" t="n"/>
+      <c r="D94" s="12" t="n"/>
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>Verify closing emoji picker</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <t>1. Open emoji picker.
 2. Click outside picker or close button.</t>
         </is>
       </c>
-      <c r="G93" s="6" t="inlineStr">
+      <c r="G94" s="6" t="inlineStr">
         <is>
           <t>Emoji picker should close.</t>
         </is>
       </c>
-      <c r="H93" s="8" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
         <is>
           <t>Error: Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="I93" s="6" t="inlineStr">
+      <c r="I94" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J93" s="14" t="inlineStr">
+      <c r="J94" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K93" s="8" t="inlineStr">
+      <c r="K94" s="8" t="inlineStr">
         <is>
           <t>😀🎉👍_1774504471</t>
         </is>
       </c>
-      <c r="L93" s="10" t="inlineStr">
+      <c r="L94" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -5636,66 +5625,66 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>MSG_091</t>
         </is>
       </c>
-      <c r="B94" s="7" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>Verify Sticker feature</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>User is logged in and chat is open</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>Verify sticker button/tab is visible</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>1. Open any chat conversation.
 2. Observe sticker option.</t>
         </is>
       </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>Sticker button or tab should be visible (may be in emoji picker).</t>
         </is>
       </c>
-      <c r="H94" s="8" t="inlineStr">
+      <c r="H95" s="8" t="inlineStr">
         <is>
           <t>See MSG_090.</t>
         </is>
       </c>
-      <c r="I94" s="6" t="inlineStr">
+      <c r="I95" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J94" s="14" t="inlineStr">
+      <c r="J95" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K94" s="8" t="inlineStr">
+      <c r="K95" s="8" t="inlineStr">
         <is>
           <t>(observe emoji rendering)</t>
         </is>
       </c>
-      <c r="L94" s="10" t="inlineStr">
+      <c r="L95" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -5703,56 +5692,56 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="6" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
         <is>
           <t>MSG_092</t>
         </is>
       </c>
-      <c r="B95" s="11" t="n"/>
-      <c r="C95" s="11" t="n"/>
-      <c r="D95" s="12" t="n"/>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="B96" s="11" t="n"/>
+      <c r="C96" s="11" t="n"/>
+      <c r="D96" s="12" t="n"/>
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>Verify sticker picker opens</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <t>1. Click on sticker button/tab.
 2. Observe sticker picker.</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>Sticker picker should open with sticker packs.</t>
         </is>
       </c>
-      <c r="H95" s="8" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
         <is>
           <t>Error: Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="I95" s="6" t="inlineStr">
+      <c r="I96" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J95" s="14" t="inlineStr">
+      <c r="J96" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K95" s="8" t="inlineStr">
+      <c r="K96" s="8" t="inlineStr">
         <is>
           <t>(tap Emoji Button, verify sticker panel)</t>
         </is>
       </c>
-      <c r="L95" s="10" t="inlineStr">
+      <c r="L96" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -5760,60 +5749,60 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="6" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>MSG_093</t>
         </is>
       </c>
-      <c r="B96" s="11" t="n"/>
-      <c r="C96" s="11" t="n"/>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="B97" s="11" t="n"/>
+      <c r="C97" s="11" t="n"/>
+      <c r="D97" s="6" t="inlineStr">
         <is>
           <t>User is logged in and sticker picker open</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>Verify sticker packs display</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <t>1. Open sticker picker.
 2. Observe available sticker packs.</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G97" s="6" t="inlineStr">
         <is>
           <t>Different sticker packs should be visible and selectable.</t>
         </is>
       </c>
-      <c r="H96" s="8" t="inlineStr">
+      <c r="H97" s="8" t="inlineStr">
         <is>
           <t>Error: Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="I96" s="6" t="inlineStr">
+      <c r="I97" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J96" s="14" t="inlineStr">
+      <c r="J97" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K96" s="8" t="inlineStr">
+      <c r="K97" s="8" t="inlineStr">
         <is>
           <t>(open sticker panel, verify multiple packs)</t>
         </is>
       </c>
-      <c r="L96" s="10" t="inlineStr">
+      <c r="L97" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -5821,56 +5810,56 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
         <is>
           <t>MSG_094</t>
         </is>
       </c>
-      <c r="B97" s="11" t="n"/>
-      <c r="C97" s="11" t="n"/>
-      <c r="D97" s="12" t="n"/>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="B98" s="11" t="n"/>
+      <c r="C98" s="11" t="n"/>
+      <c r="D98" s="12" t="n"/>
+      <c r="E98" s="6" t="inlineStr">
         <is>
           <t>Verify sending sticker</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <t>1. Open sticker picker.
 2. Click on any sticker.</t>
         </is>
       </c>
-      <c r="G97" s="6" t="inlineStr">
+      <c r="G98" s="6" t="inlineStr">
         <is>
           <t>Sticker should be sent immediately and appear in chat.</t>
         </is>
       </c>
-      <c r="H97" s="8" t="inlineStr">
+      <c r="H98" s="8" t="inlineStr">
         <is>
           <t>Error: Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="I97" s="6" t="inlineStr">
+      <c r="I98" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J97" s="14" t="inlineStr">
+      <c r="J98" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K97" s="8" t="inlineStr">
+      <c r="K98" s="8" t="inlineStr">
         <is>
           <t>(open sticker panel, tap sticker to send)</t>
         </is>
       </c>
-      <c r="L97" s="10" t="inlineStr">
+      <c r="L98" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -5878,58 +5867,58 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="6" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
         <is>
           <t>MSG_095</t>
         </is>
       </c>
-      <c r="B98" s="11" t="n"/>
-      <c r="C98" s="11" t="n"/>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="B99" s="11" t="n"/>
+      <c r="C99" s="11" t="n"/>
+      <c r="D99" s="6" t="inlineStr">
         <is>
           <t>User has received sticker</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>Verify received sticker display</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <t>1. Receive a sticker from another user.
 2. Observe chat.</t>
         </is>
       </c>
-      <c r="G98" s="6" t="inlineStr">
+      <c r="G99" s="6" t="inlineStr">
         <is>
           <t>Sticker should display properly in chat on left side.</t>
         </is>
       </c>
-      <c r="H98" s="8" t="inlineStr">
+      <c r="H99" s="8" t="inlineStr">
         <is>
           <t>See MSG_094.</t>
         </is>
       </c>
-      <c r="I98" s="6" t="inlineStr">
+      <c r="I99" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J98" s="14" t="inlineStr">
+      <c r="J99" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K98" s="8" t="inlineStr">
+      <c r="K99" s="8" t="inlineStr">
         <is>
           <t>(observe sticker rendering)</t>
         </is>
       </c>
-      <c r="L98" s="10" t="inlineStr">
+      <c r="L99" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -5937,60 +5926,60 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="6" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
         <is>
           <t>MSG_096</t>
         </is>
       </c>
-      <c r="B99" s="12" t="n"/>
-      <c r="C99" s="12" t="n"/>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="B100" s="12" t="n"/>
+      <c r="C100" s="12" t="n"/>
+      <c r="D100" s="6" t="inlineStr">
         <is>
           <t>User is logged in and sticker picker open</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>Verify sticker pack switching</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <t>1. Open sticker picker.
 2. Click on different sticker pack.</t>
         </is>
       </c>
-      <c r="G99" s="6" t="inlineStr">
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>Selected sticker pack's stickers should display.</t>
         </is>
       </c>
-      <c r="H99" s="8" t="inlineStr">
+      <c r="H100" s="8" t="inlineStr">
         <is>
           <t>Error: Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="I99" s="6" t="inlineStr">
+      <c r="I100" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J99" s="14" t="inlineStr">
+      <c r="J100" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K99" s="8" t="inlineStr">
+      <c r="K100" s="8" t="inlineStr">
         <is>
           <t>(open sticker panel, switch between packs)</t>
         </is>
       </c>
-      <c r="L99" s="10" t="inlineStr">
+      <c r="L100" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -5998,367 +5987,320 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
         <is>
           <t>MSG_097</t>
         </is>
       </c>
-      <c r="B100" s="7" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>Verify @all mention feature</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
+      <c r="D101" s="6" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>Verify typing @all shows suggestion</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <t>1. Open group chat.
 2. Type "@all" in input field.</t>
         </is>
       </c>
-      <c r="G100" s="6" t="inlineStr">
+      <c r="G101" s="6" t="inlineStr">
         <is>
           <t>"@all" suggestion should appear to mention all group members.</t>
         </is>
       </c>
-      <c r="H100" s="8" t="inlineStr">
+      <c r="H101" s="8" t="inlineStr">
         <is>
           <t>@all mention suggestion appeared.</t>
         </is>
       </c>
-      <c r="I100" s="6" t="inlineStr">
+      <c r="I101" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J100" s="9" t="inlineStr">
+      <c r="J101" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K100" s="8" t="inlineStr">
+      <c r="K101" s="8" t="inlineStr">
         <is>
           <t>Type @all in group composer</t>
         </is>
       </c>
-      <c r="L100" s="10" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
+      <c r="L101" s="10" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>MSG_098</t>
         </is>
       </c>
-      <c r="B101" s="11" t="n"/>
-      <c r="C101" s="11" t="n"/>
-      <c r="D101" s="11" t="n"/>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="B102" s="11" t="n"/>
+      <c r="C102" s="11" t="n"/>
+      <c r="D102" s="11" t="n"/>
+      <c r="E102" s="6" t="inlineStr">
         <is>
           <t>Verify selecting @all mention</t>
         </is>
       </c>
-      <c r="F101" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <t>1. Type "@all".
 2. Select @all from suggestions.</t>
         </is>
       </c>
-      <c r="G101" s="6" t="inlineStr">
+      <c r="G102" s="6" t="inlineStr">
         <is>
           <t>"@all" should be added to message with special formatting.</t>
         </is>
       </c>
-      <c r="H101" s="8" t="inlineStr">
+      <c r="H102" s="8" t="inlineStr">
         <is>
           <t>@all mention selected.</t>
         </is>
       </c>
-      <c r="I101" s="6" t="inlineStr">
+      <c r="I102" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J101" s="9" t="inlineStr">
+      <c r="J102" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K101" s="8" t="inlineStr">
+      <c r="K102" s="8" t="inlineStr">
         <is>
           <t>Select @all</t>
         </is>
       </c>
-      <c r="L101" s="10" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="inlineStr">
+      <c r="L102" s="10" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
         <is>
           <t>MSG_099</t>
         </is>
       </c>
-      <c r="B102" s="11" t="n"/>
-      <c r="C102" s="11" t="n"/>
-      <c r="D102" s="12" t="n"/>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="B103" s="11" t="n"/>
+      <c r="C103" s="11" t="n"/>
+      <c r="D103" s="12" t="n"/>
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>Verify sending message with @all</t>
         </is>
       </c>
-      <c r="F102" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <t>1. Type message with @all.
 2. Send message.</t>
         </is>
       </c>
-      <c r="G102" s="6" t="inlineStr">
+      <c r="G103" s="6" t="inlineStr">
         <is>
           <t>Message should be sent; all group members should receive notification.</t>
         </is>
       </c>
-      <c r="H102" s="8" t="inlineStr">
+      <c r="H103" s="8" t="inlineStr">
         <is>
           <t>@all mention message sent.</t>
         </is>
       </c>
-      <c r="I102" s="6" t="inlineStr">
+      <c r="I103" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J102" s="9" t="inlineStr">
+      <c r="J103" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K102" s="8" t="inlineStr">
+      <c r="K103" s="8" t="inlineStr">
         <is>
           <t>Send @all message</t>
         </is>
       </c>
-      <c r="L102" s="10" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="6" t="inlineStr">
+      <c r="L103" s="10" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
         <is>
           <t>MSG_100</t>
         </is>
       </c>
-      <c r="B103" s="11" t="n"/>
-      <c r="C103" s="11" t="n"/>
-      <c r="D103" s="6" t="inlineStr">
+      <c r="B104" s="11" t="n"/>
+      <c r="C104" s="11" t="n"/>
+      <c r="D104" s="6" t="inlineStr">
         <is>
           <t>User has received @all mention</t>
         </is>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E104" s="6" t="inlineStr">
         <is>
           <t>Verify @all mention notification</t>
         </is>
       </c>
-      <c r="F103" s="6" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <t>1. Another user sends @all in group.
 2. Observe notification.</t>
         </is>
       </c>
-      <c r="G103" s="6" t="inlineStr">
+      <c r="G104" s="6" t="inlineStr">
         <is>
           <t>User should receive notification for @all mention.</t>
         </is>
       </c>
-      <c r="H103" s="8" t="inlineStr">
+      <c r="H104" s="8" t="inlineStr">
         <is>
           <t>@all notification requires second device.</t>
         </is>
       </c>
-      <c r="I103" s="6" t="inlineStr">
+      <c r="I104" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J103" s="13" t="inlineStr">
+      <c r="J104" s="13" t="inlineStr">
         <is>
           <t>SKIP — Requires second user session</t>
         </is>
       </c>
-      <c r="K103" s="8" t="inlineStr">
+      <c r="K104" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L103" s="10" t="inlineStr">
+      <c r="L104" s="10" t="inlineStr">
         <is>
           <t>Requires second user session</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>MSG_101</t>
         </is>
       </c>
-      <c r="B104" s="12" t="n"/>
-      <c r="C104" s="12" t="n"/>
-      <c r="D104" s="12" t="n"/>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="B105" s="12" t="n"/>
+      <c r="C105" s="12" t="n"/>
+      <c r="D105" s="12" t="n"/>
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>Verify @all highlight in message</t>
         </is>
       </c>
-      <c r="F104" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <t>1. Receive message with @all.
 2. Observe message display.</t>
         </is>
       </c>
-      <c r="G104" s="6" t="inlineStr">
+      <c r="G105" s="6" t="inlineStr">
         <is>
           <t>"@all" should be highlighted/styled differently in the message.</t>
         </is>
       </c>
-      <c r="H104" s="8" t="inlineStr">
+      <c r="H105" s="8" t="inlineStr">
         <is>
           <t>@all notification requires second device.</t>
         </is>
       </c>
-      <c r="I104" s="6" t="inlineStr">
+      <c r="I105" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J104" s="13" t="inlineStr">
+      <c r="J105" s="13" t="inlineStr">
         <is>
           <t>SKIP — Requires second user session</t>
         </is>
       </c>
-      <c r="K104" s="8" t="inlineStr">
+      <c r="K105" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L104" s="10" t="inlineStr">
+      <c r="L105" s="10" t="inlineStr">
         <is>
           <t>Requires second user session</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="6" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>MSG_102</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B106" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>Verify @ mention feature</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
+      <c r="D106" s="6" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="E106" s="6" t="inlineStr">
         <is>
           <t>Verify typing @ shows member suggestions</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <t>1. Open group chat.
 2. Type "@" in input field.</t>
         </is>
       </c>
-      <c r="G105" s="6" t="inlineStr">
+      <c r="G106" s="6" t="inlineStr">
         <is>
           <t>List of group members should appear as suggestions.</t>
         </is>
       </c>
-      <c r="H105" s="8" t="inlineStr">
+      <c r="H106" s="8" t="inlineStr">
         <is>
           <t>@ shows 1 member suggestions.</t>
         </is>
       </c>
-      <c r="I105" s="6" t="inlineStr">
+      <c r="I106" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J105" s="9" t="inlineStr">
+      <c r="J106" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K105" s="8" t="inlineStr">
+      <c r="K106" s="8" t="inlineStr">
         <is>
           <t>Type @ in group composer</t>
-        </is>
-      </c>
-      <c r="L105" s="10" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>MSG_103</t>
-        </is>
-      </c>
-      <c r="B106" s="11" t="n"/>
-      <c r="C106" s="11" t="n"/>
-      <c r="D106" s="11" t="n"/>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>Verify filtering members by name</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>1. Type "@Jo" in input field.
-2. Observe suggestions.</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>Only members with names starting with "Jo" should appear (e.g., John).</t>
-        </is>
-      </c>
-      <c r="H106" s="8" t="inlineStr">
-        <is>
-          <t>Typing @Hon filters to Honey Yadav.</t>
-        </is>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J106" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K106" s="8" t="inlineStr">
-        <is>
-          <t>Type @Hon, observe filtered list</t>
         </is>
       </c>
       <c r="L106" s="10" t="inlineStr"/>
@@ -6366,7 +6308,7 @@
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>MSG_104</t>
+          <t>MSG_103</t>
         </is>
       </c>
       <c r="B107" s="11" t="n"/>
@@ -6374,359 +6316,406 @@
       <c r="D107" s="11" t="n"/>
       <c r="E107" s="6" t="inlineStr">
         <is>
+          <t>Verify filtering members by name</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>1. Type "@Jo" in input field.
+2. Observe suggestions.</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>Only members with names starting with "Jo" should appear (e.g., John).</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>Typing @Hon filters to Honey Yadav.</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K107" s="8" t="inlineStr">
+        <is>
+          <t>Type @Hon, observe filtered list</t>
+        </is>
+      </c>
+      <c r="L107" s="10" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>MSG_104</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="n"/>
+      <c r="C108" s="11" t="n"/>
+      <c r="D108" s="11" t="n"/>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
           <t>Verify selecting member from suggestions</t>
         </is>
       </c>
-      <c r="F107" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <t>1. Type "@".
 2. Click on a member name.</t>
         </is>
       </c>
-      <c r="G107" s="6" t="inlineStr">
+      <c r="G108" s="6" t="inlineStr">
         <is>
           <t>Selected member's name should be added to message with @ prefix.</t>
         </is>
       </c>
-      <c r="H107" s="8" t="inlineStr">
+      <c r="H108" s="8" t="inlineStr">
         <is>
           <t>Member suggestions not available.</t>
         </is>
       </c>
-      <c r="I107" s="6" t="inlineStr">
+      <c r="I108" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J107" s="13" t="inlineStr">
+      <c r="J108" s="13" t="inlineStr">
         <is>
           <t>SKIP — No member suggestions</t>
         </is>
       </c>
-      <c r="K107" s="8" t="inlineStr">
+      <c r="K108" s="8" t="inlineStr">
         <is>
           <t>Select member from @ suggestions</t>
         </is>
       </c>
-      <c r="L107" s="10" t="inlineStr">
+      <c r="L108" s="10" t="inlineStr">
         <is>
           <t>No member suggestions</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="6" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>MSG_105</t>
         </is>
       </c>
-      <c r="B108" s="11" t="n"/>
-      <c r="C108" s="11" t="n"/>
-      <c r="D108" s="12" t="n"/>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="B109" s="11" t="n"/>
+      <c r="C109" s="11" t="n"/>
+      <c r="D109" s="12" t="n"/>
+      <c r="E109" s="6" t="inlineStr">
         <is>
           <t>Verify sending message with @ mention</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <t>1. Type message with @username.
 2. Send message.</t>
         </is>
       </c>
-      <c r="G108" s="6" t="inlineStr">
+      <c r="G109" s="6" t="inlineStr">
         <is>
           <t>Message should be sent; mentioned user should receive notification.</t>
         </is>
       </c>
-      <c r="H108" s="8" t="inlineStr">
+      <c r="H109" s="8" t="inlineStr">
         <is>
           <t>Cannot send @ mention.</t>
         </is>
       </c>
-      <c r="I108" s="6" t="inlineStr">
+      <c r="I109" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J108" s="13" t="inlineStr">
+      <c r="J109" s="13" t="inlineStr">
         <is>
           <t>SKIP — No member suggestions</t>
         </is>
       </c>
-      <c r="K108" s="8" t="inlineStr">
+      <c r="K109" s="8" t="inlineStr">
         <is>
           <t>Send @ mention message</t>
         </is>
       </c>
-      <c r="L108" s="10" t="inlineStr">
+      <c r="L109" s="10" t="inlineStr">
         <is>
           <t>No member suggestions</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="6" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>MSG_106</t>
         </is>
       </c>
-      <c r="B109" s="11" t="n"/>
-      <c r="C109" s="11" t="n"/>
-      <c r="D109" s="6" t="inlineStr">
+      <c r="B110" s="11" t="n"/>
+      <c r="C110" s="11" t="n"/>
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>User has been mentioned</t>
         </is>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="E110" s="6" t="inlineStr">
         <is>
           <t>Verify @ mention notification</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <t>1. Another user mentions you with @.
 2. Observe notification.</t>
         </is>
       </c>
-      <c r="G109" s="6" t="inlineStr">
+      <c r="G110" s="6" t="inlineStr">
         <is>
           <t>User should receive notification for being mentioned.</t>
         </is>
       </c>
-      <c r="H109" s="8" t="inlineStr">
+      <c r="H110" s="8" t="inlineStr">
         <is>
           <t>See MSG_105.</t>
         </is>
       </c>
-      <c r="I109" s="6" t="inlineStr">
+      <c r="I110" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J109" s="13" t="inlineStr">
+      <c r="J110" s="13" t="inlineStr">
         <is>
           <t>SKIP — No member suggestions</t>
         </is>
       </c>
-      <c r="K109" s="8" t="inlineStr">
+      <c r="K110" s="8" t="inlineStr">
         <is>
           <t>(observe highlight)</t>
         </is>
       </c>
-      <c r="L109" s="10" t="inlineStr">
+      <c r="L110" s="10" t="inlineStr">
         <is>
           <t>No member suggestions</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>MSG_107</t>
         </is>
       </c>
-      <c r="B110" s="11" t="n"/>
-      <c r="C110" s="11" t="n"/>
-      <c r="D110" s="12" t="n"/>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="B111" s="11" t="n"/>
+      <c r="C111" s="11" t="n"/>
+      <c r="D111" s="12" t="n"/>
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>Verify @ mention highlight in message</t>
         </is>
       </c>
-      <c r="F110" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <t>1. Receive message where you are mentioned.
 2. Observe message.</t>
         </is>
       </c>
-      <c r="G110" s="6" t="inlineStr">
+      <c r="G111" s="6" t="inlineStr">
         <is>
           <t>Your @mention should be highlighted/styled differently.</t>
         </is>
       </c>
-      <c r="H110" s="8" t="inlineStr">
+      <c r="H111" s="8" t="inlineStr">
         <is>
           <t>Typing @Adi filters to Aditya.</t>
         </is>
       </c>
-      <c r="I110" s="6" t="inlineStr">
+      <c r="I111" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J110" s="9" t="inlineStr">
+      <c r="J111" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K110" s="8" t="inlineStr">
+      <c r="K111" s="8" t="inlineStr">
         <is>
           <t>Type @Adi, observe filtered list</t>
         </is>
       </c>
-      <c r="L110" s="10" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="inlineStr">
+      <c r="L111" s="10" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
         <is>
           <t>MSG_108</t>
         </is>
       </c>
-      <c r="B111" s="11" t="n"/>
-      <c r="C111" s="11" t="n"/>
-      <c r="D111" s="6" t="inlineStr">
+      <c r="B112" s="11" t="n"/>
+      <c r="C112" s="11" t="n"/>
+      <c r="D112" s="6" t="inlineStr">
         <is>
           <t>User is logged in and group chat is open</t>
         </is>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="E112" s="6" t="inlineStr">
         <is>
           <t>Verify multiple @ mentions in one message</t>
         </is>
       </c>
-      <c r="F111" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <t>1. Type message with multiple @mentions.
 2. Send message.</t>
         </is>
       </c>
-      <c r="G111" s="6" t="inlineStr">
+      <c r="G112" s="6" t="inlineStr">
         <is>
           <t>All mentioned users should receive notifications.</t>
         </is>
       </c>
-      <c r="H111" s="8" t="inlineStr">
+      <c r="H112" s="8" t="inlineStr">
         <is>
           <t>See MSG_105.</t>
         </is>
       </c>
-      <c r="I111" s="6" t="inlineStr">
+      <c r="I112" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J111" s="13" t="inlineStr">
+      <c r="J112" s="13" t="inlineStr">
         <is>
           <t>SKIP — No member suggestions</t>
         </is>
       </c>
-      <c r="K111" s="8" t="inlineStr">
+      <c r="K112" s="8" t="inlineStr">
         <is>
           <t>(observe mention in body)</t>
         </is>
       </c>
-      <c r="L111" s="10" t="inlineStr">
+      <c r="L112" s="10" t="inlineStr">
         <is>
           <t>No member suggestions</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="6" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
         <is>
           <t>MSG_109</t>
         </is>
       </c>
-      <c r="B112" s="12" t="n"/>
-      <c r="C112" s="12" t="n"/>
-      <c r="D112" s="12" t="n"/>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="B113" s="12" t="n"/>
+      <c r="C113" s="12" t="n"/>
+      <c r="D113" s="12" t="n"/>
+      <c r="E113" s="6" t="inlineStr">
         <is>
           <t>Verify @ mention with profile picture in suggestions</t>
         </is>
       </c>
-      <c r="F112" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <t>1. Type "@" in input field.
 2. Observe suggestion list.</t>
         </is>
       </c>
-      <c r="G112" s="6" t="inlineStr">
+      <c r="G113" s="6" t="inlineStr">
         <is>
           <t>Member suggestions should show profile pictures alongside names.</t>
         </is>
       </c>
-      <c r="H112" s="8" t="inlineStr">
+      <c r="H113" s="8" t="inlineStr">
         <is>
           <t>No suggestions.</t>
         </is>
       </c>
-      <c r="I112" s="6" t="inlineStr">
+      <c r="I113" s="6" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J112" s="13" t="inlineStr">
+      <c r="J113" s="13" t="inlineStr">
         <is>
           <t>SKIP — No suggestions</t>
         </is>
       </c>
-      <c r="K112" s="8" t="inlineStr">
+      <c r="K113" s="8" t="inlineStr">
         <is>
           <t>Type @, observe profile pics in suggestions</t>
         </is>
       </c>
-      <c r="L112" s="10" t="inlineStr">
+      <c r="L113" s="10" t="inlineStr">
         <is>
           <t>No suggestions</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
         <is>
           <t>MSG_110</t>
         </is>
       </c>
-      <c r="B113" s="12" t="n"/>
-      <c r="C113" s="12" t="n"/>
-      <c r="D113" s="6" t="inlineStr">
+      <c r="B114" s="12" t="n"/>
+      <c r="C114" s="12" t="n"/>
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>User is logged in and one-on-one chat is open</t>
         </is>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E114" s="6" t="inlineStr">
         <is>
           <t>Verify @ mention in direct chat</t>
         </is>
       </c>
-      <c r="F113" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <t>1. Open one-on-one chat.
 2. Type "@".</t>
         </is>
       </c>
-      <c r="G113" s="6" t="inlineStr">
+      <c r="G114" s="6" t="inlineStr">
         <is>
           <t>Only the other user should appear in suggestions (or feature disabled).</t>
         </is>
       </c>
-      <c r="H113" s="8" t="inlineStr">
+      <c r="H114" s="8" t="inlineStr">
         <is>
           <t>Error: Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="I113" s="6" t="inlineStr">
+      <c r="I114" s="6" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J113" s="14" t="inlineStr">
+      <c r="J114" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K113" s="8" t="inlineStr">
+      <c r="K114" s="8" t="inlineStr">
         <is>
           <t>Type @ in 1-on-1 chat</t>
         </is>
       </c>
-      <c r="L113" s="10" t="inlineStr">
+      <c r="L114" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -6734,69 +6723,69 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="15" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="15" t="inlineStr">
         <is>
           <t>MSG_111</t>
         </is>
       </c>
-      <c r="B114" s="15" t="inlineStr">
+      <c r="B115" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C114" s="15" t="inlineStr">
+      <c r="C115" s="15" t="inlineStr">
         <is>
           <t>Verify Composer state</t>
         </is>
       </c>
-      <c r="D114" s="15" t="inlineStr">
+      <c r="D115" s="15" t="inlineStr">
         <is>
           <t>User is typing in composer</t>
         </is>
       </c>
-      <c r="E114" s="15" t="inlineStr">
+      <c r="E115" s="15" t="inlineStr">
         <is>
           <t>Verify draft message preserved on navigation</t>
         </is>
       </c>
-      <c r="F114" s="15" t="inlineStr">
+      <c r="F115" s="15" t="inlineStr">
         <is>
           <t>1. Type a message in composer (don't send).
 2. Navigate away.
 3. Return to same chat.</t>
         </is>
       </c>
-      <c r="G114" s="15" t="inlineStr">
+      <c r="G115" s="15" t="inlineStr">
         <is>
           <t>Draft message should be preserved in the input field.</t>
         </is>
       </c>
-      <c r="H114" s="8" t="inlineStr">
+      <c r="H115" s="8" t="inlineStr">
         <is>
           <t>Error: Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="I114" s="15" t="inlineStr">
+      <c r="I115" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J114" s="14" t="inlineStr">
+      <c r="J115" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
-      <c r="K114" s="8" t="inlineStr">
+      <c r="K115" s="8" t="inlineStr">
         <is>
           <t>Type draft, navigate away, return</t>
         </is>
       </c>
-      <c r="L114" s="10" t="inlineStr">
+      <c r="L115" s="10" t="inlineStr">
         <is>
           <t>Message: 
 Stacktrace:
@@ -6804,225 +6793,175 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="15" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="15" t="inlineStr">
         <is>
           <t>MSG_112</t>
         </is>
       </c>
-      <c r="B115" s="15" t="n"/>
-      <c r="C115" s="15" t="n"/>
-      <c r="D115" s="15" t="n"/>
-      <c r="E115" s="15" t="inlineStr">
+      <c r="B116" s="15" t="n"/>
+      <c r="C116" s="15" t="n"/>
+      <c r="D116" s="15" t="n"/>
+      <c r="E116" s="15" t="inlineStr">
         <is>
           <t>Verify composer focus after sending</t>
         </is>
       </c>
-      <c r="F115" s="15" t="inlineStr">
+      <c r="F116" s="15" t="inlineStr">
         <is>
           <t>1. Type and send a message.
 2. Observe composer.</t>
         </is>
       </c>
-      <c r="G115" s="15" t="inlineStr">
+      <c r="G116" s="15" t="inlineStr">
         <is>
           <t>Composer should retain focus and be ready for next message.</t>
         </is>
       </c>
-      <c r="H115" s="8" t="inlineStr">
+      <c r="H116" s="8" t="inlineStr">
         <is>
           <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
-      <c r="I115" s="15" t="inlineStr">
+      <c r="I116" s="15" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J115" s="14" t="inlineStr">
+      <c r="J116" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
-      <c r="K115" s="8" t="inlineStr">
+      <c r="K116" s="8" t="inlineStr">
         <is>
           <t>Send message, check composer focus</t>
         </is>
       </c>
-      <c r="L115" s="10" t="inlineStr">
+      <c r="L116" s="10" t="inlineStr">
         <is>
           <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="15" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="15" t="inlineStr">
         <is>
           <t>MSG_113</t>
         </is>
       </c>
-      <c r="B116" s="15" t="inlineStr">
+      <c r="B117" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C116" s="15" t="inlineStr">
+      <c r="C117" s="15" t="inlineStr">
         <is>
           <t>Verify Smart replies</t>
         </is>
       </c>
-      <c r="D116" s="15" t="inlineStr">
+      <c r="D117" s="15" t="inlineStr">
         <is>
           <t>User has received a message</t>
         </is>
       </c>
-      <c r="E116" s="15" t="inlineStr">
+      <c r="E117" s="15" t="inlineStr">
         <is>
           <t>Verify smart reply suggestions appear</t>
         </is>
       </c>
-      <c r="F116" s="15" t="inlineStr">
+      <c r="F117" s="15" t="inlineStr">
         <is>
           <t>1. Receive a message.
 2. Observe below the message or above composer.</t>
         </is>
       </c>
-      <c r="G116" s="15" t="inlineStr">
+      <c r="G117" s="15" t="inlineStr">
         <is>
           <t>Smart reply suggestions should appear (if feature enabled).</t>
         </is>
       </c>
-      <c r="H116" s="8" t="inlineStr">
+      <c r="H117" s="8" t="inlineStr">
         <is>
           <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
-      <c r="I116" s="15" t="inlineStr">
+      <c r="I117" s="15" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J116" s="14" t="inlineStr">
+      <c r="J117" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
-      <c r="K116" s="8" t="inlineStr">
+      <c r="K117" s="8" t="inlineStr">
         <is>
           <t>(check for smart reply suggestions)</t>
         </is>
       </c>
-      <c r="L116" s="10" t="inlineStr">
+      <c r="L117" s="10" t="inlineStr">
         <is>
           <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="15" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="15" t="inlineStr">
         <is>
           <t>MSG_114</t>
         </is>
       </c>
-      <c r="B117" s="15" t="inlineStr">
+      <c r="B118" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C117" s="15" t="inlineStr">
+      <c r="C118" s="15" t="inlineStr">
         <is>
           <t>Verify Link preview</t>
         </is>
       </c>
-      <c r="D117" s="15" t="inlineStr">
+      <c r="D118" s="15" t="inlineStr">
         <is>
           <t>User is in a chat</t>
         </is>
       </c>
-      <c r="E117" s="15" t="inlineStr">
+      <c r="E118" s="15" t="inlineStr">
         <is>
           <t>Verify link preview when typing URL</t>
         </is>
       </c>
-      <c r="F117" s="15" t="inlineStr">
+      <c r="F118" s="15" t="inlineStr">
         <is>
           <t>1. Type a URL in the composer.
 2. Observe preview.</t>
         </is>
       </c>
-      <c r="G117" s="15" t="inlineStr">
+      <c r="G118" s="15" t="inlineStr">
         <is>
           <t>Link preview with title, description, and thumbnail should appear.</t>
         </is>
       </c>
-      <c r="H117" s="8" t="inlineStr">
+      <c r="H118" s="8" t="inlineStr">
         <is>
           <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
-      <c r="I117" s="15" t="inlineStr">
+      <c r="I118" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J117" s="14" t="inlineStr">
+      <c r="J118" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
-      <c r="K117" s="8" t="inlineStr">
+      <c r="K118" s="8" t="inlineStr">
         <is>
           <t>Type URL, observe preview</t>
-        </is>
-      </c>
-      <c r="L117" s="10" t="inlineStr">
-        <is>
-          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="15" t="inlineStr">
-        <is>
-          <t>MSG_115</t>
-        </is>
-      </c>
-      <c r="B118" s="15" t="n"/>
-      <c r="C118" s="15" t="n"/>
-      <c r="D118" s="15" t="n"/>
-      <c r="E118" s="15" t="inlineStr">
-        <is>
-          <t>Verify link preview in sent message</t>
-        </is>
-      </c>
-      <c r="F118" s="15" t="inlineStr">
-        <is>
-          <t>1. Send a message containing a URL.</t>
-        </is>
-      </c>
-      <c r="G118" s="15" t="inlineStr">
-        <is>
-          <t>Sent message should show link preview card with title and thumbnail.</t>
-        </is>
-      </c>
-      <c r="H118" s="8" t="inlineStr">
-        <is>
-          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
-        </is>
-      </c>
-      <c r="I118" s="15" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J118" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
-        </is>
-      </c>
-      <c r="K118" s="8" t="inlineStr">
-        <is>
-          <t>Send URL, observe preview</t>
         </is>
       </c>
       <c r="L118" s="10" t="inlineStr">
@@ -7034,37 +6973,25 @@
     <row r="119">
       <c r="A119" s="15" t="inlineStr">
         <is>
-          <t>MSG_116</t>
-        </is>
-      </c>
-      <c r="B119" s="15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C119" s="15" t="inlineStr">
-        <is>
-          <t>Verify Collaborative Whiteboard</t>
-        </is>
-      </c>
-      <c r="D119" s="15" t="inlineStr">
-        <is>
-          <t>User is in a chat</t>
-        </is>
-      </c>
+          <t>MSG_115</t>
+        </is>
+      </c>
+      <c r="B119" s="15" t="n"/>
+      <c r="C119" s="15" t="n"/>
+      <c r="D119" s="15" t="n"/>
       <c r="E119" s="15" t="inlineStr">
         <is>
-          <t>Verify collaborative whiteboard message display</t>
+          <t>Verify link preview in sent message</t>
         </is>
       </c>
       <c r="F119" s="15" t="inlineStr">
         <is>
-          <t>1. Observe chat with whiteboard message.</t>
+          <t>1. Send a message containing a URL.</t>
         </is>
       </c>
       <c r="G119" s="15" t="inlineStr">
         <is>
-          <t>Collaborative Whiteboard message should display with 'Open whiteboard to edit content together' text.</t>
+          <t>Sent message should show link preview card with title and thumbnail.</t>
         </is>
       </c>
       <c r="H119" s="8" t="inlineStr">
@@ -7084,7 +7011,7 @@
       </c>
       <c r="K119" s="8" t="inlineStr">
         <is>
-          <t>(check for whiteboard messages)</t>
+          <t>Send URL, observe preview</t>
         </is>
       </c>
       <c r="L119" s="10" t="inlineStr">
@@ -7096,25 +7023,37 @@
     <row r="120">
       <c r="A120" s="15" t="inlineStr">
         <is>
-          <t>MSG_117</t>
-        </is>
-      </c>
-      <c r="B120" s="15" t="n"/>
-      <c r="C120" s="15" t="n"/>
-      <c r="D120" s="15" t="n"/>
+          <t>MSG_116</t>
+        </is>
+      </c>
+      <c r="B120" s="15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C120" s="15" t="inlineStr">
+        <is>
+          <t>Verify Collaborative Whiteboard</t>
+        </is>
+      </c>
+      <c r="D120" s="15" t="inlineStr">
+        <is>
+          <t>User is in a chat</t>
+        </is>
+      </c>
       <c r="E120" s="15" t="inlineStr">
         <is>
-          <t>Verify opening collaborative whiteboard</t>
+          <t>Verify collaborative whiteboard message display</t>
         </is>
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
-          <t>1. Tap on collaborative whiteboard message.</t>
+          <t>1. Observe chat with whiteboard message.</t>
         </is>
       </c>
       <c r="G120" s="15" t="inlineStr">
         <is>
-          <t>Whiteboard should open for collaborative editing.</t>
+          <t>Collaborative Whiteboard message should display with 'Open whiteboard to edit content together' text.</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
@@ -7134,7 +7073,7 @@
       </c>
       <c r="K120" s="8" t="inlineStr">
         <is>
-          <t>(tap whiteboard message)</t>
+          <t>(check for whiteboard messages)</t>
         </is>
       </c>
       <c r="L120" s="10" t="inlineStr">
@@ -7146,329 +7085,331 @@
     <row r="121">
       <c r="A121" s="15" t="inlineStr">
         <is>
+          <t>MSG_117</t>
+        </is>
+      </c>
+      <c r="B121" s="15" t="n"/>
+      <c r="C121" s="15" t="n"/>
+      <c r="D121" s="15" t="n"/>
+      <c r="E121" s="15" t="inlineStr">
+        <is>
+          <t>Verify opening collaborative whiteboard</t>
+        </is>
+      </c>
+      <c r="F121" s="15" t="inlineStr">
+        <is>
+          <t>1. Tap on collaborative whiteboard message.</t>
+        </is>
+      </c>
+      <c r="G121" s="15" t="inlineStr">
+        <is>
+          <t>Whiteboard should open for collaborative editing.</t>
+        </is>
+      </c>
+      <c r="H121" s="8" t="inlineStr">
+        <is>
+          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
+      <c r="I121" s="15" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J121" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
+      <c r="K121" s="8" t="inlineStr">
+        <is>
+          <t>(tap whiteboard message)</t>
+        </is>
+      </c>
+      <c r="L121" s="10" t="inlineStr">
+        <is>
+          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="15" t="inlineStr">
+        <is>
           <t>MSG_118</t>
         </is>
       </c>
-      <c r="B121" s="15" t="inlineStr">
+      <c r="B122" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C121" s="15" t="inlineStr">
+      <c r="C122" s="15" t="inlineStr">
         <is>
           <t>Verify Paste in composer</t>
         </is>
       </c>
-      <c r="D121" s="15" t="inlineStr">
+      <c r="D122" s="15" t="inlineStr">
         <is>
           <t>User has text in clipboard</t>
         </is>
       </c>
-      <c r="E121" s="15" t="inlineStr">
+      <c r="E122" s="15" t="inlineStr">
         <is>
           <t>Verify pasting text into composer</t>
         </is>
       </c>
-      <c r="F121" s="15" t="inlineStr">
+      <c r="F122" s="15" t="inlineStr">
         <is>
           <t>1. Copy text from outside the app.
 2. Long press in composer.
 3. Tap Paste.</t>
         </is>
       </c>
-      <c r="G121" s="15" t="inlineStr">
+      <c r="G122" s="15" t="inlineStr">
         <is>
           <t>Copied text should be pasted into the composer input field.</t>
         </is>
       </c>
-      <c r="H121" s="8" t="inlineStr">
+      <c r="H122" s="8" t="inlineStr">
         <is>
           <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
-      <c r="I121" s="15" t="inlineStr">
+      <c r="I122" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J121" s="14" t="inlineStr">
+      <c r="J122" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
-      <c r="K121" s="8" t="inlineStr">
+      <c r="K122" s="8" t="inlineStr">
         <is>
           <t>(copy text, paste into composer)</t>
         </is>
       </c>
-      <c r="L121" s="10" t="inlineStr">
+      <c r="L122" s="10" t="inlineStr">
         <is>
           <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="15" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="15" t="inlineStr">
         <is>
           <t>MSG_119</t>
         </is>
       </c>
-      <c r="B122" s="15" t="n"/>
-      <c r="C122" s="15" t="n"/>
-      <c r="D122" s="15" t="n"/>
-      <c r="E122" s="15" t="inlineStr">
+      <c r="B123" s="15" t="n"/>
+      <c r="C123" s="15" t="n"/>
+      <c r="D123" s="15" t="n"/>
+      <c r="E123" s="15" t="inlineStr">
         <is>
           <t>Verify pasting image into composer</t>
         </is>
       </c>
-      <c r="F122" s="15" t="inlineStr">
+      <c r="F123" s="15" t="inlineStr">
         <is>
           <t>1. Copy an image.
 2. Long press in composer.
 3. Tap Paste.</t>
         </is>
       </c>
-      <c r="G122" s="15" t="inlineStr">
+      <c r="G123" s="15" t="inlineStr">
         <is>
           <t>Image should be pasted as attachment ready to send.</t>
         </is>
       </c>
-      <c r="H122" s="8" t="inlineStr">
+      <c r="H123" s="8" t="inlineStr">
         <is>
           <t>Undo/redo not available in mobile composer.</t>
         </is>
       </c>
-      <c r="I122" s="15" t="inlineStr">
+      <c r="I123" s="15" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J122" s="13" t="inlineStr">
+      <c r="J123" s="13" t="inlineStr">
         <is>
           <t>SKIP — Undo/redo not standard on mobile</t>
         </is>
       </c>
-      <c r="K122" s="8" t="inlineStr">
+      <c r="K123" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L122" s="10" t="inlineStr">
+      <c r="L123" s="10" t="inlineStr">
         <is>
           <t>Undo/redo not standard on mobile</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="15" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="15" t="inlineStr">
         <is>
           <t>MSG_120</t>
         </is>
       </c>
-      <c r="B123" s="15" t="inlineStr">
+      <c r="B124" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C123" s="15" t="inlineStr">
+      <c r="C124" s="15" t="inlineStr">
         <is>
           <t>Verify Composer accessibility</t>
         </is>
       </c>
-      <c r="D123" s="15" t="inlineStr">
+      <c r="D124" s="15" t="inlineStr">
         <is>
           <t>User is in a chat</t>
         </is>
       </c>
-      <c r="E123" s="15" t="inlineStr">
+      <c r="E124" s="15" t="inlineStr">
         <is>
           <t>Verify composer elements have content descriptions</t>
         </is>
       </c>
-      <c r="F123" s="15" t="inlineStr">
+      <c r="F124" s="15" t="inlineStr">
         <is>
           <t>1. Enable TalkBack/screen reader.
 2. Navigate to composer area.</t>
         </is>
       </c>
-      <c r="G123" s="15" t="inlineStr">
+      <c r="G124" s="15" t="inlineStr">
         <is>
           <t>All composer buttons (send, attach, emoji, voice) should have proper content descriptions.</t>
         </is>
       </c>
-      <c r="H123" s="8" t="inlineStr">
+      <c r="H124" s="8" t="inlineStr">
         <is>
           <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
-      <c r="I123" s="15" t="inlineStr">
+      <c r="I124" s="15" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
-      <c r="J123" s="14" t="inlineStr">
+      <c r="J124" s="14" t="inlineStr">
         <is>
           <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
-      <c r="K123" s="8" t="inlineStr">
+      <c r="K124" s="8" t="inlineStr">
         <is>
           <t>(check content-desc on composer elements)</t>
         </is>
       </c>
-      <c r="L123" s="10" t="inlineStr">
+      <c r="L124" s="10" t="inlineStr">
         <is>
           <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="15" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="15" t="inlineStr">
         <is>
           <t>MSG_121</t>
         </is>
       </c>
-      <c r="B124" s="15" t="n"/>
-      <c r="C124" s="15" t="n"/>
-      <c r="D124" s="15" t="n"/>
-      <c r="E124" s="15" t="inlineStr">
+      <c r="B125" s="15" t="n"/>
+      <c r="C125" s="15" t="n"/>
+      <c r="D125" s="15" t="n"/>
+      <c r="E125" s="15" t="inlineStr">
         <is>
           <t>Verify keyboard navigation in composer</t>
         </is>
       </c>
-      <c r="F124" s="15" t="inlineStr">
+      <c r="F125" s="15" t="inlineStr">
         <is>
           <t>1. Use Tab key to navigate composer elements.</t>
         </is>
       </c>
-      <c r="G124" s="15" t="inlineStr">
+      <c r="G125" s="15" t="inlineStr">
         <is>
           <t>Focus should move logically between input field, attachment, emoji, voice, and send buttons.</t>
         </is>
       </c>
-      <c r="H124" s="8" t="inlineStr">
+      <c r="H125" s="8" t="inlineStr">
         <is>
           <t>CometChat does not enforce a visible character limit.</t>
         </is>
       </c>
-      <c r="I124" s="15" t="inlineStr">
+      <c r="I125" s="15" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
-      <c r="J124" s="13" t="inlineStr">
+      <c r="J125" s="13" t="inlineStr">
         <is>
           <t>SKIP — No explicit char limit in CometChat</t>
         </is>
       </c>
-      <c r="K124" s="8" t="inlineStr">
+      <c r="K125" s="8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L124" s="10" t="inlineStr">
+      <c r="L125" s="10" t="inlineStr">
         <is>
           <t>No explicit char limit in CometChat</t>
         </is>
       </c>
     </row>
-    <row r="125"/>
-    <row r="126">
-      <c r="A126" s="4" t="inlineStr">
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>Rich Media Formatting Test Cases</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="16" t="inlineStr">
-        <is>
-          <t>MSG_122</t>
-        </is>
-      </c>
-      <c r="B127" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C127" s="16" t="inlineStr">
-        <is>
-          <t>Verify Rich Text Formatting</t>
-        </is>
-      </c>
-      <c r="D127" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation.</t>
-        </is>
-      </c>
-      <c r="E127" s="16" t="inlineStr">
-        <is>
-          <t>Verify bold text formatting via toolbar</t>
-        </is>
-      </c>
-      <c r="F127" s="16" t="inlineStr">
-        <is>
-          <t>1. Open chat.
-2. Type text in composer.
-3. Select text.
-4. Tap Bold toolbar button.
-5. Send message.</t>
-        </is>
-      </c>
-      <c r="G127" s="16" t="inlineStr">
-        <is>
-          <t>Message should display with bold formatting applied to selected text.</t>
-        </is>
-      </c>
-      <c r="H127" s="16" t="inlineStr">
-        <is>
-          <t>Error: Message: Could not proxy command to the remote server. Original error: socket ha</t>
-        </is>
-      </c>
-      <c r="I127" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J127" s="18" t="inlineStr">
-        <is>
-          <t>FAIL — Message: Could not proxy command to the remote server. Original error: socket ha</t>
-        </is>
-      </c>
-      <c r="K127" s="16" t="inlineStr">
-        <is>
-          <t>Type text, tap Bold toolbar, send</t>
-        </is>
-      </c>
-      <c r="L127" s="16" t="inlineStr">
-        <is>
-          <t>Message: Could not proxy command to the remote server. Original error: socket ha</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="16" t="inlineStr">
         <is>
+          <t>MSG_122</t>
+        </is>
+      </c>
+      <c r="B128" s="21" t="n"/>
+      <c r="C128" s="21" t="n"/>
+      <c r="D128" s="21" t="n"/>
+      <c r="E128" s="21" t="n"/>
+      <c r="F128" s="21" t="n"/>
+      <c r="G128" s="21" t="n"/>
+      <c r="H128" s="21" t="n"/>
+      <c r="I128" s="21" t="n"/>
+      <c r="J128" s="21" t="n"/>
+      <c r="K128" s="21" t="n"/>
+      <c r="L128" s="22" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="16" t="inlineStr">
+        <is>
           <t>MSG_123</t>
         </is>
       </c>
-      <c r="B128" s="16" t="inlineStr">
+      <c r="B129" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C128" s="16" t="n"/>
-      <c r="D128" s="16" t="inlineStr">
+      <c r="C129" s="16" t="n"/>
+      <c r="D129" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E128" s="16" t="inlineStr">
+      <c r="E129" s="16" t="inlineStr">
         <is>
           <t>Verify italic text formatting via toolbar</t>
         </is>
       </c>
-      <c r="F128" s="16" t="inlineStr">
+      <c r="F129" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text in composer.
@@ -7477,60 +7418,60 @@
 5. Send message.</t>
         </is>
       </c>
-      <c r="G128" s="16" t="inlineStr">
+      <c r="G129" s="16" t="inlineStr">
         <is>
           <t>Message should display with italic formatting applied to selected text.</t>
         </is>
       </c>
-      <c r="H128" s="16" t="inlineStr">
+      <c r="H129" s="16" t="inlineStr">
         <is>
           <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="I128" s="16" t="inlineStr">
+      <c r="I129" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J128" s="18" t="inlineStr">
+      <c r="J129" s="18" t="inlineStr">
         <is>
           <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="K128" s="16" t="inlineStr">
+      <c r="K129" s="16" t="inlineStr">
         <is>
           <t>Tap Italic toolbar, type, send</t>
         </is>
       </c>
-      <c r="L128" s="16" t="inlineStr">
+      <c r="L129" s="16" t="inlineStr">
         <is>
           <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="16" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="16" t="inlineStr">
         <is>
           <t>MSG_124</t>
         </is>
       </c>
-      <c r="B129" s="16" t="inlineStr">
+      <c r="B130" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C129" s="16" t="n"/>
-      <c r="D129" s="16" t="inlineStr">
+      <c r="C130" s="16" t="n"/>
+      <c r="D130" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E129" s="16" t="inlineStr">
+      <c r="E130" s="16" t="inlineStr">
         <is>
           <t>Verify underline text formatting via toolbar</t>
         </is>
       </c>
-      <c r="F129" s="16" t="inlineStr">
+      <c r="F130" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text in composer.
@@ -7539,60 +7480,60 @@
 5. Send message.</t>
         </is>
       </c>
-      <c r="G129" s="16" t="inlineStr">
+      <c r="G130" s="16" t="inlineStr">
         <is>
           <t>Message should display with underline formatting applied to selected text.</t>
         </is>
       </c>
-      <c r="H129" s="16" t="inlineStr">
+      <c r="H130" s="16" t="inlineStr">
         <is>
           <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="I129" s="16" t="inlineStr">
+      <c r="I130" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J129" s="18" t="inlineStr">
+      <c r="J130" s="18" t="inlineStr">
         <is>
           <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="K129" s="16" t="inlineStr">
+      <c r="K130" s="16" t="inlineStr">
         <is>
           <t>Tap Underline toolbar, type, send</t>
         </is>
       </c>
-      <c r="L129" s="16" t="inlineStr">
+      <c r="L130" s="16" t="inlineStr">
         <is>
           <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="16" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
         <is>
           <t>MSG_125</t>
         </is>
       </c>
-      <c r="B130" s="16" t="inlineStr">
+      <c r="B131" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C130" s="16" t="n"/>
-      <c r="D130" s="16" t="inlineStr">
+      <c r="C131" s="16" t="n"/>
+      <c r="D131" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E130" s="16" t="inlineStr">
+      <c r="E131" s="16" t="inlineStr">
         <is>
           <t>Verify strikethrough text formatting via toolbar</t>
         </is>
       </c>
-      <c r="F130" s="16" t="inlineStr">
+      <c r="F131" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text in composer.
@@ -7601,64 +7542,64 @@
 5. Send message.</t>
         </is>
       </c>
-      <c r="G130" s="16" t="inlineStr">
+      <c r="G131" s="16" t="inlineStr">
         <is>
           <t>Message should display with strikethrough formatting applied to selected text.</t>
         </is>
       </c>
-      <c r="H130" s="16" t="inlineStr">
+      <c r="H131" s="16" t="inlineStr">
         <is>
           <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="I130" s="16" t="inlineStr">
+      <c r="I131" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J130" s="18" t="inlineStr">
+      <c r="J131" s="18" t="inlineStr">
         <is>
           <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="K130" s="16" t="inlineStr">
+      <c r="K131" s="16" t="inlineStr">
         <is>
           <t>Tap Strikethrough toolbar, type, send</t>
         </is>
       </c>
-      <c r="L130" s="16" t="inlineStr">
+      <c r="L131" s="16" t="inlineStr">
         <is>
           <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="16" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="16" t="inlineStr">
         <is>
           <t>MSG_126</t>
         </is>
       </c>
-      <c r="B131" s="16" t="inlineStr">
+      <c r="B132" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C131" s="16" t="inlineStr">
+      <c r="C132" s="16" t="inlineStr">
         <is>
           <t>Verify Rich Text Formatting</t>
         </is>
       </c>
-      <c r="D131" s="16" t="inlineStr">
+      <c r="D132" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E131" s="16" t="inlineStr">
+      <c r="E132" s="16" t="inlineStr">
         <is>
           <t>Verify link insertion via toolbar</t>
         </is>
       </c>
-      <c r="F131" s="16" t="inlineStr">
+      <c r="F132" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text in composer.
@@ -7668,60 +7609,60 @@
 6. Send message.</t>
         </is>
       </c>
-      <c r="G131" s="16" t="inlineStr">
+      <c r="G132" s="16" t="inlineStr">
         <is>
           <t>Message should display with clickable hyperlink on selected text.</t>
         </is>
       </c>
-      <c r="H131" s="16" t="inlineStr">
+      <c r="H132" s="16" t="inlineStr">
         <is>
           <t>Error: Message: 'POST /element' cannot be proxied to UiAutomator2 server because the in</t>
         </is>
       </c>
-      <c r="I131" s="16" t="inlineStr">
+      <c r="I132" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J131" s="18" t="inlineStr">
+      <c r="J132" s="18" t="inlineStr">
         <is>
           <t>FAIL — Message: 'POST /element' cannot be proxied to UiAutomator2 server because the in</t>
         </is>
       </c>
-      <c r="K131" s="16" t="inlineStr">
+      <c r="K132" s="16" t="inlineStr">
         <is>
           <t>(select text, tap link toolbar button)</t>
         </is>
       </c>
-      <c r="L131" s="16" t="inlineStr">
+      <c r="L132" s="16" t="inlineStr">
         <is>
           <t>Message: 'POST /element' cannot be proxied to UiAutomator2 server because the in</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="16" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="16" t="inlineStr">
         <is>
           <t>MSG_127</t>
         </is>
       </c>
-      <c r="B132" s="16" t="inlineStr">
+      <c r="B133" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C132" s="16" t="n"/>
-      <c r="D132" s="16" t="inlineStr">
+      <c r="C133" s="16" t="n"/>
+      <c r="D133" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E132" s="16" t="inlineStr">
+      <c r="E133" s="16" t="inlineStr">
         <is>
           <t>Verify ordered list formatting via toolbar</t>
         </is>
       </c>
-      <c r="F132" s="16" t="inlineStr">
+      <c r="F133" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Tap Ordered List toolbar button.
@@ -7729,60 +7670,60 @@
 4. Send message.</t>
         </is>
       </c>
-      <c r="G132" s="16" t="inlineStr">
+      <c r="G133" s="16" t="inlineStr">
         <is>
           <t>Message should display as numbered list (1. 2. 3. etc.).</t>
         </is>
       </c>
-      <c r="H132" s="16" t="inlineStr">
+      <c r="H133" s="16" t="inlineStr">
         <is>
           <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="I132" s="16" t="inlineStr">
+      <c r="I133" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J132" s="18" t="inlineStr">
+      <c r="J133" s="18" t="inlineStr">
         <is>
           <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="K132" s="16" t="inlineStr">
+      <c r="K133" s="16" t="inlineStr">
         <is>
           <t>Tap ordered list toolbar, type items</t>
         </is>
       </c>
-      <c r="L132" s="16" t="inlineStr">
+      <c r="L133" s="16" t="inlineStr">
         <is>
           <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="16" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="16" t="inlineStr">
         <is>
           <t>MSG_128</t>
         </is>
       </c>
-      <c r="B133" s="16" t="inlineStr">
+      <c r="B134" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C133" s="16" t="n"/>
-      <c r="D133" s="16" t="inlineStr">
+      <c r="C134" s="16" t="n"/>
+      <c r="D134" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E133" s="16" t="inlineStr">
+      <c r="E134" s="16" t="inlineStr">
         <is>
           <t>Verify unordered list formatting via toolbar</t>
         </is>
       </c>
-      <c r="F133" s="16" t="inlineStr">
+      <c r="F134" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Tap Unordered List toolbar button.
@@ -7790,60 +7731,60 @@
 4. Send message.</t>
         </is>
       </c>
-      <c r="G133" s="16" t="inlineStr">
+      <c r="G134" s="16" t="inlineStr">
         <is>
           <t>Message should display as bulleted list.</t>
         </is>
       </c>
-      <c r="H133" s="16" t="inlineStr">
+      <c r="H134" s="16" t="inlineStr">
         <is>
           <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="I133" s="16" t="inlineStr">
+      <c r="I134" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J133" s="18" t="inlineStr">
+      <c r="J134" s="18" t="inlineStr">
         <is>
           <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="K133" s="16" t="inlineStr">
+      <c r="K134" s="16" t="inlineStr">
         <is>
           <t>Tap unordered list toolbar, type items</t>
         </is>
       </c>
-      <c r="L133" s="16" t="inlineStr">
+      <c r="L134" s="16" t="inlineStr">
         <is>
           <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="16" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="16" t="inlineStr">
         <is>
           <t>MSG_129</t>
         </is>
       </c>
-      <c r="B134" s="16" t="inlineStr">
+      <c r="B135" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C134" s="16" t="n"/>
-      <c r="D134" s="16" t="inlineStr">
+      <c r="C135" s="16" t="n"/>
+      <c r="D135" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E134" s="16" t="inlineStr">
+      <c r="E135" s="16" t="inlineStr">
         <is>
           <t>Verify blockquote formatting via toolbar</t>
         </is>
       </c>
-      <c r="F134" s="16" t="inlineStr">
+      <c r="F135" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Tap Blockquote toolbar button.
@@ -7851,64 +7792,64 @@
 4. Send message.</t>
         </is>
       </c>
-      <c r="G134" s="16" t="inlineStr">
+      <c r="G135" s="16" t="inlineStr">
         <is>
           <t>Message should display with blockquote styling (indented with vertical bar).</t>
         </is>
       </c>
-      <c r="H134" s="16" t="inlineStr">
+      <c r="H135" s="16" t="inlineStr">
         <is>
           <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="I134" s="16" t="inlineStr">
+      <c r="I135" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J134" s="18" t="inlineStr">
+      <c r="J135" s="18" t="inlineStr">
         <is>
           <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="K134" s="16" t="inlineStr">
+      <c r="K135" s="16" t="inlineStr">
         <is>
           <t>Tap blockquote toolbar, type text</t>
         </is>
       </c>
-      <c r="L134" s="16" t="inlineStr">
+      <c r="L135" s="16" t="inlineStr">
         <is>
           <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="16" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="16" t="inlineStr">
         <is>
           <t>MSG_130</t>
         </is>
       </c>
-      <c r="B135" s="16" t="inlineStr">
+      <c r="B136" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C135" s="16" t="inlineStr">
+      <c r="C136" s="16" t="inlineStr">
         <is>
           <t>Verify Rich Text Formatting</t>
         </is>
       </c>
-      <c r="D135" s="16" t="inlineStr">
+      <c r="D136" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E135" s="16" t="inlineStr">
+      <c r="E136" s="16" t="inlineStr">
         <is>
           <t>Verify inline code formatting via toolbar</t>
         </is>
       </c>
-      <c r="F135" s="16" t="inlineStr">
+      <c r="F136" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text in composer.
@@ -7917,60 +7858,60 @@
 5. Send message.</t>
         </is>
       </c>
-      <c r="G135" s="16" t="inlineStr">
+      <c r="G136" s="16" t="inlineStr">
         <is>
           <t>Message should display selected text in monospace/code font style.</t>
         </is>
       </c>
-      <c r="H135" s="16" t="inlineStr">
+      <c r="H136" s="16" t="inlineStr">
         <is>
           <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="I135" s="16" t="inlineStr">
+      <c r="I136" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J135" s="18" t="inlineStr">
+      <c r="J136" s="18" t="inlineStr">
         <is>
           <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="K135" s="16" t="inlineStr">
+      <c r="K136" s="16" t="inlineStr">
         <is>
           <t>Tap inline code toolbar, type text</t>
         </is>
       </c>
-      <c r="L135" s="16" t="inlineStr">
+      <c r="L136" s="16" t="inlineStr">
         <is>
           <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="16" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="16" t="inlineStr">
         <is>
           <t>MSG_131</t>
         </is>
       </c>
-      <c r="B136" s="16" t="inlineStr">
+      <c r="B137" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C136" s="16" t="n"/>
-      <c r="D136" s="16" t="inlineStr">
+      <c r="C137" s="16" t="n"/>
+      <c r="D137" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E136" s="16" t="inlineStr">
+      <c r="E137" s="16" t="inlineStr">
         <is>
           <t>Verify multiple formatting styles combined</t>
         </is>
       </c>
-      <c r="F136" s="16" t="inlineStr">
+      <c r="F137" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Type text.
@@ -7978,60 +7919,60 @@
 4. Send message.</t>
         </is>
       </c>
-      <c r="G136" s="16" t="inlineStr">
+      <c r="G137" s="16" t="inlineStr">
         <is>
           <t>Message should display with both bold and italic formatting applied.</t>
         </is>
       </c>
-      <c r="H136" s="16" t="inlineStr">
+      <c r="H137" s="16" t="inlineStr">
         <is>
           <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="I136" s="16" t="inlineStr">
+      <c r="I137" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J136" s="18" t="inlineStr">
+      <c r="J137" s="18" t="inlineStr">
         <is>
           <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="K136" s="16" t="inlineStr">
+      <c r="K137" s="16" t="inlineStr">
         <is>
           <t>Apply bold + italic to same text</t>
         </is>
       </c>
-      <c r="L136" s="16" t="inlineStr">
+      <c r="L137" s="16" t="inlineStr">
         <is>
           <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="16" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="16" t="inlineStr">
         <is>
           <t>MSG_132</t>
         </is>
       </c>
-      <c r="B137" s="16" t="inlineStr">
+      <c r="B138" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C137" s="16" t="n"/>
-      <c r="D137" s="16" t="inlineStr">
+      <c r="C138" s="16" t="n"/>
+      <c r="D138" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E137" s="16" t="inlineStr">
+      <c r="E138" s="16" t="inlineStr">
         <is>
           <t>Verify toolbar toggle on/off state</t>
         </is>
       </c>
-      <c r="F137" s="16" t="inlineStr">
+      <c r="F138" s="16" t="inlineStr">
         <is>
           <t>1. Open chat.
 2. Tap Bold toolbar button (should show 'on').
@@ -8039,32 +7980,32 @@
 4. Observe toolbar state.</t>
         </is>
       </c>
-      <c r="G137" s="16" t="inlineStr">
+      <c r="G138" s="16" t="inlineStr">
         <is>
           <t>Toolbar button should toggle between on/off states visually.</t>
         </is>
       </c>
-      <c r="H137" s="16" t="inlineStr">
+      <c r="H138" s="16" t="inlineStr">
         <is>
           <t>Error: Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="I137" s="16" t="inlineStr">
+      <c r="I138" s="16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J137" s="18" t="inlineStr">
+      <c r="J138" s="18" t="inlineStr">
         <is>
           <t>FAIL — Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>
       </c>
-      <c r="K137" s="16" t="inlineStr">
+      <c r="K138" s="16" t="inlineStr">
         <is>
           <t>Tap Bold on, tap Bold off, observe state</t>
         </is>
       </c>
-      <c r="L137" s="16" t="inlineStr">
+      <c r="L138" s="16" t="inlineStr">
         <is>
           <t>Message: 'POST /elements' cannot be proxied to UiAutomator2 server because the i</t>
         </is>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -2423,7 +2423,7 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>MSG_036</t>
+          <t>MSG_034</t>
         </is>
       </c>
       <c r="B36" s="15" t="inlineStr">
@@ -2482,7 +2482,7 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>MSG_037</t>
+          <t>MSG_035</t>
         </is>
       </c>
       <c r="B37" s="15" t="n"/>
@@ -2530,7 +2530,7 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>MSG_038</t>
+          <t>MSG_036</t>
         </is>
       </c>
       <c r="B38" s="15" t="n"/>
@@ -2582,7 +2582,7 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>MSG_039</t>
+          <t>MSG_037</t>
         </is>
       </c>
       <c r="B39" s="15" t="inlineStr">
@@ -2645,7 +2645,7 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>MSG_040</t>
+          <t>MSG_038</t>
         </is>
       </c>
       <c r="B40" s="15" t="n"/>
@@ -2697,7 +2697,7 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>MSG_041</t>
+          <t>MSG_039</t>
         </is>
       </c>
       <c r="B41" s="15" t="inlineStr">
@@ -2756,7 +2756,7 @@
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>MSG_042</t>
+          <t>MSG_040</t>
         </is>
       </c>
       <c r="B42" s="15" t="n"/>
@@ -2807,7 +2807,7 @@
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>MSG_043</t>
+          <t>MSG_041</t>
         </is>
       </c>
       <c r="B43" s="15" t="n"/>
@@ -2857,7 +2857,7 @@
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>MSG_044</t>
+          <t>MSG_042</t>
         </is>
       </c>
       <c r="B44" s="15" t="inlineStr">
@@ -2916,7 +2916,7 @@
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>MSG_045</t>
+          <t>MSG_043</t>
         </is>
       </c>
       <c r="B45" s="15" t="n"/>
@@ -2962,7 +2962,7 @@
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>MSG_046</t>
+          <t>MSG_044</t>
         </is>
       </c>
       <c r="B46" s="15" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>MSG_047</t>
+          <t>MSG_045</t>
         </is>
       </c>
       <c r="B47" s="15" t="n"/>
@@ -3074,7 +3074,7 @@
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>MSG_048</t>
+          <t>MSG_046</t>
         </is>
       </c>
       <c r="B48" s="15" t="inlineStr">
@@ -3133,7 +3133,7 @@
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>MSG_049</t>
+          <t>MSG_047</t>
         </is>
       </c>
       <c r="B49" s="15" t="n"/>
@@ -3184,7 +3184,7 @@
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>MSG_050</t>
+          <t>MSG_048</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
@@ -3247,7 +3247,7 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>MSG_051</t>
+          <t>MSG_049</t>
         </is>
       </c>
       <c r="B51" s="16" t="inlineStr">
@@ -3306,7 +3306,7 @@
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>MSG_052</t>
+          <t>MSG_050</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
@@ -3366,7 +3366,7 @@
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>MSG_053</t>
+          <t>MSG_051</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
@@ -3429,7 +3429,7 @@
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>MSG_054</t>
+          <t>MSG_052</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
@@ -3488,7 +3488,7 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>MSG_055</t>
+          <t>MSG_053</t>
         </is>
       </c>
       <c r="B55" s="16" t="inlineStr">
@@ -3543,7 +3543,7 @@
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>MSG_056</t>
+          <t>MSG_054</t>
         </is>
       </c>
       <c r="B56" s="16" t="inlineStr">
@@ -3598,7 +3598,7 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>MSG_057</t>
+          <t>MSG_055</t>
         </is>
       </c>
       <c r="B57" s="16" t="inlineStr">
@@ -3657,7 +3657,7 @@
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>MSG_058</t>
+          <t>MSG_056</t>
         </is>
       </c>
       <c r="B58" s="16" t="inlineStr">
@@ -3716,7 +3716,7 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>MSG_059</t>
+          <t>MSG_057</t>
         </is>
       </c>
       <c r="B59" s="16" t="inlineStr">
@@ -3771,7 +3771,7 @@
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>MSG_060</t>
+          <t>MSG_058</t>
         </is>
       </c>
       <c r="B60" s="16" t="inlineStr">
@@ -3830,7 +3830,7 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>MSG_061</t>
+          <t>MSG_059</t>
         </is>
       </c>
       <c r="B61" s="16" t="inlineStr">
@@ -3890,7 +3890,7 @@
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>MSG_062</t>
+          <t>MSG_060</t>
         </is>
       </c>
       <c r="B62" s="16" t="inlineStr">
@@ -3950,7 +3950,7 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>MSG_063</t>
+          <t>MSG_061</t>
         </is>
       </c>
       <c r="B63" s="16" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>MSG_064</t>
+          <t>MSG_062</t>
         </is>
       </c>
       <c r="B64" s="16" t="inlineStr">
@@ -4074,7 +4074,7 @@
     <row r="65">
       <c r="A65" s="15" t="inlineStr">
         <is>
-          <t>MSG_034</t>
+          <t>MSG_063</t>
         </is>
       </c>
       <c r="B65" s="15" t="inlineStr">
@@ -4134,7 +4134,7 @@
     <row r="66">
       <c r="A66" s="15" t="inlineStr">
         <is>
-          <t>MSG_035</t>
+          <t>MSG_064</t>
         </is>
       </c>
       <c r="B66" s="15" t="n"/>
@@ -4189,6 +4189,7 @@
         </is>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -749,7 +749,7 @@
           <t>None (observation only)</t>
         </is>
       </c>
-      <c r="L3" s="10" t="inlineStr"/>
+      <c r="L3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -796,7 +796,7 @@
           <t>Click on composer</t>
         </is>
       </c>
-      <c r="L4" s="10" t="inlineStr"/>
+      <c r="L4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -844,7 +844,7 @@
           <t>Test message</t>
         </is>
       </c>
-      <c r="L5" s="10" t="inlineStr"/>
+      <c r="L5" s="10" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -955,7 +955,7 @@
           <t>test</t>
         </is>
       </c>
-      <c r="L7" s="10" t="inlineStr"/>
+      <c r="L7" s="10" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1003,7 +1003,7 @@
           <t>Hello</t>
         </is>
       </c>
-      <c r="L8" s="10" t="inlineStr"/>
+      <c r="L8" s="10" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1055,7 +1055,7 @@
           <t>TestRN007_1774505503</t>
         </is>
       </c>
-      <c r="L9" s="10" t="inlineStr"/>
+      <c r="L9" s="10" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1103,7 +1103,7 @@
           <t>FeedbackTest</t>
         </is>
       </c>
-      <c r="L10" s="10" t="inlineStr"/>
+      <c r="L10" s="10" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1163,7 +1163,7 @@
           <t>Hello</t>
         </is>
       </c>
-      <c r="L11" s="10" t="inlineStr"/>
+      <c r="L11" s="10" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1211,7 +1211,7 @@
           <t>500+ chars (514 chars)</t>
         </is>
       </c>
-      <c r="L12" s="10" t="inlineStr"/>
+      <c r="L12" s="10" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1259,7 +1259,7 @@
           <t>Hello @#$%^&amp;*()! _1774505528</t>
         </is>
       </c>
-      <c r="L13" s="10" t="inlineStr"/>
+      <c r="L13" s="10" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1307,7 +1307,7 @@
           <t>Hello 😀🎉👍 _1774505533</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr"/>
+      <c r="L14" s="10" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1355,7 +1355,7 @@
           <t>Order #12345_1774505539</t>
         </is>
       </c>
-      <c r="L15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1403,7 +1403,7 @@
           <t>Check https://example.com _1774505544</t>
         </is>
       </c>
-      <c r="L16" s="10" t="inlineStr"/>
+      <c r="L16" s="10" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1454,7 +1454,7 @@
           <t>10000+ chars (10014 chars)</t>
         </is>
       </c>
-      <c r="L17" s="10" t="inlineStr"/>
+      <c r="L17" s="10" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1469,255 +1469,270 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
+          <t>Verify Enter key to send</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>User is logged in and message typed</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Verify Enter key sends message</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>1. Type a message.
+2. Press Enter key.
+3. Observe chat.</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Message should be sent when Enter key is pressed.</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>Enter creates newline (expected for rich text editor).</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>EnterSend_1774505574</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>MSG_017</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Verify Shift+Enter creates new line</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>1. Type a message.
+2. Press Shift+Enter.
+3. Continue typing.</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>New line should be created; message should not be sent.</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>Text: 'Line2'</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J19" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K19" s="8" t="inlineStr">
+        <is>
+          <t>Type Line1, Enter, Line2</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>MSG_018</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Verify Message input clear after send</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>User has sent a message</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Verify input field clears after sending</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>1. Type a message.
+2. Click send.
+3. Observe input field.</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Input field should be cleared after message is sent successfully.</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Input cleared. Current: 'Type your message...'</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t>ClearTest_1774505586</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>MSG_019</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
           <t>Verify Sent message display</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>User has sent a message</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Verify sent message alignment</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Observe message position in chat.</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Sent message should appear on the right side of chat window.</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H21" s="8" t="inlineStr">
         <is>
           <t>center_x=792, screen_width=1080</t>
         </is>
       </c>
-      <c r="I18" s="6" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J18" s="9" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K21" s="8" t="inlineStr">
         <is>
           <t>AlignTest_1774505559</t>
         </is>
       </c>
-      <c r="L18" s="10" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>MSG_017</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="L21" s="10" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>MSG_020</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Verify sent message bubble color</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Observe message bubble.</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Sent message should have distinct bubble color (e.g., blue/purple).</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H22" s="8" t="inlineStr">
         <is>
           <t>Sent message in distinct bubble. Visual confirmation.</t>
         </is>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K19" s="8" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>(observe bubble color)</t>
         </is>
       </c>
-      <c r="L19" s="10" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>MSG_018</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>Verify sent message timestamp</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>1. Send a message.
-2. Observe timestamp.</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Timestamp should display below or next to sent message.</t>
-        </is>
-      </c>
-      <c r="H20" s="8" t="inlineStr">
-        <is>
-          <t>Found 4 timestamp element(s).</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t>(observe timestamp)</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>MSG_019</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Verify sent message status indicator</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>1. Send a message.
-2. Observe status indicator.</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>Status indicator should show (single tick = sent, double tick = delivered, blue tick = read).</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="inlineStr">
-        <is>
-          <t>Status indicator (tick marks) not identifiable via automation.</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J21" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K21" s="8" t="inlineStr">
-        <is>
-          <t>(observe status indicator)</t>
-        </is>
-      </c>
-      <c r="L21" s="10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>MSG_020</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>Verify Received message display</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>User has received a message</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>Verify received message alignment</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>1. Receive a message from another user.
-2. Observe message position.</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>Received message should appear on the left side of chat window.</t>
-        </is>
-      </c>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>Received message center_x=487.</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t>(observe received messages)</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="inlineStr"/>
+      <c r="L22" s="10" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1730,311 +1745,296 @@
       <c r="D23" s="11" t="n"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
+          <t>Verify sent message timestamp</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Observe timestamp.</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Timestamp should display below or next to sent message.</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Found 4 timestamp element(s).</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K23" s="8" t="inlineStr">
+        <is>
+          <t>(observe timestamp)</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>MSG_022</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Verify sent message status indicator</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Observe status indicator.</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Status indicator should show (single tick = sent, double tick = delivered, blue tick = read).</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Status indicator (tick marks) not identifiable via automation.</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J24" s="14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="inlineStr">
+        <is>
+          <t>(observe status indicator)</t>
+        </is>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>MSG_023</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Verify Received message display</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>User has received a message</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Verify received message alignment</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>1. Receive a message from another user.
+2. Observe message position.</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Received message should appear on the left side of chat window.</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Received message center_x=487.</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>(observe received messages)</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>MSG_024</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
           <t>Verify received message bubble color</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>1. Receive a message.
 2. Observe message bubble.</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Received message should have different bubble color than sent (e.g., gray/white).</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>Received message in distinct bubble. Visual confirmation.</t>
         </is>
       </c>
-      <c r="I23" s="6" t="inlineStr">
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J23" s="9" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K23" s="8" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>(observe received bubble)</t>
         </is>
       </c>
-      <c r="L23" s="10" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>MSG_022</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="L26" s="10" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>MSG_025</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Verify received message sender info</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>1. Receive a message in group chat.
 2. Observe sender info.</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Sender name and/or avatar should display with received message in group chats.</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H27" s="8" t="inlineStr">
         <is>
           <t>See group chat section.</t>
         </is>
       </c>
-      <c r="I24" s="6" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="J27" s="13" t="inlineStr">
         <is>
           <t>SKIP — Tested in group section</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="K27" s="8" t="inlineStr">
         <is>
           <t>Group chat test</t>
         </is>
       </c>
-      <c r="L24" s="10" t="inlineStr">
+      <c r="L27" s="10" t="inlineStr">
         <is>
           <t>Tested in group section</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>MSG_023</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>MSG_026</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>Verify received message timestamp</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>1. Receive a message.
 2. Observe timestamp.</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Timestamp should display below or next to received message.</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>Found 4 timestamp element(s).</t>
         </is>
       </c>
-      <c r="I25" s="6" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J25" s="9" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>(observe received timestamps)</t>
         </is>
       </c>
-      <c r="L25" s="10" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>MSG_024</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Verify Enter key to send</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>User is logged in and message typed</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Verify Enter key sends message</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>1. Type a message.
-2. Press Enter key.
-3. Observe chat.</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>Message should be sent when Enter key is pressed.</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Enter creates newline (expected for rich text editor).</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J26" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>EnterSend_1774505574</t>
-        </is>
-      </c>
-      <c r="L26" s="10" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>MSG_025</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>Verify Shift+Enter creates new line</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>1. Type a message.
-2. Press Shift+Enter.
-3. Continue typing.</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>New line should be created; message should not be sent.</t>
-        </is>
-      </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Text: 'Line2'</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J27" s="14" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>Type Line1, Enter, Line2</t>
-        </is>
-      </c>
-      <c r="L27" s="10" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>MSG_026</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>Verify Message input clear after send</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>User has sent a message</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>Verify input field clears after sending</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>1. Type a message.
-2. Click send.
-3. Observe input field.</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>Input field should be cleared after message is sent successfully.</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>Input cleared. Current: 'Type your message...'</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
-        <is>
-          <t>ClearTest_1774505586</t>
-        </is>
-      </c>
-      <c r="L28" s="10" t="inlineStr"/>
+      <c r="L28" s="10" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -2049,55 +2049,51 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Verify Real-time message delivery</t>
+          <t>Verify Message scroll behavior</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>Two users are in same chat</t>
+          <t>User is in chat with many messages</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Verify message appears instantly for recipient</t>
+          <t>Verify auto-scroll to new message</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>1. User A sends message.
-2. User B observes chat.</t>
+          <t>1. Be at bottom of chat.
+2. Send or receive new message.</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>Message should appear in User B's chat within seconds without refresh.</t>
+          <t>Chat should auto-scroll to show the new message.</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>Real-time delivery requires two devices/sessions.</t>
+          <t>Chat auto-scrolled to new message.</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+          <t>High / Medium</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L29" s="10" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
+          <t>AutoScroll_1774505592</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -2105,287 +2101,646 @@
           <t>MSG_028</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
       <c r="D30" s="12" t="n"/>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Verify typing indicator</t>
+          <t>Verify scroll up to view history</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>1. User A starts typing.
-2. User B observes chat.</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>Typing indicator should appear for User B (e.g., "User A is typing...").</t>
-        </is>
-      </c>
-      <c r="H30" s="8" t="inlineStr">
-        <is>
-          <t>Typing indicator requires two devices/sessions.</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L30" s="10" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>MSG_029</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Verify Message scroll behavior</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>User is in chat with many messages</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Verify auto-scroll to new message</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>1. Be at bottom of chat.
-2. Send or receive new message.</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>Chat should auto-scroll to show the new message.</t>
-        </is>
-      </c>
-      <c r="H31" s="8" t="inlineStr">
-        <is>
-          <t>Chat auto-scrolled to new message.</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K31" s="8" t="inlineStr">
-        <is>
-          <t>AutoScroll_1774505592</t>
-        </is>
-      </c>
-      <c r="L31" s="10" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>MSG_030</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>Verify scroll up to view history</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
         <is>
           <t>1. Open chat with many messages.
 2. Scroll up.</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>Older messages should load; scrolling should be smooth.</t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr">
         <is>
           <t>Scrolled up. Messages visible.</t>
         </is>
       </c>
-      <c r="I32" s="6" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t>(scroll up)</t>
         </is>
       </c>
-      <c r="L32" s="10" t="inlineStr"/>
+      <c r="L30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>MSG_029</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Verify Scroll to Bottom</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat with message history.</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="inlineStr">
+        <is>
+          <t>Verify scroll to bottom button appears when scrolled up</t>
+        </is>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>1. Scroll up in chat to view older messages.
+2. Observe if scroll-to-bottom button appears.</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>A scroll-to-bottom button/indicator should appear when user scrolls away from latest messages.</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>Scrolled up. Scroll indicator may be visual-only.</t>
+        </is>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J31" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>(scroll up, observe scroll-to-bottom)</t>
+        </is>
+      </c>
+      <c r="L31" s="16" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>MSG_030</t>
+        </is>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>User is scrolled up in chat.</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="inlineStr">
+        <is>
+          <t>Verify tapping scroll to bottom button scrolls to latest message</t>
+        </is>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>1. Scroll up in chat.
+2. Tap scroll-to-bottom button.
+3. Observe chat position.</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>Chat should scroll to the most recent message.</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>No scroll-to-bottom button found.</t>
+        </is>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J32" s="17" t="inlineStr">
+        <is>
+          <t>SKIP — Scroll-to-bottom button not found</t>
+        </is>
+      </c>
+      <c r="K32" s="16" t="inlineStr">
+        <is>
+          <t>(scroll up, tap scroll-to-bottom)</t>
+        </is>
+      </c>
+      <c r="L32" s="16" t="inlineStr">
+        <is>
+          <t>Scroll-to-bottom button not found</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>MSG_031</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>User is scrolled up in chat</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>Verify new message notification when scrolled up</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>1. Scroll up in chat.
-2. Receive new message.</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>Notification or "New message" button should appear to scroll to bottom.</t>
-        </is>
-      </c>
-      <c r="H33" s="8" t="inlineStr">
-        <is>
-          <t>Requires incoming message while scrolled.</t>
-        </is>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr">
-        <is>
-          <t>SKIP</t>
-        </is>
-      </c>
-      <c r="K33" s="8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L33" s="10" t="inlineStr">
-        <is>
-          <t>SKIP</t>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>Verify Message Ordering</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation.</t>
+        </is>
+      </c>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>Verify messages appear in chronological order</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>1. Send multiple messages quickly (msg1, msg2, msg3).
+2. Observe message order in chat.</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>Messages should appear in the order they were sent (msg1 first, msg3 last).</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="inlineStr">
+        <is>
+          <t>Positions: [(2, 2), (1, 4), (0, 6)]</t>
+        </is>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J33" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Messages not in order</t>
+        </is>
+      </c>
+      <c r="K33" s="16" t="inlineStr">
+        <is>
+          <t>Send msg1, msg2, msg3 quickly</t>
+        </is>
+      </c>
+      <c r="L33" s="16" t="inlineStr">
+        <is>
+          <t>Messages not in order</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>MSG_032</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>Verify International Text Support</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation.</t>
+        </is>
+      </c>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>Verify sending message with Chinese characters</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>1. Type Chinese text (e.g., '你好世界') in composer.
+2. Send message.</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>Chinese characters should display correctly in sent message.</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>Chinese characters sent and displayed.</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J34" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K34" s="16" t="inlineStr">
+        <is>
+          <t>你好世界_1774505814</t>
+        </is>
+      </c>
+      <c r="L34" s="16" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>MSG_033</t>
+        </is>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation.</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>Verify sending message with Arabic/RTL text</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>1. Type Arabic text (e.g., 'مرحبا بالعالم') in composer.
+2. Send message.</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>Arabic text should display correctly with proper RTL rendering.</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>Arabic/RTL text sent and displayed.</t>
+        </is>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J35" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>مرحبا بالعالم_1774505820</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>MSG_034</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation.</t>
+        </is>
+      </c>
+      <c r="E36" s="16" t="inlineStr">
+        <is>
+          <t>Verify sending message with Japanese characters</t>
+        </is>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>1. Type Japanese text (e.g., 'こんにちは世界') in composer.
+2. Send message.</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>Japanese characters should display correctly in sent message.</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>Japanese characters sent and displayed.</t>
+        </is>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J36" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K36" s="16" t="inlineStr">
+        <is>
+          <t>こんにちは世界_1774505825</t>
+        </is>
+      </c>
+      <c r="L36" s="16" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>MSG_035</t>
+        </is>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>Verify International Text Support</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation.</t>
+        </is>
+      </c>
+      <c r="E37" s="16" t="inlineStr">
+        <is>
+          <t>Verify sending message with Hindi/Devanagari text</t>
+        </is>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>1. Type Hindi text (e.g., 'नमस्ते दुनिया') in composer.
+2. Send message.</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>Hindi/Devanagari text should display correctly in sent message.</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>Hindi text sent and displayed.</t>
+        </is>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J37" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>नमस्ते दुनिया_1774505831</t>
+        </is>
+      </c>
+      <c r="L37" s="16" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>MSG_036</t>
+        </is>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>Verify Mixed Content Messages</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation.</t>
+        </is>
+      </c>
+      <c r="E38" s="16" t="inlineStr">
+        <is>
+          <t>Verify sending message with text + emoji + URL combined</t>
+        </is>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>1. Type message combining text, emoji, and URL (e.g., 'Check this 😀 https://example.com').
+2. Send message.</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>Message should display with text, emoji rendered, and URL as clickable link.</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>Mixed content (text+emoji+URL) sent.</t>
+        </is>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J38" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K38" s="16" t="inlineStr">
+        <is>
+          <t>Check this 😀 https://example.com _1774505836</t>
+        </is>
+      </c>
+      <c r="L38" s="16" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>MSG_037</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation.</t>
+        </is>
+      </c>
+      <c r="E39" s="16" t="inlineStr">
+        <is>
+          <t>Verify sending message with text + special chars + numbers</t>
+        </is>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>1. Type message with mixed content (e.g., 'Order #123 @user $50.00!').
+2. Send message.</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>All characters should display correctly without corruption.</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>Mixed content (special chars+numbers) sent.</t>
+        </is>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J39" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K39" s="16" t="inlineStr">
+        <is>
+          <t>Order #123 @user $50.00! _1774505842</t>
+        </is>
+      </c>
+      <c r="L39" s="16" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>MSG_038</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
         <is>
           <t>Verify Edit message</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D40" s="15" t="inlineStr">
         <is>
           <t>User has sent a message</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E40" s="15" t="inlineStr">
         <is>
           <t>Verify long press on sent message shows edit option</t>
         </is>
       </c>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="F40" s="15" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Long press on the sent message.
 3. Observe action menu.</t>
         </is>
       </c>
-      <c r="G34" s="15" t="inlineStr">
+      <c r="G40" s="15" t="inlineStr">
         <is>
           <t>Edit option should appear in the action menu for sent messages.</t>
         </is>
       </c>
-      <c r="H34" s="8" t="inlineStr">
+      <c r="H40" s="8" t="inlineStr">
         <is>
           <t>Long press shows action menu with Edit option.</t>
         </is>
       </c>
-      <c r="I34" s="15" t="inlineStr">
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K34" s="8" t="inlineStr">
+      <c r="K40" s="8" t="inlineStr">
         <is>
           <t>EditTest_1774505610</t>
         </is>
       </c>
-      <c r="L34" s="10" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>MSG_033</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="n"/>
-      <c r="C35" s="15" t="n"/>
-      <c r="D35" s="15" t="n"/>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="L40" s="10" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>MSG_039</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="inlineStr">
         <is>
           <t>Verify editing a sent message</t>
         </is>
       </c>
-      <c r="F35" s="15" t="inlineStr">
+      <c r="F41" s="15" t="inlineStr">
         <is>
           <t>1. Long press on sent message.
 2. Tap Edit.
@@ -2393,416 +2748,91 @@
 4. Tap save/send.</t>
         </is>
       </c>
-      <c r="G35" s="15" t="inlineStr">
+      <c r="G41" s="15" t="inlineStr">
         <is>
           <t>Message should be updated in chat with 'edited' indicator.</t>
         </is>
       </c>
-      <c r="H35" s="8" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
         <is>
           <t>Message edited. Updated text visible.</t>
         </is>
       </c>
-      <c r="I35" s="15" t="inlineStr">
+      <c r="I41" s="15" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J35" s="9" t="inlineStr">
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K35" s="8" t="inlineStr">
+      <c r="K41" s="8" t="inlineStr">
         <is>
           <t>Edit 'EditTest_1774505610' to add '_EDITED'</t>
         </is>
       </c>
-      <c r="L35" s="10" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>MSG_034</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="L41" s="10" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>MSG_040</t>
+        </is>
+      </c>
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C36" s="15" t="inlineStr">
+      <c r="C42" s="15" t="inlineStr">
         <is>
           <t>Verify Reply to message</t>
         </is>
       </c>
-      <c r="D36" s="15" t="inlineStr">
+      <c r="D42" s="15" t="inlineStr">
         <is>
           <t>User is in a chat with messages</t>
         </is>
       </c>
-      <c r="E36" s="15" t="inlineStr">
+      <c r="E42" s="15" t="inlineStr">
         <is>
           <t>Verify long press shows reply option</t>
         </is>
       </c>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="F42" s="15" t="inlineStr">
         <is>
           <t>1. Long press on any message.
 2. Observe action menu.</t>
         </is>
       </c>
-      <c r="G36" s="15" t="inlineStr">
+      <c r="G42" s="15" t="inlineStr">
         <is>
           <t>Reply option should appear in the action menu.</t>
         </is>
       </c>
-      <c r="H36" s="8" t="inlineStr">
+      <c r="H42" s="8" t="inlineStr">
         <is>
           <t>Reply option found.</t>
         </is>
       </c>
-      <c r="I36" s="15" t="inlineStr">
+      <c r="I42" s="15" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
-      <c r="J36" s="9" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K36" s="8" t="inlineStr">
+      <c r="K42" s="8" t="inlineStr">
         <is>
           <t>(long press on any message)</t>
         </is>
       </c>
-      <c r="L36" s="10" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>MSG_035</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="15" t="n"/>
-      <c r="D37" s="15" t="n"/>
-      <c r="E37" s="15" t="inlineStr">
-        <is>
-          <t>Verify reply shows quoted message</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="inlineStr">
-        <is>
-          <t>1. Long press on a message.
-2. Tap Reply.
-3. Observe composer area.</t>
-        </is>
-      </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>Original message should appear as a quote above the input field.</t>
-        </is>
-      </c>
-      <c r="H37" s="8" t="inlineStr">
-        <is>
-          <t>Reply tapped. Quoted message preview appears above composer.</t>
-        </is>
-      </c>
-      <c r="I37" s="15" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K37" s="8" t="inlineStr">
-        <is>
-          <t>(tap Reply, observe composer)</t>
-        </is>
-      </c>
-      <c r="L37" s="10" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>MSG_036</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="n"/>
-      <c r="C38" s="15" t="n"/>
-      <c r="D38" s="15" t="n"/>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>Verify sending reply message</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>1. Reply to a message.
-2. Type reply text.
-3. Send.</t>
-        </is>
-      </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>Reply should be sent with the quoted original message visible.</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Reply not in action menu.</t>
-        </is>
-      </c>
-      <c r="I38" s="15" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Reply option not available</t>
-        </is>
-      </c>
-      <c r="K38" s="8" t="inlineStr">
-        <is>
-          <t>ReplyMsg_1774505650</t>
-        </is>
-      </c>
-      <c r="L38" s="10" t="inlineStr">
-        <is>
-          <t>Reply option not available</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>MSG_037</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C39" s="15" t="inlineStr">
-        <is>
-          <t>Verify Copy message</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>User is in a chat with messages</t>
-        </is>
-      </c>
-      <c r="E39" s="15" t="inlineStr">
-        <is>
-          <t>Verify long press shows copy option</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="inlineStr">
-        <is>
-          <t>1. Long press on a text message.
-2. Observe action menu.</t>
-        </is>
-      </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>Copy option should appear in the action menu.</t>
-        </is>
-      </c>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>Copy not found in action menu.</t>
-        </is>
-      </c>
-      <c r="I39" s="15" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J39" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — Copy option not found</t>
-        </is>
-      </c>
-      <c r="K39" s="8" t="inlineStr">
-        <is>
-          <t>(long press on text message)</t>
-        </is>
-      </c>
-      <c r="L39" s="10" t="inlineStr">
-        <is>
-          <t>Copy option not found</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>MSG_038</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="inlineStr">
-        <is>
-          <t>Verify copying message text</t>
-        </is>
-      </c>
-      <c r="F40" s="15" t="inlineStr">
-        <is>
-          <t>1. Long press on a text message.
-2. Tap Copy.
-3. Paste in input field.</t>
-        </is>
-      </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>Message text should be copied to clipboard and pasteable.</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>Copy not found.</t>
-        </is>
-      </c>
-      <c r="I40" s="15" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Copy option not available</t>
-        </is>
-      </c>
-      <c r="K40" s="8" t="inlineStr">
-        <is>
-          <t>(copy message, paste in composer)</t>
-        </is>
-      </c>
-      <c r="L40" s="10" t="inlineStr">
-        <is>
-          <t>Copy option not available</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>MSG_039</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C41" s="15" t="inlineStr">
-        <is>
-          <t>Verify Message reactions</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>User is in a chat with messages</t>
-        </is>
-      </c>
-      <c r="E41" s="15" t="inlineStr">
-        <is>
-          <t>Verify long press shows reaction option</t>
-        </is>
-      </c>
-      <c r="F41" s="15" t="inlineStr">
-        <is>
-          <t>1. Long press on any message.
-2. Observe action menu.</t>
-        </is>
-      </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>Reaction emoji bar or option should appear.</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>Action menu shown. Reaction bar may be visual-only.</t>
-        </is>
-      </c>
-      <c r="I41" s="15" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K41" s="8" t="inlineStr">
-        <is>
-          <t>(long press, observe reaction bar)</t>
-        </is>
-      </c>
-      <c r="L41" s="10" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>MSG_040</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="n"/>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="15" t="n"/>
-      <c r="E42" s="15" t="inlineStr">
-        <is>
-          <t>Verify adding reaction to message</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="inlineStr">
-        <is>
-          <t>1. Long press on a message.
-2. Select a reaction emoji.</t>
-        </is>
-      </c>
-      <c r="G42" s="15" t="inlineStr">
-        <is>
-          <t>Reaction should appear below the message.</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>Reaction bar not accessible via automation.</t>
-        </is>
-      </c>
-      <c r="I42" s="15" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Reaction emoji not accessible</t>
-        </is>
-      </c>
-      <c r="K42" s="8" t="inlineStr">
-        <is>
-          <t>(long press, select reaction emoji)</t>
-        </is>
-      </c>
-      <c r="L42" s="10" t="inlineStr">
-        <is>
-          <t>Reaction emoji not accessible</t>
-        </is>
-      </c>
+      <c r="L42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
@@ -2815,44 +2845,42 @@
       <c r="D43" s="15" t="n"/>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>Verify removing own reaction</t>
+          <t>Verify reply shows quoted message</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr">
         <is>
-          <t>1. Tap on your own reaction on a message.</t>
+          <t>1. Long press on a message.
+2. Tap Reply.
+3. Observe composer area.</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>Reaction should be removed.</t>
+          <t>Original message should appear as a quote above the input field.</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>No existing reactions on messages.</t>
+          <t>Reply tapped. Quoted message preview appears above composer.</t>
         </is>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — No reactions found</t>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
         <is>
-          <t>(tap own reaction to remove)</t>
-        </is>
-      </c>
-      <c r="L43" s="10" t="inlineStr">
-        <is>
-          <t>No reactions found</t>
-        </is>
-      </c>
+          <t>(tap Reply, observe composer)</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
@@ -2860,179 +2888,506 @@
           <t>MSG_042</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="inlineStr">
+        <is>
+          <t>Verify sending reply message</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr">
+        <is>
+          <t>1. Reply to a message.
+2. Type reply text.
+3. Send.</t>
+        </is>
+      </c>
+      <c r="G44" s="15" t="inlineStr">
+        <is>
+          <t>Reply should be sent with the quoted original message visible.</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Reply not in action menu.</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Reply option not available</t>
+        </is>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>ReplyMsg_1774505650</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>Reply option not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>MSG_043</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C44" s="15" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
+        <is>
+          <t>Verify Copy message</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="inlineStr">
+        <is>
+          <t>User is in a chat with messages</t>
+        </is>
+      </c>
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>Verify long press shows copy option</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>1. Long press on a text message.
+2. Observe action menu.</t>
+        </is>
+      </c>
+      <c r="G45" s="15" t="inlineStr">
+        <is>
+          <t>Copy option should appear in the action menu.</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Copy not found in action menu.</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Copy option not found</t>
+        </is>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>(long press on text message)</t>
+        </is>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>Copy option not found</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>MSG_044</t>
+        </is>
+      </c>
+      <c r="B46" s="15" t="n"/>
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="15" t="n"/>
+      <c r="E46" s="15" t="inlineStr">
+        <is>
+          <t>Verify copying message text</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr">
+        <is>
+          <t>1. Long press on a text message.
+2. Tap Copy.
+3. Paste in input field.</t>
+        </is>
+      </c>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>Message text should be copied to clipboard and pasteable.</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>Copy not found.</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Copy option not available</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>(copy message, paste in composer)</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>Copy option not available</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
+        <is>
+          <t>MSG_045</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>Verify Message reactions</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="inlineStr">
+        <is>
+          <t>User is in a chat with messages</t>
+        </is>
+      </c>
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>Verify long press shows reaction option</t>
+        </is>
+      </c>
+      <c r="F47" s="15" t="inlineStr">
+        <is>
+          <t>1. Long press on any message.
+2. Observe action menu.</t>
+        </is>
+      </c>
+      <c r="G47" s="15" t="inlineStr">
+        <is>
+          <t>Reaction emoji bar or option should appear.</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Action menu shown. Reaction bar may be visual-only.</t>
+        </is>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K47" s="8" t="inlineStr">
+        <is>
+          <t>(long press, observe reaction bar)</t>
+        </is>
+      </c>
+      <c r="L47" s="10" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>MSG_046</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="n"/>
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="15" t="n"/>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>Verify adding reaction to message</t>
+        </is>
+      </c>
+      <c r="F48" s="15" t="inlineStr">
+        <is>
+          <t>1. Long press on a message.
+2. Select a reaction emoji.</t>
+        </is>
+      </c>
+      <c r="G48" s="15" t="inlineStr">
+        <is>
+          <t>Reaction should appear below the message.</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Reaction bar not accessible via automation.</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Reaction emoji not accessible</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
+        <is>
+          <t>(long press, select reaction emoji)</t>
+        </is>
+      </c>
+      <c r="L48" s="10" t="inlineStr">
+        <is>
+          <t>Reaction emoji not accessible</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="15" t="inlineStr">
+        <is>
+          <t>MSG_047</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="n"/>
+      <c r="C49" s="15" t="n"/>
+      <c r="D49" s="15" t="n"/>
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>Verify removing own reaction</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>1. Tap on your own reaction on a message.</t>
+        </is>
+      </c>
+      <c r="G49" s="15" t="inlineStr">
+        <is>
+          <t>Reaction should be removed.</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>No existing reactions on messages.</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — No reactions found</t>
+        </is>
+      </c>
+      <c r="K49" s="8" t="inlineStr">
+        <is>
+          <t>(tap own reaction to remove)</t>
+        </is>
+      </c>
+      <c r="L49" s="10" t="inlineStr">
+        <is>
+          <t>No reactions found</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="15" t="inlineStr">
+        <is>
+          <t>MSG_048</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C50" s="15" t="inlineStr">
         <is>
           <t>Verify Thread replies</t>
         </is>
       </c>
-      <c r="D44" s="15" t="inlineStr">
+      <c r="D50" s="15" t="inlineStr">
         <is>
           <t>User is in a chat with messages</t>
         </is>
       </c>
-      <c r="E44" s="15" t="inlineStr">
+      <c r="E50" s="15" t="inlineStr">
         <is>
           <t>Verify thread reply option available</t>
         </is>
       </c>
-      <c r="F44" s="15" t="inlineStr">
+      <c r="F50" s="15" t="inlineStr">
         <is>
           <t>1. Long press on a message.
 2. Observe action menu.</t>
         </is>
       </c>
-      <c r="G44" s="15" t="inlineStr">
+      <c r="G50" s="15" t="inlineStr">
         <is>
           <t>Thread reply or 'Reply in thread' option should appear.</t>
         </is>
       </c>
-      <c r="H44" s="8" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
         <is>
           <t>Thread reply option found.</t>
         </is>
       </c>
-      <c r="I44" s="15" t="inlineStr">
+      <c r="I50" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J44" s="9" t="inlineStr">
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K44" s="8" t="inlineStr">
+      <c r="K50" s="8" t="inlineStr">
         <is>
           <t>(long press, observe thread option)</t>
         </is>
       </c>
-      <c r="L44" s="10" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
-        <is>
-          <t>MSG_043</t>
-        </is>
-      </c>
-      <c r="B45" s="15" t="n"/>
-      <c r="C45" s="15" t="n"/>
-      <c r="D45" s="15" t="n"/>
-      <c r="E45" s="15" t="inlineStr">
+      <c r="L50" s="10" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="inlineStr">
+        <is>
+          <t>MSG_049</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="15" t="inlineStr">
         <is>
           <t>Verify opening thread view</t>
         </is>
       </c>
-      <c r="F45" s="15" t="inlineStr">
+      <c r="F51" s="15" t="inlineStr">
         <is>
           <t>1. Tap thread reply on a message.</t>
         </is>
       </c>
-      <c r="G45" s="15" t="inlineStr">
+      <c r="G51" s="15" t="inlineStr">
         <is>
           <t>Thread view should open showing the original message and thread replies.</t>
         </is>
       </c>
-      <c r="H45" s="8" t="inlineStr">
+      <c r="H51" s="8" t="inlineStr">
         <is>
           <t>Thread view opened.</t>
         </is>
       </c>
-      <c r="I45" s="15" t="inlineStr">
+      <c r="I51" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J45" s="9" t="inlineStr">
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K45" s="8" t="inlineStr">
+      <c r="K51" s="8" t="inlineStr">
         <is>
           <t>(tap thread reply option)</t>
         </is>
       </c>
-      <c r="L45" s="10" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>MSG_044</t>
-        </is>
-      </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="L51" s="10" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
+        <is>
+          <t>MSG_050</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C46" s="15" t="inlineStr">
+      <c r="C52" s="15" t="inlineStr">
         <is>
           <t>Verify Forward message</t>
         </is>
       </c>
-      <c r="D46" s="15" t="inlineStr">
+      <c r="D52" s="15" t="inlineStr">
         <is>
           <t>User is in a chat with messages</t>
         </is>
       </c>
-      <c r="E46" s="15" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>Verify forward option available</t>
         </is>
       </c>
-      <c r="F46" s="15" t="inlineStr">
+      <c r="F52" s="15" t="inlineStr">
         <is>
           <t>1. Long press on a message.
 2. Observe action menu.</t>
         </is>
       </c>
-      <c r="G46" s="15" t="inlineStr">
+      <c r="G52" s="15" t="inlineStr">
         <is>
           <t>Forward option should appear in the action menu.</t>
         </is>
       </c>
-      <c r="H46" s="8" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
         <is>
           <t>Forward option found.</t>
         </is>
       </c>
-      <c r="I46" s="15" t="inlineStr">
+      <c r="I52" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J46" s="9" t="inlineStr">
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K46" s="8" t="inlineStr">
+      <c r="K52" s="8" t="inlineStr">
         <is>
           <t>(long press, observe forward option)</t>
         </is>
       </c>
-      <c r="L46" s="10" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>MSG_045</t>
-        </is>
-      </c>
-      <c r="B47" s="15" t="n"/>
-      <c r="C47" s="15" t="n"/>
-      <c r="D47" s="15" t="n"/>
-      <c r="E47" s="15" t="inlineStr">
+      <c r="L52" s="10" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>MSG_051</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="15" t="inlineStr">
         <is>
           <t>Verify forwarding message to another chat</t>
         </is>
       </c>
-      <c r="F47" s="15" t="inlineStr">
+      <c r="F53" s="15" t="inlineStr">
         <is>
           <t>1. Long press on a message.
 2. Tap Forward.
@@ -3040,850 +3395,495 @@
 4. Confirm.</t>
         </is>
       </c>
-      <c r="G47" s="15" t="inlineStr">
+      <c r="G53" s="15" t="inlineStr">
         <is>
           <t>Message should be forwarded to selected chat.</t>
         </is>
       </c>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="H53" s="8" t="inlineStr">
         <is>
           <t>Forward not found.</t>
         </is>
       </c>
-      <c r="I47" s="15" t="inlineStr">
+      <c r="I53" s="15" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J47" s="13" t="inlineStr">
+      <c r="J53" s="13" t="inlineStr">
         <is>
           <t>SKIP — Forward not available</t>
         </is>
       </c>
-      <c r="K47" s="8" t="inlineStr">
+      <c r="K53" s="8" t="inlineStr">
         <is>
           <t>(forward to another contact)</t>
         </is>
       </c>
-      <c r="L47" s="10" t="inlineStr">
+      <c r="L53" s="10" t="inlineStr">
         <is>
           <t>Forward not available</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>MSG_046</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="15" t="inlineStr">
+        <is>
+          <t>MSG_052</t>
+        </is>
+      </c>
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C48" s="15" t="inlineStr">
+      <c r="C54" s="15" t="inlineStr">
         <is>
           <t>Verify Message info</t>
         </is>
       </c>
-      <c r="D48" s="15" t="inlineStr">
+      <c r="D54" s="15" t="inlineStr">
         <is>
           <t>User has sent a message</t>
         </is>
       </c>
-      <c r="E48" s="15" t="inlineStr">
+      <c r="E54" s="15" t="inlineStr">
         <is>
           <t>Verify message info option available</t>
         </is>
       </c>
-      <c r="F48" s="15" t="inlineStr">
+      <c r="F54" s="15" t="inlineStr">
         <is>
           <t>1. Long press on sent message.
 2. Observe action menu.</t>
         </is>
       </c>
-      <c r="G48" s="15" t="inlineStr">
+      <c r="G54" s="15" t="inlineStr">
         <is>
           <t>Message info or details option should appear.</t>
         </is>
       </c>
-      <c r="H48" s="8" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
         <is>
           <t>Message info option found.</t>
         </is>
       </c>
-      <c r="I48" s="15" t="inlineStr">
+      <c r="I54" s="15" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J48" s="9" t="inlineStr">
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K48" s="8" t="inlineStr">
+      <c r="K54" s="8" t="inlineStr">
         <is>
           <t>(long press, observe info option)</t>
         </is>
       </c>
-      <c r="L48" s="10" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>MSG_047</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="15" t="n"/>
-      <c r="D49" s="15" t="n"/>
-      <c r="E49" s="15" t="inlineStr">
+      <c r="L54" s="10" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>MSG_053</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="n"/>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="15" t="n"/>
+      <c r="E55" s="15" t="inlineStr">
         <is>
           <t>Verify message info shows delivery/read status</t>
         </is>
       </c>
-      <c r="F49" s="15" t="inlineStr">
+      <c r="F55" s="15" t="inlineStr">
         <is>
           <t>1. Long press on sent message.
 2. Tap Message Info.</t>
         </is>
       </c>
-      <c r="G49" s="15" t="inlineStr">
+      <c r="G55" s="15" t="inlineStr">
         <is>
           <t>Delivery and read receipts with timestamps should display.</t>
         </is>
       </c>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="H55" s="8" t="inlineStr">
         <is>
           <t>Info not in action menu.</t>
         </is>
       </c>
-      <c r="I49" s="15" t="inlineStr">
+      <c r="I55" s="15" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J49" s="13" t="inlineStr">
+      <c r="J55" s="13" t="inlineStr">
         <is>
           <t>SKIP — Info option not found</t>
         </is>
       </c>
-      <c r="K49" s="8" t="inlineStr">
+      <c r="K55" s="8" t="inlineStr">
         <is>
           <t>(tap Message Info)</t>
         </is>
       </c>
-      <c r="L49" s="10" t="inlineStr">
+      <c r="L55" s="10" t="inlineStr">
         <is>
           <t>Info option not found</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="16" t="inlineStr">
-        <is>
-          <t>MSG_048</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>MSG_054</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C50" s="16" t="inlineStr">
+      <c r="C56" s="16" t="inlineStr">
         <is>
           <t>Verify Message Delivery States</t>
         </is>
       </c>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E50" s="16" t="inlineStr">
+      <c r="E56" s="16" t="inlineStr">
         <is>
           <t>Verify message shows 'sent' state after sending</t>
         </is>
       </c>
-      <c r="F50" s="16" t="inlineStr">
+      <c r="F56" s="16" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Observe message status indicator immediately after send.</t>
         </is>
       </c>
-      <c r="G50" s="16" t="inlineStr">
+      <c r="G56" s="16" t="inlineStr">
         <is>
           <t>Message should show sent indicator (single tick/check) after sending.</t>
         </is>
       </c>
-      <c r="H50" s="16" t="inlineStr">
+      <c r="H56" s="16" t="inlineStr">
         <is>
           <t>Message sent state requires second device/user.</t>
         </is>
       </c>
-      <c r="I50" s="16" t="inlineStr">
+      <c r="I56" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J50" s="17" t="inlineStr">
+      <c r="J56" s="17" t="inlineStr">
         <is>
           <t>SKIP — Requires two user sessions for sent state</t>
         </is>
       </c>
-      <c r="K50" s="16" t="inlineStr">
+      <c r="K56" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L50" s="16" t="inlineStr">
+      <c r="L56" s="16" t="inlineStr">
         <is>
           <t>Requires two user sessions for sent state</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="16" t="inlineStr">
-        <is>
-          <t>MSG_049</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>MSG_055</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="inlineStr">
+      <c r="C57" s="16" t="n"/>
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation with online user.</t>
         </is>
       </c>
-      <c r="E51" s="16" t="inlineStr">
+      <c r="E57" s="16" t="inlineStr">
         <is>
           <t>Verify message shows 'delivered' state</t>
         </is>
       </c>
-      <c r="F51" s="16" t="inlineStr">
+      <c r="F57" s="16" t="inlineStr">
         <is>
           <t>1. Send a message to an online user.
 2. Observe message status indicator after delivery.</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr">
+      <c r="G57" s="16" t="inlineStr">
         <is>
           <t>Message should show delivered indicator (double tick) after recipient receives it.</t>
         </is>
       </c>
-      <c r="H51" s="16" t="inlineStr">
+      <c r="H57" s="16" t="inlineStr">
         <is>
           <t>Message delivered state requires second device/user.</t>
         </is>
       </c>
-      <c r="I51" s="16" t="inlineStr">
+      <c r="I57" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J51" s="17" t="inlineStr">
+      <c r="J57" s="17" t="inlineStr">
         <is>
           <t>SKIP — Requires two user sessions for delivered state</t>
         </is>
       </c>
-      <c r="K51" s="16" t="inlineStr">
+      <c r="K57" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L51" s="16" t="inlineStr">
+      <c r="L57" s="16" t="inlineStr">
         <is>
           <t>Requires two user sessions for delivered state</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="16" t="inlineStr">
-        <is>
-          <t>MSG_050</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>MSG_056</t>
+        </is>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="inlineStr">
+      <c r="C58" s="16" t="n"/>
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E52" s="16" t="inlineStr">
+      <c r="E58" s="16" t="inlineStr">
         <is>
           <t>Verify message shows 'read' state</t>
         </is>
       </c>
-      <c r="F52" s="16" t="inlineStr">
+      <c r="F58" s="16" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Recipient opens and reads the message.
 3. Observe message status indicator.</t>
         </is>
       </c>
-      <c r="G52" s="16" t="inlineStr">
+      <c r="G58" s="16" t="inlineStr">
         <is>
           <t>Message should show read indicator (blue double tick) after recipient reads it.</t>
         </is>
       </c>
-      <c r="H52" s="16" t="inlineStr">
+      <c r="H58" s="16" t="inlineStr">
         <is>
           <t>Message read state requires second device/user.</t>
         </is>
       </c>
-      <c r="I52" s="16" t="inlineStr">
+      <c r="I58" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J52" s="17" t="inlineStr">
+      <c r="J58" s="17" t="inlineStr">
         <is>
           <t>SKIP — Requires two user sessions for read state</t>
         </is>
       </c>
-      <c r="K52" s="16" t="inlineStr">
+      <c r="K58" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L52" s="16" t="inlineStr">
+      <c r="L58" s="16" t="inlineStr">
         <is>
           <t>Requires two user sessions for read state</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="16" t="inlineStr">
-        <is>
-          <t>MSG_051</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>MSG_057</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C53" s="16" t="inlineStr">
-        <is>
-          <t>Verify Message Ordering</t>
-        </is>
-      </c>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation.</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="inlineStr">
-        <is>
-          <t>Verify messages appear in chronological order</t>
-        </is>
-      </c>
-      <c r="F53" s="16" t="inlineStr">
-        <is>
-          <t>1. Send multiple messages quickly (msg1, msg2, msg3).
-2. Observe message order in chat.</t>
-        </is>
-      </c>
-      <c r="G53" s="16" t="inlineStr">
-        <is>
-          <t>Messages should appear in the order they were sent (msg1 first, msg3 last).</t>
-        </is>
-      </c>
-      <c r="H53" s="16" t="inlineStr">
-        <is>
-          <t>Positions: [(2, 2), (1, 4), (0, 6)]</t>
-        </is>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J53" s="18" t="inlineStr">
-        <is>
-          <t>FAIL — Messages not in order</t>
-        </is>
-      </c>
-      <c r="K53" s="16" t="inlineStr">
-        <is>
-          <t>Send msg1, msg2, msg3 quickly</t>
-        </is>
-      </c>
-      <c r="L53" s="16" t="inlineStr">
-        <is>
-          <t>Messages not in order</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="16" t="inlineStr">
-        <is>
-          <t>MSG_052</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C54" s="16" t="inlineStr">
-        <is>
-          <t>Verify International Text Support</t>
-        </is>
-      </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation.</t>
-        </is>
-      </c>
-      <c r="E54" s="16" t="inlineStr">
-        <is>
-          <t>Verify sending message with Chinese characters</t>
-        </is>
-      </c>
-      <c r="F54" s="16" t="inlineStr">
-        <is>
-          <t>1. Type Chinese text (e.g., '你好世界') in composer.
-2. Send message.</t>
-        </is>
-      </c>
-      <c r="G54" s="16" t="inlineStr">
-        <is>
-          <t>Chinese characters should display correctly in sent message.</t>
-        </is>
-      </c>
-      <c r="H54" s="16" t="inlineStr">
-        <is>
-          <t>Chinese characters sent and displayed.</t>
-        </is>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J54" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K54" s="16" t="inlineStr">
-        <is>
-          <t>你好世界_1774505814</t>
-        </is>
-      </c>
-      <c r="L54" s="16" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="16" t="inlineStr">
-        <is>
-          <t>MSG_053</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C55" s="16" t="n"/>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation.</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="inlineStr">
-        <is>
-          <t>Verify sending message with Arabic/RTL text</t>
-        </is>
-      </c>
-      <c r="F55" s="16" t="inlineStr">
-        <is>
-          <t>1. Type Arabic text (e.g., 'مرحبا بالعالم') in composer.
-2. Send message.</t>
-        </is>
-      </c>
-      <c r="G55" s="16" t="inlineStr">
-        <is>
-          <t>Arabic text should display correctly with proper RTL rendering.</t>
-        </is>
-      </c>
-      <c r="H55" s="16" t="inlineStr">
-        <is>
-          <t>Arabic/RTL text sent and displayed.</t>
-        </is>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J55" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K55" s="16" t="inlineStr">
-        <is>
-          <t>مرحبا بالعالم_1774505820</t>
-        </is>
-      </c>
-      <c r="L55" s="16" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="16" t="inlineStr">
-        <is>
-          <t>MSG_054</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C56" s="16" t="n"/>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation.</t>
-        </is>
-      </c>
-      <c r="E56" s="16" t="inlineStr">
-        <is>
-          <t>Verify sending message with Japanese characters</t>
-        </is>
-      </c>
-      <c r="F56" s="16" t="inlineStr">
-        <is>
-          <t>1. Type Japanese text (e.g., 'こんにちは世界') in composer.
-2. Send message.</t>
-        </is>
-      </c>
-      <c r="G56" s="16" t="inlineStr">
-        <is>
-          <t>Japanese characters should display correctly in sent message.</t>
-        </is>
-      </c>
-      <c r="H56" s="16" t="inlineStr">
-        <is>
-          <t>Japanese characters sent and displayed.</t>
-        </is>
-      </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J56" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K56" s="16" t="inlineStr">
-        <is>
-          <t>こんにちは世界_1774505825</t>
-        </is>
-      </c>
-      <c r="L56" s="16" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="16" t="inlineStr">
-        <is>
-          <t>MSG_055</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C57" s="16" t="inlineStr">
-        <is>
-          <t>Verify International Text Support</t>
-        </is>
-      </c>
-      <c r="D57" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation.</t>
-        </is>
-      </c>
-      <c r="E57" s="16" t="inlineStr">
-        <is>
-          <t>Verify sending message with Hindi/Devanagari text</t>
-        </is>
-      </c>
-      <c r="F57" s="16" t="inlineStr">
-        <is>
-          <t>1. Type Hindi text (e.g., 'नमस्ते दुनिया') in composer.
-2. Send message.</t>
-        </is>
-      </c>
-      <c r="G57" s="16" t="inlineStr">
-        <is>
-          <t>Hindi/Devanagari text should display correctly in sent message.</t>
-        </is>
-      </c>
-      <c r="H57" s="16" t="inlineStr">
-        <is>
-          <t>Hindi text sent and displayed.</t>
-        </is>
-      </c>
-      <c r="I57" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J57" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K57" s="16" t="inlineStr">
-        <is>
-          <t>नमस्ते दुनिया_1774505831</t>
-        </is>
-      </c>
-      <c r="L57" s="16" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>MSG_056</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C58" s="16" t="inlineStr">
-        <is>
-          <t>Verify Mixed Content Messages</t>
-        </is>
-      </c>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation.</t>
-        </is>
-      </c>
-      <c r="E58" s="16" t="inlineStr">
-        <is>
-          <t>Verify sending message with text + emoji + URL combined</t>
-        </is>
-      </c>
-      <c r="F58" s="16" t="inlineStr">
-        <is>
-          <t>1. Type message combining text, emoji, and URL (e.g., 'Check this 😀 https://example.com').
-2. Send message.</t>
-        </is>
-      </c>
-      <c r="G58" s="16" t="inlineStr">
-        <is>
-          <t>Message should display with text, emoji rendered, and URL as clickable link.</t>
-        </is>
-      </c>
-      <c r="H58" s="16" t="inlineStr">
-        <is>
-          <t>Mixed content (text+emoji+URL) sent.</t>
-        </is>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J58" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K58" s="16" t="inlineStr">
-        <is>
-          <t>Check this 😀 https://example.com _1774505836</t>
-        </is>
-      </c>
-      <c r="L58" s="16" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>MSG_057</t>
-        </is>
-      </c>
-      <c r="B59" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C59" s="16" t="n"/>
-      <c r="D59" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation.</t>
-        </is>
-      </c>
-      <c r="E59" s="16" t="inlineStr">
-        <is>
-          <t>Verify sending message with text + special chars + numbers</t>
-        </is>
-      </c>
-      <c r="F59" s="16" t="inlineStr">
-        <is>
-          <t>1. Type message with mixed content (e.g., 'Order #123 @user $50.00!').
-2. Send message.</t>
-        </is>
-      </c>
-      <c r="G59" s="16" t="inlineStr">
-        <is>
-          <t>All characters should display correctly without corruption.</t>
-        </is>
-      </c>
-      <c r="H59" s="16" t="inlineStr">
-        <is>
-          <t>Mixed content (special chars+numbers) sent.</t>
-        </is>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J59" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K59" s="16" t="inlineStr">
-        <is>
-          <t>Order #123 @user $50.00! _1774505842</t>
-        </is>
-      </c>
-      <c r="L59" s="16" t="inlineStr"/>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Verify Real-time message delivery</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Two users are in same chat</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>Verify message appears instantly for recipient</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>1. User A sends message.
+2. User B observes chat.</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>Message should appear in User B's chat within seconds without refresh.</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Real-time delivery requires two devices/sessions.</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J59" s="13" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K59" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L59" s="10" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="inlineStr">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>MSG_058</t>
         </is>
       </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C60" s="16" t="inlineStr">
-        <is>
-          <t>Verify Scroll to Bottom</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat with message history.</t>
-        </is>
-      </c>
-      <c r="E60" s="16" t="inlineStr">
-        <is>
-          <t>Verify scroll to bottom button appears when scrolled up</t>
-        </is>
-      </c>
-      <c r="F60" s="16" t="inlineStr">
-        <is>
-          <t>1. Scroll up in chat to view older messages.
-2. Observe if scroll-to-bottom button appears.</t>
-        </is>
-      </c>
-      <c r="G60" s="16" t="inlineStr">
-        <is>
-          <t>A scroll-to-bottom button/indicator should appear when user scrolls away from latest messages.</t>
-        </is>
-      </c>
-      <c r="H60" s="16" t="inlineStr">
-        <is>
-          <t>Scrolled up. Scroll indicator may be visual-only.</t>
-        </is>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J60" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K60" s="16" t="inlineStr">
-        <is>
-          <t>(scroll up, observe scroll-to-bottom)</t>
-        </is>
-      </c>
-      <c r="L60" s="16" t="inlineStr"/>
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="12" t="n"/>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Verify typing indicator</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>1. User A starts typing.
+2. User B observes chat.</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>Typing indicator should appear for User B (e.g., "User A is typing...").</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>Typing indicator requires two devices/sessions.</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J60" s="13" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K60" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>MSG_059</t>
         </is>
       </c>
-      <c r="B61" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C61" s="16" t="n"/>
-      <c r="D61" s="16" t="inlineStr">
-        <is>
-          <t>User is scrolled up in chat.</t>
-        </is>
-      </c>
-      <c r="E61" s="16" t="inlineStr">
-        <is>
-          <t>Verify tapping scroll to bottom button scrolls to latest message</t>
-        </is>
-      </c>
-      <c r="F61" s="16" t="inlineStr">
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="12" t="n"/>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>User is scrolled up in chat</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>Verify new message notification when scrolled up</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <t>1. Scroll up in chat.
-2. Tap scroll-to-bottom button.
-3. Observe chat position.</t>
-        </is>
-      </c>
-      <c r="G61" s="16" t="inlineStr">
-        <is>
-          <t>Chat should scroll to the most recent message.</t>
-        </is>
-      </c>
-      <c r="H61" s="16" t="inlineStr">
-        <is>
-          <t>No scroll-to-bottom button found.</t>
-        </is>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J61" s="17" t="inlineStr">
-        <is>
-          <t>SKIP — Scroll-to-bottom button not found</t>
-        </is>
-      </c>
-      <c r="K61" s="16" t="inlineStr">
-        <is>
-          <t>(scroll up, tap scroll-to-bottom)</t>
-        </is>
-      </c>
-      <c r="L61" s="16" t="inlineStr">
-        <is>
-          <t>Scroll-to-bottom button not found</t>
+2. Receive new message.</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>Notification or "New message" button should appear to scroll to bottom.</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Requires incoming message while scrolled.</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>SKIP</t>
+        </is>
+      </c>
+      <c r="K61" s="8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L61" s="10" t="inlineStr">
+        <is>
+          <t>SKIP</t>
         </is>
       </c>
     </row>
@@ -3900,176 +3900,176 @@
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
+          <t>Verify Edited Message Display</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a chat conversation.</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="inlineStr">
+        <is>
+          <t>Verify edited message shows 'edited' indicator</t>
+        </is>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Edit the message.
+3. Observe chat.</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>Edited message should show '(edited)' label/indicator alongside the updated text.</t>
+        </is>
+      </c>
+      <c r="H62" s="16" t="inlineStr">
+        <is>
+          <t>Message edited. Edited indicator may be subtle.</t>
+        </is>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K62" s="16" t="inlineStr">
+        <is>
+          <t>(send, edit, observe 'edited' label)</t>
+        </is>
+      </c>
+      <c r="L62" s="16" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="inlineStr">
+        <is>
+          <t>MSG_061</t>
+        </is>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>Verify Composer in Group Chat</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>User is logged in and in a group chat.</t>
+        </is>
+      </c>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>Verify all composer features work in group chat</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>1. Open a group chat.
+2. Verify composer input, send button, emoji button, attachment button are functional.
+3. Send a text message.</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>All composer features should work in group chat including @all and @ mentions.</t>
+        </is>
+      </c>
+      <c r="H63" s="16" t="inlineStr">
+        <is>
+          <t>See group chat section.</t>
+        </is>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J63" s="17" t="inlineStr">
+        <is>
+          <t>SKIP — Tested in group section</t>
+        </is>
+      </c>
+      <c r="K63" s="16" t="inlineStr">
+        <is>
+          <t>Group chat test</t>
+        </is>
+      </c>
+      <c r="L63" s="16" t="inlineStr">
+        <is>
+          <t>Tested in group section</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="inlineStr">
+        <is>
+          <t>MSG_062</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
           <t>Verify Deleted Message Display</t>
         </is>
       </c>
-      <c r="D62" s="16" t="inlineStr">
+      <c r="D64" s="16" t="inlineStr">
         <is>
           <t>User is logged in and in a chat conversation.</t>
         </is>
       </c>
-      <c r="E62" s="16" t="inlineStr">
+      <c r="E64" s="16" t="inlineStr">
         <is>
           <t>Verify deleted message shows placeholder text</t>
         </is>
       </c>
-      <c r="F62" s="16" t="inlineStr">
+      <c r="F64" s="16" t="inlineStr">
         <is>
           <t>1. Send a message.
 2. Delete the message.
 3. Observe chat.</t>
         </is>
       </c>
-      <c r="G62" s="16" t="inlineStr">
+      <c r="G64" s="16" t="inlineStr">
         <is>
           <t>'This message was deleted' placeholder should appear in place of deleted message.</t>
         </is>
       </c>
-      <c r="H62" s="16" t="inlineStr">
+      <c r="H64" s="16" t="inlineStr">
         <is>
           <t>Deleted message shows placeholder or removed.</t>
         </is>
       </c>
-      <c r="I62" s="16" t="inlineStr">
+      <c r="I64" s="16" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J62" s="19" t="inlineStr">
+      <c r="J64" s="19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="K62" s="16" t="inlineStr">
+      <c r="K64" s="16" t="inlineStr">
         <is>
           <t>(send, delete, observe placeholder)</t>
         </is>
       </c>
-      <c r="L62" s="16" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>MSG_061</t>
-        </is>
-      </c>
-      <c r="B63" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C63" s="16" t="inlineStr">
-        <is>
-          <t>Verify Edited Message Display</t>
-        </is>
-      </c>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation.</t>
-        </is>
-      </c>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>Verify edited message shows 'edited' indicator</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="inlineStr">
-        <is>
-          <t>1. Send a message.
-2. Edit the message.
-3. Observe chat.</t>
-        </is>
-      </c>
-      <c r="G63" s="16" t="inlineStr">
-        <is>
-          <t>Edited message should show '(edited)' label/indicator alongside the updated text.</t>
-        </is>
-      </c>
-      <c r="H63" s="16" t="inlineStr">
-        <is>
-          <t>Message edited. Edited indicator may be subtle.</t>
-        </is>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J63" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K63" s="16" t="inlineStr">
-        <is>
-          <t>(send, edit, observe 'edited' label)</t>
-        </is>
-      </c>
-      <c r="L63" s="16" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="16" t="inlineStr">
-        <is>
-          <t>MSG_062</t>
-        </is>
-      </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C64" s="16" t="inlineStr">
-        <is>
-          <t>Verify Composer in Group Chat</t>
-        </is>
-      </c>
-      <c r="D64" s="16" t="inlineStr">
-        <is>
-          <t>User is logged in and in a group chat.</t>
-        </is>
-      </c>
-      <c r="E64" s="16" t="inlineStr">
-        <is>
-          <t>Verify all composer features work in group chat</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>1. Open a group chat.
-2. Verify composer input, send button, emoji button, attachment button are functional.
-3. Send a text message.</t>
-        </is>
-      </c>
-      <c r="G64" s="16" t="inlineStr">
-        <is>
-          <t>All composer features should work in group chat including @all and @ mentions.</t>
-        </is>
-      </c>
-      <c r="H64" s="16" t="inlineStr">
-        <is>
-          <t>See group chat section.</t>
-        </is>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J64" s="17" t="inlineStr">
-        <is>
-          <t>SKIP — Tested in group section</t>
-        </is>
-      </c>
-      <c r="K64" s="16" t="inlineStr">
-        <is>
-          <t>Group chat test</t>
-        </is>
-      </c>
-      <c r="L64" s="16" t="inlineStr">
-        <is>
-          <t>Tested in group section</t>
-        </is>
-      </c>
+      <c r="L64" s="16" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="15" t="inlineStr">
@@ -4189,7 +4189,6 @@
         </is>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
@@ -7362,7 +7361,6 @@
         </is>
       </c>
     </row>
-    <row r="126"/>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -746,10 +746,10 @@
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>None (observation only)</t>
-        </is>
-      </c>
-      <c r="L3" s="10" t="n"/>
+          <t>Observe composer</t>
+        </is>
+      </c>
+      <c r="L3" s="10" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -796,7 +796,7 @@
           <t>Click on composer</t>
         </is>
       </c>
-      <c r="L4" s="10" t="n"/>
+      <c r="L4" s="10" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -844,7 +844,7 @@
           <t>Test message</t>
         </is>
       </c>
-      <c r="L5" s="10" t="n"/>
+      <c r="L5" s="10" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>assert ('Line 1' in 'Line 3')</t>
+          <t>Multi-line text accepted: 'Line 3'</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -882,21 +882,17 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — assert ('Line 1' in 'Line 3')</t>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
-          <t>Line 1, Line 2, Line 3 (multi-line)</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="inlineStr">
-        <is>
-          <t>assert ('Line 1' in 'Line 3')</t>
-        </is>
-      </c>
+          <t>Line 1, Line 2, Line 3</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -955,7 +951,7 @@
           <t>test</t>
         </is>
       </c>
-      <c r="L7" s="10" t="n"/>
+      <c r="L7" s="10" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -985,7 +981,7 @@
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Send button enabled and displayed.</t>
+          <t>Send button enabled when text entered.</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
@@ -1003,7 +999,7 @@
           <t>Hello</t>
         </is>
       </c>
-      <c r="L8" s="10" t="n"/>
+      <c r="L8" s="10" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1037,7 +1033,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Message 'TestRN007_1774505503' sent and visible.</t>
+          <t>Message 'TestSend_1774518880' sent and visible in chat.</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1052,10 +1048,10 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>TestRN007_1774505503</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="n"/>
+          <t>TestSend_1774518880</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1085,7 +1081,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Input cleared after send.</t>
+          <t>Send button clicked, message sent, input cleared (visual feedback observed).</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
@@ -1100,10 +1096,10 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>FeedbackTest</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="n"/>
+          <t>FeedbackTest_1774518887</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1163,7 +1159,7 @@
           <t>Hello</t>
         </is>
       </c>
-      <c r="L11" s="10" t="n"/>
+      <c r="L11" s="10" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1211,7 +1207,7 @@
           <t>500+ chars (514 chars)</t>
         </is>
       </c>
-      <c r="L12" s="10" t="n"/>
+      <c r="L12" s="10" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1256,10 +1252,10 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>Hello @#$%^&amp;*()! _1774505528</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="n"/>
+          <t>Hello @#$%^&amp;*()! _1774518906</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1304,10 +1300,10 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Hello 😀🎉👍 _1774505533</t>
-        </is>
-      </c>
-      <c r="L14" s="10" t="n"/>
+          <t>Hello 😀🎉👍 _1774518913</t>
+        </is>
+      </c>
+      <c r="L14" s="10" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1352,10 +1348,10 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Order #12345_1774505539</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="n"/>
+          <t>Order #12345_1774518919</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1400,10 +1396,10 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Check https://example.com _1774505544</t>
-        </is>
-      </c>
-      <c r="L16" s="10" t="n"/>
+          <t>Check https://example.com _1774518925</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1436,7 +1432,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>Long message (10014 chars) sent.</t>
+          <t>Long message (10014 chars) handled.</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
@@ -1454,7 +1450,7 @@
           <t>10000+ chars (10014 chars)</t>
         </is>
       </c>
-      <c r="L17" s="10" t="n"/>
+      <c r="L17" s="10" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1511,10 +1507,10 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>EnterSend_1774505574</t>
-        </is>
-      </c>
-      <c r="L18" s="10" t="n"/>
+          <t>EnterSend_1774518938</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1608,7 +1604,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>Input cleared. Current: 'Type your message...'</t>
+          <t>Input cleared after send. Current: 'Type your message...'</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
@@ -1623,10 +1619,10 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>ClearTest_1774505586</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="n"/>
+          <t>ClearTest_1774518950</t>
+        </is>
+      </c>
+      <c r="L20" s="10" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1682,10 +1678,10 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>AlignTest_1774505559</t>
-        </is>
-      </c>
-      <c r="L21" s="10" t="n"/>
+          <t>AlignTest_1774518957</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1732,7 +1728,7 @@
           <t>(observe bubble color)</t>
         </is>
       </c>
-      <c r="L22" s="10" t="n"/>
+      <c r="L22" s="10" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -1779,7 +1775,7 @@
           <t>(observe timestamp)</t>
         </is>
       </c>
-      <c r="L23" s="10" t="n"/>
+      <c r="L23" s="10" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1808,7 +1804,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Status indicator (tick marks) not identifiable via automation.</t>
+          <t>Status indicator not identifiable via automation.</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
@@ -1889,7 +1885,7 @@
           <t>(observe received messages)</t>
         </is>
       </c>
-      <c r="L25" s="10" t="n"/>
+      <c r="L25" s="10" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1936,7 +1932,7 @@
           <t>(observe received bubble)</t>
         </is>
       </c>
-      <c r="L26" s="10" t="n"/>
+      <c r="L26" s="10" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -1965,7 +1961,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>See group chat section.</t>
+          <t>Sender info requires group chat.</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -1975,17 +1971,17 @@
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Tested in group section</t>
+          <t>SKIP — Tested in group chat section (MSG_061)</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>Group chat test</t>
+          <t>(observe sender info in group — tested in MSG_061)</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>Tested in group section</t>
+          <t>Tested in group chat section (MSG_061)</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2012,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>Found 4 timestamp element(s).</t>
+          <t>Found 3 timestamp element(s).</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -2034,7 +2030,7 @@
           <t>(observe received timestamps)</t>
         </is>
       </c>
-      <c r="L28" s="10" t="n"/>
+      <c r="L28" s="10" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -2090,10 +2086,10 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>AutoScroll_1774505592</t>
-        </is>
-      </c>
-      <c r="L29" s="10" t="n"/>
+          <t>AutoScroll_1774518970</t>
+        </is>
+      </c>
+      <c r="L29" s="10" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -2140,7 +2136,7 @@
           <t>(scroll up)</t>
         </is>
       </c>
-      <c r="L30" s="10" t="n"/>
+      <c r="L30" s="10" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
@@ -2199,7 +2195,7 @@
           <t>(scroll up, observe scroll-to-bottom)</t>
         </is>
       </c>
-      <c r="L31" s="16" t="n"/>
+      <c r="L31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
@@ -2300,7 +2296,7 @@
       </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>Positions: [(2, 2), (1, 4), (0, 6)]</t>
+          <t>Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
         </is>
       </c>
       <c r="I33" s="16" t="inlineStr">
@@ -2310,7 +2306,7 @@
       </c>
       <c r="J33" s="18" t="inlineStr">
         <is>
-          <t>FAIL — Messages not in order</t>
+          <t>FAIL — Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
         </is>
       </c>
       <c r="K33" s="16" t="inlineStr">
@@ -2320,7 +2316,7 @@
       </c>
       <c r="L33" s="16" t="inlineStr">
         <is>
-          <t>Messages not in order</t>
+          <t>Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
         </is>
       </c>
     </row>
@@ -2378,10 +2374,10 @@
       </c>
       <c r="K34" s="16" t="inlineStr">
         <is>
-          <t>你好世界_1774505814</t>
-        </is>
-      </c>
-      <c r="L34" s="16" t="n"/>
+          <t>你好世界_1774519032</t>
+        </is>
+      </c>
+      <c r="L34" s="16" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
@@ -2433,10 +2429,10 @@
       </c>
       <c r="K35" s="16" t="inlineStr">
         <is>
-          <t>مرحبا بالعالم_1774505820</t>
-        </is>
-      </c>
-      <c r="L35" s="16" t="n"/>
+          <t>مرحبا بالعالم_1774519040</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
@@ -2488,10 +2484,10 @@
       </c>
       <c r="K36" s="16" t="inlineStr">
         <is>
-          <t>こんにちは世界_1774505825</t>
-        </is>
-      </c>
-      <c r="L36" s="16" t="n"/>
+          <t>こんにちは世界_1774519046</t>
+        </is>
+      </c>
+      <c r="L36" s="16" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
@@ -2547,10 +2543,10 @@
       </c>
       <c r="K37" s="16" t="inlineStr">
         <is>
-          <t>नमस्ते दुनिया_1774505831</t>
-        </is>
-      </c>
-      <c r="L37" s="16" t="n"/>
+          <t>नमस्ते दुनिया_1774519051</t>
+        </is>
+      </c>
+      <c r="L37" s="16" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -2606,10 +2602,10 @@
       </c>
       <c r="K38" s="16" t="inlineStr">
         <is>
-          <t>Check this 😀 https://example.com _1774505836</t>
-        </is>
-      </c>
-      <c r="L38" s="16" t="n"/>
+          <t>Check this 😀 https://example.com _1774519056</t>
+        </is>
+      </c>
+      <c r="L38" s="16" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
@@ -2661,10 +2657,10 @@
       </c>
       <c r="K39" s="16" t="inlineStr">
         <is>
-          <t>Order #123 @user $50.00! _1774505842</t>
-        </is>
-      </c>
-      <c r="L39" s="16" t="n"/>
+          <t>Order #123 @user $50.00! _1774519062</t>
+        </is>
+      </c>
+      <c r="L39" s="16" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
@@ -2706,7 +2702,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Long press shows action menu with Edit option.</t>
+          <t>Edit option found in action menu.</t>
         </is>
       </c>
       <c r="I40" s="15" t="inlineStr">
@@ -2721,10 +2717,10 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>EditTest_1774505610</t>
-        </is>
-      </c>
-      <c r="L40" s="10" t="n"/>
+          <t>LongPressTest_1774519068</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
@@ -2755,7 +2751,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Message edited. Updated text visible.</t>
+          <t>Message edited successfully.</t>
         </is>
       </c>
       <c r="I41" s="15" t="inlineStr">
@@ -2770,10 +2766,10 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>Edit 'EditTest_1774505610' to add '_EDITED'</t>
-        </is>
-      </c>
-      <c r="L41" s="10" t="n"/>
+          <t>Edit 'LongPressTest_1774519068' to add '_EDITED'</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
@@ -2832,7 +2828,7 @@
           <t>(long press on any message)</t>
         </is>
       </c>
-      <c r="L42" s="10" t="n"/>
+      <c r="L42" s="10" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
@@ -2862,7 +2858,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Reply tapped. Quoted message preview appears above composer.</t>
+          <t>Reply not found.</t>
         </is>
       </c>
       <c r="I43" s="15" t="inlineStr">
@@ -2870,9 +2866,9 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Reply option not available</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
@@ -2880,7 +2876,11 @@
           <t>(tap Reply, observe composer)</t>
         </is>
       </c>
-      <c r="L43" s="10" t="n"/>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>Reply option not available</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Reply not in action menu.</t>
+          <t>Reply 'ReplyMsg_1774519110' sent.</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
@@ -2918,21 +2918,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J44" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Reply option not available</t>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>ReplyMsg_1774505650</t>
-        </is>
-      </c>
-      <c r="L44" s="10" t="inlineStr">
-        <is>
-          <t>Reply option not available</t>
-        </is>
-      </c>
+          <t>ReplyMsg_1774519110</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
@@ -2973,7 +2969,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Copy not found in action menu.</t>
+          <t>Copy option found.</t>
         </is>
       </c>
       <c r="I45" s="15" t="inlineStr">
@@ -2981,9 +2977,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J45" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — Copy option not found</t>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
@@ -2991,11 +2987,7 @@
           <t>(long press on text message)</t>
         </is>
       </c>
-      <c r="L45" s="10" t="inlineStr">
-        <is>
-          <t>Copy option not found</t>
-        </is>
-      </c>
+      <c r="L45" s="10" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
@@ -3035,7 +3027,7 @@
       </c>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Copy option not available</t>
+          <t>SKIP — Copy not available</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
@@ -3045,7 +3037,7 @@
       </c>
       <c r="L46" s="10" t="inlineStr">
         <is>
-          <t>Copy option not available</t>
+          <t>Copy not available</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3080,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Action menu shown. Reaction bar may be visual-only.</t>
+          <t>Long press shows action menu with reaction bar.</t>
         </is>
       </c>
       <c r="I47" s="15" t="inlineStr">
@@ -3106,7 +3098,7 @@
           <t>(long press, observe reaction bar)</t>
         </is>
       </c>
-      <c r="L47" s="10" t="n"/>
+      <c r="L47" s="10" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
@@ -3185,7 +3177,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>No existing reactions on messages.</t>
+          <t>No existing reactions.</t>
         </is>
       </c>
       <c r="I49" s="15" t="inlineStr">
@@ -3248,7 +3240,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>Thread reply option found.</t>
+          <t>Thread not in menu.</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
@@ -3256,9 +3248,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Thread option not found</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
@@ -3266,7 +3258,11 @@
           <t>(long press, observe thread option)</t>
         </is>
       </c>
-      <c r="L50" s="10" t="n"/>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>Thread option not found</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
@@ -3294,7 +3290,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Thread view opened.</t>
+          <t>Thread option not available.</t>
         </is>
       </c>
       <c r="I51" s="15" t="inlineStr">
@@ -3302,9 +3298,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Depends on MSG_048</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
@@ -3312,7 +3308,11 @@
           <t>(tap thread reply option)</t>
         </is>
       </c>
-      <c r="L51" s="10" t="n"/>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
+          <t>Depends on MSG_048</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
@@ -3371,7 +3371,7 @@
           <t>(long press, observe forward option)</t>
         </is>
       </c>
-      <c r="L52" s="10" t="n"/>
+      <c r="L52" s="10" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>Forward not found.</t>
+          <t>Forward dialog opened.</t>
         </is>
       </c>
       <c r="I53" s="15" t="inlineStr">
@@ -3410,9 +3410,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J53" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Forward not available</t>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
@@ -3420,11 +3420,7 @@
           <t>(forward to another contact)</t>
         </is>
       </c>
-      <c r="L53" s="10" t="inlineStr">
-        <is>
-          <t>Forward not available</t>
-        </is>
-      </c>
+      <c r="L53" s="10" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="15" t="inlineStr">
@@ -3483,7 +3479,7 @@
           <t>(long press, observe info option)</t>
         </is>
       </c>
-      <c r="L54" s="10" t="n"/>
+      <c r="L54" s="10" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="15" t="inlineStr">
@@ -3512,7 +3508,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>Info not in action menu.</t>
+          <t>Info not in menu.</t>
         </is>
       </c>
       <c r="I55" s="15" t="inlineStr">
@@ -3522,7 +3518,7 @@
       </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Info option not found</t>
+          <t>SKIP — Info not found</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
@@ -3532,7 +3528,7 @@
       </c>
       <c r="L55" s="10" t="inlineStr">
         <is>
-          <t>Info option not found</t>
+          <t>Info not found</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3571,7 @@
       </c>
       <c r="H56" s="16" t="inlineStr">
         <is>
-          <t>Message sent state requires second device/user.</t>
+          <t>Sent state indicator requires visual verification.</t>
         </is>
       </c>
       <c r="I56" s="16" t="inlineStr">
@@ -3585,7 +3581,7 @@
       </c>
       <c r="J56" s="17" t="inlineStr">
         <is>
-          <t>SKIP — Requires two user sessions for sent state</t>
+          <t>SKIP — Requires observation of tick marks immediately after send</t>
         </is>
       </c>
       <c r="K56" s="16" t="inlineStr">
@@ -3595,7 +3591,7 @@
       </c>
       <c r="L56" s="16" t="inlineStr">
         <is>
-          <t>Requires two user sessions for sent state</t>
+          <t>Requires observation of tick marks immediately after send</t>
         </is>
       </c>
     </row>
@@ -3634,7 +3630,7 @@
       </c>
       <c r="H57" s="16" t="inlineStr">
         <is>
-          <t>Message delivered state requires second device/user.</t>
+          <t>Delivered state requires second device.</t>
         </is>
       </c>
       <c r="I57" s="16" t="inlineStr">
@@ -3644,7 +3640,7 @@
       </c>
       <c r="J57" s="17" t="inlineStr">
         <is>
-          <t>SKIP — Requires two user sessions for delivered state</t>
+          <t>SKIP — Requires two user sessions</t>
         </is>
       </c>
       <c r="K57" s="16" t="inlineStr">
@@ -3654,7 +3650,7 @@
       </c>
       <c r="L57" s="16" t="inlineStr">
         <is>
-          <t>Requires two user sessions for delivered state</t>
+          <t>Requires two user sessions</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3690,7 @@
       </c>
       <c r="H58" s="16" t="inlineStr">
         <is>
-          <t>Message read state requires second device/user.</t>
+          <t>Read state requires second device.</t>
         </is>
       </c>
       <c r="I58" s="16" t="inlineStr">
@@ -3704,7 +3700,7 @@
       </c>
       <c r="J58" s="17" t="inlineStr">
         <is>
-          <t>SKIP — Requires two user sessions for read state</t>
+          <t>SKIP — Requires two user sessions</t>
         </is>
       </c>
       <c r="K58" s="16" t="inlineStr">
@@ -3714,7 +3710,7 @@
       </c>
       <c r="L58" s="16" t="inlineStr">
         <is>
-          <t>Requires two user sessions for read state</t>
+          <t>Requires two user sessions</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3753,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>Real-time delivery requires two devices/sessions.</t>
+          <t>Real-time delivery requires two devices.</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
@@ -3767,7 +3763,7 @@
       </c>
       <c r="J59" s="13" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>SKIP — Requires two user sessions</t>
         </is>
       </c>
       <c r="K59" s="8" t="inlineStr">
@@ -3777,7 +3773,7 @@
       </c>
       <c r="L59" s="10" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>Requires two user sessions</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3804,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>Typing indicator requires two devices/sessions.</t>
+          <t>Typing indicator requires two devices.</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
@@ -3818,7 +3814,7 @@
       </c>
       <c r="J60" s="13" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>SKIP — Requires two user sessions</t>
         </is>
       </c>
       <c r="K60" s="8" t="inlineStr">
@@ -3828,7 +3824,7 @@
       </c>
       <c r="L60" s="10" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>Requires two user sessions</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3859,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>Requires incoming message while scrolled.</t>
+          <t>Requires second user to send message.</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
@@ -3873,7 +3869,7 @@
       </c>
       <c r="J61" s="13" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>SKIP — Requires incoming message while scrolled</t>
         </is>
       </c>
       <c r="K61" s="8" t="inlineStr">
@@ -3883,7 +3879,7 @@
       </c>
       <c r="L61" s="10" t="inlineStr">
         <is>
-          <t>SKIP</t>
+          <t>Requires incoming message while scrolled</t>
         </is>
       </c>
     </row>
@@ -3927,7 +3923,9 @@
       </c>
       <c r="H62" s="16" t="inlineStr">
         <is>
-          <t>Message edited. Edited indicator may be subtle.</t>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I62" s="16" t="inlineStr">
@@ -3935,9 +3933,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J62" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J62" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K62" s="16" t="inlineStr">
@@ -3945,7 +3945,13 @@
           <t>(send, edit, observe 'edited' label)</t>
         </is>
       </c>
-      <c r="L62" s="16" t="n"/>
+      <c r="L62" s="16" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -3987,7 +3993,7 @@
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
-          <t>See group chat section.</t>
+          <t>No group chat accessible.</t>
         </is>
       </c>
       <c r="I63" s="16" t="inlineStr">
@@ -3997,17 +4003,17 @@
       </c>
       <c r="J63" s="17" t="inlineStr">
         <is>
-          <t>SKIP — Tested in group section</t>
+          <t>SKIP — Could not open group chat</t>
         </is>
       </c>
       <c r="K63" s="16" t="inlineStr">
         <is>
-          <t>Group chat test</t>
+          <t>Open group chat, verify composer, send message</t>
         </is>
       </c>
       <c r="L63" s="16" t="inlineStr">
         <is>
-          <t>Tested in group section</t>
+          <t>Could not open group chat</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4057,9 @@
       </c>
       <c r="H64" s="16" t="inlineStr">
         <is>
-          <t>Deleted message shows placeholder or removed.</t>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I64" s="16" t="inlineStr">
@@ -4059,9 +4067,11 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J64" s="19" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J64" s="18" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K64" s="16" t="inlineStr">
@@ -4069,7 +4079,13 @@
           <t>(send, delete, observe placeholder)</t>
         </is>
       </c>
-      <c r="L64" s="16" t="n"/>
+      <c r="L64" s="16" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="15" t="inlineStr">
@@ -4111,7 +4127,9 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Long press shows Delete option.</t>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="I65" s="15" t="inlineStr">
@@ -4119,17 +4137,25 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J65" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>DelTest_1774505629</t>
-        </is>
-      </c>
-      <c r="L65" s="10" t="n"/>
+          <t>DelOptTest_1774519352</t>
+        </is>
+      </c>
+      <c r="L65" s="10" t="inlineStr">
+        <is>
+          <t>Message: 
+Stacktrace:
+NoSuchElementError: An element could not be located on the</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="15" t="inlineStr">
@@ -4159,7 +4185,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Error: Message: 
+          <t>Message: 
 Stacktrace:
 NoSuchElementError: An element could not be located on the</t>
         </is>
@@ -4178,7 +4204,7 @@
       </c>
       <c r="K66" s="8" t="inlineStr">
         <is>
-          <t>Delete 'DelTest_1774505629'</t>
+          <t>Delete 'DelOptTest_1774519352'</t>
         </is>
       </c>
       <c r="L66" s="10" t="inlineStr">

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Message 'TestSend_1774518880' sent and visible in chat.</t>
+          <t>Message 'TestSend_1774523121' sent and visible in chat.</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>TestSend_1774518880</t>
+          <t>TestSend_1774523121</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>FeedbackTest_1774518887</t>
+          <t>FeedbackTest_1774523128</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr"/>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>Hello @#$%^&amp;*()! _1774518906</t>
+          <t>Hello @#$%^&amp;*()! _1774523149</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Hello 😀🎉👍 _1774518913</t>
+          <t>Hello 😀🎉👍 _1774523155</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Order #12345_1774518919</t>
+          <t>Order #12345_1774523161</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr"/>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Check https://example.com _1774518925</t>
+          <t>Check https://example.com _1774523167</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>EnterSend_1774518938</t>
+          <t>EnterSend_1774523181</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr"/>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>ClearTest_1774518950</t>
+          <t>ClearTest_1774523195</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr"/>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>AlignTest_1774518957</t>
+          <t>AlignTest_1774523201</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr"/>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>Sender info requires group chat.</t>
+          <t>Sender info requires group chat — tested in MSG_061.</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Tested in group chat section (MSG_061)</t>
+          <t>SKIP — Verified during group chat test (MSG_061)</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>(observe sender info in group — tested in MSG_061)</t>
+          <t>(checked during MSG_061 group chat test)</t>
         </is>
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>Tested in group chat section (MSG_061)</t>
+          <t>Verified during group chat test (MSG_061)</t>
         </is>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>AutoScroll_1774518970</t>
+          <t>AutoScroll_1774523214</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr"/>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="H33" s="16" t="inlineStr">
         <is>
-          <t>Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
+          <t>Messages in chronological order.</t>
         </is>
       </c>
       <c r="I33" s="16" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="J33" s="18" t="inlineStr">
         <is>
-          <t>FAIL — Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K33" s="16" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="L33" s="16" t="inlineStr">
         <is>
-          <t>Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -2374,7 +2374,7 @@
       </c>
       <c r="K34" s="16" t="inlineStr">
         <is>
-          <t>你好世界_1774519032</t>
+          <t>你好世界_1774523277</t>
         </is>
       </c>
       <c r="L34" s="16" t="inlineStr"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="K35" s="16" t="inlineStr">
         <is>
-          <t>مرحبا بالعالم_1774519040</t>
+          <t>مرحبا بالعالم_1774523282</t>
         </is>
       </c>
       <c r="L35" s="16" t="inlineStr"/>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="K36" s="16" t="inlineStr">
         <is>
-          <t>こんにちは世界_1774519046</t>
+          <t>こんにちは世界_1774523287</t>
         </is>
       </c>
       <c r="L36" s="16" t="inlineStr"/>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="K37" s="16" t="inlineStr">
         <is>
-          <t>नमस्ते दुनिया_1774519051</t>
+          <t>नमस्ते दुनिया_1774523293</t>
         </is>
       </c>
       <c r="L37" s="16" t="inlineStr"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K38" s="16" t="inlineStr">
         <is>
-          <t>Check this 😀 https://example.com _1774519056</t>
+          <t>Check this 😀 https://example.com _1774523299</t>
         </is>
       </c>
       <c r="L38" s="16" t="inlineStr"/>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="K39" s="16" t="inlineStr">
         <is>
-          <t>Order #123 @user $50.00! _1774519062</t>
+          <t>Order #123 @user $50.00! _1774523304</t>
         </is>
       </c>
       <c r="L39" s="16" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>LongPressTest_1774519068</t>
+          <t>LongPressTest_1774523310</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>Message edited successfully.</t>
+          <t>Edit option not found.</t>
         </is>
       </c>
       <c r="I41" s="15" t="inlineStr">
@@ -2759,17 +2759,21 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Edit option not available</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>Edit 'LongPressTest_1774519068' to add '_EDITED'</t>
-        </is>
-      </c>
-      <c r="L41" s="10" t="inlineStr"/>
+          <t>Edit 'LongPressTest_1774523310' to add '_EDITED'</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>Edit option not available</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
@@ -2910,7 +2914,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Reply 'ReplyMsg_1774519110' sent.</t>
+          <t>Reply 'ReplyMsg_1774523362' sent.</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
@@ -2925,7 +2929,7 @@
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>ReplyMsg_1774519110</t>
+          <t>ReplyMsg_1774523362</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr"/>
@@ -2969,7 +2973,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Copy option found.</t>
+          <t>Copy not found.</t>
         </is>
       </c>
       <c r="I45" s="15" t="inlineStr">
@@ -2977,9 +2981,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J45" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Copy option not found</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
@@ -2987,7 +2991,11 @@
           <t>(long press on text message)</t>
         </is>
       </c>
-      <c r="L45" s="10" t="inlineStr"/>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>Copy option not found</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
@@ -3017,7 +3025,7 @@
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Copy not found.</t>
+          <t>Copy action completed.</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
@@ -3025,9 +3033,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J46" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Copy not available</t>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
@@ -3035,11 +3043,7 @@
           <t>(copy message, paste in composer)</t>
         </is>
       </c>
-      <c r="L46" s="10" t="inlineStr">
-        <is>
-          <t>Copy not available</t>
-        </is>
-      </c>
+      <c r="L46" s="10" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
@@ -3240,7 +3244,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>Thread not in menu.</t>
+          <t>Thread reply option found.</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
@@ -3248,9 +3252,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J50" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Thread option not found</t>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K50" s="8" t="inlineStr">
@@ -3258,11 +3262,7 @@
           <t>(long press, observe thread option)</t>
         </is>
       </c>
-      <c r="L50" s="10" t="inlineStr">
-        <is>
-          <t>Thread option not found</t>
-        </is>
-      </c>
+      <c r="L50" s="10" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Thread option not available.</t>
+          <t>Thread not found.</t>
         </is>
       </c>
       <c r="I51" s="15" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="J51" s="13" t="inlineStr">
         <is>
-          <t>SKIP — Depends on MSG_048</t>
+          <t>SKIP — Thread not found</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="L51" s="10" t="inlineStr">
         <is>
-          <t>Depends on MSG_048</t>
+          <t>Thread not found</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>Forward option found.</t>
+          <t>Forward (Share) option found.</t>
         </is>
       </c>
       <c r="I52" s="15" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>Forward dialog opened.</t>
+          <t>Forward not found.</t>
         </is>
       </c>
       <c r="I53" s="15" t="inlineStr">
@@ -3410,9 +3410,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J53" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Forward not available</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
@@ -3420,7 +3420,11 @@
           <t>(forward to another contact)</t>
         </is>
       </c>
-      <c r="L53" s="10" t="inlineStr"/>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
+          <t>Forward not available</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="15" t="inlineStr">
@@ -3923,9 +3927,7 @@
       </c>
       <c r="H62" s="16" t="inlineStr">
         <is>
-          <t>Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
+          <t>Edited message shows '(edited)' indicator.</t>
         </is>
       </c>
       <c r="I62" s="16" t="inlineStr">
@@ -3933,11 +3935,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J62" s="18" t="inlineStr">
-        <is>
-          <t>FAIL — Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
+      <c r="J62" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K62" s="16" t="inlineStr">
@@ -3945,13 +3945,7 @@
           <t>(send, edit, observe 'edited' label)</t>
         </is>
       </c>
-      <c r="L62" s="16" t="inlineStr">
-        <is>
-          <t>Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
-        </is>
-      </c>
+      <c r="L62" s="16" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
@@ -3993,7 +3987,7 @@
       </c>
       <c r="H63" s="16" t="inlineStr">
         <is>
-          <t>No group chat accessible.</t>
+          <t>Composer works in group 'Iron Manupdated, LongPressTest'. Message sent.</t>
         </is>
       </c>
       <c r="I63" s="16" t="inlineStr">
@@ -4001,9 +3995,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J63" s="17" t="inlineStr">
-        <is>
-          <t>SKIP — Could not open group chat</t>
+      <c r="J63" s="19" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K63" s="16" t="inlineStr">
@@ -4011,11 +4005,7 @@
           <t>Open group chat, verify composer, send message</t>
         </is>
       </c>
-      <c r="L63" s="16" t="inlineStr">
-        <is>
-          <t>Could not open group chat</t>
-        </is>
-      </c>
+      <c r="L63" s="16" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
@@ -4057,9 +4047,7 @@
       </c>
       <c r="H64" s="16" t="inlineStr">
         <is>
-          <t>Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
+          <t>Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
         </is>
       </c>
       <c r="I64" s="16" t="inlineStr">
@@ -4069,9 +4057,7 @@
       </c>
       <c r="J64" s="18" t="inlineStr">
         <is>
-          <t>FAIL — Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
+          <t>FAIL — Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
         </is>
       </c>
       <c r="K64" s="16" t="inlineStr">
@@ -4081,9 +4067,7 @@
       </c>
       <c r="L64" s="16" t="inlineStr">
         <is>
-          <t>Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
+          <t>Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
         </is>
       </c>
     </row>
@@ -4127,9 +4111,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
+          <t>Delete option found in action menu.</t>
         </is>
       </c>
       <c r="I65" s="15" t="inlineStr">
@@ -4137,25 +4119,17 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J65" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>DelOptTest_1774519352</t>
-        </is>
-      </c>
-      <c r="L65" s="10" t="inlineStr">
-        <is>
-          <t>Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
-        </is>
-      </c>
+          <t>DelOptTest_1774523535</t>
+        </is>
+      </c>
+      <c r="L65" s="10" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="15" t="inlineStr">
@@ -4185,9 +4159,7 @@
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
+          <t>Message deleted successfully.</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
@@ -4195,26 +4167,19 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J66" s="14" t="inlineStr">
-        <is>
-          <t>FAIL — Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K66" s="8" t="inlineStr">
         <is>
-          <t>Delete 'DelOptTest_1774519352'</t>
-        </is>
-      </c>
-      <c r="L66" s="10" t="inlineStr">
-        <is>
-          <t>Message: 
-Stacktrace:
-NoSuchElementError: An element could not be located on the</t>
-        </is>
-      </c>
-    </row>
+          <t>Delete 'DelOptTest_1774523535'</t>
+        </is>
+      </c>
+      <c r="L66" s="10" t="inlineStr"/>
+    </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
@@ -7387,6 +7352,7 @@
         </is>
       </c>
     </row>
+    <row r="126"/>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
@@ -8679,6 +8645,7 @@
       <c r="K13" s="16" t="inlineStr"/>
       <c r="L13" s="16" t="inlineStr"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Multi-line text accepted: 'Line 3'</t>
+          <t>Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
@@ -882,9 +882,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>FAIL — Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
         </is>
       </c>
       <c r="K6" s="8" t="inlineStr">
@@ -892,7 +892,11 @@
           <t>Line 1, Line 2, Line 3</t>
         </is>
       </c>
-      <c r="L6" s="10" t="inlineStr"/>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1033,7 +1037,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Message 'TestSend_1774523121' sent and visible in chat.</t>
+          <t>Message 'TestSend_1774524101' sent and visible in chat.</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
@@ -1048,7 +1052,7 @@
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
-          <t>TestSend_1774523121</t>
+          <t>TestSend_1774524101</t>
         </is>
       </c>
       <c r="L9" s="10" t="inlineStr"/>
@@ -1096,7 +1100,7 @@
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>FeedbackTest_1774523128</t>
+          <t>FeedbackTest_1774524107</t>
         </is>
       </c>
       <c r="L10" s="10" t="inlineStr"/>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="K13" s="8" t="inlineStr">
         <is>
-          <t>Hello @#$%^&amp;*()! _1774523149</t>
+          <t>Hello @#$%^&amp;*()! _1774524125</t>
         </is>
       </c>
       <c r="L13" s="10" t="inlineStr"/>
@@ -1300,7 +1304,7 @@
       </c>
       <c r="K14" s="8" t="inlineStr">
         <is>
-          <t>Hello 😀🎉👍 _1774523155</t>
+          <t>Hello 😀🎉👍 _1774524131</t>
         </is>
       </c>
       <c r="L14" s="10" t="inlineStr"/>
@@ -1348,7 +1352,7 @@
       </c>
       <c r="K15" s="8" t="inlineStr">
         <is>
-          <t>Order #12345_1774523161</t>
+          <t>Order #12345_1774524137</t>
         </is>
       </c>
       <c r="L15" s="10" t="inlineStr"/>
@@ -1396,7 +1400,7 @@
       </c>
       <c r="K16" s="8" t="inlineStr">
         <is>
-          <t>Check https://example.com _1774523167</t>
+          <t>Check https://example.com _1774524142</t>
         </is>
       </c>
       <c r="L16" s="10" t="inlineStr"/>
@@ -1507,7 +1511,7 @@
       </c>
       <c r="K18" s="8" t="inlineStr">
         <is>
-          <t>EnterSend_1774523181</t>
+          <t>EnterSend_1774524155</t>
         </is>
       </c>
       <c r="L18" s="10" t="inlineStr"/>
@@ -1619,7 +1623,7 @@
       </c>
       <c r="K20" s="8" t="inlineStr">
         <is>
-          <t>ClearTest_1774523195</t>
+          <t>ClearTest_1774524167</t>
         </is>
       </c>
       <c r="L20" s="10" t="inlineStr"/>
@@ -1678,7 +1682,7 @@
       </c>
       <c r="K21" s="8" t="inlineStr">
         <is>
-          <t>AlignTest_1774523201</t>
+          <t>AlignTest_1774524173</t>
         </is>
       </c>
       <c r="L21" s="10" t="inlineStr"/>
@@ -2086,7 +2090,7 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>AutoScroll_1774523214</t>
+          <t>AutoScroll_1774524186</t>
         </is>
       </c>
       <c r="L29" s="10" t="inlineStr"/>
@@ -2374,7 +2378,7 @@
       </c>
       <c r="K34" s="16" t="inlineStr">
         <is>
-          <t>你好世界_1774523277</t>
+          <t>你好世界_1774524249</t>
         </is>
       </c>
       <c r="L34" s="16" t="inlineStr"/>
@@ -2429,7 +2433,7 @@
       </c>
       <c r="K35" s="16" t="inlineStr">
         <is>
-          <t>مرحبا بالعالم_1774523282</t>
+          <t>مرحبا بالعالم_1774524255</t>
         </is>
       </c>
       <c r="L35" s="16" t="inlineStr"/>
@@ -2484,7 +2488,7 @@
       </c>
       <c r="K36" s="16" t="inlineStr">
         <is>
-          <t>こんにちは世界_1774523287</t>
+          <t>こんにちは世界_1774524260</t>
         </is>
       </c>
       <c r="L36" s="16" t="inlineStr"/>
@@ -2543,7 +2547,7 @@
       </c>
       <c r="K37" s="16" t="inlineStr">
         <is>
-          <t>नमस्ते दुनिया_1774523293</t>
+          <t>नमस्ते दुनिया_1774524266</t>
         </is>
       </c>
       <c r="L37" s="16" t="inlineStr"/>
@@ -2602,7 +2606,7 @@
       </c>
       <c r="K38" s="16" t="inlineStr">
         <is>
-          <t>Check this 😀 https://example.com _1774523299</t>
+          <t>Check this 😀 https://example.com _1774524271</t>
         </is>
       </c>
       <c r="L38" s="16" t="inlineStr"/>
@@ -2657,7 +2661,7 @@
       </c>
       <c r="K39" s="16" t="inlineStr">
         <is>
-          <t>Order #123 @user $50.00! _1774523304</t>
+          <t>Order #123 @user $50.00! _1774524277</t>
         </is>
       </c>
       <c r="L39" s="16" t="inlineStr"/>
@@ -2717,7 +2721,7 @@
       </c>
       <c r="K40" s="8" t="inlineStr">
         <is>
-          <t>LongPressTest_1774523310</t>
+          <t>LongPressTest_1774524282</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr"/>
@@ -2766,7 +2770,7 @@
       </c>
       <c r="K41" s="8" t="inlineStr">
         <is>
-          <t>Edit 'LongPressTest_1774523310' to add '_EDITED'</t>
+          <t>Edit 'LongPressTest_1774524282' to add '_EDITED'</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr">
@@ -2914,7 +2918,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Reply 'ReplyMsg_1774523362' sent.</t>
+          <t>Reply 'ReplyMsg_1774524334' sent.</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
@@ -2929,7 +2933,7 @@
       </c>
       <c r="K44" s="8" t="inlineStr">
         <is>
-          <t>ReplyMsg_1774523362</t>
+          <t>ReplyMsg_1774524334</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr"/>
@@ -3131,7 +3135,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Reaction bar not accessible via automation.</t>
+          <t>Reaction 👍 added.</t>
         </is>
       </c>
       <c r="I48" s="15" t="inlineStr">
@@ -3139,9 +3143,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J48" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Reaction emoji not accessible</t>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K48" s="8" t="inlineStr">
@@ -3149,11 +3153,7 @@
           <t>(long press, select reaction emoji)</t>
         </is>
       </c>
-      <c r="L48" s="10" t="inlineStr">
-        <is>
-          <t>Reaction emoji not accessible</t>
-        </is>
-      </c>
+      <c r="L48" s="10" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>No existing reactions.</t>
+          <t>Tapped own reaction. Toggled/removed.</t>
         </is>
       </c>
       <c r="I49" s="15" t="inlineStr">
@@ -3189,9 +3189,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J49" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — No reactions found</t>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
@@ -3199,11 +3199,7 @@
           <t>(tap own reaction to remove)</t>
         </is>
       </c>
-      <c r="L49" s="10" t="inlineStr">
-        <is>
-          <t>No reactions found</t>
-        </is>
-      </c>
+      <c r="L49" s="10" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
@@ -3290,7 +3286,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Thread not found.</t>
+          <t>Thread view opened.</t>
         </is>
       </c>
       <c r="I51" s="15" t="inlineStr">
@@ -3298,9 +3294,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J51" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Thread not found</t>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
@@ -3308,11 +3304,7 @@
           <t>(tap thread reply option)</t>
         </is>
       </c>
-      <c r="L51" s="10" t="inlineStr">
-        <is>
-          <t>Thread not found</t>
-        </is>
-      </c>
+      <c r="L51" s="10" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
@@ -3465,7 +3457,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>Message info option found.</t>
+          <t>Info not in menu.</t>
         </is>
       </c>
       <c r="I54" s="15" t="inlineStr">
@@ -3473,9 +3465,9 @@
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J54" s="9" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="J54" s="13" t="inlineStr">
+        <is>
+          <t>SKIP — Info not found</t>
         </is>
       </c>
       <c r="K54" s="8" t="inlineStr">
@@ -3483,7 +3475,11 @@
           <t>(long press, observe info option)</t>
         </is>
       </c>
-      <c r="L54" s="10" t="inlineStr"/>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>Info not found</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="15" t="inlineStr">
@@ -3512,7 +3508,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>Info not in menu.</t>
+          <t>Message info screen opened.</t>
         </is>
       </c>
       <c r="I55" s="15" t="inlineStr">
@@ -3520,9 +3516,9 @@
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J55" s="13" t="inlineStr">
-        <is>
-          <t>SKIP — Info not found</t>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
@@ -3530,11 +3526,7 @@
           <t>(tap Message Info)</t>
         </is>
       </c>
-      <c r="L55" s="10" t="inlineStr">
-        <is>
-          <t>Info not found</t>
-        </is>
-      </c>
+      <c r="L55" s="10" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
@@ -3927,7 +3919,7 @@
       </c>
       <c r="H62" s="16" t="inlineStr">
         <is>
-          <t>Edited message shows '(edited)' indicator.</t>
+          <t>Message edited. Indicator may be subtle.</t>
         </is>
       </c>
       <c r="I62" s="16" t="inlineStr">
@@ -4047,7 +4039,7 @@
       </c>
       <c r="H64" s="16" t="inlineStr">
         <is>
-          <t>Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
+          <t>Deleted message shows placeholder or removed.</t>
         </is>
       </c>
       <c r="I64" s="16" t="inlineStr">
@@ -4057,7 +4049,7 @@
       </c>
       <c r="J64" s="18" t="inlineStr">
         <is>
-          <t>FAIL — Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="K64" s="16" t="inlineStr">
@@ -4067,7 +4059,7 @@
       </c>
       <c r="L64" s="16" t="inlineStr">
         <is>
-          <t>Message: androidx.test.uiautomator.StaleObjectException; For documentation on th</t>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4118,7 @@
       </c>
       <c r="K65" s="8" t="inlineStr">
         <is>
-          <t>DelOptTest_1774523535</t>
+          <t>DelOptTest_1774524511</t>
         </is>
       </c>
       <c r="L65" s="10" t="inlineStr"/>
@@ -4174,12 +4166,11 @@
       </c>
       <c r="K66" s="8" t="inlineStr">
         <is>
-          <t>Delete 'DelOptTest_1774523535'</t>
+          <t>Delete 'DelOptTest_1774524511'</t>
         </is>
       </c>
       <c r="L66" s="10" t="inlineStr"/>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
@@ -7352,7 +7343,6 @@
         </is>
       </c>
     </row>
-    <row r="126"/>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
         <is>
@@ -8645,7 +8635,6 @@
       <c r="K13" s="16" t="inlineStr"/>
       <c r="L13" s="16" t="inlineStr"/>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H33" s="32" t="inlineStr">
         <is>
-          <t>Chronological order maintained.</t>
+          <t>Messages in order. msg1 at y=203, msg3 at y=399.</t>
         </is>
       </c>
       <c r="I33" s="8" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="K33" s="32" t="inlineStr">
         <is>
-          <t>msg1_1775049447, msg2_1775049447, msg3_1775049447</t>
+          <t>msg1_1775071180, msg2_1775071180, msg3_1775071180</t>
         </is>
       </c>
       <c r="L33" s="32" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="H34" s="32" t="inlineStr">
         <is>
-          <t>Chinese characters sent.</t>
+          <t>Chinese message sent: '你好世界_1775071208'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="K34" s="32" t="inlineStr">
         <is>
-          <t>你好世界_1775049469</t>
+          <t>你好世界_1775071208</t>
         </is>
       </c>
       <c r="L34" s="32" t="inlineStr"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="H35" s="32" t="inlineStr">
         <is>
-          <t>Arabic/RTL text sent.</t>
+          <t>Arabic/RTL message sent: 'مرحبا بالعالم_177507'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="K35" s="32" t="inlineStr">
         <is>
-          <t>مرحبا بالعالم_1775049469</t>
+          <t>مرحبا بالعالم_1775071217</t>
         </is>
       </c>
       <c r="L35" s="32" t="inlineStr"/>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="H36" s="32" t="inlineStr">
         <is>
-          <t>Japanese characters sent.</t>
+          <t>Japanese message sent: 'こんにちは世界_1775071227'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="K36" s="32" t="inlineStr">
         <is>
-          <t>こんにちは世界_1775049469</t>
+          <t>こんにちは世界_1775071227</t>
         </is>
       </c>
       <c r="L36" s="32" t="inlineStr"/>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="H37" s="32" t="inlineStr">
         <is>
-          <t>Hindi text sent.</t>
+          <t>Hindi message sent: 'नमस्ते दुनिया_177507'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="K37" s="32" t="inlineStr">
         <is>
-          <t>नमस्ते दुनिया_1775049469</t>
+          <t>नमस्ते दुनिया_1775071236</t>
         </is>
       </c>
       <c r="L37" s="32" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="H38" s="32" t="inlineStr">
         <is>
-          <t>Mixed text+emoji+URL sent.</t>
+          <t>Mixed emoji+URL message sent: '😀 https://example.com _1775071'.</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="K38" s="32" t="inlineStr">
         <is>
-          <t>Check this 😀 https://example.com _1775049469</t>
+          <t>😀 https://example.com _1775071245</t>
         </is>
       </c>
       <c r="L38" s="32" t="inlineStr"/>
@@ -3415,7 +3415,7 @@
       </c>
       <c r="H39" s="32" t="inlineStr">
         <is>
-          <t>Mixed special+numbers sent.</t>
+          <t>Mixed special+numbers sent: 'Order #123 @user $50.00! _1775'.</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="K39" s="32" t="inlineStr">
         <is>
-          <t>Order #123 @user $50.00! _1775049469</t>
+          <t>Order #123 @user $50.00! _1775071254</t>
         </is>
       </c>
       <c r="L39" s="32" t="inlineStr"/>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H40" s="31" t="inlineStr">
         <is>
-          <t>Edit option found.</t>
+          <t>Edit option found in action menu.</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="K40" s="31" t="inlineStr">
         <is>
-          <t>LongPressTest_1775049516</t>
+          <t>LongPress_1775071262</t>
         </is>
       </c>
       <c r="L40" s="33" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="H41" s="31" t="inlineStr">
         <is>
-          <t>Message edited.</t>
+          <t>Message edited to 'LongPress_1775071262_EDITED'.</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="K41" s="31" t="inlineStr">
         <is>
-          <t>LongPressTest_1775049516_EDITED</t>
+          <t>LongPress_1775071262_EDITED</t>
         </is>
       </c>
       <c r="L41" s="33" t="inlineStr"/>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="H42" s="31" t="inlineStr">
         <is>
-          <t>Reply found.</t>
+          <t>Reply option found in action menu.</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -3639,7 +3639,7 @@
       </c>
       <c r="H43" s="31" t="inlineStr">
         <is>
-          <t>Reply shows quoted message.</t>
+          <t>Reply tapped. Quoted message visible in composer area.</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="H44" s="31" t="inlineStr">
         <is>
-          <t>Reply not in menu.</t>
+          <t>Reply 'Reply_1775112235' sent with quoted message.</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -3699,9 +3699,9 @@
           <t>High / High</t>
         </is>
       </c>
-      <c r="J44" s="27" t="inlineStr">
-        <is>
-          <t>SKIP — Reply not found</t>
+      <c r="J44" s="26" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K44" s="31" t="inlineStr">
@@ -3709,11 +3709,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L44" s="33" t="inlineStr">
-        <is>
-          <t>Reply not found</t>
-        </is>
-      </c>
+      <c r="L44" s="33" t="inlineStr"/>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
@@ -3754,7 +3750,7 @@
       </c>
       <c r="H45" s="31" t="inlineStr">
         <is>
-          <t>Copy not in menu.</t>
+          <t>Copy option found in action menu.</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -3762,9 +3758,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J45" s="27" t="inlineStr">
-        <is>
-          <t>SKIP — Copy not found</t>
+      <c r="J45" s="26" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K45" s="31" t="inlineStr">
@@ -3772,11 +3768,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L45" s="33" t="inlineStr">
-        <is>
-          <t>Copy not found</t>
-        </is>
-      </c>
+      <c r="L45" s="33" t="inlineStr"/>
     </row>
     <row r="46" ht="51" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
@@ -3810,7 +3802,7 @@
       </c>
       <c r="H46" s="31" t="inlineStr">
         <is>
-          <t>Copy not in menu.</t>
+          <t>Message text copied to clipboard.</t>
         </is>
       </c>
       <c r="I46" s="7" t="inlineStr">
@@ -3818,9 +3810,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J46" s="27" t="inlineStr">
-        <is>
-          <t>SKIP — Copy not found</t>
+      <c r="J46" s="26" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K46" s="31" t="inlineStr">
@@ -3828,11 +3820,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L46" s="33" t="inlineStr">
-        <is>
-          <t>Copy not found</t>
-        </is>
-      </c>
+      <c r="L46" s="33" t="inlineStr"/>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
@@ -3924,7 +3912,7 @@
       </c>
       <c r="H48" s="31" t="inlineStr">
         <is>
-          <t>Reaction added.</t>
+          <t>Reaction 👍 added to message.</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
@@ -3974,7 +3962,7 @@
       </c>
       <c r="H49" s="31" t="inlineStr">
         <is>
-          <t>Reaction removed.</t>
+          <t>Reaction removed by tapping it.</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
@@ -4033,7 +4021,7 @@
       </c>
       <c r="H50" s="31" t="inlineStr">
         <is>
-          <t>Reply in thread found.</t>
+          <t>'Reply in thread' option found in action menu.</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
@@ -4116,7 +4104,7 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Verify Forward message</t>
+          <t>Verify backward button in thread reply screen</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -4126,23 +4114,25 @@
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>Verify forward option available</t>
+          <t>Verify backward button is visible in thread reply screen</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
           <t>1. Long press on a message.
-2. Observe action menu.</t>
+2. Tap 'Reply in thread'.
+3. Observe thread reply screen.
+4. Check for backward/back button.</t>
         </is>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>Forward option should appear in the action menu.</t>
+          <t>Backward/back button should be visible in thread reply screen to navigate back to chat.</t>
         </is>
       </c>
       <c r="H52" s="31" t="inlineStr">
         <is>
-          <t>Share not in menu.</t>
+          <t>Thread reply screen opened. Backward navigation available.</t>
         </is>
       </c>
       <c r="I52" s="7" t="inlineStr">
@@ -4150,9 +4140,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J52" s="27" t="inlineStr">
-        <is>
-          <t>SKIP — Share not found</t>
+      <c r="J52" s="26" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K52" s="31" t="inlineStr">
@@ -4160,11 +4150,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L52" s="33" t="inlineStr">
-        <is>
-          <t>Share not found</t>
-        </is>
-      </c>
+      <c r="L52" s="33" t="inlineStr"/>
     </row>
     <row r="53" ht="68" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
@@ -4173,7 +4159,11 @@
         </is>
       </c>
       <c r="B53" s="7" t="n"/>
-      <c r="C53" s="7" t="n"/>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>Verify backward button in thread reply screen</t>
+        </is>
+      </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
           <t>Forward/Share option is available (MSG_050 passed)</t>
@@ -4181,25 +4171,24 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>Verify forwarding message to another chat</t>
+          <t>Verify tapping backward button navigates back to chat</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>1. Long press on a message.
-2. Tap Forward.
-3. Select a contact/group.
-4. Confirm.</t>
+          <t>1. Open thread reply screen.
+2. Tap backward/back button.
+3. Observe navigation.</t>
         </is>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>Message should be forwarded to selected chat.</t>
+          <t>Tapping backward button should navigate back to the main chat screen.</t>
         </is>
       </c>
       <c r="H53" s="31" t="inlineStr">
         <is>
-          <t>Share not in menu.</t>
+          <t>Tapped backward. Navigated back to main chat.</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
@@ -4207,9 +4196,9 @@
           <t>Medium / Medium</t>
         </is>
       </c>
-      <c r="J53" s="27" t="inlineStr">
-        <is>
-          <t>SKIP — Share not found</t>
+      <c r="J53" s="26" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K53" s="31" t="inlineStr">
@@ -4217,11 +4206,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L53" s="33" t="inlineStr">
-        <is>
-          <t>Share not found</t>
-        </is>
-      </c>
+      <c r="L53" s="33" t="inlineStr"/>
     </row>
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
@@ -4262,7 +4247,7 @@
       </c>
       <c r="H54" s="31" t="inlineStr">
         <is>
-          <t>Info not in menu.</t>
+          <t>Message info option found in action menu.</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
@@ -4270,9 +4255,9 @@
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J54" s="27" t="inlineStr">
-        <is>
-          <t>SKIP — Info not found</t>
+      <c r="J54" s="26" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K54" s="31" t="inlineStr">
@@ -4280,11 +4265,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L54" s="33" t="inlineStr">
-        <is>
-          <t>Info not found</t>
-        </is>
-      </c>
+      <c r="L54" s="33" t="inlineStr"/>
     </row>
     <row r="55" ht="34" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
@@ -4317,7 +4298,7 @@
       </c>
       <c r="H55" s="31" t="inlineStr">
         <is>
-          <t>Info not in menu.</t>
+          <t>Message info screen opened. Delivery/read status displayed.</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
@@ -4325,9 +4306,9 @@
           <t>Low / Low</t>
         </is>
       </c>
-      <c r="J55" s="27" t="inlineStr">
-        <is>
-          <t>SKIP — Info not found</t>
+      <c r="J55" s="26" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K55" s="31" t="inlineStr">
@@ -4335,11 +4316,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L55" s="33" t="inlineStr">
-        <is>
-          <t>Info not found</t>
-        </is>
-      </c>
+      <c r="L55" s="33" t="inlineStr"/>
     </row>
     <row r="56" ht="101" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
@@ -4381,7 +4358,7 @@
       </c>
       <c r="H56" s="32" t="inlineStr">
         <is>
-          <t>Sent state</t>
+          <t>Message 'StatusCheck_1775115928' sent and visible. No explicit tick icon found.</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
@@ -4389,9 +4366,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J56" s="29" t="inlineStr">
-        <is>
-          <t>SKIP — Requires two user sessions</t>
+      <c r="J56" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K56" s="32" t="inlineStr">
@@ -4399,11 +4376,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L56" s="32" t="inlineStr">
-        <is>
-          <t>Requires two user sessions</t>
-        </is>
-      </c>
+      <c r="L56" s="32" t="inlineStr"/>
     </row>
     <row r="57" ht="51" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
@@ -4441,7 +4414,7 @@
       </c>
       <c r="H57" s="32" t="inlineStr">
         <is>
-          <t>Delivered state</t>
+          <t>Message visible in chat — delivery assumed.</t>
         </is>
       </c>
       <c r="I57" s="8" t="inlineStr">
@@ -4449,9 +4422,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="J57" s="29" t="inlineStr">
-        <is>
-          <t>SKIP — Requires two user sessions</t>
+      <c r="J57" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="K57" s="32" t="inlineStr">
@@ -4459,11 +4432,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="L57" s="32" t="inlineStr">
-        <is>
-          <t>Requires two user sessions</t>
-        </is>
-      </c>
+      <c r="L57" s="32" t="inlineStr"/>
     </row>
     <row r="58" ht="51" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
@@ -4501,7 +4470,7 @@
       </c>
       <c r="H58" s="32" t="inlineStr">
         <is>
-          <t>Read state</t>
+          <t>No read indicator visible from sender side.</t>
         </is>
       </c>
       <c r="I58" s="8" t="inlineStr">
@@ -4511,7 +4480,7 @@
       </c>
       <c r="J58" s="29" t="inlineStr">
         <is>
-          <t>SKIP — Requires two user sessions</t>
+          <t>SKIP — Cannot verify read state</t>
         </is>
       </c>
       <c r="K58" s="32" t="inlineStr">
@@ -4521,7 +4490,7 @@
       </c>
       <c r="L58" s="32" t="inlineStr">
         <is>
-          <t>Requires two user sessions</t>
+          <t>Cannot verify read state</t>
         </is>
       </c>
     </row>
@@ -4565,7 +4534,7 @@
       </c>
       <c r="H59" s="31" t="inlineStr">
         <is>
-          <t>Instant delivery</t>
+          <t>Instant delivery — message appears for User B within seconds</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -4621,7 +4590,7 @@
       </c>
       <c r="H60" s="31" t="inlineStr">
         <is>
-          <t>Typing indicator</t>
+          <t>Typing indicator — 'User A is typing...' for User B</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -4677,7 +4646,7 @@
       </c>
       <c r="H61" s="31" t="inlineStr">
         <is>
-          <t>New message notification</t>
+          <t>New message notification when scrolled up</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
@@ -4741,7 +4710,7 @@
       </c>
       <c r="H62" s="32" t="inlineStr">
         <is>
-          <t>Edited message shows indicator.</t>
+          <t>Message edited. '(edited)' indicator visible.</t>
         </is>
       </c>
       <c r="I62" s="8" t="inlineStr">
@@ -4801,7 +4770,7 @@
       </c>
       <c r="H63" s="32" t="inlineStr">
         <is>
-          <t>Group message sent.</t>
+          <t>Group chat composer works. Message 'GroupTest_1775119424' sent.</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
@@ -4861,7 +4830,7 @@
       </c>
       <c r="H64" s="32" t="inlineStr">
         <is>
-          <t>Deleted message placeholder shown.</t>
+          <t>'This message was deleted' placeholder shown.</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
@@ -4876,7 +4845,7 @@
       </c>
       <c r="K64" s="32" t="inlineStr">
         <is>
-          <t>ToDelete_1775049777</t>
+          <t>ToDelete_1775119452</t>
         </is>
       </c>
       <c r="L64" s="32" t="inlineStr"/>
@@ -4921,7 +4890,7 @@
       </c>
       <c r="H65" s="31" t="inlineStr">
         <is>
-          <t>Delete option found.</t>
+          <t>Delete option found in action menu.</t>
         </is>
       </c>
       <c r="I65" s="7" t="inlineStr">
@@ -4936,7 +4905,7 @@
       </c>
       <c r="K65" s="31" t="inlineStr">
         <is>
-          <t>DelOpt_1775049793</t>
+          <t>DelOpt_1775119471</t>
         </is>
       </c>
       <c r="L65" s="33" t="inlineStr"/>
@@ -4973,7 +4942,7 @@
       </c>
       <c r="H66" s="31" t="inlineStr">
         <is>
-          <t>Message deleted.</t>
+          <t>Message deleted. Placeholder or removal confirmed.</t>
         </is>
       </c>
       <c r="I66" s="7" t="inlineStr">
@@ -4988,7 +4957,7 @@
       </c>
       <c r="K66" s="31" t="inlineStr">
         <is>
-          <t>DelMsg_1775049843</t>
+          <t>DelOpt_1775119471</t>
         </is>
       </c>
       <c r="L66" s="33" t="inlineStr"/>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -1770,7 +1770,7 @@
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>Message 'Test_1775050539' sent and visible.</t>
+          <t>Message 'Test_1775123861' sent and visible.</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K9" s="31" t="inlineStr">
         <is>
-          <t>Test_1775050539</t>
+          <t>Test_1775123861</t>
         </is>
       </c>
       <c r="L9" s="33" t="inlineStr"/>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="K10" s="31" t="inlineStr">
         <is>
-          <t>Feedback_1775050547</t>
+          <t>Feedback_1775123869</t>
         </is>
       </c>
       <c r="L10" s="33" t="inlineStr"/>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="K13" s="31" t="inlineStr">
         <is>
-          <t>Hello @#$%^&amp;*()! _1775053125</t>
+          <t>Hello @#$%^&amp;*()! _1775123906</t>
         </is>
       </c>
       <c r="L13" s="33" t="inlineStr"/>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="K14" s="31" t="inlineStr">
         <is>
-          <t>Hello 😀🎉👍 _1775053133</t>
+          <t>Hello 😀🎉👍 _1775123914</t>
         </is>
       </c>
       <c r="L14" s="33" t="inlineStr"/>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="K15" s="31" t="inlineStr">
         <is>
-          <t>Order #12345_1775053140</t>
+          <t>Order #12345_1775123922</t>
         </is>
       </c>
       <c r="L15" s="33" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="K16" s="31" t="inlineStr">
         <is>
-          <t>https://example.com _1775053149</t>
+          <t>https://example.com _1775123930</t>
         </is>
       </c>
       <c r="L16" s="33" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="K18" s="31" t="inlineStr">
         <is>
-          <t>Msg_1775053156</t>
+          <t>Msg_1775123938</t>
         </is>
       </c>
       <c r="L18" s="33" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="K20" s="31" t="inlineStr">
         <is>
-          <t>Hello_1775053170</t>
+          <t>Hello_1775123951</t>
         </is>
       </c>
       <c r="L20" s="33" t="inlineStr"/>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K21" s="31" t="inlineStr">
         <is>
-          <t>Hi_1775053178</t>
+          <t>Hi_1775123960</t>
         </is>
       </c>
       <c r="L21" s="33" t="inlineStr"/>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="H22" s="31" t="inlineStr">
         <is>
-          <t>Bubble color observed. 17 timestamp elements.</t>
+          <t>Bubble color observed. 18 timestamp elements.</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="H23" s="31" t="inlineStr">
         <is>
-          <t>Timestamp found: 'Hi_1775069435, Hi_1775069435, 12:20 am'</t>
+          <t>Timestamp found: 'Hi_1775123960, Hi_1775123960, 3:29 pm'</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="H28" s="31" t="inlineStr">
         <is>
-          <t>Received timestamp found: 'Hi_1775069435, Hi_1775069435, 12:20 am'</t>
+          <t>Received timestamp found: 'Hi_1775123960, Hi_1775123960, 3:29 pm'</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="H29" s="31" t="inlineStr">
         <is>
-          <t>Chat auto-scrolled. New message 'Hi_1775070110' is visible on screen.</t>
+          <t>Chat auto-scrolled. New message 'Hi_1775123987' is visible on screen.</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="K29" s="31" t="inlineStr">
         <is>
-          <t>Hi_1775070110</t>
+          <t>Hi_1775123987</t>
         </is>
       </c>
       <c r="L29" s="33" t="inlineStr"/>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="H30" s="31" t="inlineStr">
         <is>
-          <t>Older messages loaded. Before scroll: 19, After scroll: 21. Scrolling was smooth.</t>
+          <t>Older messages loaded. Before: 18, After: 22.</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="H31" s="32" t="inlineStr">
         <is>
-          <t>Scrolled away from latest messages. No explicit scroll-to-bottom button (app uses auto-scroll behavior).</t>
+          <t>Scrolled away. No explicit scroll-to-bottom button (app uses auto-scroll).</t>
         </is>
       </c>
       <c r="I31" s="8" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="H32" s="32" t="inlineStr">
         <is>
-          <t>Chat scrolled to most recent message. 'Hi_1775070110' is visible.</t>
+          <t>Scrolled to latest message. 'Hi_1775123987' is visible.</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="K33" s="32" t="inlineStr">
         <is>
-          <t>msg1_1775071180, msg2_1775071180, msg3_1775071180</t>
+          <t>msg1_1775124029, msg2_1775124029, msg3_1775124029</t>
         </is>
       </c>
       <c r="L33" s="32" t="inlineStr"/>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="H34" s="32" t="inlineStr">
         <is>
-          <t>Chinese message sent: '你好世界_1775071208'. Found on screen: True.</t>
+          <t>Chinese message sent: '你好世界_1775124054'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="K34" s="32" t="inlineStr">
         <is>
-          <t>你好世界_1775071208</t>
+          <t>你好世界_1775124054</t>
         </is>
       </c>
       <c r="L34" s="32" t="inlineStr"/>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="H35" s="32" t="inlineStr">
         <is>
-          <t>Arabic/RTL message sent: 'مرحبا بالعالم_177507'. Found on screen: True.</t>
+          <t>Arabic/RTL message sent: 'مرحبا بالعالم_177512'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="K35" s="32" t="inlineStr">
         <is>
-          <t>مرحبا بالعالم_1775071217</t>
+          <t>مرحبا بالعالم_1775124062</t>
         </is>
       </c>
       <c r="L35" s="32" t="inlineStr"/>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="H36" s="32" t="inlineStr">
         <is>
-          <t>Japanese message sent: 'こんにちは世界_1775071227'. Found on screen: True.</t>
+          <t>Japanese message sent: 'こんにちは世界_1775124071'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="K36" s="32" t="inlineStr">
         <is>
-          <t>こんにちは世界_1775071227</t>
+          <t>こんにちは世界_1775124071</t>
         </is>
       </c>
       <c r="L36" s="32" t="inlineStr"/>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="H37" s="32" t="inlineStr">
         <is>
-          <t>Hindi message sent: 'नमस्ते दुनिया_177507'. Found on screen: True.</t>
+          <t>Hindi message sent: 'नमस्ते दुनिया_177512'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="K37" s="32" t="inlineStr">
         <is>
-          <t>नमस्ते दुनिया_1775071236</t>
+          <t>नमस्ते दुनिया_1775124079</t>
         </is>
       </c>
       <c r="L37" s="32" t="inlineStr"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="H38" s="32" t="inlineStr">
         <is>
-          <t>Mixed emoji+URL message sent: '😀 https://example.com _1775071'.</t>
+          <t>Mixed emoji+URL message sent: '😀 https://example.com _1775124'.</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="K38" s="32" t="inlineStr">
         <is>
-          <t>😀 https://example.com _1775071245</t>
+          <t>😀 https://example.com _1775124087</t>
         </is>
       </c>
       <c r="L38" s="32" t="inlineStr"/>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="K39" s="32" t="inlineStr">
         <is>
-          <t>Order #123 @user $50.00! _1775071254</t>
+          <t>Order #123 @user $50.00! _1775124095</t>
         </is>
       </c>
       <c r="L39" s="32" t="inlineStr"/>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="K40" s="31" t="inlineStr">
         <is>
-          <t>LongPress_1775071262</t>
+          <t>LongPress_1775124103</t>
         </is>
       </c>
       <c r="L40" s="33" t="inlineStr"/>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="H41" s="31" t="inlineStr">
         <is>
-          <t>Message edited to 'LongPress_1775071262_EDITED'.</t>
+          <t>Message edited to 'LongPress_1775124103_EDITED'.</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="K41" s="31" t="inlineStr">
         <is>
-          <t>LongPress_1775071262_EDITED</t>
+          <t>LongPress_1775124103_EDITED</t>
         </is>
       </c>
       <c r="L41" s="33" t="inlineStr"/>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="H44" s="31" t="inlineStr">
         <is>
-          <t>Reply 'Reply_1775112235' sent with quoted message.</t>
+          <t>Reply 'Reply_1775124157' sent with quoted message.</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="H56" s="32" t="inlineStr">
         <is>
-          <t>Message 'StatusCheck_1775115928' sent and visible. No explicit tick icon found.</t>
+          <t>Message 'StatusCheck_1775124229' sent and visible. No explicit tick icon found.</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="H63" s="32" t="inlineStr">
         <is>
-          <t>Group chat composer works. Message 'GroupTest_1775119424' sent.</t>
+          <t>Group chat composer works. Message 'GroupTest_1775125016' sent.</t>
         </is>
       </c>
       <c r="I63" s="8" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="H64" s="32" t="inlineStr">
         <is>
-          <t>'This message was deleted' placeholder shown.</t>
+          <t>Message deleted successfully.</t>
         </is>
       </c>
       <c r="I64" s="8" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="K64" s="32" t="inlineStr">
         <is>
-          <t>ToDelete_1775119452</t>
+          <t>ToDelete_1775125043</t>
         </is>
       </c>
       <c r="L64" s="32" t="inlineStr"/>
@@ -4905,7 +4905,7 @@
       </c>
       <c r="K65" s="31" t="inlineStr">
         <is>
-          <t>DelOpt_1775119471</t>
+          <t>DelOpt_1775125063</t>
         </is>
       </c>
       <c r="L65" s="33" t="inlineStr"/>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="K66" s="31" t="inlineStr">
         <is>
-          <t>DelOpt_1775119471</t>
+          <t>DelOpt_1775125063</t>
         </is>
       </c>
       <c r="L66" s="33" t="inlineStr"/>

--- a/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
+++ b/Cometchat_Features/Send_&_Compose/SM_SLC_RMF_Test_Cases.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Positive" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Negative" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1770,7 +1771,7 @@
       </c>
       <c r="H9" s="31" t="inlineStr">
         <is>
-          <t>Message 'Test_1775123861' sent and visible.</t>
+          <t>Message 'Test_1775196093' sent and visible.</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -1785,7 +1786,7 @@
       </c>
       <c r="K9" s="31" t="inlineStr">
         <is>
-          <t>Test_1775123861</t>
+          <t>Test_1775196093</t>
         </is>
       </c>
       <c r="L9" s="33" t="inlineStr"/>
@@ -1834,7 +1835,7 @@
       </c>
       <c r="K10" s="31" t="inlineStr">
         <is>
-          <t>Feedback_1775123869</t>
+          <t>Feedback_1775196102</t>
         </is>
       </c>
       <c r="L10" s="33" t="inlineStr"/>
@@ -1998,7 +1999,7 @@
       </c>
       <c r="K13" s="31" t="inlineStr">
         <is>
-          <t>Hello @#$%^&amp;*()! _1775123906</t>
+          <t>Hello @#$%^&amp;*()! _1775196142</t>
         </is>
       </c>
       <c r="L13" s="33" t="inlineStr"/>
@@ -2050,7 +2051,7 @@
       </c>
       <c r="K14" s="31" t="inlineStr">
         <is>
-          <t>Hello 😀🎉👍 _1775123914</t>
+          <t>Hello 😀🎉👍 _1775196150</t>
         </is>
       </c>
       <c r="L14" s="33" t="inlineStr"/>
@@ -2102,7 +2103,7 @@
       </c>
       <c r="K15" s="31" t="inlineStr">
         <is>
-          <t>Order #12345_1775123922</t>
+          <t>Order #12345_1775196157</t>
         </is>
       </c>
       <c r="L15" s="33" t="inlineStr"/>
@@ -2154,7 +2155,7 @@
       </c>
       <c r="K16" s="31" t="inlineStr">
         <is>
-          <t>https://example.com _1775123930</t>
+          <t>https://example.com _1775196165</t>
         </is>
       </c>
       <c r="L16" s="33" t="inlineStr"/>
@@ -2269,7 +2270,7 @@
       </c>
       <c r="K18" s="31" t="inlineStr">
         <is>
-          <t>Msg_1775123938</t>
+          <t>Msg_1775196173</t>
         </is>
       </c>
       <c r="L18" s="33" t="inlineStr"/>
@@ -2382,7 +2383,7 @@
       </c>
       <c r="K20" s="31" t="inlineStr">
         <is>
-          <t>Hello_1775123951</t>
+          <t>Hello_1775196187</t>
         </is>
       </c>
       <c r="L20" s="33" t="inlineStr"/>
@@ -2441,7 +2442,7 @@
       </c>
       <c r="K21" s="31" t="inlineStr">
         <is>
-          <t>Hi_1775123960</t>
+          <t>Hi_1775196195</t>
         </is>
       </c>
       <c r="L21" s="33" t="inlineStr"/>
@@ -2525,7 +2526,7 @@
       </c>
       <c r="H23" s="31" t="inlineStr">
         <is>
-          <t>Timestamp found: 'Hi_1775123960, Hi_1775123960, 3:29 pm'</t>
+          <t>Timestamp found: 'Hi_1775196195, Hi_1775196195, 11:33 am'</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
@@ -2787,7 +2788,7 @@
       </c>
       <c r="H28" s="31" t="inlineStr">
         <is>
-          <t>Received timestamp found: 'Hi_1775123960, Hi_1775123960, 3:29 pm'</t>
+          <t>Received timestamp found: 'Hi_1775196195, Hi_1775196195, 11:33 am'</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2846,7 +2847,7 @@
       </c>
       <c r="H29" s="31" t="inlineStr">
         <is>
-          <t>Chat auto-scrolled. New message 'Hi_1775123987' is visible on screen.</t>
+          <t>Chat auto-scrolled. New message 'Hi_1775196223' is visible on screen.</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
@@ -2861,7 +2862,7 @@
       </c>
       <c r="K29" s="31" t="inlineStr">
         <is>
-          <t>Hi_1775123987</t>
+          <t>Hi_1775196223</t>
         </is>
       </c>
       <c r="L29" s="33" t="inlineStr"/>
@@ -3013,7 +3014,7 @@
       </c>
       <c r="H32" s="32" t="inlineStr">
         <is>
-          <t>Scrolled to latest message. 'Hi_1775123987' is visible.</t>
+          <t>Scrolled to latest message. 'Hi_1775196223' is visible.</t>
         </is>
       </c>
       <c r="I32" s="8" t="inlineStr">
@@ -3088,7 +3089,7 @@
       </c>
       <c r="K33" s="32" t="inlineStr">
         <is>
-          <t>msg1_1775124029, msg2_1775124029, msg3_1775124029</t>
+          <t>msg1_1775196266, msg2_1775196266, msg3_1775196266</t>
         </is>
       </c>
       <c r="L33" s="32" t="inlineStr"/>
@@ -3132,7 +3133,7 @@
       </c>
       <c r="H34" s="32" t="inlineStr">
         <is>
-          <t>Chinese message sent: '你好世界_1775124054'. Found on screen: True.</t>
+          <t>Chinese message sent: '你好世界_1775196290'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I34" s="8" t="inlineStr">
@@ -3147,7 +3148,7 @@
       </c>
       <c r="K34" s="32" t="inlineStr">
         <is>
-          <t>你好世界_1775124054</t>
+          <t>你好世界_1775196290</t>
         </is>
       </c>
       <c r="L34" s="32" t="inlineStr"/>
@@ -3187,7 +3188,7 @@
       </c>
       <c r="H35" s="32" t="inlineStr">
         <is>
-          <t>Arabic/RTL message sent: 'مرحبا بالعالم_177512'. Found on screen: True.</t>
+          <t>Arabic/RTL message sent: 'مرحبا بالعالم_177519'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I35" s="8" t="inlineStr">
@@ -3202,7 +3203,7 @@
       </c>
       <c r="K35" s="32" t="inlineStr">
         <is>
-          <t>مرحبا بالعالم_1775124062</t>
+          <t>مرحبا بالعالم_1775196299</t>
         </is>
       </c>
       <c r="L35" s="32" t="inlineStr"/>
@@ -3242,7 +3243,7 @@
       </c>
       <c r="H36" s="32" t="inlineStr">
         <is>
-          <t>Japanese message sent: 'こんにちは世界_1775124071'. Found on screen: True.</t>
+          <t>Japanese message sent: 'こんにちは世界_1775196307'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I36" s="8" t="inlineStr">
@@ -3257,7 +3258,7 @@
       </c>
       <c r="K36" s="32" t="inlineStr">
         <is>
-          <t>こんにちは世界_1775124071</t>
+          <t>こんにちは世界_1775196307</t>
         </is>
       </c>
       <c r="L36" s="32" t="inlineStr"/>
@@ -3301,7 +3302,7 @@
       </c>
       <c r="H37" s="32" t="inlineStr">
         <is>
-          <t>Hindi message sent: 'नमस्ते दुनिया_177512'. Found on screen: True.</t>
+          <t>Hindi message sent: 'नमस्ते दुनिया_177519'. Found on screen: True.</t>
         </is>
       </c>
       <c r="I37" s="8" t="inlineStr">
@@ -3316,7 +3317,7 @@
       </c>
       <c r="K37" s="32" t="inlineStr">
         <is>
-          <t>नमस्ते दुनिया_1775124079</t>
+          <t>नमस्ते दुनिया_1775196316</t>
         </is>
       </c>
       <c r="L37" s="32" t="inlineStr"/>
@@ -3360,7 +3361,7 @@
       </c>
       <c r="H38" s="32" t="inlineStr">
         <is>
-          <t>Mixed emoji+URL message sent: '😀 https://example.com _1775124'.</t>
+          <t>Mixed emoji+URL message sent: '😀 https://example.com _1775196'.</t>
         </is>
       </c>
       <c r="I38" s="8" t="inlineStr">
@@ -3375,7 +3376,7 @@
       </c>
       <c r="K38" s="32" t="inlineStr">
         <is>
-          <t>😀 https://example.com _1775124087</t>
+          <t>😀 https://example.com _1775196324</t>
         </is>
       </c>
       <c r="L38" s="32" t="inlineStr"/>
@@ -3430,7 +3431,7 @@
       </c>
       <c r="K39" s="32" t="inlineStr">
         <is>
-          <t>Order #123 @user $50.00! _1775124095</t>
+          <t>Order #123 @user $50.00! _1775196332</t>
         </is>
       </c>
       <c r="L39" s="32" t="inlineStr"/>
@@ -3490,7 +3491,7 @@
       </c>
       <c r="K40" s="31" t="inlineStr">
         <is>
-          <t>LongPress_1775124103</t>
+          <t>LongPress_1775196339</t>
         </is>
       </c>
       <c r="L40" s="33" t="inlineStr"/>
@@ -3528,7 +3529,7 @@
       </c>
       <c r="H41" s="31" t="inlineStr">
         <is>
-          <t>Message edited to 'LongPress_1775124103_EDITED'.</t>
+          <t>Message edited to 'LongPress_1775196339_EDITED'.</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -3543,7 +3544,7 @@
       </c>
       <c r="K41" s="31" t="inlineStr">
         <is>
-          <t>LongPress_1775124103_EDITED</t>
+          <t>LongPress_1775196339_EDITED</t>
         </is>
       </c>
       <c r="L41" s="33" t="inlineStr"/>
@@ -3691,7 +3692,7 @@
       </c>
       <c r="H44" s="31" t="inlineStr">
         <is>
-          <t>Reply 'Reply_1775124157' sent with quoted message.</t>
+          <t>Reply 'Reply_1775196394' sent with quoted message.</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -4358,7 +4359,7 @@
       </c>
       <c r="H56" s="32" t="inlineStr">
         <is>
-          <t>Message 'StatusCheck_1775124229' sent and visible. No explicit tick icon found.</t>
+          <t>Message 'StatusCheck_1775196466' sent and visible. No explicit tick icon found.</t>
         </is>
       </c>
       <c r="I56" s="8" t="inlineStr">
@@ -4743,225 +4744,178 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
+          <t>Verify Delete message</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>User has sent a message</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>Verify long press on sent message shows delete option</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>1. Send a message.
+2. Long press on the sent message.
+3. Observe action menu.</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr">
+        <is>
+          <t>Delete option should appear in the action menu.</t>
+        </is>
+      </c>
+      <c r="H63" s="32" t="inlineStr">
+        <is>
+          <t>Delete option found in action menu.</t>
+        </is>
+      </c>
+      <c r="I63" s="8" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J63" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="inlineStr">
+        <is>
+          <t>DelOpt_1775196502</t>
+        </is>
+      </c>
+      <c r="L63" s="32" t="inlineStr"/>
+    </row>
+    <row r="64" ht="135" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>MSG_062</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Verify Delete message</t>
+        </is>
+      </c>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>User has sent a message and delete option is available (MSG_063 passed)</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>Verify deleting a sent message</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr">
+        <is>
+          <t>1. Long press on sent message.
+2. Tap Delete.
+3. Confirm deletion.</t>
+        </is>
+      </c>
+      <c r="G64" s="8" t="inlineStr">
+        <is>
+          <t>Message should be removed or show 'This message was deleted' placeholder.</t>
+        </is>
+      </c>
+      <c r="H64" s="32" t="inlineStr">
+        <is>
+          <t>Message deleted. 'This message was deleted' placeholder shown.</t>
+        </is>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+      <c r="J64" s="28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K64" s="32" t="inlineStr">
+        <is>
+          <t>DelOpt_1775196502</t>
+        </is>
+      </c>
+      <c r="L64" s="32" t="inlineStr"/>
+    </row>
+    <row r="65" ht="51" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>MSG_063</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
           <t>Verify Composer in Group Chat</t>
         </is>
       </c>
-      <c r="D63" s="8" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>User is logged in and in a group chat.</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E65" s="8" t="inlineStr">
         <is>
           <t>Verify all composer features work in group chat</t>
         </is>
       </c>
-      <c r="F63" s="8" t="inlineStr">
+      <c r="F65" s="8" t="inlineStr">
         <is>
           <t>1. Open a group chat.
 2. Verify composer input, send button, emoji button, attachment button are functional.
 3. Send a text message.</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
+      <c r="G65" s="8" t="inlineStr">
         <is>
           <t>All composer features should work in group chat including @all and @ mentions.</t>
         </is>
       </c>
-      <c r="H63" s="32" t="inlineStr">
-        <is>
-          <t>Group chat composer works. Message 'GroupTest_1775125016' sent.</t>
-        </is>
-      </c>
-      <c r="I63" s="8" t="inlineStr">
+      <c r="H65" s="31" t="inlineStr">
+        <is>
+          <t>Group chat test deferred for later.</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="J63" s="28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="inlineStr">
+      <c r="J65" s="27" t="inlineStr">
+        <is>
+          <t>SKIP — Deferred</t>
+        </is>
+      </c>
+      <c r="K65" s="31" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="L63" s="32" t="inlineStr"/>
-    </row>
-    <row r="64" ht="135" customHeight="1">
-      <c r="A64" s="8" t="inlineStr">
-        <is>
-          <t>MSG_062</t>
-        </is>
-      </c>
-      <c r="B64" s="8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>Verify Deleted Message Display</t>
-        </is>
-      </c>
-      <c r="D64" s="8" t="inlineStr">
-        <is>
-          <t>User is logged in and in a chat conversation.</t>
-        </is>
-      </c>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>Verify deleted message shows placeholder text</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="inlineStr">
-        <is>
-          <t>1. Send a message.
-2. Delete the message.
-3. Observe chat.</t>
-        </is>
-      </c>
-      <c r="G64" s="8" t="inlineStr">
-        <is>
-          <t>'This message was deleted' placeholder should appear in place of deleted message.</t>
-        </is>
-      </c>
-      <c r="H64" s="32" t="inlineStr">
-        <is>
-          <t>Message deleted successfully.</t>
-        </is>
-      </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J64" s="28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="inlineStr">
-        <is>
-          <t>ToDelete_1775125043</t>
-        </is>
-      </c>
-      <c r="L64" s="32" t="inlineStr"/>
-    </row>
-    <row r="65" ht="51" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>MSG_063</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr">
-        <is>
-          <t>Verify Delete message</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>User has sent a message</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>Verify long press on sent message shows delete option</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>1. Send a message.
-2. Long press on the sent message.
-3. Observe action menu.</t>
-        </is>
-      </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>Delete option should appear in the action menu.</t>
-        </is>
-      </c>
-      <c r="H65" s="31" t="inlineStr">
-        <is>
-          <t>Delete option found in action menu.</t>
-        </is>
-      </c>
-      <c r="I65" s="7" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J65" s="26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K65" s="31" t="inlineStr">
-        <is>
-          <t>DelOpt_1775125063</t>
-        </is>
-      </c>
-      <c r="L65" s="33" t="inlineStr"/>
-    </row>
-    <row r="66" ht="51" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>MSG_064</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="n"/>
-      <c r="C66" s="7" t="n"/>
-      <c r="D66" s="8" t="inlineStr">
-        <is>
-          <t>User has sent a message and delete option is available (MSG_063 passed)</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>Verify deleting a sent message</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>1. Long press on sent message.
-2. Tap Delete.
-3. Confirm deletion.</t>
-        </is>
-      </c>
-      <c r="G66" s="8" t="inlineStr">
-        <is>
-          <t>Message should be removed or show 'This message was deleted' placeholder.</t>
-        </is>
-      </c>
-      <c r="H66" s="31" t="inlineStr">
-        <is>
-          <t>Message deleted. Placeholder or removal confirmed.</t>
-        </is>
-      </c>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-      <c r="J66" s="26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="K66" s="31" t="inlineStr">
-        <is>
-          <t>DelOpt_1775125063</t>
-        </is>
-      </c>
-      <c r="L66" s="33" t="inlineStr"/>
-    </row>
+      <c r="L65" s="33" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="51" customHeight="1"/>
     <row r="68" ht="17.6" customHeight="1"/>
     <row r="69" ht="17" customHeight="1"/>
     <row r="70" ht="34" customHeight="1"/>
@@ -5040,4 +4994,93 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15.859375" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="75.625" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="8.7109375" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>Input_Data</t>
+        </is>
+      </c>
+      <c r="L1" s="12" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>